--- a/Financial Analysis/INSG.xlsx
+++ b/Financial Analysis/INSG.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28526"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28730"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\antos\Desktop\Financial Analysis\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\antos\Documents\GitHub\FinanceModels\Financial Analysis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6A5DC9C0-6F39-4F65-8F82-3AB167D6434C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{19947843-3BE5-4C04-B41A-4D43DA246813}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{34A2EE39-018E-4F29-BBB7-6210648CE1A5}"/>
   </bookViews>
@@ -350,7 +350,7 @@
     <t>Q425</t>
   </si>
   <si>
-    <t>Heavily undervalued</t>
+    <t>Slightly overvalued</t>
   </si>
 </sst>
 </file>
@@ -466,14 +466,14 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>34</xdr:col>
-      <xdr:colOff>22860</xdr:colOff>
+      <xdr:col>35</xdr:col>
+      <xdr:colOff>15240</xdr:colOff>
       <xdr:row>0</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>34</xdr:col>
-      <xdr:colOff>22860</xdr:colOff>
+      <xdr:col>35</xdr:col>
+      <xdr:colOff>15240</xdr:colOff>
       <xdr:row>39</xdr:row>
       <xdr:rowOff>83820</xdr:rowOff>
     </xdr:to>
@@ -490,7 +490,7 @@
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="21488400" y="0"/>
+          <a:off x="22090380" y="0"/>
           <a:ext cx="0" cy="7216140"/>
         </a:xfrm>
         <a:prstGeom prst="line">
@@ -516,14 +516,14 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>46</xdr:col>
-      <xdr:colOff>30480</xdr:colOff>
+      <xdr:col>47</xdr:col>
+      <xdr:colOff>15240</xdr:colOff>
       <xdr:row>0</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>46</xdr:col>
-      <xdr:colOff>30480</xdr:colOff>
+      <xdr:col>47</xdr:col>
+      <xdr:colOff>15240</xdr:colOff>
       <xdr:row>39</xdr:row>
       <xdr:rowOff>68580</xdr:rowOff>
     </xdr:to>
@@ -540,8 +540,8 @@
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="26418540" y="0"/>
-          <a:ext cx="0" cy="6835140"/>
+          <a:off x="29451300" y="0"/>
+          <a:ext cx="0" cy="7200900"/>
         </a:xfrm>
         <a:prstGeom prst="line">
           <a:avLst/>
@@ -889,17 +889,17 @@
         <v>1</v>
       </c>
       <c r="D3" s="10">
-        <v>6.1</v>
+        <v>8.4700000000000006</v>
       </c>
       <c r="E3" s="3">
-        <v>45751</v>
+        <v>45804</v>
       </c>
       <c r="F3" s="3">
         <f ca="1">TODAY()</f>
-        <v>45751</v>
+        <v>45804</v>
       </c>
       <c r="G3" s="3">
-        <v>45777</v>
+        <v>45875</v>
       </c>
     </row>
     <row r="4" spans="2:7" x14ac:dyDescent="0.3">
@@ -907,11 +907,10 @@
         <v>2</v>
       </c>
       <c r="D4" s="4">
-        <f>14</f>
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>78</v>
+        <v>84</v>
       </c>
     </row>
     <row r="5" spans="2:7" x14ac:dyDescent="0.3">
@@ -920,7 +919,7 @@
       </c>
       <c r="D5" s="4">
         <f>D3*D4</f>
-        <v>85.399999999999991</v>
+        <v>127.05000000000001</v>
       </c>
     </row>
     <row r="6" spans="2:7" x14ac:dyDescent="0.3">
@@ -928,11 +927,11 @@
         <v>4</v>
       </c>
       <c r="D6" s="4">
-        <f>39.6</f>
-        <v>39.6</v>
+        <f>35.1</f>
+        <v>35.1</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>78</v>
+        <v>84</v>
       </c>
     </row>
     <row r="7" spans="2:7" x14ac:dyDescent="0.3">
@@ -944,7 +943,7 @@
         <v>56.699999999999996</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>78</v>
+        <v>84</v>
       </c>
     </row>
     <row r="8" spans="2:7" x14ac:dyDescent="0.3">
@@ -953,7 +952,7 @@
       </c>
       <c r="D8" s="4">
         <f>D6-D7</f>
-        <v>-17.099999999999994</v>
+        <v>-21.599999999999994</v>
       </c>
     </row>
     <row r="9" spans="2:7" x14ac:dyDescent="0.3">
@@ -962,7 +961,7 @@
       </c>
       <c r="D9" s="4">
         <f>D5-D8</f>
-        <v>102.49999999999999</v>
+        <v>148.65</v>
       </c>
     </row>
   </sheetData>
@@ -1206,20 +1205,19 @@
         <v>25.5</v>
       </c>
       <c r="AI3" s="6">
-        <f>AE3*1.5</f>
-        <v>22.950000000000003</v>
+        <v>17.8</v>
       </c>
       <c r="AJ3" s="6">
-        <f>AF3*1.3</f>
-        <v>33.67</v>
+        <f>AF3*1.1</f>
+        <v>28.490000000000002</v>
       </c>
       <c r="AK3" s="6">
-        <f>AG3*1.1</f>
-        <v>35.53</v>
+        <f>AG3*0.97</f>
+        <v>31.330999999999996</v>
       </c>
       <c r="AL3" s="6">
-        <f>AH3*1.4</f>
-        <v>35.699999999999996</v>
+        <f>AH3*1.3</f>
+        <v>33.15</v>
       </c>
       <c r="AS3" s="4">
         <v>143.5</v>
@@ -1233,47 +1231,47 @@
       </c>
       <c r="AV3" s="4">
         <f>SUM(AI3:AL3)</f>
-        <v>127.85</v>
+        <v>110.77100000000002</v>
       </c>
       <c r="AW3" s="4">
         <f>AV3*1.15</f>
-        <v>147.02749999999997</v>
+        <v>127.38665</v>
       </c>
       <c r="AX3" s="4">
         <f>AW3*1.1</f>
-        <v>161.73024999999998</v>
+        <v>140.125315</v>
       </c>
       <c r="AY3" s="4">
         <f>AX3*1.08</f>
-        <v>174.66866999999999</v>
+        <v>151.33534020000002</v>
       </c>
       <c r="AZ3" s="4">
         <f>AY3*1.05</f>
-        <v>183.40210350000001</v>
+        <v>158.90210721000003</v>
       </c>
       <c r="BA3" s="4">
         <f>AZ3*1.04</f>
-        <v>190.73818764000001</v>
+        <v>165.25819149840004</v>
       </c>
       <c r="BB3" s="4">
         <f>BA3*1.03</f>
-        <v>196.46033326920002</v>
+        <v>170.21593724335204</v>
       </c>
       <c r="BC3" s="4">
         <f>BB3*1.02</f>
-        <v>200.38953993458404</v>
+        <v>173.6202559882191</v>
       </c>
       <c r="BD3" s="4">
         <f>BC3*1.02</f>
-        <v>204.39733073327571</v>
+        <v>177.09266110798347</v>
       </c>
       <c r="BE3" s="4">
         <f>BD3*1.02</f>
-        <v>208.48527734794123</v>
+        <v>180.63451433014313</v>
       </c>
       <c r="BF3" s="4">
         <f>BE3*1.02</f>
-        <v>212.65498289490006</v>
+        <v>184.24720461674599</v>
       </c>
     </row>
     <row r="4" spans="2:58" x14ac:dyDescent="0.3">
@@ -1331,8 +1329,7 @@
         <v>10.4</v>
       </c>
       <c r="AI4" s="6">
-        <f>AF4*0.85</f>
-        <v>11.305</v>
+        <v>1.9</v>
       </c>
       <c r="AJ4" s="6">
         <f>AG4*1.01</f>
@@ -1344,7 +1341,7 @@
       </c>
       <c r="AL4" s="6">
         <f t="shared" si="0"/>
-        <v>11.418049999999999</v>
+        <v>1.9189999999999998</v>
       </c>
       <c r="AS4" s="4">
         <v>43.6</v>
@@ -1358,47 +1355,47 @@
       </c>
       <c r="AV4" s="4">
         <f>SUM(AI4:AL4)</f>
-        <v>43.024049999999995</v>
+        <v>24.12</v>
       </c>
       <c r="AW4" s="4">
         <f t="shared" ref="AW4:BF4" si="1">AV4*0.98</f>
-        <v>42.163568999999995</v>
+        <v>23.637599999999999</v>
       </c>
       <c r="AX4" s="4">
         <f t="shared" si="1"/>
-        <v>41.320297619999998</v>
+        <v>23.164847999999999</v>
       </c>
       <c r="AY4" s="4">
         <f t="shared" si="1"/>
-        <v>40.493891667599996</v>
+        <v>22.701551039999998</v>
       </c>
       <c r="AZ4" s="4">
         <f t="shared" si="1"/>
-        <v>39.684013834247999</v>
+        <v>22.2475200192</v>
       </c>
       <c r="BA4" s="4">
         <f t="shared" si="1"/>
-        <v>38.890333557563039</v>
+        <v>21.802569618815998</v>
       </c>
       <c r="BB4" s="4">
         <f t="shared" si="1"/>
-        <v>38.112526886411779</v>
+        <v>21.366518226439677</v>
       </c>
       <c r="BC4" s="4">
         <f t="shared" si="1"/>
-        <v>37.350276348683543</v>
+        <v>20.939187861910884</v>
       </c>
       <c r="BD4" s="4">
         <f t="shared" si="1"/>
-        <v>36.60327082170987</v>
+        <v>20.520404104672668</v>
       </c>
       <c r="BE4" s="4">
         <f t="shared" si="1"/>
-        <v>35.871205405275674</v>
+        <v>20.109996022579214</v>
       </c>
       <c r="BF4" s="4">
         <f t="shared" si="1"/>
-        <v>35.153781297170163</v>
+        <v>19.707796102127631</v>
       </c>
     </row>
     <row r="5" spans="2:58" x14ac:dyDescent="0.3">
@@ -1512,19 +1509,19 @@
       </c>
       <c r="AI5" s="6">
         <f t="shared" si="3"/>
-        <v>34.255000000000003</v>
+        <v>19.7</v>
       </c>
       <c r="AJ5" s="6">
         <f t="shared" si="3"/>
-        <v>43.466999999999999</v>
+        <v>38.286999999999999</v>
       </c>
       <c r="AK5" s="6">
         <f t="shared" si="3"/>
-        <v>46.034000000000006</v>
+        <v>41.834999999999994</v>
       </c>
       <c r="AL5" s="6">
         <f t="shared" si="3"/>
-        <v>47.118049999999997</v>
+        <v>35.068999999999996</v>
       </c>
       <c r="AN5" s="4">
         <f>SUM(C5:F5)</f>
@@ -1560,47 +1557,47 @@
       </c>
       <c r="AV5" s="4">
         <f>AV3+AV4</f>
-        <v>170.87404999999998</v>
+        <v>134.89100000000002</v>
       </c>
       <c r="AW5" s="4">
         <f t="shared" ref="AW5:BF5" si="4">AW3+AW4</f>
-        <v>189.19106899999997</v>
+        <v>151.02424999999999</v>
       </c>
       <c r="AX5" s="4">
         <f t="shared" si="4"/>
-        <v>203.05054761999997</v>
+        <v>163.29016300000001</v>
       </c>
       <c r="AY5" s="4">
         <f t="shared" si="4"/>
-        <v>215.16256166759999</v>
+        <v>174.03689124000002</v>
       </c>
       <c r="AZ5" s="4">
         <f t="shared" si="4"/>
-        <v>223.086117334248</v>
+        <v>181.14962722920004</v>
       </c>
       <c r="BA5" s="4">
         <f t="shared" si="4"/>
-        <v>229.62852119756303</v>
+        <v>187.06076111721603</v>
       </c>
       <c r="BB5" s="4">
         <f t="shared" si="4"/>
-        <v>234.57286015561181</v>
+        <v>191.58245546979171</v>
       </c>
       <c r="BC5" s="4">
         <f t="shared" si="4"/>
-        <v>237.73981628326757</v>
+        <v>194.55944385012998</v>
       </c>
       <c r="BD5" s="4">
         <f t="shared" si="4"/>
-        <v>241.00060155498556</v>
+        <v>197.61306521265615</v>
       </c>
       <c r="BE5" s="4">
         <f t="shared" si="4"/>
-        <v>244.35648275321691</v>
+        <v>200.74451035272236</v>
       </c>
       <c r="BF5" s="4">
         <f t="shared" si="4"/>
-        <v>247.80876419207021</v>
+        <v>203.95500071887363</v>
       </c>
     </row>
     <row r="6" spans="2:58" x14ac:dyDescent="0.3">
@@ -1704,8 +1701,7 @@
         <v>12.2</v>
       </c>
       <c r="AI6" s="6">
-        <f>AE6*0.8</f>
-        <v>12.48</v>
+        <v>12</v>
       </c>
       <c r="AJ6" s="6">
         <f>AF6*0.6</f>
@@ -1753,47 +1749,47 @@
       </c>
       <c r="AV6" s="4">
         <f>SUM(AI6:AL6)</f>
-        <v>51.1</v>
+        <v>50.620000000000005</v>
       </c>
       <c r="AW6" s="4">
         <f>AV6*1.14</f>
-        <v>58.253999999999998</v>
+        <v>57.706800000000001</v>
       </c>
       <c r="AX6" s="4">
         <f>AW6*1.07</f>
-        <v>62.331780000000002</v>
+        <v>61.746276000000002</v>
       </c>
       <c r="AY6" s="4">
         <f>AX6*1.04</f>
-        <v>64.825051200000004</v>
+        <v>64.216127040000003</v>
       </c>
       <c r="AZ6" s="4">
         <f>AY6*1.03</f>
-        <v>66.769802736000003</v>
+        <v>66.142610851200004</v>
       </c>
       <c r="BA6" s="4">
         <f>AZ6*1.02</f>
-        <v>68.10519879072001</v>
+        <v>67.465463068224011</v>
       </c>
       <c r="BB6" s="4">
         <f t="shared" ref="BB6:BF6" si="5">BA6*1.02</f>
-        <v>69.467302766534416</v>
+        <v>68.814772329588493</v>
       </c>
       <c r="BC6" s="4">
         <f t="shared" si="5"/>
-        <v>70.856648821865107</v>
+        <v>70.191067776180262</v>
       </c>
       <c r="BD6" s="4">
         <f t="shared" si="5"/>
-        <v>72.273781798302409</v>
+        <v>71.594889131703866</v>
       </c>
       <c r="BE6" s="4">
         <f t="shared" si="5"/>
-        <v>73.719257434268457</v>
+        <v>73.026786914337947</v>
       </c>
       <c r="BF6" s="4">
         <f t="shared" si="5"/>
-        <v>75.193642582953828</v>
+        <v>74.487322652624712</v>
       </c>
     </row>
     <row r="7" spans="2:58" s="1" customFormat="1" x14ac:dyDescent="0.3">
@@ -1930,19 +1926,19 @@
       </c>
       <c r="AI7" s="7">
         <f t="shared" si="16"/>
-        <v>46.734999999999999</v>
+        <v>31.7</v>
       </c>
       <c r="AJ7" s="7">
         <f t="shared" si="16"/>
-        <v>55.466999999999999</v>
+        <v>50.286999999999999</v>
       </c>
       <c r="AK7" s="7">
         <f t="shared" si="16"/>
-        <v>59.234000000000009</v>
+        <v>55.034999999999997</v>
       </c>
       <c r="AL7" s="7">
         <f t="shared" si="16"/>
-        <v>60.538049999999998</v>
+        <v>48.488999999999997</v>
       </c>
       <c r="AN7" s="7">
         <f>AN5+AN6</f>
@@ -1978,47 +1974,47 @@
       </c>
       <c r="AV7" s="7">
         <f t="shared" si="17"/>
-        <v>221.97404999999998</v>
+        <v>185.51100000000002</v>
       </c>
       <c r="AW7" s="7">
         <f t="shared" si="17"/>
-        <v>247.44506899999996</v>
+        <v>208.73104999999998</v>
       </c>
       <c r="AX7" s="7">
         <f t="shared" si="17"/>
-        <v>265.38232761999996</v>
+        <v>225.036439</v>
       </c>
       <c r="AY7" s="7">
         <f t="shared" si="17"/>
-        <v>279.98761286759998</v>
+        <v>238.25301828000002</v>
       </c>
       <c r="AZ7" s="7">
         <f t="shared" si="17"/>
-        <v>289.85592007024798</v>
+        <v>247.29223808040004</v>
       </c>
       <c r="BA7" s="7">
         <f t="shared" si="17"/>
-        <v>297.73371998828304</v>
+        <v>254.52622418544004</v>
       </c>
       <c r="BB7" s="7">
         <f t="shared" ref="BB7:BF7" si="18">BB5+BB6</f>
-        <v>304.04016292214624</v>
+        <v>260.39722779938018</v>
       </c>
       <c r="BC7" s="7">
         <f t="shared" si="18"/>
-        <v>308.59646510513267</v>
+        <v>264.75051162631024</v>
       </c>
       <c r="BD7" s="7">
         <f t="shared" si="18"/>
-        <v>313.27438335328799</v>
+        <v>269.20795434436002</v>
       </c>
       <c r="BE7" s="7">
         <f t="shared" si="18"/>
-        <v>318.07574018748539</v>
+        <v>273.77129726706028</v>
       </c>
       <c r="BF7" s="7">
         <f t="shared" si="18"/>
-        <v>323.00240677502404</v>
+        <v>278.44232337149833</v>
       </c>
     </row>
     <row r="8" spans="2:58" x14ac:dyDescent="0.3">
@@ -2122,20 +2118,19 @@
         <v>28.6</v>
       </c>
       <c r="AI8" s="4">
-        <f>AI5*0.76</f>
-        <v>26.033800000000003</v>
+        <v>15.4</v>
       </c>
       <c r="AJ8" s="4">
         <f>AJ5*0.77</f>
-        <v>33.469589999999997</v>
+        <v>29.480989999999998</v>
       </c>
       <c r="AK8" s="4">
         <f>AK5*0.8</f>
-        <v>36.827200000000005</v>
+        <v>33.467999999999996</v>
       </c>
       <c r="AL8" s="4">
         <f>AL5*0.8</f>
-        <v>37.69444</v>
+        <v>28.055199999999999</v>
       </c>
       <c r="AN8" s="4">
         <f>SUM(C8:F8)</f>
@@ -2171,47 +2166,47 @@
       </c>
       <c r="AV8" s="4">
         <f>SUM(AI8:AL8)</f>
-        <v>134.02503000000002</v>
+        <v>106.40418999999999</v>
       </c>
       <c r="AW8" s="4">
         <f t="shared" ref="AW8:BF8" si="19">AW5*0.79</f>
-        <v>149.46094450999999</v>
+        <v>119.3091575</v>
       </c>
       <c r="AX8" s="4">
         <f t="shared" si="19"/>
-        <v>160.40993261979997</v>
+        <v>128.99922877</v>
       </c>
       <c r="AY8" s="4">
         <f t="shared" si="19"/>
-        <v>169.97842371740398</v>
+        <v>137.48914407960001</v>
       </c>
       <c r="AZ8" s="4">
         <f t="shared" si="19"/>
-        <v>176.23803269405593</v>
+        <v>143.10820551106804</v>
       </c>
       <c r="BA8" s="4">
         <f t="shared" si="19"/>
-        <v>181.40653174607479</v>
+        <v>147.77800128260068</v>
       </c>
       <c r="BB8" s="4">
         <f t="shared" si="19"/>
-        <v>185.31255952293333</v>
+        <v>151.35013982113546</v>
       </c>
       <c r="BC8" s="4">
         <f t="shared" si="19"/>
-        <v>187.81445486378138</v>
+        <v>153.70196064160268</v>
       </c>
       <c r="BD8" s="4">
         <f t="shared" si="19"/>
-        <v>190.39047522843862</v>
+        <v>156.11432151799838</v>
       </c>
       <c r="BE8" s="4">
         <f t="shared" si="19"/>
-        <v>193.04162137504136</v>
+        <v>158.58816317865066</v>
       </c>
       <c r="BF8" s="4">
         <f t="shared" si="19"/>
-        <v>195.76892371173548</v>
+        <v>161.12445056791017</v>
       </c>
     </row>
     <row r="9" spans="2:58" x14ac:dyDescent="0.3">
@@ -2317,8 +2312,7 @@
         <v>1.6</v>
       </c>
       <c r="AI9" s="4">
-        <f>AI6*0.13</f>
-        <v>1.6224000000000001</v>
+        <v>1.3</v>
       </c>
       <c r="AJ9" s="4">
         <f t="shared" ref="AJ9:AL9" si="20">AJ6*0.13</f>
@@ -2366,47 +2360,47 @@
       </c>
       <c r="AV9" s="4">
         <f>SUM(AI9:AL9)</f>
-        <v>6.6430000000000007</v>
+        <v>6.3206000000000007</v>
       </c>
       <c r="AW9" s="4">
         <f t="shared" ref="AW9:BF9" si="21">AW6*0.25</f>
-        <v>14.563499999999999</v>
+        <v>14.4267</v>
       </c>
       <c r="AX9" s="4">
         <f t="shared" si="21"/>
-        <v>15.582945</v>
+        <v>15.436569</v>
       </c>
       <c r="AY9" s="4">
         <f t="shared" si="21"/>
-        <v>16.206262800000001</v>
+        <v>16.054031760000001</v>
       </c>
       <c r="AZ9" s="4">
         <f t="shared" si="21"/>
-        <v>16.692450684000001</v>
+        <v>16.535652712800001</v>
       </c>
       <c r="BA9" s="4">
         <f t="shared" si="21"/>
-        <v>17.026299697680003</v>
+        <v>16.866365767056003</v>
       </c>
       <c r="BB9" s="4">
         <f t="shared" si="21"/>
-        <v>17.366825691633604</v>
+        <v>17.203693082397123</v>
       </c>
       <c r="BC9" s="4">
         <f t="shared" si="21"/>
-        <v>17.714162205466277</v>
+        <v>17.547766944045065</v>
       </c>
       <c r="BD9" s="4">
         <f t="shared" si="21"/>
-        <v>18.068445449575602</v>
+        <v>17.898722282925966</v>
       </c>
       <c r="BE9" s="4">
         <f t="shared" si="21"/>
-        <v>18.429814358567114</v>
+        <v>18.256696728584487</v>
       </c>
       <c r="BF9" s="4">
         <f t="shared" si="21"/>
-        <v>18.798410645738457</v>
+        <v>18.621830663156178</v>
       </c>
     </row>
     <row r="10" spans="2:58" x14ac:dyDescent="0.3">
@@ -2543,19 +2537,19 @@
       </c>
       <c r="AI10" s="4">
         <f t="shared" ref="AI10:AL10" si="33">AI8+AI9</f>
-        <v>27.656200000000002</v>
+        <v>16.7</v>
       </c>
       <c r="AJ10" s="4">
         <f t="shared" si="33"/>
-        <v>35.029589999999999</v>
+        <v>31.040989999999997</v>
       </c>
       <c r="AK10" s="4">
         <f t="shared" si="33"/>
-        <v>38.543200000000006</v>
+        <v>35.183999999999997</v>
       </c>
       <c r="AL10" s="4">
         <f t="shared" si="33"/>
-        <v>39.439039999999999</v>
+        <v>29.799799999999998</v>
       </c>
       <c r="AN10" s="4">
         <f>AN8+AN9</f>
@@ -2591,47 +2585,47 @@
       </c>
       <c r="AV10" s="4">
         <f t="shared" si="34"/>
-        <v>140.66803000000002</v>
+        <v>112.72478999999998</v>
       </c>
       <c r="AW10" s="4">
         <f t="shared" si="34"/>
-        <v>164.02444451</v>
+        <v>133.73585750000001</v>
       </c>
       <c r="AX10" s="4">
         <f t="shared" si="34"/>
-        <v>175.99287761979997</v>
+        <v>144.43579776999999</v>
       </c>
       <c r="AY10" s="4">
         <f t="shared" si="34"/>
-        <v>186.18468651740397</v>
+        <v>153.5431758396</v>
       </c>
       <c r="AZ10" s="4">
         <f t="shared" si="34"/>
-        <v>192.93048337805592</v>
+        <v>159.64385822386805</v>
       </c>
       <c r="BA10" s="4">
         <f t="shared" si="34"/>
-        <v>198.43283144375479</v>
+        <v>164.64436704965669</v>
       </c>
       <c r="BB10" s="4">
         <f t="shared" ref="BB10:BF10" si="35">BB8+BB9</f>
-        <v>202.67938521456693</v>
+        <v>168.55383290353257</v>
       </c>
       <c r="BC10" s="4">
         <f t="shared" si="35"/>
-        <v>205.52861706924764</v>
+        <v>171.24972758564775</v>
       </c>
       <c r="BD10" s="4">
         <f t="shared" si="35"/>
-        <v>208.45892067801421</v>
+        <v>174.01304380092435</v>
       </c>
       <c r="BE10" s="4">
         <f t="shared" si="35"/>
-        <v>211.47143573360847</v>
+        <v>176.84485990723516</v>
       </c>
       <c r="BF10" s="4">
         <f t="shared" si="35"/>
-        <v>214.56733435747395</v>
+        <v>179.74628123106635</v>
       </c>
     </row>
     <row r="11" spans="2:58" s="1" customFormat="1" x14ac:dyDescent="0.3">
@@ -2768,19 +2762,19 @@
       </c>
       <c r="AI11" s="7">
         <f t="shared" ref="AI11:AL11" si="47">AI7-AI10</f>
-        <v>19.078799999999998</v>
+        <v>15</v>
       </c>
       <c r="AJ11" s="7">
         <f t="shared" si="47"/>
-        <v>20.43741</v>
+        <v>19.246010000000002</v>
       </c>
       <c r="AK11" s="7">
         <f t="shared" si="47"/>
-        <v>20.690800000000003</v>
+        <v>19.850999999999999</v>
       </c>
       <c r="AL11" s="7">
         <f t="shared" si="47"/>
-        <v>21.09901</v>
+        <v>18.6892</v>
       </c>
       <c r="AN11" s="7">
         <f>AN7-AN10</f>
@@ -2816,47 +2810,47 @@
       </c>
       <c r="AV11" s="7">
         <f t="shared" si="48"/>
-        <v>81.306019999999961</v>
+        <v>72.78621000000004</v>
       </c>
       <c r="AW11" s="7">
         <f t="shared" si="48"/>
-        <v>83.420624489999966</v>
+        <v>74.995192499999973</v>
       </c>
       <c r="AX11" s="7">
         <f t="shared" si="48"/>
-        <v>89.389450000199986</v>
+        <v>80.600641230000008</v>
       </c>
       <c r="AY11" s="7">
         <f t="shared" si="48"/>
-        <v>93.802926350196003</v>
+        <v>84.709842440400024</v>
       </c>
       <c r="AZ11" s="7">
         <f t="shared" si="48"/>
-        <v>96.925436692192051</v>
+        <v>87.648379856531989</v>
       </c>
       <c r="BA11" s="7">
         <f t="shared" si="48"/>
-        <v>99.300888544528249</v>
+        <v>89.881857135783349</v>
       </c>
       <c r="BB11" s="7">
         <f t="shared" ref="BB11:BF11" si="49">BB7-BB10</f>
-        <v>101.3607777075793</v>
+        <v>91.843394895847609</v>
       </c>
       <c r="BC11" s="7">
         <f t="shared" si="49"/>
-        <v>103.06784803588502</v>
+        <v>93.500784040662495</v>
       </c>
       <c r="BD11" s="7">
         <f t="shared" si="49"/>
-        <v>104.81546267527378</v>
+        <v>95.194910543435668</v>
       </c>
       <c r="BE11" s="7">
         <f t="shared" si="49"/>
-        <v>106.60430445387692</v>
+        <v>96.926437359825115</v>
       </c>
       <c r="BF11" s="7">
         <f t="shared" si="49"/>
-        <v>108.43507241755009</v>
+        <v>98.696042140431985</v>
       </c>
     </row>
     <row r="12" spans="2:58" x14ac:dyDescent="0.3">
@@ -2960,8 +2954,7 @@
         <v>5.6</v>
       </c>
       <c r="AI12" s="4">
-        <f>AE12*1.02</f>
-        <v>5.0999999999999996</v>
+        <v>4.5</v>
       </c>
       <c r="AJ12" s="4">
         <f t="shared" ref="AJ12:AL12" si="50">AF12*1.02</f>
@@ -3009,47 +3002,47 @@
       </c>
       <c r="AV12" s="4">
         <f>SUM(AI12:AL12)</f>
-        <v>21.726000000000003</v>
+        <v>21.125999999999998</v>
       </c>
       <c r="AW12" s="4">
         <f>AV12*1.04</f>
-        <v>22.595040000000004</v>
+        <v>21.971039999999999</v>
       </c>
       <c r="AX12" s="4">
         <f>AW12*1.03</f>
-        <v>23.272891200000004</v>
+        <v>22.630171199999999</v>
       </c>
       <c r="AY12" s="4">
         <f>AX12*1.02</f>
-        <v>23.738349024000005</v>
+        <v>23.082774623999999</v>
       </c>
       <c r="AZ12" s="4">
         <f>AY12*1.02</f>
-        <v>24.213116004480007</v>
+        <v>23.544430116480001</v>
       </c>
       <c r="BA12" s="4">
         <f>AZ12*1.02</f>
-        <v>24.697378324569609</v>
+        <v>24.015318718809603</v>
       </c>
       <c r="BB12" s="4">
         <f t="shared" ref="BB12:BF12" si="51">BA12*1.02</f>
-        <v>25.191325891061002</v>
+        <v>24.495625093185794</v>
       </c>
       <c r="BC12" s="4">
         <f t="shared" si="51"/>
-        <v>25.695152408882223</v>
+        <v>24.985537595049511</v>
       </c>
       <c r="BD12" s="4">
         <f t="shared" si="51"/>
-        <v>26.209055457059868</v>
+        <v>25.485248346950502</v>
       </c>
       <c r="BE12" s="4">
         <f t="shared" si="51"/>
-        <v>26.733236566201064</v>
+        <v>25.994953313889514</v>
       </c>
       <c r="BF12" s="4">
         <f t="shared" si="51"/>
-        <v>27.267901297525086</v>
+        <v>26.514852380167305</v>
       </c>
     </row>
     <row r="13" spans="2:58" x14ac:dyDescent="0.3">
@@ -3153,20 +3146,19 @@
         <v>3.8</v>
       </c>
       <c r="AI13" s="4">
-        <f>AI7*0.11</f>
-        <v>5.1408500000000004</v>
+        <v>3.9</v>
       </c>
       <c r="AJ13" s="4">
         <f>AJ7*0.1</f>
-        <v>5.5467000000000004</v>
+        <v>5.0287000000000006</v>
       </c>
       <c r="AK13" s="4">
         <f>AK7*0.1</f>
-        <v>5.9234000000000009</v>
+        <v>5.5034999999999998</v>
       </c>
       <c r="AL13" s="4">
         <f>AL7*0.1</f>
-        <v>6.0538050000000005</v>
+        <v>4.8489000000000004</v>
       </c>
       <c r="AN13" s="4">
         <f>SUM(C13:F13)</f>
@@ -3202,47 +3194,47 @@
       </c>
       <c r="AV13" s="4">
         <f>SUM(AI13:AL13)</f>
-        <v>22.664755000000003</v>
+        <v>19.281100000000002</v>
       </c>
       <c r="AW13" s="4">
         <f>AW7*0.08</f>
-        <v>19.795605519999999</v>
+        <v>16.698484000000001</v>
       </c>
       <c r="AX13" s="4">
         <f t="shared" ref="AX13:BF13" si="52">AX7*0.08</f>
-        <v>21.230586209599998</v>
+        <v>18.002915120000001</v>
       </c>
       <c r="AY13" s="4">
         <f t="shared" si="52"/>
-        <v>22.399009029407999</v>
+        <v>19.060241462400001</v>
       </c>
       <c r="AZ13" s="4">
         <f t="shared" si="52"/>
-        <v>23.188473605619837</v>
+        <v>19.783379046432003</v>
       </c>
       <c r="BA13" s="4">
         <f t="shared" si="52"/>
-        <v>23.818697599062645</v>
+        <v>20.362097934835205</v>
       </c>
       <c r="BB13" s="4">
         <f t="shared" si="52"/>
-        <v>24.323213033771701</v>
+        <v>20.831778223950415</v>
       </c>
       <c r="BC13" s="4">
         <f t="shared" si="52"/>
-        <v>24.687717208410614</v>
+        <v>21.18004093010482</v>
       </c>
       <c r="BD13" s="4">
         <f t="shared" si="52"/>
-        <v>25.061950668263041</v>
+        <v>21.536636347548804</v>
       </c>
       <c r="BE13" s="4">
         <f t="shared" si="52"/>
-        <v>25.446059214998833</v>
+        <v>21.901703781364823</v>
       </c>
       <c r="BF13" s="4">
         <f t="shared" si="52"/>
-        <v>25.840192542001923</v>
+        <v>22.275385869719866</v>
       </c>
     </row>
     <row r="14" spans="2:58" x14ac:dyDescent="0.3">
@@ -3346,8 +3338,7 @@
         <v>4.5</v>
       </c>
       <c r="AI14" s="4">
-        <f>AE14*1.01</f>
-        <v>5.05</v>
+        <v>4.5</v>
       </c>
       <c r="AJ14" s="4">
         <f t="shared" ref="AJ14:AL14" si="53">AF14*1.01</f>
@@ -3395,47 +3386,47 @@
       </c>
       <c r="AV14" s="4">
         <f>SUM(AI14:AL14)</f>
-        <v>20.301000000000002</v>
+        <v>19.750999999999998</v>
       </c>
       <c r="AW14" s="4">
         <f>AV14*1.02</f>
-        <v>20.707020000000004</v>
+        <v>20.146019999999996</v>
       </c>
       <c r="AX14" s="4">
         <f>AW14*1.01</f>
-        <v>20.914090200000004</v>
+        <v>20.347480199999996</v>
       </c>
       <c r="AY14" s="4">
         <f>AX14*1.01</f>
-        <v>21.123231102000005</v>
+        <v>20.550955001999995</v>
       </c>
       <c r="AZ14" s="4">
         <f>AY14*1.01</f>
-        <v>21.334463413020007</v>
+        <v>20.756464552019995</v>
       </c>
       <c r="BA14" s="4">
         <f>AZ14*1.01</f>
-        <v>21.547808047150209</v>
+        <v>20.964029197540196</v>
       </c>
       <c r="BB14" s="4">
         <f t="shared" ref="BB14:BF14" si="54">BA14*1.01</f>
-        <v>21.763286127621711</v>
+        <v>21.173669489515596</v>
       </c>
       <c r="BC14" s="4">
         <f t="shared" si="54"/>
-        <v>21.98091898889793</v>
+        <v>21.385406184410751</v>
       </c>
       <c r="BD14" s="4">
         <f t="shared" si="54"/>
-        <v>22.20072817878691</v>
+        <v>21.599260246254858</v>
       </c>
       <c r="BE14" s="4">
         <f t="shared" si="54"/>
-        <v>22.422735460574781</v>
+        <v>21.815252848717407</v>
       </c>
       <c r="BF14" s="4">
         <f t="shared" si="54"/>
-        <v>22.64696281518053</v>
+        <v>22.033405377204581</v>
       </c>
     </row>
     <row r="15" spans="2:58" x14ac:dyDescent="0.3">
@@ -3552,7 +3543,8 @@
         <v>2.2999999999999998</v>
       </c>
       <c r="AI15" s="4">
-        <v>3</v>
+        <f>2.1+0.4</f>
+        <v>2.5</v>
       </c>
       <c r="AJ15" s="4">
         <v>3</v>
@@ -3597,7 +3589,7 @@
       </c>
       <c r="AV15" s="4">
         <f>SUM(AI15:AL15)</f>
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AW15" s="4">
         <v>0</v>
@@ -3764,19 +3756,19 @@
       </c>
       <c r="AI16" s="4">
         <f t="shared" ref="AI16:AL16" si="66">AI12+AI13+AI14+AI15</f>
-        <v>18.290849999999999</v>
+        <v>15.4</v>
       </c>
       <c r="AJ16" s="4">
         <f t="shared" si="66"/>
-        <v>20.014700000000001</v>
+        <v>19.496700000000001</v>
       </c>
       <c r="AK16" s="4">
         <f t="shared" si="66"/>
-        <v>19.075400000000002</v>
+        <v>18.6555</v>
       </c>
       <c r="AL16" s="4">
         <f t="shared" si="66"/>
-        <v>19.310805000000002</v>
+        <v>18.105899999999998</v>
       </c>
       <c r="AN16" s="4">
         <f>AN12+AN13+AN14+AN15</f>
@@ -3812,47 +3804,47 @@
       </c>
       <c r="AV16" s="4">
         <f t="shared" si="67"/>
-        <v>76.691755000000001</v>
+        <v>71.65809999999999</v>
       </c>
       <c r="AW16" s="4">
         <f t="shared" si="67"/>
-        <v>63.097665520000007</v>
+        <v>58.815543999999989</v>
       </c>
       <c r="AX16" s="4">
         <f t="shared" si="67"/>
-        <v>65.417567609600013</v>
+        <v>60.980566519999996</v>
       </c>
       <c r="AY16" s="4">
         <f t="shared" si="67"/>
-        <v>67.260589155408013</v>
+        <v>62.693971088399991</v>
       </c>
       <c r="AZ16" s="4">
         <f t="shared" si="67"/>
-        <v>68.736053023119851</v>
+        <v>64.084273714931996</v>
       </c>
       <c r="BA16" s="4">
         <f t="shared" si="67"/>
-        <v>70.06388397078247</v>
+        <v>65.341445851185</v>
       </c>
       <c r="BB16" s="4">
         <f t="shared" ref="BB16:BF16" si="68">BB12+BB13+BB14+BB15</f>
-        <v>71.277825052454418</v>
+        <v>66.501072806651806</v>
       </c>
       <c r="BC16" s="4">
         <f t="shared" si="68"/>
-        <v>72.363788606190766</v>
+        <v>67.550984709565085</v>
       </c>
       <c r="BD16" s="4">
         <f t="shared" si="68"/>
-        <v>73.471734304109816</v>
+        <v>68.621144940754164</v>
       </c>
       <c r="BE16" s="4">
         <f t="shared" si="68"/>
-        <v>74.602031241774682</v>
+        <v>69.711909943971747</v>
       </c>
       <c r="BF16" s="4">
         <f t="shared" si="68"/>
-        <v>75.755056654707545</v>
+        <v>70.823643627091741</v>
       </c>
     </row>
     <row r="17" spans="2:168" s="1" customFormat="1" x14ac:dyDescent="0.3">
@@ -3989,19 +3981,19 @@
       </c>
       <c r="AI17" s="7">
         <f t="shared" ref="AI17:AL17" si="80">AI11-AI16</f>
-        <v>0.7879499999999986</v>
+        <v>-0.40000000000000036</v>
       </c>
       <c r="AJ17" s="7">
         <f t="shared" si="80"/>
-        <v>0.42270999999999859</v>
+        <v>-0.25068999999999875</v>
       </c>
       <c r="AK17" s="7">
         <f t="shared" si="80"/>
-        <v>1.6154000000000011</v>
+        <v>1.1954999999999991</v>
       </c>
       <c r="AL17" s="7">
         <f t="shared" si="80"/>
-        <v>1.7882049999999978</v>
+        <v>0.58330000000000126</v>
       </c>
       <c r="AN17" s="7">
         <f>AN11-AN16</f>
@@ -4037,47 +4029,47 @@
       </c>
       <c r="AV17" s="7">
         <f t="shared" si="81"/>
-        <v>4.6142649999999605</v>
+        <v>1.1281100000000492</v>
       </c>
       <c r="AW17" s="7">
         <f t="shared" si="81"/>
-        <v>20.322958969999959</v>
+        <v>16.179648499999985</v>
       </c>
       <c r="AX17" s="7">
         <f t="shared" si="81"/>
-        <v>23.971882390599973</v>
+        <v>19.620074710000011</v>
       </c>
       <c r="AY17" s="7">
         <f t="shared" si="81"/>
-        <v>26.54233719478799</v>
+        <v>22.015871352000033</v>
       </c>
       <c r="AZ17" s="7">
         <f t="shared" si="81"/>
-        <v>28.1893836690722</v>
+        <v>23.564106141599993</v>
       </c>
       <c r="BA17" s="7">
         <f t="shared" si="81"/>
-        <v>29.237004573745779</v>
+        <v>24.540411284598349</v>
       </c>
       <c r="BB17" s="7">
         <f t="shared" ref="BB17:BF17" si="82">BB11-BB16</f>
-        <v>30.082952655124885</v>
+        <v>25.342322089195804</v>
       </c>
       <c r="BC17" s="7">
         <f t="shared" si="82"/>
-        <v>30.704059429694254</v>
+        <v>25.94979933109741</v>
       </c>
       <c r="BD17" s="7">
         <f t="shared" si="82"/>
-        <v>31.343728371163962</v>
+        <v>26.573765602681505</v>
       </c>
       <c r="BE17" s="7">
         <f t="shared" si="82"/>
-        <v>32.002273212102239</v>
+        <v>27.214527415853368</v>
       </c>
       <c r="BF17" s="7">
         <f t="shared" si="82"/>
-        <v>32.680015762842544</v>
+        <v>27.872398513340244</v>
       </c>
     </row>
     <row r="18" spans="2:168" x14ac:dyDescent="0.3">
@@ -4185,7 +4177,7 @@
         <v>16.5</v>
       </c>
       <c r="AI18" s="4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AJ18" s="4">
         <v>2</v>
@@ -4230,47 +4222,47 @@
       </c>
       <c r="AV18" s="4">
         <f>SUM(AI18:AL18)</f>
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AW18" s="4">
         <f t="shared" ref="AW18:BA18" si="83">AV18*0.8</f>
-        <v>6.4</v>
+        <v>5.6000000000000005</v>
       </c>
       <c r="AX18" s="4">
         <f t="shared" si="83"/>
-        <v>5.120000000000001</v>
+        <v>4.4800000000000004</v>
       </c>
       <c r="AY18" s="4">
         <f t="shared" si="83"/>
-        <v>4.096000000000001</v>
+        <v>3.5840000000000005</v>
       </c>
       <c r="AZ18" s="4">
         <f t="shared" si="83"/>
-        <v>3.276800000000001</v>
+        <v>2.8672000000000004</v>
       </c>
       <c r="BA18" s="4">
         <f t="shared" si="83"/>
-        <v>2.6214400000000011</v>
+        <v>2.2937600000000002</v>
       </c>
       <c r="BB18" s="4">
         <f t="shared" ref="BB18:BB19" si="84">BA18*0.8</f>
-        <v>2.0971520000000008</v>
+        <v>1.8350080000000002</v>
       </c>
       <c r="BC18" s="4">
         <f t="shared" ref="BC18:BC19" si="85">BB18*0.8</f>
-        <v>1.6777216000000008</v>
+        <v>1.4680064000000002</v>
       </c>
       <c r="BD18" s="4">
         <f t="shared" ref="BD18:BD19" si="86">BC18*0.8</f>
-        <v>1.3421772800000007</v>
+        <v>1.1744051200000001</v>
       </c>
       <c r="BE18" s="4">
         <f t="shared" ref="BE18:BE19" si="87">BD18*0.8</f>
-        <v>1.0737418240000005</v>
+        <v>0.93952409600000009</v>
       </c>
       <c r="BF18" s="4">
         <f t="shared" ref="BF18:BF19" si="88">BE18*0.8</f>
-        <v>0.85899345920000048</v>
+        <v>0.75161927680000007</v>
       </c>
     </row>
     <row r="19" spans="2:168" x14ac:dyDescent="0.3">
@@ -4377,7 +4369,7 @@
         <v>1.2</v>
       </c>
       <c r="AI19" s="4">
-        <v>-1</v>
+        <v>-0.3</v>
       </c>
       <c r="AJ19" s="4">
         <v>-1</v>
@@ -4422,47 +4414,47 @@
       </c>
       <c r="AV19" s="4">
         <f>SUM(AI19:AL19)</f>
-        <v>-4</v>
+        <v>-3.3</v>
       </c>
       <c r="AW19" s="4">
         <f t="shared" ref="AW19:BA19" si="89">AV19*0.8</f>
-        <v>-3.2</v>
+        <v>-2.64</v>
       </c>
       <c r="AX19" s="4">
         <f t="shared" si="89"/>
-        <v>-2.5600000000000005</v>
+        <v>-2.1120000000000001</v>
       </c>
       <c r="AY19" s="4">
         <f t="shared" si="89"/>
-        <v>-2.0480000000000005</v>
+        <v>-1.6896000000000002</v>
       </c>
       <c r="AZ19" s="4">
         <f t="shared" si="89"/>
-        <v>-1.6384000000000005</v>
+        <v>-1.3516800000000002</v>
       </c>
       <c r="BA19" s="4">
         <f t="shared" si="89"/>
-        <v>-1.3107200000000006</v>
+        <v>-1.0813440000000003</v>
       </c>
       <c r="BB19" s="4">
         <f t="shared" si="84"/>
-        <v>-1.0485760000000004</v>
+        <v>-0.86507520000000027</v>
       </c>
       <c r="BC19" s="4">
         <f t="shared" si="85"/>
-        <v>-0.83886080000000041</v>
+        <v>-0.69206016000000026</v>
       </c>
       <c r="BD19" s="4">
         <f t="shared" si="86"/>
-        <v>-0.67108864000000035</v>
+        <v>-0.55364812800000018</v>
       </c>
       <c r="BE19" s="4">
         <f t="shared" si="87"/>
-        <v>-0.53687091200000026</v>
+        <v>-0.44291850240000019</v>
       </c>
       <c r="BF19" s="4">
         <f t="shared" si="88"/>
-        <v>-0.42949672960000024</v>
+        <v>-0.35433480192000016</v>
       </c>
     </row>
     <row r="20" spans="2:168" s="1" customFormat="1" x14ac:dyDescent="0.3">
@@ -4599,19 +4591,19 @@
       </c>
       <c r="AI20" s="7">
         <f t="shared" si="100"/>
-        <v>-0.2120500000000014</v>
+        <v>-1.1000000000000003</v>
       </c>
       <c r="AJ20" s="7">
         <f t="shared" si="100"/>
-        <v>-0.57729000000000141</v>
+        <v>-1.2506899999999987</v>
       </c>
       <c r="AK20" s="7">
         <f t="shared" si="100"/>
-        <v>0.61540000000000106</v>
+        <v>0.19549999999999912</v>
       </c>
       <c r="AL20" s="7">
         <f t="shared" si="100"/>
-        <v>0.78820499999999782</v>
+        <v>-0.41669999999999874</v>
       </c>
       <c r="AN20" s="7">
         <f>AN17-AN18-AN19</f>
@@ -4647,47 +4639,47 @@
       </c>
       <c r="AV20" s="7">
         <f t="shared" si="101"/>
-        <v>0.61426499999996054</v>
+        <v>-2.5718899999999509</v>
       </c>
       <c r="AW20" s="7">
         <f t="shared" si="101"/>
-        <v>17.12295896999996</v>
+        <v>13.219648499999984</v>
       </c>
       <c r="AX20" s="7">
         <f t="shared" si="101"/>
-        <v>21.41188239059997</v>
+        <v>17.252074710000009</v>
       </c>
       <c r="AY20" s="7">
         <f t="shared" si="101"/>
-        <v>24.494337194787992</v>
+        <v>20.121471352000032</v>
       </c>
       <c r="AZ20" s="7">
         <f t="shared" si="101"/>
-        <v>26.550983669072199</v>
+        <v>22.048586141599994</v>
       </c>
       <c r="BA20" s="7">
         <f t="shared" si="101"/>
-        <v>27.926284573745779</v>
+        <v>23.327995284598352</v>
       </c>
       <c r="BB20" s="7">
         <f t="shared" ref="BB20:BF20" si="102">BB17-BB18-BB19</f>
-        <v>29.034376655124884</v>
+        <v>24.372389289195802</v>
       </c>
       <c r="BC20" s="7">
         <f t="shared" si="102"/>
-        <v>29.865198629694252</v>
+        <v>25.17385309109741</v>
       </c>
       <c r="BD20" s="7">
         <f t="shared" si="102"/>
-        <v>30.672639731163962</v>
+        <v>25.953008610681504</v>
       </c>
       <c r="BE20" s="7">
         <f t="shared" si="102"/>
-        <v>31.465402300102241</v>
+        <v>26.71792182225337</v>
       </c>
       <c r="BF20" s="7">
         <f t="shared" si="102"/>
-        <v>32.25051903324254</v>
+        <v>27.475114038460244</v>
       </c>
     </row>
     <row r="21" spans="2:168" x14ac:dyDescent="0.3">
@@ -4840,43 +4832,43 @@
       </c>
       <c r="AW21" s="4">
         <f t="shared" ref="AW21:BA21" si="103">AW20*0.2</f>
-        <v>3.4245917939999924</v>
+        <v>2.6439296999999971</v>
       </c>
       <c r="AX21" s="4">
         <f t="shared" si="103"/>
-        <v>4.2823764781199944</v>
+        <v>3.4504149420000019</v>
       </c>
       <c r="AY21" s="4">
         <f t="shared" si="103"/>
-        <v>4.8988674389575984</v>
+        <v>4.0242942704000066</v>
       </c>
       <c r="AZ21" s="4">
         <f t="shared" si="103"/>
-        <v>5.3101967338144398</v>
+        <v>4.409717228319999</v>
       </c>
       <c r="BA21" s="4">
         <f t="shared" si="103"/>
-        <v>5.5852569147491558</v>
+        <v>4.6655990569196701</v>
       </c>
       <c r="BB21" s="4">
         <f t="shared" ref="BB21:BF21" si="104">BB20*0.2</f>
-        <v>5.806875331024977</v>
+        <v>4.8744778578391603</v>
       </c>
       <c r="BC21" s="4">
         <f t="shared" si="104"/>
-        <v>5.9730397259388504</v>
+        <v>5.0347706182194827</v>
       </c>
       <c r="BD21" s="4">
         <f t="shared" si="104"/>
-        <v>6.1345279462327928</v>
+        <v>5.190601722136301</v>
       </c>
       <c r="BE21" s="4">
         <f t="shared" si="104"/>
-        <v>6.2930804600204482</v>
+        <v>5.343584364450674</v>
       </c>
       <c r="BF21" s="4">
         <f t="shared" si="104"/>
-        <v>6.4501038066485084</v>
+        <v>5.4950228076920489</v>
       </c>
     </row>
     <row r="22" spans="2:168" x14ac:dyDescent="0.3">
@@ -4981,7 +4973,7 @@
         <v>-15.9</v>
       </c>
       <c r="AI22" s="4">
-        <v>0</v>
+        <v>-0.4</v>
       </c>
       <c r="AJ22" s="4">
         <v>0</v>
@@ -5026,47 +5018,47 @@
       </c>
       <c r="AV22" s="4">
         <f>SUM(AI22:AL22)</f>
-        <v>0</v>
+        <v>-0.4</v>
       </c>
       <c r="AW22" s="4">
         <f t="shared" ref="AW22:BA22" si="105">AV22*1.1</f>
-        <v>0</v>
+        <v>-0.44000000000000006</v>
       </c>
       <c r="AX22" s="4">
         <f t="shared" si="105"/>
-        <v>0</v>
+        <v>-0.4840000000000001</v>
       </c>
       <c r="AY22" s="4">
         <f t="shared" si="105"/>
-        <v>0</v>
+        <v>-0.5324000000000001</v>
       </c>
       <c r="AZ22" s="4">
         <f t="shared" si="105"/>
-        <v>0</v>
+        <v>-0.58564000000000016</v>
       </c>
       <c r="BA22" s="4">
         <f t="shared" si="105"/>
-        <v>0</v>
+        <v>-0.64420400000000022</v>
       </c>
       <c r="BB22" s="4">
         <f t="shared" ref="BB22" si="106">BA22*1.1</f>
-        <v>0</v>
+        <v>-0.70862440000000027</v>
       </c>
       <c r="BC22" s="4">
         <f t="shared" ref="BC22" si="107">BB22*1.1</f>
-        <v>0</v>
+        <v>-0.77948684000000035</v>
       </c>
       <c r="BD22" s="4">
         <f t="shared" ref="BD22" si="108">BC22*1.1</f>
-        <v>0</v>
+        <v>-0.85743552400000045</v>
       </c>
       <c r="BE22" s="4">
         <f t="shared" ref="BE22" si="109">BD22*1.1</f>
-        <v>0</v>
+        <v>-0.94317907640000054</v>
       </c>
       <c r="BF22" s="4">
         <f t="shared" ref="BF22" si="110">BE22*1.1</f>
-        <v>0</v>
+        <v>-1.0374969840400006</v>
       </c>
     </row>
     <row r="23" spans="2:168" s="1" customFormat="1" x14ac:dyDescent="0.3">
@@ -5203,19 +5195,19 @@
       </c>
       <c r="AI23" s="7">
         <f t="shared" ref="AI23:AL23" si="122">AI20-AI21-AI22</f>
-        <v>-0.2120500000000014</v>
+        <v>-0.70000000000000029</v>
       </c>
       <c r="AJ23" s="7">
         <f t="shared" si="122"/>
-        <v>-0.57729000000000141</v>
+        <v>-1.2506899999999987</v>
       </c>
       <c r="AK23" s="7">
         <f t="shared" si="122"/>
-        <v>0.61540000000000106</v>
+        <v>0.19549999999999912</v>
       </c>
       <c r="AL23" s="7">
         <f t="shared" si="122"/>
-        <v>0.78820499999999782</v>
+        <v>-0.41669999999999874</v>
       </c>
       <c r="AN23" s="7">
         <f>AN20-AN21-AN22</f>
@@ -5251,487 +5243,487 @@
       </c>
       <c r="AV23" s="7">
         <f t="shared" si="123"/>
-        <v>0.61426499999996054</v>
+        <v>-2.171889999999951</v>
       </c>
       <c r="AW23" s="7">
         <f t="shared" si="123"/>
-        <v>13.698367175999968</v>
+        <v>11.015718799999986</v>
       </c>
       <c r="AX23" s="7">
         <f t="shared" si="123"/>
-        <v>17.129505912479978</v>
+        <v>14.285659768000007</v>
       </c>
       <c r="AY23" s="7">
         <f t="shared" si="123"/>
-        <v>19.595469755830393</v>
+        <v>16.629577081600026</v>
       </c>
       <c r="AZ23" s="7">
         <f t="shared" si="123"/>
-        <v>21.240786935257759</v>
+        <v>18.224508913279998</v>
       </c>
       <c r="BA23" s="7">
         <f t="shared" si="123"/>
-        <v>22.341027658996623</v>
+        <v>19.306600227678679</v>
       </c>
       <c r="BB23" s="7">
         <f t="shared" ref="BB23:BF23" si="124">BB20-BB21-BB22</f>
-        <v>23.227501324099908</v>
+        <v>20.206535831356643</v>
       </c>
       <c r="BC23" s="7">
         <f t="shared" si="124"/>
-        <v>23.892158903755401</v>
+        <v>20.918569312877928</v>
       </c>
       <c r="BD23" s="7">
         <f t="shared" si="124"/>
-        <v>24.538111784931168</v>
+        <v>21.619842412545204</v>
       </c>
       <c r="BE23" s="7">
         <f t="shared" si="124"/>
-        <v>25.172321840081793</v>
+        <v>22.317516534202696</v>
       </c>
       <c r="BF23" s="7">
         <f t="shared" si="124"/>
-        <v>25.800415226594033</v>
+        <v>23.017588214808196</v>
       </c>
       <c r="BG23" s="1">
         <f>BF23*(1+$BI$32)</f>
-        <v>25.542411074328093</v>
+        <v>22.787412332660114</v>
       </c>
       <c r="BH23" s="1">
         <f t="shared" ref="BH23:DS23" si="125">BG23*(1+$BI$32)</f>
-        <v>25.286986963584813</v>
+        <v>22.559538209333514</v>
       </c>
       <c r="BI23" s="1">
         <f t="shared" si="125"/>
-        <v>25.034117093948964</v>
+        <v>22.333942827240179</v>
       </c>
       <c r="BJ23" s="1">
         <f t="shared" si="125"/>
-        <v>24.783775923009475</v>
+        <v>22.110603398967775</v>
       </c>
       <c r="BK23" s="1">
         <f t="shared" si="125"/>
-        <v>24.535938163779381</v>
+        <v>21.889497364978098</v>
       </c>
       <c r="BL23" s="1">
         <f t="shared" si="125"/>
-        <v>24.290578782141587</v>
+        <v>21.670602391328316</v>
       </c>
       <c r="BM23" s="1">
         <f t="shared" si="125"/>
-        <v>24.04767299432017</v>
+        <v>21.453896367415034</v>
       </c>
       <c r="BN23" s="1">
         <f t="shared" si="125"/>
-        <v>23.807196264376969</v>
+        <v>21.239357403740883</v>
       </c>
       <c r="BO23" s="1">
         <f t="shared" si="125"/>
-        <v>23.569124301733201</v>
+        <v>21.026963829703472</v>
       </c>
       <c r="BP23" s="1">
         <f t="shared" si="125"/>
-        <v>23.333433058715869</v>
+        <v>20.816694191406437</v>
       </c>
       <c r="BQ23" s="1">
         <f t="shared" si="125"/>
-        <v>23.10009872812871</v>
+        <v>20.608527249492372</v>
       </c>
       <c r="BR23" s="1">
         <f t="shared" si="125"/>
-        <v>22.869097740847423</v>
+        <v>20.402441976997448</v>
       </c>
       <c r="BS23" s="1">
         <f t="shared" si="125"/>
-        <v>22.64040676343895</v>
+        <v>20.198417557227472</v>
       </c>
       <c r="BT23" s="1">
         <f t="shared" si="125"/>
-        <v>22.414002695804559</v>
+        <v>19.996433381655198</v>
       </c>
       <c r="BU23" s="1">
         <f t="shared" si="125"/>
-        <v>22.189862668846512</v>
+        <v>19.796469047838645</v>
       </c>
       <c r="BV23" s="1">
         <f t="shared" si="125"/>
-        <v>21.967964042158048</v>
+        <v>19.598504357360259</v>
       </c>
       <c r="BW23" s="1">
         <f t="shared" si="125"/>
-        <v>21.748284401736466</v>
+        <v>19.402519313786655</v>
       </c>
       <c r="BX23" s="1">
         <f t="shared" si="125"/>
-        <v>21.530801557719101</v>
+        <v>19.208494120648787</v>
       </c>
       <c r="BY23" s="1">
         <f t="shared" si="125"/>
-        <v>21.315493542141912</v>
+        <v>19.016409179442299</v>
       </c>
       <c r="BZ23" s="1">
         <f t="shared" si="125"/>
-        <v>21.102338606720494</v>
+        <v>18.826245087647877</v>
       </c>
       <c r="CA23" s="1">
         <f t="shared" si="125"/>
-        <v>20.89131522065329</v>
+        <v>18.637982636771397</v>
       </c>
       <c r="CB23" s="1">
         <f t="shared" si="125"/>
-        <v>20.682402068446756</v>
+        <v>18.451602810403685</v>
       </c>
       <c r="CC23" s="1">
         <f t="shared" si="125"/>
-        <v>20.475578047762287</v>
+        <v>18.267086782299646</v>
       </c>
       <c r="CD23" s="1">
         <f t="shared" si="125"/>
-        <v>20.270822267284665</v>
+        <v>18.084415914476651</v>
       </c>
       <c r="CE23" s="1">
         <f t="shared" si="125"/>
-        <v>20.068114044611818</v>
+        <v>17.903571755331885</v>
       </c>
       <c r="CF23" s="1">
         <f t="shared" si="125"/>
-        <v>19.8674329041657</v>
+        <v>17.724536037778567</v>
       </c>
       <c r="CG23" s="1">
         <f t="shared" si="125"/>
-        <v>19.668758575124041</v>
+        <v>17.547290677400781</v>
       </c>
       <c r="CH23" s="1">
         <f t="shared" si="125"/>
-        <v>19.472070989372799</v>
+        <v>17.371817770626773</v>
       </c>
       <c r="CI23" s="1">
         <f t="shared" si="125"/>
-        <v>19.277350279479069</v>
+        <v>17.198099592920506</v>
       </c>
       <c r="CJ23" s="1">
         <f t="shared" si="125"/>
-        <v>19.08457677668428</v>
+        <v>17.026118596991303</v>
       </c>
       <c r="CK23" s="1">
         <f t="shared" si="125"/>
-        <v>18.893731008917438</v>
+        <v>16.85585741102139</v>
       </c>
       <c r="CL23" s="1">
         <f t="shared" si="125"/>
-        <v>18.704793698828265</v>
+        <v>16.687298836911175</v>
       </c>
       <c r="CM23" s="1">
         <f t="shared" si="125"/>
-        <v>18.517745761839983</v>
+        <v>16.520425848542065</v>
       </c>
       <c r="CN23" s="1">
         <f t="shared" si="125"/>
-        <v>18.332568304221581</v>
+        <v>16.355221590056644</v>
       </c>
       <c r="CO23" s="1">
         <f t="shared" si="125"/>
-        <v>18.149242621179365</v>
+        <v>16.191669374156078</v>
       </c>
       <c r="CP23" s="1">
         <f t="shared" si="125"/>
-        <v>17.967750194967572</v>
+        <v>16.029752680414518</v>
       </c>
       <c r="CQ23" s="1">
         <f t="shared" si="125"/>
-        <v>17.788072693017895</v>
+        <v>15.869455153610373</v>
       </c>
       <c r="CR23" s="1">
         <f t="shared" si="125"/>
-        <v>17.610191966087715</v>
+        <v>15.710760602074268</v>
       </c>
       <c r="CS23" s="1">
         <f t="shared" si="125"/>
-        <v>17.434090046426839</v>
+        <v>15.553652996053525</v>
       </c>
       <c r="CT23" s="1">
         <f t="shared" si="125"/>
-        <v>17.259749145962569</v>
+        <v>15.39811646609299</v>
       </c>
       <c r="CU23" s="1">
         <f t="shared" si="125"/>
-        <v>17.087151654502943</v>
+        <v>15.24413530143206</v>
       </c>
       <c r="CV23" s="1">
         <f t="shared" si="125"/>
-        <v>16.916280137957912</v>
+        <v>15.091693948417738</v>
       </c>
       <c r="CW23" s="1">
         <f t="shared" si="125"/>
-        <v>16.747117336578334</v>
+        <v>14.94077700893356</v>
       </c>
       <c r="CX23" s="1">
         <f t="shared" si="125"/>
-        <v>16.579646163212551</v>
+        <v>14.791369238844224</v>
       </c>
       <c r="CY23" s="1">
         <f t="shared" si="125"/>
-        <v>16.413849701580425</v>
+        <v>14.643455546455781</v>
       </c>
       <c r="CZ23" s="1">
         <f t="shared" si="125"/>
-        <v>16.249711204564619</v>
+        <v>14.497020990991224</v>
       </c>
       <c r="DA23" s="1">
         <f t="shared" si="125"/>
-        <v>16.087214092518973</v>
+        <v>14.352050781081312</v>
       </c>
       <c r="DB23" s="1">
         <f t="shared" si="125"/>
-        <v>15.926341951593784</v>
+        <v>14.208530273270499</v>
       </c>
       <c r="DC23" s="1">
         <f t="shared" si="125"/>
-        <v>15.767078532077846</v>
+        <v>14.066444970537795</v>
       </c>
       <c r="DD23" s="1">
         <f t="shared" si="125"/>
-        <v>15.609407746757068</v>
+        <v>13.925780520832417</v>
       </c>
       <c r="DE23" s="1">
         <f t="shared" si="125"/>
-        <v>15.453313669289496</v>
+        <v>13.786522715624093</v>
       </c>
       <c r="DF23" s="1">
         <f t="shared" si="125"/>
-        <v>15.2987805325966</v>
+        <v>13.648657488467853</v>
       </c>
       <c r="DG23" s="1">
         <f t="shared" si="125"/>
-        <v>15.145792727270635</v>
+        <v>13.512170913583175</v>
       </c>
       <c r="DH23" s="1">
         <f t="shared" si="125"/>
-        <v>14.994334799997928</v>
+        <v>13.377049204447342</v>
       </c>
       <c r="DI23" s="1">
         <f t="shared" si="125"/>
-        <v>14.844391451997948</v>
+        <v>13.243278712402869</v>
       </c>
       <c r="DJ23" s="1">
         <f t="shared" si="125"/>
-        <v>14.695947537477968</v>
+        <v>13.11084592527884</v>
       </c>
       <c r="DK23" s="1">
         <f t="shared" si="125"/>
-        <v>14.548988062103188</v>
+        <v>12.979737466026052</v>
       </c>
       <c r="DL23" s="1">
         <f t="shared" si="125"/>
-        <v>14.403498181482156</v>
+        <v>12.849940091365792</v>
       </c>
       <c r="DM23" s="1">
         <f t="shared" si="125"/>
-        <v>14.259463199667335</v>
+        <v>12.721440690452134</v>
       </c>
       <c r="DN23" s="1">
         <f t="shared" si="125"/>
-        <v>14.116868567670663</v>
+        <v>12.594226283547613</v>
       </c>
       <c r="DO23" s="1">
         <f t="shared" si="125"/>
-        <v>13.975699881993956</v>
+        <v>12.468284020712137</v>
       </c>
       <c r="DP23" s="1">
         <f t="shared" si="125"/>
-        <v>13.835942883174017</v>
+        <v>12.343601180505015</v>
       </c>
       <c r="DQ23" s="1">
         <f t="shared" si="125"/>
-        <v>13.697583454342276</v>
+        <v>12.220165168699964</v>
       </c>
       <c r="DR23" s="1">
         <f t="shared" si="125"/>
-        <v>13.560607619798853</v>
+        <v>12.097963517012964</v>
       </c>
       <c r="DS23" s="1">
         <f t="shared" si="125"/>
-        <v>13.425001543600864</v>
+        <v>11.976983881842834</v>
       </c>
       <c r="DT23" s="1">
         <f t="shared" ref="DT23:FL23" si="126">DS23*(1+$BI$32)</f>
-        <v>13.290751528164854</v>
+        <v>11.857214043024406</v>
       </c>
       <c r="DU23" s="1">
         <f t="shared" si="126"/>
-        <v>13.157844012883206</v>
+        <v>11.738641902594162</v>
       </c>
       <c r="DV23" s="1">
         <f t="shared" si="126"/>
-        <v>13.026265572754374</v>
+        <v>11.62125548356822</v>
       </c>
       <c r="DW23" s="1">
         <f t="shared" si="126"/>
-        <v>12.896002917026831</v>
+        <v>11.505042928732538</v>
       </c>
       <c r="DX23" s="1">
         <f t="shared" si="126"/>
-        <v>12.767042887856562</v>
+        <v>11.389992499445212</v>
       </c>
       <c r="DY23" s="1">
         <f t="shared" si="126"/>
-        <v>12.639372458977995</v>
+        <v>11.276092574450759</v>
       </c>
       <c r="DZ23" s="1">
         <f t="shared" si="126"/>
-        <v>12.512978734388215</v>
+        <v>11.163331648706251</v>
       </c>
       <c r="EA23" s="1">
         <f t="shared" si="126"/>
-        <v>12.387848947044333</v>
+        <v>11.051698332219189</v>
       </c>
       <c r="EB23" s="1">
         <f t="shared" si="126"/>
-        <v>12.263970457573889</v>
+        <v>10.941181348896997</v>
       </c>
       <c r="EC23" s="1">
         <f t="shared" si="126"/>
-        <v>12.141330752998149</v>
+        <v>10.831769535408027</v>
       </c>
       <c r="ED23" s="1">
         <f t="shared" si="126"/>
-        <v>12.019917445468167</v>
+        <v>10.723451840053947</v>
       </c>
       <c r="EE23" s="1">
         <f t="shared" si="126"/>
-        <v>11.899718271013485</v>
+        <v>10.616217321653407</v>
       </c>
       <c r="EF23" s="1">
         <f t="shared" si="126"/>
-        <v>11.78072108830335</v>
+        <v>10.510055148436873</v>
       </c>
       <c r="EG23" s="1">
         <f t="shared" si="126"/>
-        <v>11.662913877420317</v>
+        <v>10.404954596952503</v>
       </c>
       <c r="EH23" s="1">
         <f t="shared" si="126"/>
-        <v>11.546284738646115</v>
+        <v>10.300905050982978</v>
       </c>
       <c r="EI23" s="1">
         <f t="shared" si="126"/>
-        <v>11.430821891259654</v>
+        <v>10.197896000473149</v>
       </c>
       <c r="EJ23" s="1">
         <f t="shared" si="126"/>
-        <v>11.316513672347059</v>
+        <v>10.095917040468418</v>
       </c>
       <c r="EK23" s="1">
         <f t="shared" si="126"/>
-        <v>11.203348535623588</v>
+        <v>9.9949578700637343</v>
       </c>
       <c r="EL23" s="1">
         <f t="shared" si="126"/>
-        <v>11.091315050267353</v>
+        <v>9.8950082913630961</v>
       </c>
       <c r="EM23" s="1">
         <f t="shared" si="126"/>
-        <v>10.980401899764679</v>
+        <v>9.7960582084494643</v>
       </c>
       <c r="EN23" s="1">
         <f t="shared" si="126"/>
-        <v>10.870597880767033</v>
+        <v>9.6980976263649694</v>
       </c>
       <c r="EO23" s="1">
         <f t="shared" si="126"/>
-        <v>10.761891901959363</v>
+        <v>9.6011166501013196</v>
       </c>
       <c r="EP23" s="1">
         <f t="shared" si="126"/>
-        <v>10.654272982939769</v>
+        <v>9.5051054836003068</v>
       </c>
       <c r="EQ23" s="1">
         <f t="shared" si="126"/>
-        <v>10.547730253110371</v>
+        <v>9.4100544287643029</v>
       </c>
       <c r="ER23" s="1">
         <f t="shared" si="126"/>
-        <v>10.442252950579267</v>
+        <v>9.3159538844766594</v>
       </c>
       <c r="ES23" s="1">
         <f t="shared" si="126"/>
-        <v>10.337830421073473</v>
+        <v>9.2227943456318933</v>
       </c>
       <c r="ET23" s="1">
         <f t="shared" si="126"/>
-        <v>10.234452116862739</v>
+        <v>9.1305664021755746</v>
       </c>
       <c r="EU23" s="1">
         <f t="shared" si="126"/>
-        <v>10.132107595694112</v>
+        <v>9.0392607381538195</v>
       </c>
       <c r="EV23" s="1">
         <f t="shared" si="126"/>
-        <v>10.030786519737172</v>
+        <v>8.948868130772281</v>
       </c>
       <c r="EW23" s="1">
         <f t="shared" si="126"/>
-        <v>9.9304786545397992</v>
+        <v>8.8593794494645586</v>
       </c>
       <c r="EX23" s="1">
         <f t="shared" si="126"/>
-        <v>9.8311738679944014</v>
+        <v>8.770785654969913</v>
       </c>
       <c r="EY23" s="1">
         <f t="shared" si="126"/>
-        <v>9.7328621293144568</v>
+        <v>8.6830777984202143</v>
       </c>
       <c r="EZ23" s="1">
         <f t="shared" si="126"/>
-        <v>9.6355335080213127</v>
+        <v>8.596247020436012</v>
       </c>
       <c r="FA23" s="1">
         <f t="shared" si="126"/>
-        <v>9.5391781729410994</v>
+        <v>8.5102845502316526</v>
       </c>
       <c r="FB23" s="1">
         <f t="shared" si="126"/>
-        <v>9.4437863912116882</v>
+        <v>8.4251817047293365</v>
       </c>
       <c r="FC23" s="1">
         <f t="shared" si="126"/>
-        <v>9.349348527299572</v>
+        <v>8.3409298876820426</v>
       </c>
       <c r="FD23" s="1">
         <f t="shared" si="126"/>
-        <v>9.2558550420265764</v>
+        <v>8.2575205888052228</v>
       </c>
       <c r="FE23" s="1">
         <f t="shared" si="126"/>
-        <v>9.1632964916063102</v>
+        <v>8.174945382917171</v>
       </c>
       <c r="FF23" s="1">
         <f t="shared" si="126"/>
-        <v>9.0716635266902479</v>
+        <v>8.0931959290879991</v>
       </c>
       <c r="FG23" s="1">
         <f t="shared" si="126"/>
-        <v>8.9809468914233452</v>
+        <v>8.0122639697971199</v>
       </c>
       <c r="FH23" s="1">
         <f t="shared" si="126"/>
-        <v>8.8911374225091109</v>
+        <v>7.9321413300991486</v>
       </c>
       <c r="FI23" s="1">
         <f t="shared" si="126"/>
-        <v>8.8022260482840196</v>
+        <v>7.8528199167981567</v>
       </c>
       <c r="FJ23" s="1">
         <f t="shared" si="126"/>
-        <v>8.7142037878011784</v>
+        <v>7.7742917176301747</v>
       </c>
       <c r="FK23" s="1">
         <f t="shared" si="126"/>
-        <v>8.6270617499231665</v>
+        <v>7.6965488004538729</v>
       </c>
       <c r="FL23" s="1">
         <f t="shared" si="126"/>
-        <v>8.5407911324239354</v>
+        <v>7.6195833124493344</v>
       </c>
     </row>
     <row r="24" spans="2:168" x14ac:dyDescent="0.3">
@@ -5836,20 +5828,16 @@
         <v>14</v>
       </c>
       <c r="AI24" s="4">
-        <f>14</f>
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AJ24" s="4">
-        <f>14</f>
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AK24" s="4">
-        <f>14</f>
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AL24" s="4">
-        <f>14</f>
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AN24" s="4">
         <v>97.16</v>
@@ -5877,48 +5865,37 @@
         <v>14</v>
       </c>
       <c r="AV24" s="4">
-        <f>14</f>
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AW24" s="4">
-        <f>14</f>
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AX24" s="4">
-        <f>14</f>
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AY24" s="4">
-        <f>14</f>
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AZ24" s="4">
-        <f>14</f>
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="BA24" s="4">
-        <f>14</f>
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="BB24" s="4">
-        <f>14</f>
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="BC24" s="4">
-        <f>14</f>
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="BD24" s="4">
-        <f>14</f>
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="BE24" s="4">
-        <f>14</f>
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="BF24" s="4">
-        <f>14</f>
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="25" spans="2:168" s="1" customFormat="1" x14ac:dyDescent="0.3">
@@ -6055,19 +6032,19 @@
       </c>
       <c r="AI25" s="8">
         <f t="shared" ref="AI25:AL25" si="138">AI23/AI24</f>
-        <v>-1.5146428571428672E-2</v>
+        <v>-4.6666666666666683E-2</v>
       </c>
       <c r="AJ25" s="8">
         <f t="shared" si="138"/>
-        <v>-4.1235000000000098E-2</v>
+        <v>-8.337933333333325E-2</v>
       </c>
       <c r="AK25" s="8">
         <f t="shared" si="138"/>
-        <v>4.3957142857142931E-2</v>
+        <v>1.3033333333333275E-2</v>
       </c>
       <c r="AL25" s="8">
         <f t="shared" si="138"/>
-        <v>5.6300357142856985E-2</v>
+        <v>-2.7779999999999916E-2</v>
       </c>
       <c r="AN25" s="8">
         <f>AN23/AN24</f>
@@ -6103,47 +6080,47 @@
       </c>
       <c r="AV25" s="8">
         <f t="shared" si="139"/>
-        <v>4.3876071428568607E-2</v>
+        <v>-0.14479266666666341</v>
       </c>
       <c r="AW25" s="8">
         <f t="shared" si="139"/>
-        <v>0.97845479828571202</v>
+        <v>0.73438125333333237</v>
       </c>
       <c r="AX25" s="8">
         <f t="shared" si="139"/>
-        <v>1.2235361366057127</v>
+        <v>0.95237731786666713</v>
       </c>
       <c r="AY25" s="8">
         <f t="shared" si="139"/>
-        <v>1.3996764111307425</v>
+        <v>1.1086384721066684</v>
       </c>
       <c r="AZ25" s="8">
         <f t="shared" si="139"/>
-        <v>1.5171990668041258</v>
+        <v>1.2149672608853332</v>
       </c>
       <c r="BA25" s="8">
         <f t="shared" si="139"/>
-        <v>1.5957876899283303</v>
+        <v>1.2871066818452452</v>
       </c>
       <c r="BB25" s="8">
         <f t="shared" ref="BB25:BF25" si="140">BB23/BB24</f>
-        <v>1.6591072374357076</v>
+        <v>1.3471023887571094</v>
       </c>
       <c r="BC25" s="8">
         <f t="shared" si="140"/>
-        <v>1.7065827788396715</v>
+        <v>1.3945712875251952</v>
       </c>
       <c r="BD25" s="8">
         <f t="shared" si="140"/>
-        <v>1.7527222703522263</v>
+        <v>1.4413228275030137</v>
       </c>
       <c r="BE25" s="8">
         <f t="shared" si="140"/>
-        <v>1.7980229885772709</v>
+        <v>1.4878344356135131</v>
       </c>
       <c r="BF25" s="8">
         <f t="shared" si="140"/>
-        <v>1.8428868018995739</v>
+        <v>1.534505880987213</v>
       </c>
     </row>
     <row r="27" spans="2:168" x14ac:dyDescent="0.3">
@@ -6172,19 +6149,19 @@
       </c>
       <c r="AI27" s="9">
         <f t="shared" ref="AI27:AI31" si="144">AI3/AE3-1</f>
-        <v>0.50000000000000022</v>
+        <v>0.1633986928104576</v>
       </c>
       <c r="AJ27" s="9">
         <f t="shared" ref="AJ27:AJ31" si="145">AJ3/AF3-1</f>
-        <v>0.30000000000000004</v>
+        <v>0.10000000000000009</v>
       </c>
       <c r="AK27" s="9">
         <f t="shared" ref="AK27:AK31" si="146">AK3/AG3-1</f>
-        <v>0.10000000000000009</v>
+        <v>-3.0000000000000027E-2</v>
       </c>
       <c r="AL27" s="9">
         <f t="shared" ref="AL27:AL31" si="147">AL3/AH3-1</f>
-        <v>0.39999999999999991</v>
+        <v>0.30000000000000004</v>
       </c>
       <c r="AT27" s="9">
         <f t="shared" ref="AO27:BA30" si="148">AT3/AS3-1</f>
@@ -6196,7 +6173,7 @@
       </c>
       <c r="AV27" s="9">
         <f t="shared" ref="AV27:AV28" si="150">AV3/AU3-1</f>
-        <v>0.29141414141414135</v>
+        <v>0.11889898989899006</v>
       </c>
       <c r="AW27" s="9">
         <f t="shared" ref="AW27:AW28" si="151">AW3/AV3-1</f>
@@ -6204,7 +6181,7 @@
       </c>
       <c r="AX27" s="9">
         <f t="shared" ref="AX27:AX28" si="152">AX3/AW3-1</f>
-        <v>0.10000000000000009</v>
+        <v>9.9999999999999867E-2</v>
       </c>
       <c r="AY27" s="9">
         <f t="shared" ref="AY27:AY28" si="153">AY3/AX3-1</f>
@@ -6265,7 +6242,7 @@
       </c>
       <c r="AI28" s="9">
         <f t="shared" si="144"/>
-        <v>-0.20387323943661972</v>
+        <v>-0.86619718309859151</v>
       </c>
       <c r="AJ28" s="9">
         <f t="shared" si="145"/>
@@ -6277,7 +6254,7 @@
       </c>
       <c r="AL28" s="9">
         <f t="shared" si="147"/>
-        <v>9.7889423076922943E-2</v>
+        <v>-0.81548076923076929</v>
       </c>
       <c r="AT28" s="9">
         <f t="shared" si="148"/>
@@ -6289,15 +6266,15 @@
       </c>
       <c r="AV28" s="9">
         <f t="shared" si="150"/>
-        <v>-9.6133403361344683E-2</v>
+        <v>-0.49327731092436977</v>
       </c>
       <c r="AW28" s="9">
         <f t="shared" si="151"/>
-        <v>-2.0000000000000018E-2</v>
+        <v>-2.0000000000000129E-2</v>
       </c>
       <c r="AX28" s="9">
         <f t="shared" si="152"/>
-        <v>-1.9999999999999907E-2</v>
+        <v>-2.0000000000000018E-2</v>
       </c>
       <c r="AY28" s="9">
         <f t="shared" si="153"/>
@@ -6309,7 +6286,7 @@
       </c>
       <c r="BA28" s="9">
         <f t="shared" si="155"/>
-        <v>-2.0000000000000018E-2</v>
+        <v>-2.0000000000000129E-2</v>
       </c>
       <c r="BB28" s="9">
         <f t="shared" si="156"/>
@@ -6317,15 +6294,15 @@
       </c>
       <c r="BC28" s="9">
         <f t="shared" si="157"/>
-        <v>-2.0000000000000018E-2</v>
+        <v>-1.9999999999999907E-2</v>
       </c>
       <c r="BD28" s="9">
         <f t="shared" si="158"/>
-        <v>-2.0000000000000018E-2</v>
+        <v>-1.9999999999999907E-2</v>
       </c>
       <c r="BE28" s="9">
         <f t="shared" si="159"/>
-        <v>-1.9999999999999907E-2</v>
+        <v>-2.0000000000000018E-2</v>
       </c>
       <c r="BF28" s="9">
         <f t="shared" si="160"/>
@@ -6450,19 +6427,19 @@
       </c>
       <c r="AI29" s="9">
         <f t="shared" si="144"/>
-        <v>0.16118644067796617</v>
+        <v>-0.33220338983050846</v>
       </c>
       <c r="AJ29" s="9">
         <f t="shared" si="145"/>
-        <v>0.10885204081632649</v>
+        <v>-2.3290816326530739E-2</v>
       </c>
       <c r="AK29" s="9">
         <f t="shared" si="146"/>
-        <v>9.6047619047619159E-2</v>
+        <v>-3.9285714285716145E-3</v>
       </c>
       <c r="AL29" s="9">
         <f t="shared" si="147"/>
-        <v>0.31248050139275763</v>
+        <v>-2.3147632311977806E-2</v>
       </c>
       <c r="AN29" s="9"/>
       <c r="AO29" s="9">
@@ -6495,47 +6472,47 @@
       </c>
       <c r="AV29" s="9">
         <f t="shared" si="148"/>
-        <v>0.16558015006821281</v>
+        <v>-7.9870395634379143E-2</v>
       </c>
       <c r="AW29" s="9">
         <f t="shared" si="148"/>
-        <v>0.10719602537658579</v>
+        <v>0.11960212319576535</v>
       </c>
       <c r="AX29" s="9">
         <f t="shared" si="148"/>
-        <v>7.3256516247075076E-2</v>
+        <v>8.1218168605373009E-2</v>
       </c>
       <c r="AY29" s="9">
         <f t="shared" si="148"/>
-        <v>5.9650240738415183E-2</v>
+        <v>6.5813690442577455E-2</v>
       </c>
       <c r="AZ29" s="9">
         <f t="shared" si="148"/>
-        <v>3.682590319262391E-2</v>
+        <v>4.0869128025226686E-2</v>
       </c>
       <c r="BA29" s="9">
         <f t="shared" si="148"/>
-        <v>2.932680859523229E-2</v>
+        <v>3.2631223030544332E-2</v>
       </c>
       <c r="BB29" s="9">
         <f t="shared" ref="BB29:BB31" si="175">BB5/BA5-1</f>
-        <v>2.1531902623693977E-2</v>
+        <v>2.4172329491070066E-2</v>
       </c>
       <c r="BC29" s="9">
         <f t="shared" ref="BC29:BC31" si="176">BC5/BB5-1</f>
-        <v>1.350094859889106E-2</v>
+        <v>1.5538940520613886E-2</v>
       </c>
       <c r="BD29" s="9">
         <f t="shared" ref="BD29:BD31" si="177">BD5/BC5-1</f>
-        <v>1.3715772657251213E-2</v>
+        <v>1.5695055979284112E-2</v>
       </c>
       <c r="BE29" s="9">
         <f t="shared" ref="BE29:BE31" si="178">BE5/BD5-1</f>
-        <v>1.3924783492565984E-2</v>
+        <v>1.5846346681057666E-2</v>
       </c>
       <c r="BF29" s="9">
         <f t="shared" ref="BF29:BF31" si="179">BF5/BE5-1</f>
-        <v>1.4128053407692409E-2</v>
+        <v>1.5992917368002901E-2</v>
       </c>
     </row>
     <row r="30" spans="2:168" x14ac:dyDescent="0.3">
@@ -6656,7 +6633,7 @@
       </c>
       <c r="AI30" s="9">
         <f t="shared" si="144"/>
-        <v>-0.19999999999999996</v>
+        <v>-0.23076923076923073</v>
       </c>
       <c r="AJ30" s="9">
         <f t="shared" si="145"/>
@@ -6701,7 +6678,7 @@
       </c>
       <c r="AV30" s="9">
         <f t="shared" si="148"/>
-        <v>-0.14548494983277582</v>
+        <v>-0.15351170568561856</v>
       </c>
       <c r="AW30" s="9">
         <f t="shared" si="148"/>
@@ -6862,19 +6839,19 @@
       </c>
       <c r="AI31" s="9">
         <f t="shared" si="144"/>
-        <v>3.6252771618625168E-2</v>
+        <v>-0.29711751662971175</v>
       </c>
       <c r="AJ31" s="9">
         <f t="shared" si="145"/>
-        <v>-6.3057432432432448E-2</v>
+        <v>-0.15055743243243247</v>
       </c>
       <c r="AK31" s="9">
         <f t="shared" si="146"/>
-        <v>9.6925925925926082E-2</v>
+        <v>1.9166666666666554E-2</v>
       </c>
       <c r="AL31" s="9">
         <f t="shared" si="147"/>
-        <v>0.25858731808731816</v>
+        <v>8.0873180873182182E-3</v>
       </c>
       <c r="AN31" s="9"/>
       <c r="AO31" s="9">
@@ -6907,47 +6884,47 @@
       </c>
       <c r="AV31" s="9">
         <f t="shared" si="182"/>
-        <v>7.5455668604651249E-2</v>
+        <v>-0.10120639534883702</v>
       </c>
       <c r="AW31" s="9">
         <f t="shared" si="182"/>
-        <v>0.11474773289940865</v>
+        <v>0.1251680493340015</v>
       </c>
       <c r="AX31" s="9">
         <f t="shared" si="182"/>
-        <v>7.2489860850692533E-2</v>
+        <v>7.8116739220159159E-2</v>
       </c>
       <c r="AY31" s="9">
         <f t="shared" si="182"/>
-        <v>5.5034882610997649E-2</v>
+        <v>5.8730840830626629E-2</v>
       </c>
       <c r="AZ31" s="9">
         <f t="shared" si="182"/>
-        <v>3.5245513548181506E-2</v>
+        <v>3.7939581482140605E-2</v>
       </c>
       <c r="BA31" s="9">
         <f t="shared" si="182"/>
-        <v>2.7178330241196536E-2</v>
+        <v>2.9252782704356717E-2</v>
       </c>
       <c r="BB31" s="9">
         <f t="shared" si="175"/>
-        <v>2.1181487048599568E-2</v>
+        <v>2.3066399671503701E-2</v>
       </c>
       <c r="BC31" s="9">
         <f t="shared" si="176"/>
-        <v>1.4985856273709297E-2</v>
+        <v>1.6717857804092962E-2</v>
       </c>
       <c r="BD31" s="9">
         <f t="shared" si="177"/>
-        <v>1.5158690319286849E-2</v>
+        <v>1.6836389439508936E-2</v>
       </c>
       <c r="BE31" s="9">
         <f t="shared" si="178"/>
-        <v>1.5326362732897891E-2</v>
+        <v>1.6950995871626517E-2</v>
       </c>
       <c r="BF31" s="9">
         <f t="shared" si="179"/>
-        <v>1.5488973112613547E-2</v>
+        <v>1.7061781680792976E-2</v>
       </c>
     </row>
     <row r="32" spans="2:168" x14ac:dyDescent="0.3">
@@ -7084,15 +7061,15 @@
       </c>
       <c r="AI32" s="9">
         <f t="shared" ref="AI32:AL32" si="186">(AI5-AI8)/AI5</f>
-        <v>0.23999999999999996</v>
+        <v>0.21827411167512686</v>
       </c>
       <c r="AJ32" s="9">
         <f t="shared" si="186"/>
-        <v>0.23000000000000007</v>
+        <v>0.23</v>
       </c>
       <c r="AK32" s="9">
         <f t="shared" si="186"/>
-        <v>0.2</v>
+        <v>0.19999999999999996</v>
       </c>
       <c r="AL32" s="9">
         <f t="shared" si="186"/>
@@ -7132,11 +7109,11 @@
       </c>
       <c r="AV32" s="9">
         <f t="shared" si="187"/>
-        <v>0.2156501821078155</v>
+        <v>0.21118391886782684</v>
       </c>
       <c r="AW32" s="9">
         <f t="shared" si="187"/>
-        <v>0.20999999999999994</v>
+        <v>0.21</v>
       </c>
       <c r="AX32" s="9">
         <f t="shared" si="187"/>
@@ -7152,11 +7129,11 @@
       </c>
       <c r="BA32" s="9">
         <f t="shared" si="187"/>
-        <v>0.21000000000000002</v>
+        <v>0.20999999999999991</v>
       </c>
       <c r="BB32" s="9">
         <f t="shared" ref="BB32:BF32" si="188">(BB5-BB8)/BB5</f>
-        <v>0.21</v>
+        <v>0.20999999999999996</v>
       </c>
       <c r="BC32" s="9">
         <f t="shared" si="188"/>
@@ -7168,11 +7145,11 @@
       </c>
       <c r="BE32" s="9">
         <f t="shared" si="188"/>
-        <v>0.21</v>
+        <v>0.21000000000000002</v>
       </c>
       <c r="BF32" s="9">
         <f t="shared" si="188"/>
-        <v>0.20999999999999994</v>
+        <v>0.21</v>
       </c>
       <c r="BH32" t="s">
         <v>51</v>
@@ -7315,7 +7292,7 @@
       </c>
       <c r="AI33" s="9">
         <f t="shared" ref="AI33:AL33" si="191">(AI6-AI9)/AI6</f>
-        <v>0.87</v>
+        <v>0.89166666666666661</v>
       </c>
       <c r="AJ33" s="9">
         <f t="shared" si="191"/>
@@ -7363,11 +7340,11 @@
       </c>
       <c r="AV33" s="9">
         <f t="shared" si="192"/>
-        <v>0.87</v>
+        <v>0.8751363097589886</v>
       </c>
       <c r="AW33" s="9">
         <f t="shared" si="192"/>
-        <v>0.75</v>
+        <v>0.75000000000000011</v>
       </c>
       <c r="AX33" s="9">
         <f t="shared" si="192"/>
@@ -7546,19 +7523,19 @@
       </c>
       <c r="AI34" s="9">
         <f t="shared" ref="AI34:AL34" si="196">AI11/AI7</f>
-        <v>0.40823365785813626</v>
+        <v>0.47318611987381703</v>
       </c>
       <c r="AJ34" s="9">
         <f t="shared" si="196"/>
-        <v>0.3684607063659473</v>
+        <v>0.38272336786843525</v>
       </c>
       <c r="AK34" s="9">
         <f t="shared" si="196"/>
-        <v>0.34930614174291791</v>
+        <v>0.36069773780321612</v>
       </c>
       <c r="AL34" s="9">
         <f t="shared" si="196"/>
-        <v>0.34852477078465527</v>
+        <v>0.38543174740662833</v>
       </c>
       <c r="AN34" s="9">
         <f t="shared" ref="AN34:BA34" si="197">AN11/AN7</f>
@@ -7594,54 +7571,54 @@
       </c>
       <c r="AV34" s="9">
         <f t="shared" si="197"/>
-        <v>0.36628614921428865</v>
+        <v>0.3923552242185101</v>
       </c>
       <c r="AW34" s="9">
         <f t="shared" si="197"/>
-        <v>0.33712785155561126</v>
+        <v>0.35929102306532729</v>
       </c>
       <c r="AX34" s="9">
         <f t="shared" si="197"/>
-        <v>0.33683271528236963</v>
+        <v>0.35816706657893749</v>
       </c>
       <c r="AY34" s="9">
         <f t="shared" si="197"/>
-        <v>0.33502527268787907</v>
+        <v>0.35554572635401921</v>
       </c>
       <c r="AZ34" s="9">
         <f t="shared" si="197"/>
-        <v>0.33439177874545983</v>
+        <v>0.3544323935797597</v>
       </c>
       <c r="BA34" s="9">
         <f t="shared" si="197"/>
-        <v>0.33352247957818187</v>
+        <v>0.35313397440060312</v>
       </c>
       <c r="BB34" s="9">
         <f t="shared" ref="BB34:BF34" si="198">BB11/BB7</f>
-        <v>0.33337956648028161</v>
+        <v>0.35270496415041414</v>
       </c>
       <c r="BC34" s="9">
         <f t="shared" si="198"/>
-        <v>0.33398907534722361</v>
+        <v>0.35316564061125166</v>
       </c>
       <c r="BD34" s="9">
         <f t="shared" si="198"/>
-        <v>0.33458038143217905</v>
+        <v>0.3536110616615219</v>
       </c>
       <c r="BE34" s="9">
         <f t="shared" si="198"/>
-        <v>0.33515383597328258</v>
+        <v>0.35404163375561848</v>
       </c>
       <c r="BF34" s="9">
         <f t="shared" si="198"/>
-        <v>0.33570979702661075</v>
+        <v>0.35445775967309223</v>
       </c>
       <c r="BH34" t="s">
         <v>53</v>
       </c>
       <c r="BI34" s="4">
         <f>NPV(BI33,AU23:FL23)</f>
-        <v>146.15716510405045</v>
+        <v>125.42907233865714</v>
       </c>
     </row>
     <row r="35" spans="2:61" x14ac:dyDescent="0.3">
@@ -7778,19 +7755,19 @@
       </c>
       <c r="AI35" s="9">
         <f t="shared" ref="AI35:AL35" si="201">AI17/AI7</f>
-        <v>1.6859955065796482E-2</v>
+        <v>-1.2618296529968466E-2</v>
       </c>
       <c r="AJ35" s="9">
         <f t="shared" si="201"/>
-        <v>7.6209277588475781E-3</v>
+        <v>-4.9851850378825292E-3</v>
       </c>
       <c r="AK35" s="9">
         <f t="shared" si="201"/>
-        <v>2.7271499476651938E-2</v>
+        <v>2.172254020168982E-2</v>
       </c>
       <c r="AL35" s="9">
         <f t="shared" si="201"/>
-        <v>2.9538529899790261E-2</v>
+        <v>1.2029532471282174E-2</v>
       </c>
       <c r="AN35" s="9">
         <f t="shared" ref="AN35:BA35" si="202">AN17/AN7</f>
@@ -7826,54 +7803,54 @@
       </c>
       <c r="AV35" s="9">
         <f t="shared" si="202"/>
-        <v>2.0787407356850772E-2</v>
+        <v>6.0810949215952103E-3</v>
       </c>
       <c r="AW35" s="9">
         <f t="shared" si="202"/>
-        <v>8.2131194014619713E-2</v>
+        <v>7.7514334834227996E-2</v>
       </c>
       <c r="AX35" s="9">
         <f t="shared" si="202"/>
-        <v>9.0329610888503581E-2</v>
+        <v>8.7186212140514766E-2</v>
       </c>
       <c r="AY35" s="9">
         <f t="shared" si="202"/>
-        <v>9.4798255261882888E-2</v>
+        <v>9.2405424749442258E-2</v>
       </c>
       <c r="AZ35" s="9">
         <f t="shared" si="202"/>
-        <v>9.7253089266696249E-2</v>
+        <v>9.5288498840545063E-2</v>
       </c>
       <c r="BA35" s="9">
         <f t="shared" si="202"/>
-        <v>9.8198499568326908E-2</v>
+        <v>9.6416042642108873E-2</v>
       </c>
       <c r="BB35" s="9">
         <f t="shared" ref="BB35:BF35" si="203">BB17/BB7</f>
-        <v>9.8944009126939084E-2</v>
+        <v>9.7321781431254265E-2</v>
       </c>
       <c r="BC35" s="9">
         <f t="shared" si="203"/>
-        <v>9.9495823515781345E-2</v>
+        <v>9.8016049796062349E-2</v>
       </c>
       <c r="BD35" s="9">
         <f t="shared" si="203"/>
-        <v>0.10005199925911847</v>
+        <v>9.8710922815785043E-2</v>
       </c>
       <c r="BE35" s="9">
         <f t="shared" si="203"/>
-        <v>0.10061211582259916</v>
+        <v>9.9406065162871898E-2</v>
       </c>
       <c r="BF35" s="9">
         <f t="shared" si="203"/>
-        <v>0.10117576549701891</v>
+        <v>0.10010115623174438</v>
       </c>
       <c r="BH35" t="s">
         <v>54</v>
       </c>
       <c r="BI35" s="4">
         <f>Main!D8</f>
-        <v>-17.099999999999994</v>
+        <v>-21.599999999999994</v>
       </c>
     </row>
     <row r="36" spans="2:61" x14ac:dyDescent="0.3">
@@ -7998,7 +7975,7 @@
       </c>
       <c r="AI36" s="9">
         <f t="shared" ref="AI36" si="206">AI12/AE12-1</f>
-        <v>2.0000000000000018E-2</v>
+        <v>-9.9999999999999978E-2</v>
       </c>
       <c r="AJ36" s="9">
         <f t="shared" ref="AJ36" si="207">AJ12/AF12-1</f>
@@ -8043,7 +8020,7 @@
       </c>
       <c r="AV36" s="9">
         <f t="shared" si="210"/>
-        <v>2.000000000000024E-2</v>
+        <v>-8.169014084506987E-3</v>
       </c>
       <c r="AW36" s="9">
         <f t="shared" si="210"/>
@@ -8090,7 +8067,7 @@
       </c>
       <c r="BI36" s="4">
         <f>BI34+BI35</f>
-        <v>129.05716510405045</v>
+        <v>103.82907233865714</v>
       </c>
     </row>
     <row r="37" spans="2:61" x14ac:dyDescent="0.3">
@@ -8227,11 +8204,11 @@
       </c>
       <c r="AI37" s="9">
         <f t="shared" ref="AI37:AL37" si="218">AI13/AI7</f>
-        <v>0.11000000000000001</v>
+        <v>0.12302839116719243</v>
       </c>
       <c r="AJ37" s="9">
         <f t="shared" si="218"/>
-        <v>0.1</v>
+        <v>0.10000000000000002</v>
       </c>
       <c r="AK37" s="9">
         <f t="shared" si="218"/>
@@ -8239,7 +8216,7 @@
       </c>
       <c r="AL37" s="9">
         <f t="shared" si="218"/>
-        <v>0.1</v>
+        <v>0.10000000000000002</v>
       </c>
       <c r="AN37" s="9">
         <f t="shared" ref="AN37:BA37" si="219">AN13/AN7</f>
@@ -8275,11 +8252,11 @@
       </c>
       <c r="AV37" s="9">
         <f t="shared" si="219"/>
-        <v>0.10210542628744218</v>
+        <v>0.10393507662618388</v>
       </c>
       <c r="AW37" s="9">
         <f t="shared" si="219"/>
-        <v>0.08</v>
+        <v>8.0000000000000016E-2</v>
       </c>
       <c r="AX37" s="9">
         <f t="shared" si="219"/>
@@ -8322,7 +8299,7 @@
       </c>
       <c r="BI37" s="10">
         <f>BI36/BA24</f>
-        <v>9.2183689360036034</v>
+        <v>6.9219381559104765</v>
       </c>
     </row>
     <row r="38" spans="2:61" x14ac:dyDescent="0.3">
@@ -8447,7 +8424,7 @@
       </c>
       <c r="AI38" s="9">
         <f t="shared" ref="AI38" si="223">AI14/AE14-1</f>
-        <v>1.0000000000000009E-2</v>
+        <v>-9.9999999999999978E-2</v>
       </c>
       <c r="AJ38" s="9">
         <f t="shared" ref="AJ38" si="224">AJ14/AF14-1</f>
@@ -8492,7 +8469,7 @@
       </c>
       <c r="AV38" s="9">
         <f t="shared" si="227"/>
-        <v>1.0000000000000009E-2</v>
+        <v>-1.7363184079602134E-2</v>
       </c>
       <c r="AW38" s="9">
         <f t="shared" si="227"/>
@@ -8539,7 +8516,7 @@
       </c>
       <c r="BI38" s="10">
         <f>Main!D3</f>
-        <v>6.1</v>
+        <v>8.4700000000000006</v>
       </c>
     </row>
     <row r="39" spans="2:61" x14ac:dyDescent="0.3">
@@ -8744,7 +8721,7 @@
       </c>
       <c r="BA39" s="9">
         <f t="shared" si="236"/>
-        <v>0.2</v>
+        <v>0.19999999999999998</v>
       </c>
       <c r="BB39" s="9">
         <f t="shared" ref="BB39:BF39" si="237">BB21/BB20</f>
@@ -8752,7 +8729,7 @@
       </c>
       <c r="BC39" s="9">
         <f t="shared" si="237"/>
-        <v>0.2</v>
+        <v>0.20000000000000004</v>
       </c>
       <c r="BD39" s="9">
         <f t="shared" si="237"/>
@@ -8771,7 +8748,7 @@
       </c>
       <c r="BI39" s="11">
         <f>BI37/BI38-1</f>
-        <v>0.51120802229567275</v>
+        <v>-0.18276999339899935</v>
       </c>
     </row>
     <row r="40" spans="2:61" x14ac:dyDescent="0.3">

--- a/Financial Analysis/INSG.xlsx
+++ b/Financial Analysis/INSG.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28730"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\antos\Documents\GitHub\FinanceModels\Financial Analysis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{19947843-3BE5-4C04-B41A-4D43DA246813}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F0A2E40F-35E9-4430-83A3-E9C5621DB011}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{34A2EE39-018E-4F29-BBB7-6210648CE1A5}"/>
   </bookViews>
@@ -350,7 +350,7 @@
     <t>Q425</t>
   </si>
   <si>
-    <t>Slightly overvalued</t>
+    <t>Overvalued</t>
   </si>
 </sst>
 </file>
@@ -889,17 +889,17 @@
         <v>1</v>
       </c>
       <c r="D3" s="10">
-        <v>8.4700000000000006</v>
+        <v>12.28</v>
       </c>
       <c r="E3" s="3">
-        <v>45804</v>
+        <v>45898</v>
       </c>
       <c r="F3" s="3">
         <f ca="1">TODAY()</f>
-        <v>45804</v>
+        <v>45898</v>
       </c>
       <c r="G3" s="3">
-        <v>45875</v>
+        <v>45959</v>
       </c>
     </row>
     <row r="4" spans="2:7" x14ac:dyDescent="0.3">
@@ -910,7 +910,7 @@
         <v>15</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
     </row>
     <row r="5" spans="2:7" x14ac:dyDescent="0.3">
@@ -919,7 +919,7 @@
       </c>
       <c r="D5" s="4">
         <f>D3*D4</f>
-        <v>127.05000000000001</v>
+        <v>184.2</v>
       </c>
     </row>
     <row r="6" spans="2:7" x14ac:dyDescent="0.3">
@@ -931,7 +931,7 @@
         <v>35.1</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
     </row>
     <row r="7" spans="2:7" x14ac:dyDescent="0.3">
@@ -943,7 +943,7 @@
         <v>56.699999999999996</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
     </row>
     <row r="8" spans="2:7" x14ac:dyDescent="0.3">
@@ -961,7 +961,7 @@
       </c>
       <c r="D9" s="4">
         <f>D5-D8</f>
-        <v>148.65</v>
+        <v>205.79999999999998</v>
       </c>
     </row>
   </sheetData>
@@ -1208,16 +1208,13 @@
         <v>17.8</v>
       </c>
       <c r="AJ3" s="6">
-        <f>AF3*1.1</f>
-        <v>28.490000000000002</v>
+        <v>17.8</v>
       </c>
       <c r="AK3" s="6">
-        <f>AG3*0.97</f>
-        <v>31.330999999999996</v>
+        <v>19</v>
       </c>
       <c r="AL3" s="6">
-        <f>AH3*1.3</f>
-        <v>33.15</v>
+        <v>19</v>
       </c>
       <c r="AS3" s="4">
         <v>143.5</v>
@@ -1231,47 +1228,47 @@
       </c>
       <c r="AV3" s="4">
         <f>SUM(AI3:AL3)</f>
-        <v>110.77100000000002</v>
+        <v>73.599999999999994</v>
       </c>
       <c r="AW3" s="4">
         <f>AV3*1.15</f>
-        <v>127.38665</v>
+        <v>84.639999999999986</v>
       </c>
       <c r="AX3" s="4">
         <f>AW3*1.1</f>
-        <v>140.125315</v>
+        <v>93.103999999999999</v>
       </c>
       <c r="AY3" s="4">
         <f>AX3*1.08</f>
-        <v>151.33534020000002</v>
+        <v>100.55232000000001</v>
       </c>
       <c r="AZ3" s="4">
         <f>AY3*1.05</f>
-        <v>158.90210721000003</v>
+        <v>105.57993600000002</v>
       </c>
       <c r="BA3" s="4">
         <f>AZ3*1.04</f>
-        <v>165.25819149840004</v>
+        <v>109.80313344000002</v>
       </c>
       <c r="BB3" s="4">
         <f>BA3*1.03</f>
-        <v>170.21593724335204</v>
+        <v>113.09722744320003</v>
       </c>
       <c r="BC3" s="4">
         <f>BB3*1.02</f>
-        <v>173.6202559882191</v>
+        <v>115.35917199206403</v>
       </c>
       <c r="BD3" s="4">
         <f>BC3*1.02</f>
-        <v>177.09266110798347</v>
+        <v>117.66635543190532</v>
       </c>
       <c r="BE3" s="4">
         <f>BD3*1.02</f>
-        <v>180.63451433014313</v>
+        <v>120.01968254054343</v>
       </c>
       <c r="BF3" s="4">
         <f>BE3*1.02</f>
-        <v>184.24720461674599</v>
+        <v>122.4200761913543</v>
       </c>
     </row>
     <row r="4" spans="2:58" x14ac:dyDescent="0.3">
@@ -1332,16 +1329,13 @@
         <v>1.9</v>
       </c>
       <c r="AJ4" s="6">
-        <f>AG4*1.01</f>
-        <v>9.7969999999999988</v>
+        <v>1.9</v>
       </c>
       <c r="AK4" s="6">
-        <f t="shared" ref="AK4:AL4" si="0">AH4*1.01</f>
-        <v>10.504000000000001</v>
+        <v>2</v>
       </c>
       <c r="AL4" s="6">
-        <f t="shared" si="0"/>
-        <v>1.9189999999999998</v>
+        <v>2</v>
       </c>
       <c r="AS4" s="4">
         <v>43.6</v>
@@ -1355,47 +1349,47 @@
       </c>
       <c r="AV4" s="4">
         <f>SUM(AI4:AL4)</f>
-        <v>24.12</v>
+        <v>7.8</v>
       </c>
       <c r="AW4" s="4">
-        <f t="shared" ref="AW4:BF4" si="1">AV4*0.98</f>
-        <v>23.637599999999999</v>
+        <f t="shared" ref="AW4:BF4" si="0">AV4*0.98</f>
+        <v>7.6440000000000001</v>
       </c>
       <c r="AX4" s="4">
-        <f t="shared" si="1"/>
-        <v>23.164847999999999</v>
+        <f t="shared" si="0"/>
+        <v>7.4911199999999996</v>
       </c>
       <c r="AY4" s="4">
-        <f t="shared" si="1"/>
-        <v>22.701551039999998</v>
+        <f t="shared" si="0"/>
+        <v>7.3412975999999999</v>
       </c>
       <c r="AZ4" s="4">
-        <f t="shared" si="1"/>
-        <v>22.2475200192</v>
+        <f t="shared" si="0"/>
+        <v>7.1944716479999995</v>
       </c>
       <c r="BA4" s="4">
-        <f t="shared" si="1"/>
-        <v>21.802569618815998</v>
+        <f t="shared" si="0"/>
+        <v>7.0505822150399995</v>
       </c>
       <c r="BB4" s="4">
-        <f t="shared" si="1"/>
-        <v>21.366518226439677</v>
+        <f t="shared" si="0"/>
+        <v>6.9095705707391994</v>
       </c>
       <c r="BC4" s="4">
-        <f t="shared" si="1"/>
-        <v>20.939187861910884</v>
+        <f t="shared" si="0"/>
+        <v>6.7713791593244155</v>
       </c>
       <c r="BD4" s="4">
-        <f t="shared" si="1"/>
-        <v>20.520404104672668</v>
+        <f t="shared" si="0"/>
+        <v>6.6359515761379271</v>
       </c>
       <c r="BE4" s="4">
-        <f t="shared" si="1"/>
-        <v>20.109996022579214</v>
+        <f t="shared" si="0"/>
+        <v>6.5032325446151686</v>
       </c>
       <c r="BF4" s="4">
-        <f t="shared" si="1"/>
-        <v>19.707796102127631</v>
+        <f t="shared" si="0"/>
+        <v>6.3731678937228651</v>
       </c>
     </row>
     <row r="5" spans="2:58" x14ac:dyDescent="0.3">
@@ -1472,56 +1466,56 @@
         <v>62.6</v>
       </c>
       <c r="Z5" s="6">
-        <f t="shared" ref="Z5:AF5" si="2">Z3+Z4</f>
+        <f t="shared" ref="Z5:AF5" si="1">Z3+Z4</f>
         <v>38</v>
       </c>
       <c r="AA5" s="6">
+        <f t="shared" si="1"/>
+        <v>34.9</v>
+      </c>
+      <c r="AB5" s="6">
+        <f t="shared" si="1"/>
+        <v>38.4</v>
+      </c>
+      <c r="AC5" s="6">
+        <f t="shared" si="1"/>
+        <v>33.6</v>
+      </c>
+      <c r="AD5" s="6">
+        <f t="shared" si="1"/>
+        <v>28.4</v>
+      </c>
+      <c r="AE5" s="6">
+        <f t="shared" si="1"/>
+        <v>29.5</v>
+      </c>
+      <c r="AF5" s="6">
+        <f t="shared" si="1"/>
+        <v>39.200000000000003</v>
+      </c>
+      <c r="AG5" s="6">
+        <f t="shared" ref="AG5:AL5" si="2">AG3+AG4</f>
+        <v>42</v>
+      </c>
+      <c r="AH5" s="6">
         <f t="shared" si="2"/>
-        <v>34.9</v>
-      </c>
-      <c r="AB5" s="6">
+        <v>35.9</v>
+      </c>
+      <c r="AI5" s="6">
         <f t="shared" si="2"/>
-        <v>38.4</v>
-      </c>
-      <c r="AC5" s="6">
+        <v>19.7</v>
+      </c>
+      <c r="AJ5" s="6">
         <f t="shared" si="2"/>
-        <v>33.6</v>
-      </c>
-      <c r="AD5" s="6">
+        <v>19.7</v>
+      </c>
+      <c r="AK5" s="6">
         <f t="shared" si="2"/>
-        <v>28.4</v>
-      </c>
-      <c r="AE5" s="6">
+        <v>21</v>
+      </c>
+      <c r="AL5" s="6">
         <f t="shared" si="2"/>
-        <v>29.5</v>
-      </c>
-      <c r="AF5" s="6">
-        <f t="shared" si="2"/>
-        <v>39.200000000000003</v>
-      </c>
-      <c r="AG5" s="6">
-        <f t="shared" ref="AG5:AL5" si="3">AG3+AG4</f>
-        <v>42</v>
-      </c>
-      <c r="AH5" s="6">
-        <f t="shared" si="3"/>
-        <v>35.9</v>
-      </c>
-      <c r="AI5" s="6">
-        <f t="shared" si="3"/>
-        <v>19.7</v>
-      </c>
-      <c r="AJ5" s="6">
-        <f t="shared" si="3"/>
-        <v>38.286999999999999</v>
-      </c>
-      <c r="AK5" s="6">
-        <f t="shared" si="3"/>
-        <v>41.834999999999994</v>
-      </c>
-      <c r="AL5" s="6">
-        <f t="shared" si="3"/>
-        <v>35.068999999999996</v>
+        <v>21</v>
       </c>
       <c r="AN5" s="4">
         <f>SUM(C5:F5)</f>
@@ -1557,47 +1551,47 @@
       </c>
       <c r="AV5" s="4">
         <f>AV3+AV4</f>
-        <v>134.89100000000002</v>
+        <v>81.399999999999991</v>
       </c>
       <c r="AW5" s="4">
-        <f t="shared" ref="AW5:BF5" si="4">AW3+AW4</f>
-        <v>151.02424999999999</v>
+        <f t="shared" ref="AW5:BF5" si="3">AW3+AW4</f>
+        <v>92.283999999999992</v>
       </c>
       <c r="AX5" s="4">
-        <f t="shared" si="4"/>
-        <v>163.29016300000001</v>
+        <f t="shared" si="3"/>
+        <v>100.59511999999999</v>
       </c>
       <c r="AY5" s="4">
-        <f t="shared" si="4"/>
-        <v>174.03689124000002</v>
+        <f t="shared" si="3"/>
+        <v>107.89361760000001</v>
       </c>
       <c r="AZ5" s="4">
-        <f t="shared" si="4"/>
-        <v>181.14962722920004</v>
+        <f t="shared" si="3"/>
+        <v>112.77440764800002</v>
       </c>
       <c r="BA5" s="4">
-        <f t="shared" si="4"/>
-        <v>187.06076111721603</v>
+        <f t="shared" si="3"/>
+        <v>116.85371565504002</v>
       </c>
       <c r="BB5" s="4">
-        <f t="shared" si="4"/>
-        <v>191.58245546979171</v>
+        <f t="shared" si="3"/>
+        <v>120.00679801393923</v>
       </c>
       <c r="BC5" s="4">
-        <f t="shared" si="4"/>
-        <v>194.55944385012998</v>
+        <f t="shared" si="3"/>
+        <v>122.13055115138845</v>
       </c>
       <c r="BD5" s="4">
-        <f t="shared" si="4"/>
-        <v>197.61306521265615</v>
+        <f t="shared" si="3"/>
+        <v>124.30230700804324</v>
       </c>
       <c r="BE5" s="4">
-        <f t="shared" si="4"/>
-        <v>200.74451035272236</v>
+        <f t="shared" si="3"/>
+        <v>126.5229150851586</v>
       </c>
       <c r="BF5" s="4">
-        <f t="shared" si="4"/>
-        <v>203.95500071887363</v>
+        <f t="shared" si="3"/>
+        <v>128.79324408507716</v>
       </c>
     </row>
     <row r="6" spans="2:58" x14ac:dyDescent="0.3">
@@ -1704,7 +1698,6 @@
         <v>12</v>
       </c>
       <c r="AJ6" s="6">
-        <f>AF6*0.6</f>
         <v>12</v>
       </c>
       <c r="AK6" s="6">
@@ -1752,44 +1745,44 @@
         <v>50.620000000000005</v>
       </c>
       <c r="AW6" s="4">
-        <f>AV6*1.14</f>
-        <v>57.706800000000001</v>
+        <f>AV6*1.15</f>
+        <v>58.213000000000001</v>
       </c>
       <c r="AX6" s="4">
-        <f>AW6*1.07</f>
-        <v>61.746276000000002</v>
+        <f>AW6*1.09</f>
+        <v>63.452170000000002</v>
       </c>
       <c r="AY6" s="4">
-        <f>AX6*1.04</f>
-        <v>64.216127040000003</v>
+        <f>AX6*1.06</f>
+        <v>67.259300200000013</v>
       </c>
       <c r="AZ6" s="4">
-        <f>AY6*1.03</f>
-        <v>66.142610851200004</v>
+        <f>AY6*1.05</f>
+        <v>70.622265210000023</v>
       </c>
       <c r="BA6" s="4">
-        <f>AZ6*1.02</f>
-        <v>67.465463068224011</v>
+        <f>AZ6*1.03</f>
+        <v>72.740933166300024</v>
       </c>
       <c r="BB6" s="4">
-        <f t="shared" ref="BB6:BF6" si="5">BA6*1.02</f>
-        <v>68.814772329588493</v>
+        <f t="shared" ref="BB6:BF6" si="4">BA6*1.02</f>
+        <v>74.195751829626033</v>
       </c>
       <c r="BC6" s="4">
-        <f t="shared" si="5"/>
-        <v>70.191067776180262</v>
+        <f t="shared" si="4"/>
+        <v>75.679666866218554</v>
       </c>
       <c r="BD6" s="4">
-        <f t="shared" si="5"/>
-        <v>71.594889131703866</v>
+        <f t="shared" si="4"/>
+        <v>77.19326020354292</v>
       </c>
       <c r="BE6" s="4">
-        <f t="shared" si="5"/>
-        <v>73.026786914337947</v>
+        <f t="shared" si="4"/>
+        <v>78.737125407613775</v>
       </c>
       <c r="BF6" s="4">
-        <f t="shared" si="5"/>
-        <v>74.487322652624712</v>
+        <f t="shared" si="4"/>
+        <v>80.311867915766058</v>
       </c>
     </row>
     <row r="7" spans="2:58" s="1" customFormat="1" x14ac:dyDescent="0.3">
@@ -1797,148 +1790,148 @@
         <v>11</v>
       </c>
       <c r="C7" s="7">
-        <f t="shared" ref="C7:P7" si="6">C5+C6</f>
+        <f t="shared" ref="C7:P7" si="5">C5+C6</f>
         <v>55.4</v>
       </c>
       <c r="D7" s="7">
+        <f t="shared" si="5"/>
+        <v>59.900000000000006</v>
+      </c>
+      <c r="E7" s="7">
+        <f t="shared" si="5"/>
+        <v>57.5</v>
+      </c>
+      <c r="F7" s="7">
+        <f t="shared" si="5"/>
+        <v>46.6</v>
+      </c>
+      <c r="G7" s="7">
+        <f t="shared" si="5"/>
+        <v>46.8</v>
+      </c>
+      <c r="H7" s="7">
+        <f t="shared" si="5"/>
+        <v>49</v>
+      </c>
+      <c r="I7" s="7">
+        <f t="shared" si="5"/>
+        <v>50.6</v>
+      </c>
+      <c r="J7" s="7">
+        <f t="shared" si="5"/>
+        <v>56.1</v>
+      </c>
+      <c r="K7" s="7">
+        <f t="shared" si="5"/>
+        <v>48.599999999999994</v>
+      </c>
+      <c r="L7" s="7">
+        <f t="shared" si="5"/>
+        <v>56</v>
+      </c>
+      <c r="M7" s="7">
+        <f t="shared" si="5"/>
+        <v>62.7</v>
+      </c>
+      <c r="N7" s="7">
+        <f t="shared" si="5"/>
+        <v>52.4</v>
+      </c>
+      <c r="O7" s="7">
+        <f t="shared" si="5"/>
+        <v>56.9</v>
+      </c>
+      <c r="P7" s="7">
+        <f t="shared" si="5"/>
+        <v>80.600000000000009</v>
+      </c>
+      <c r="Q7" s="7">
+        <f t="shared" ref="Q7:U7" si="6">Q5+Q6</f>
+        <v>90.2</v>
+      </c>
+      <c r="R7" s="7">
         <f t="shared" si="6"/>
-        <v>59.900000000000006</v>
-      </c>
-      <c r="E7" s="7">
+        <v>86.1</v>
+      </c>
+      <c r="S7" s="7">
         <f t="shared" si="6"/>
-        <v>57.5</v>
-      </c>
-      <c r="F7" s="7">
+        <v>57.6</v>
+      </c>
+      <c r="T7" s="7">
+        <f t="shared" ref="T7" si="7">T5+T6</f>
+        <v>65.7</v>
+      </c>
+      <c r="U7" s="7">
         <f t="shared" si="6"/>
-        <v>46.6</v>
-      </c>
-      <c r="G7" s="7">
-        <f t="shared" si="6"/>
-        <v>46.8</v>
-      </c>
-      <c r="H7" s="7">
-        <f t="shared" si="6"/>
-        <v>49</v>
-      </c>
-      <c r="I7" s="7">
-        <f t="shared" si="6"/>
-        <v>50.6</v>
-      </c>
-      <c r="J7" s="7">
-        <f t="shared" si="6"/>
-        <v>56.1</v>
-      </c>
-      <c r="K7" s="7">
-        <f t="shared" si="6"/>
-        <v>48.599999999999994</v>
-      </c>
-      <c r="L7" s="7">
-        <f t="shared" si="6"/>
-        <v>56</v>
-      </c>
-      <c r="M7" s="7">
-        <f t="shared" si="6"/>
-        <v>62.7</v>
-      </c>
-      <c r="N7" s="7">
-        <f t="shared" si="6"/>
-        <v>52.4</v>
-      </c>
-      <c r="O7" s="7">
-        <f t="shared" si="6"/>
-        <v>56.9</v>
-      </c>
-      <c r="P7" s="7">
-        <f t="shared" si="6"/>
-        <v>80.600000000000009</v>
-      </c>
-      <c r="Q7" s="7">
-        <f t="shared" ref="Q7:U7" si="7">Q5+Q6</f>
-        <v>90.2</v>
-      </c>
-      <c r="R7" s="7">
-        <f t="shared" si="7"/>
-        <v>86.1</v>
-      </c>
-      <c r="S7" s="7">
-        <f t="shared" si="7"/>
-        <v>57.6</v>
-      </c>
-      <c r="T7" s="7">
-        <f t="shared" ref="T7" si="8">T5+T6</f>
-        <v>65.7</v>
-      </c>
-      <c r="U7" s="7">
-        <f t="shared" si="7"/>
         <v>66.2</v>
       </c>
       <c r="V7" s="7">
-        <f t="shared" ref="V7:W7" si="9">V5+V6</f>
+        <f t="shared" ref="V7:W7" si="8">V5+V6</f>
         <v>72.900000000000006</v>
       </c>
       <c r="W7" s="7">
+        <f t="shared" si="8"/>
+        <v>61.4</v>
+      </c>
+      <c r="X7" s="7">
+        <f t="shared" ref="X7:Y7" si="9">X5+X6</f>
+        <v>61.7</v>
+      </c>
+      <c r="Y7" s="7">
         <f t="shared" si="9"/>
-        <v>61.4</v>
-      </c>
-      <c r="X7" s="7">
-        <f t="shared" ref="X7:Y7" si="10">X5+X6</f>
-        <v>61.7</v>
-      </c>
-      <c r="Y7" s="7">
-        <f t="shared" si="10"/>
         <v>69.099999999999994</v>
       </c>
       <c r="Z7" s="7">
-        <f t="shared" ref="Z7" si="11">Z5+Z6</f>
+        <f t="shared" ref="Z7" si="10">Z5+Z6</f>
         <v>53</v>
       </c>
       <c r="AA7" s="7">
-        <f t="shared" ref="AA7" si="12">AA5+AA6</f>
+        <f t="shared" ref="AA7" si="11">AA5+AA6</f>
         <v>50.8</v>
       </c>
       <c r="AB7" s="7">
-        <f t="shared" ref="AB7:AC7" si="13">AB5+AB6</f>
+        <f t="shared" ref="AB7:AC7" si="12">AB5+AB6</f>
         <v>53.599999999999994</v>
       </c>
       <c r="AC7" s="7">
-        <f t="shared" si="13"/>
+        <f t="shared" si="12"/>
         <v>40.800000000000004</v>
       </c>
       <c r="AD7" s="7">
-        <f t="shared" ref="AD7" si="14">AD5+AD6</f>
+        <f t="shared" ref="AD7" si="13">AD5+AD6</f>
         <v>42.7</v>
       </c>
       <c r="AE7" s="7">
-        <f t="shared" ref="AE7" si="15">AE5+AE6</f>
+        <f t="shared" ref="AE7" si="14">AE5+AE6</f>
         <v>45.1</v>
       </c>
       <c r="AF7" s="7">
-        <f t="shared" ref="AF7:AL7" si="16">AF5+AF6</f>
+        <f t="shared" ref="AF7:AL7" si="15">AF5+AF6</f>
         <v>59.2</v>
       </c>
       <c r="AG7" s="7">
-        <f t="shared" si="16"/>
+        <f t="shared" si="15"/>
         <v>54</v>
       </c>
       <c r="AH7" s="7">
-        <f t="shared" si="16"/>
+        <f t="shared" si="15"/>
         <v>48.099999999999994</v>
       </c>
       <c r="AI7" s="7">
-        <f t="shared" si="16"/>
+        <f t="shared" si="15"/>
         <v>31.7</v>
       </c>
       <c r="AJ7" s="7">
-        <f t="shared" si="16"/>
-        <v>50.286999999999999</v>
+        <f t="shared" si="15"/>
+        <v>31.7</v>
       </c>
       <c r="AK7" s="7">
-        <f t="shared" si="16"/>
-        <v>55.034999999999997</v>
+        <f t="shared" si="15"/>
+        <v>34.200000000000003</v>
       </c>
       <c r="AL7" s="7">
-        <f t="shared" si="16"/>
-        <v>48.488999999999997</v>
+        <f t="shared" si="15"/>
+        <v>34.42</v>
       </c>
       <c r="AN7" s="7">
         <f>AN5+AN6</f>
@@ -1957,64 +1950,64 @@
         <v>313.79999999999995</v>
       </c>
       <c r="AR7" s="7">
-        <f t="shared" ref="AR7:BA7" si="17">AR5+AR6</f>
+        <f t="shared" ref="AR7:BA7" si="16">AR5+AR6</f>
         <v>262.39999999999998</v>
       </c>
       <c r="AS7" s="7">
+        <f t="shared" si="16"/>
+        <v>245.2</v>
+      </c>
+      <c r="AT7" s="7">
+        <f t="shared" si="16"/>
+        <v>187.90000000000003</v>
+      </c>
+      <c r="AU7" s="7">
+        <f t="shared" si="16"/>
+        <v>206.39999999999998</v>
+      </c>
+      <c r="AV7" s="7">
+        <f t="shared" si="16"/>
+        <v>132.01999999999998</v>
+      </c>
+      <c r="AW7" s="7">
+        <f t="shared" si="16"/>
+        <v>150.49699999999999</v>
+      </c>
+      <c r="AX7" s="7">
+        <f t="shared" si="16"/>
+        <v>164.04729</v>
+      </c>
+      <c r="AY7" s="7">
+        <f t="shared" si="16"/>
+        <v>175.15291780000001</v>
+      </c>
+      <c r="AZ7" s="7">
+        <f t="shared" si="16"/>
+        <v>183.39667285800004</v>
+      </c>
+      <c r="BA7" s="7">
+        <f t="shared" si="16"/>
+        <v>189.59464882134006</v>
+      </c>
+      <c r="BB7" s="7">
+        <f t="shared" ref="BB7:BF7" si="17">BB5+BB6</f>
+        <v>194.20254984356527</v>
+      </c>
+      <c r="BC7" s="7">
         <f t="shared" si="17"/>
-        <v>245.2</v>
-      </c>
-      <c r="AT7" s="7">
+        <v>197.81021801760699</v>
+      </c>
+      <c r="BD7" s="7">
         <f t="shared" si="17"/>
-        <v>187.90000000000003</v>
-      </c>
-      <c r="AU7" s="7">
+        <v>201.49556721158615</v>
+      </c>
+      <c r="BE7" s="7">
         <f t="shared" si="17"/>
-        <v>206.39999999999998</v>
-      </c>
-      <c r="AV7" s="7">
+        <v>205.26004049277236</v>
+      </c>
+      <c r="BF7" s="7">
         <f t="shared" si="17"/>
-        <v>185.51100000000002</v>
-      </c>
-      <c r="AW7" s="7">
-        <f t="shared" si="17"/>
-        <v>208.73104999999998</v>
-      </c>
-      <c r="AX7" s="7">
-        <f t="shared" si="17"/>
-        <v>225.036439</v>
-      </c>
-      <c r="AY7" s="7">
-        <f t="shared" si="17"/>
-        <v>238.25301828000002</v>
-      </c>
-      <c r="AZ7" s="7">
-        <f t="shared" si="17"/>
-        <v>247.29223808040004</v>
-      </c>
-      <c r="BA7" s="7">
-        <f t="shared" si="17"/>
-        <v>254.52622418544004</v>
-      </c>
-      <c r="BB7" s="7">
-        <f t="shared" ref="BB7:BF7" si="18">BB5+BB6</f>
-        <v>260.39722779938018</v>
-      </c>
-      <c r="BC7" s="7">
-        <f t="shared" si="18"/>
-        <v>264.75051162631024</v>
-      </c>
-      <c r="BD7" s="7">
-        <f t="shared" si="18"/>
-        <v>269.20795434436002</v>
-      </c>
-      <c r="BE7" s="7">
-        <f t="shared" si="18"/>
-        <v>273.77129726706028</v>
-      </c>
-      <c r="BF7" s="7">
-        <f t="shared" si="18"/>
-        <v>278.44232337149833</v>
+        <v>209.10511200084323</v>
       </c>
     </row>
     <row r="8" spans="2:58" x14ac:dyDescent="0.3">
@@ -2121,16 +2114,15 @@
         <v>15.4</v>
       </c>
       <c r="AJ8" s="4">
-        <f>AJ5*0.77</f>
-        <v>29.480989999999998</v>
+        <v>15.4</v>
       </c>
       <c r="AK8" s="4">
         <f>AK5*0.8</f>
-        <v>33.467999999999996</v>
+        <v>16.8</v>
       </c>
       <c r="AL8" s="4">
         <f>AL5*0.8</f>
-        <v>28.055199999999999</v>
+        <v>16.8</v>
       </c>
       <c r="AN8" s="4">
         <f>SUM(C8:F8)</f>
@@ -2166,47 +2158,47 @@
       </c>
       <c r="AV8" s="4">
         <f>SUM(AI8:AL8)</f>
-        <v>106.40418999999999</v>
+        <v>64.400000000000006</v>
       </c>
       <c r="AW8" s="4">
-        <f t="shared" ref="AW8:BF8" si="19">AW5*0.79</f>
-        <v>119.3091575</v>
+        <f t="shared" ref="AW8:BF8" si="18">AW5*0.79</f>
+        <v>72.904359999999997</v>
       </c>
       <c r="AX8" s="4">
-        <f t="shared" si="19"/>
-        <v>128.99922877</v>
+        <f t="shared" si="18"/>
+        <v>79.4701448</v>
       </c>
       <c r="AY8" s="4">
-        <f t="shared" si="19"/>
-        <v>137.48914407960001</v>
+        <f t="shared" si="18"/>
+        <v>85.235957904000017</v>
       </c>
       <c r="AZ8" s="4">
-        <f t="shared" si="19"/>
-        <v>143.10820551106804</v>
+        <f t="shared" si="18"/>
+        <v>89.091782041920027</v>
       </c>
       <c r="BA8" s="4">
-        <f t="shared" si="19"/>
-        <v>147.77800128260068</v>
+        <f t="shared" si="18"/>
+        <v>92.314435367481622</v>
       </c>
       <c r="BB8" s="4">
-        <f t="shared" si="19"/>
-        <v>151.35013982113546</v>
+        <f t="shared" si="18"/>
+        <v>94.805370431011994</v>
       </c>
       <c r="BC8" s="4">
-        <f t="shared" si="19"/>
-        <v>153.70196064160268</v>
+        <f t="shared" si="18"/>
+        <v>96.483135409596869</v>
       </c>
       <c r="BD8" s="4">
-        <f t="shared" si="19"/>
-        <v>156.11432151799838</v>
+        <f t="shared" si="18"/>
+        <v>98.198822536354172</v>
       </c>
       <c r="BE8" s="4">
-        <f t="shared" si="19"/>
-        <v>158.58816317865066</v>
+        <f t="shared" si="18"/>
+        <v>99.953102917275302</v>
       </c>
       <c r="BF8" s="4">
-        <f t="shared" si="19"/>
-        <v>161.12445056791017</v>
+        <f t="shared" si="18"/>
+        <v>101.74666282721097</v>
       </c>
     </row>
     <row r="9" spans="2:58" x14ac:dyDescent="0.3">
@@ -2315,16 +2307,15 @@
         <v>1.3</v>
       </c>
       <c r="AJ9" s="4">
-        <f t="shared" ref="AJ9:AL9" si="20">AJ6*0.13</f>
-        <v>1.56</v>
+        <v>1.3</v>
       </c>
       <c r="AK9" s="4">
-        <f t="shared" si="20"/>
-        <v>1.7160000000000002</v>
+        <f>AK6*0.11</f>
+        <v>1.4520000000000002</v>
       </c>
       <c r="AL9" s="4">
-        <f t="shared" si="20"/>
-        <v>1.7446000000000002</v>
+        <f>AL6*0.11</f>
+        <v>1.4762</v>
       </c>
       <c r="AN9" s="4">
         <f>SUM(C9:F9)</f>
@@ -2360,47 +2351,47 @@
       </c>
       <c r="AV9" s="4">
         <f>SUM(AI9:AL9)</f>
-        <v>6.3206000000000007</v>
+        <v>5.5282</v>
       </c>
       <c r="AW9" s="4">
-        <f t="shared" ref="AW9:BF9" si="21">AW6*0.25</f>
-        <v>14.4267</v>
+        <f t="shared" ref="AW9:BF9" si="19">AW6*0.25</f>
+        <v>14.55325</v>
       </c>
       <c r="AX9" s="4">
-        <f t="shared" si="21"/>
-        <v>15.436569</v>
+        <f t="shared" si="19"/>
+        <v>15.863042500000001</v>
       </c>
       <c r="AY9" s="4">
-        <f t="shared" si="21"/>
-        <v>16.054031760000001</v>
+        <f t="shared" si="19"/>
+        <v>16.814825050000003</v>
       </c>
       <c r="AZ9" s="4">
-        <f t="shared" si="21"/>
-        <v>16.535652712800001</v>
+        <f t="shared" si="19"/>
+        <v>17.655566302500006</v>
       </c>
       <c r="BA9" s="4">
-        <f t="shared" si="21"/>
-        <v>16.866365767056003</v>
+        <f t="shared" si="19"/>
+        <v>18.185233291575006</v>
       </c>
       <c r="BB9" s="4">
-        <f t="shared" si="21"/>
-        <v>17.203693082397123</v>
+        <f t="shared" si="19"/>
+        <v>18.548937957406508</v>
       </c>
       <c r="BC9" s="4">
-        <f t="shared" si="21"/>
-        <v>17.547766944045065</v>
+        <f t="shared" si="19"/>
+        <v>18.919916716554638</v>
       </c>
       <c r="BD9" s="4">
-        <f t="shared" si="21"/>
-        <v>17.898722282925966</v>
+        <f t="shared" si="19"/>
+        <v>19.29831505088573</v>
       </c>
       <c r="BE9" s="4">
-        <f t="shared" si="21"/>
-        <v>18.256696728584487</v>
+        <f t="shared" si="19"/>
+        <v>19.684281351903444</v>
       </c>
       <c r="BF9" s="4">
-        <f t="shared" si="21"/>
-        <v>18.621830663156178</v>
+        <f t="shared" si="19"/>
+        <v>20.077966978941514</v>
       </c>
     </row>
     <row r="10" spans="2:58" x14ac:dyDescent="0.3">
@@ -2408,148 +2399,148 @@
         <v>23</v>
       </c>
       <c r="C10" s="4">
-        <f t="shared" ref="C10:P10" si="22">C8+C9</f>
+        <f t="shared" ref="C10:P10" si="20">C8+C9</f>
         <v>39.200000000000003</v>
       </c>
       <c r="D10" s="4">
-        <f t="shared" si="22"/>
+        <f t="shared" si="20"/>
         <v>41.300000000000004</v>
       </c>
       <c r="E10" s="4">
-        <f t="shared" si="22"/>
+        <f t="shared" si="20"/>
         <v>41.099999999999994</v>
       </c>
       <c r="F10" s="4">
-        <f t="shared" si="22"/>
+        <f t="shared" si="20"/>
         <v>28.9</v>
       </c>
       <c r="G10" s="4">
-        <f t="shared" si="22"/>
+        <f t="shared" si="20"/>
         <v>30.700000000000003</v>
       </c>
       <c r="H10" s="4">
-        <f t="shared" si="22"/>
+        <f t="shared" si="20"/>
         <v>31.6</v>
       </c>
       <c r="I10" s="4">
-        <f t="shared" si="22"/>
+        <f t="shared" si="20"/>
         <v>33</v>
       </c>
       <c r="J10" s="4">
-        <f t="shared" si="22"/>
+        <f t="shared" si="20"/>
         <v>36.299999999999997</v>
       </c>
       <c r="K10" s="4">
-        <f t="shared" si="22"/>
+        <f t="shared" si="20"/>
         <v>33.800000000000004</v>
       </c>
       <c r="L10" s="4">
-        <f t="shared" si="22"/>
+        <f t="shared" si="20"/>
         <v>40.4</v>
       </c>
       <c r="M10" s="4">
-        <f t="shared" si="22"/>
+        <f t="shared" si="20"/>
         <v>44.1</v>
       </c>
       <c r="N10" s="4">
-        <f t="shared" si="22"/>
+        <f t="shared" si="20"/>
         <v>37.299999999999997</v>
       </c>
       <c r="O10" s="4">
-        <f t="shared" si="22"/>
+        <f t="shared" si="20"/>
         <v>39.699999999999996</v>
       </c>
       <c r="P10" s="4">
-        <f t="shared" si="22"/>
+        <f t="shared" si="20"/>
         <v>58.7</v>
       </c>
       <c r="Q10" s="4">
-        <f t="shared" ref="Q10:U10" si="23">Q8+Q9</f>
+        <f t="shared" ref="Q10:U10" si="21">Q8+Q9</f>
         <v>65</v>
       </c>
       <c r="R10" s="4">
+        <f t="shared" si="21"/>
+        <v>59.6</v>
+      </c>
+      <c r="S10" s="4">
+        <f t="shared" si="21"/>
+        <v>39.1</v>
+      </c>
+      <c r="T10" s="4">
+        <f t="shared" ref="T10" si="22">T8+T9</f>
+        <v>45.300000000000004</v>
+      </c>
+      <c r="U10" s="4">
+        <f t="shared" si="21"/>
+        <v>47.300000000000004</v>
+      </c>
+      <c r="V10" s="4">
+        <f t="shared" ref="V10:W10" si="23">V8+V9</f>
+        <v>54.699999999999996</v>
+      </c>
+      <c r="W10" s="4">
         <f t="shared" si="23"/>
-        <v>59.6</v>
-      </c>
-      <c r="S10" s="4">
-        <f t="shared" si="23"/>
-        <v>39.1</v>
-      </c>
-      <c r="T10" s="4">
-        <f t="shared" ref="T10" si="24">T8+T9</f>
-        <v>45.300000000000004</v>
-      </c>
-      <c r="U10" s="4">
-        <f t="shared" si="23"/>
-        <v>47.300000000000004</v>
-      </c>
-      <c r="V10" s="4">
-        <f t="shared" ref="V10:W10" si="25">V8+V9</f>
-        <v>54.699999999999996</v>
-      </c>
-      <c r="W10" s="4">
-        <f t="shared" si="25"/>
         <v>46.1</v>
       </c>
       <c r="X10" s="4">
-        <f t="shared" ref="X10:Y10" si="26">X8+X9</f>
+        <f t="shared" ref="X10:Y10" si="24">X8+X9</f>
         <v>44</v>
       </c>
       <c r="Y10" s="4">
-        <f t="shared" si="26"/>
+        <f t="shared" si="24"/>
         <v>51.2</v>
       </c>
       <c r="Z10" s="4">
-        <f t="shared" ref="Z10" si="27">Z8+Z9</f>
+        <f t="shared" ref="Z10" si="25">Z8+Z9</f>
         <v>37.1</v>
       </c>
       <c r="AA10" s="4">
-        <f t="shared" ref="AA10" si="28">AA8+AA9</f>
+        <f t="shared" ref="AA10" si="26">AA8+AA9</f>
         <v>32.6</v>
       </c>
       <c r="AB10" s="4">
-        <f t="shared" ref="AB10:AC10" si="29">AB8+AB9</f>
+        <f t="shared" ref="AB10:AC10" si="27">AB8+AB9</f>
         <v>35.6</v>
       </c>
       <c r="AC10" s="4">
-        <f t="shared" si="29"/>
+        <f t="shared" si="27"/>
         <v>46.7</v>
       </c>
       <c r="AD10" s="4">
-        <f t="shared" ref="AD10" si="30">AD8+AD9</f>
+        <f t="shared" ref="AD10" si="28">AD8+AD9</f>
         <v>29.5</v>
       </c>
       <c r="AE10" s="4">
-        <f t="shared" ref="AE10" si="31">AE8+AE9</f>
+        <f t="shared" ref="AE10" si="29">AE8+AE9</f>
         <v>27.6</v>
       </c>
       <c r="AF10" s="4">
-        <f t="shared" ref="AF10:AH10" si="32">AF8+AF9</f>
+        <f t="shared" ref="AF10:AH10" si="30">AF8+AF9</f>
         <v>36.1</v>
       </c>
       <c r="AG10" s="4">
-        <f t="shared" si="32"/>
+        <f t="shared" si="30"/>
         <v>35.200000000000003</v>
       </c>
       <c r="AH10" s="4">
-        <f t="shared" si="32"/>
+        <f t="shared" si="30"/>
         <v>30.200000000000003</v>
       </c>
       <c r="AI10" s="4">
-        <f t="shared" ref="AI10:AL10" si="33">AI8+AI9</f>
+        <f t="shared" ref="AI10:AL10" si="31">AI8+AI9</f>
         <v>16.7</v>
       </c>
       <c r="AJ10" s="4">
-        <f t="shared" si="33"/>
-        <v>31.040989999999997</v>
+        <f t="shared" si="31"/>
+        <v>16.7</v>
       </c>
       <c r="AK10" s="4">
-        <f t="shared" si="33"/>
-        <v>35.183999999999997</v>
+        <f t="shared" si="31"/>
+        <v>18.252000000000002</v>
       </c>
       <c r="AL10" s="4">
-        <f t="shared" si="33"/>
-        <v>29.799799999999998</v>
+        <f t="shared" si="31"/>
+        <v>18.276199999999999</v>
       </c>
       <c r="AN10" s="4">
         <f>AN8+AN9</f>
@@ -2568,64 +2559,64 @@
         <v>223</v>
       </c>
       <c r="AR10" s="4">
-        <f t="shared" ref="AR10:BA10" si="34">AR8+AR9</f>
+        <f t="shared" ref="AR10:BA10" si="32">AR8+AR9</f>
         <v>186.4</v>
       </c>
       <c r="AS10" s="4">
-        <f t="shared" si="34"/>
+        <f t="shared" si="32"/>
         <v>178.4</v>
       </c>
       <c r="AT10" s="4">
-        <f t="shared" si="34"/>
+        <f t="shared" si="32"/>
         <v>144.39999999999998</v>
       </c>
       <c r="AU10" s="4">
-        <f t="shared" si="34"/>
+        <f t="shared" si="32"/>
         <v>129.1</v>
       </c>
       <c r="AV10" s="4">
-        <f t="shared" si="34"/>
-        <v>112.72478999999998</v>
+        <f t="shared" si="32"/>
+        <v>69.928200000000004</v>
       </c>
       <c r="AW10" s="4">
-        <f t="shared" si="34"/>
-        <v>133.73585750000001</v>
+        <f t="shared" si="32"/>
+        <v>87.457610000000003</v>
       </c>
       <c r="AX10" s="4">
-        <f t="shared" si="34"/>
-        <v>144.43579776999999</v>
+        <f t="shared" si="32"/>
+        <v>95.333187300000006</v>
       </c>
       <c r="AY10" s="4">
-        <f t="shared" si="34"/>
-        <v>153.5431758396</v>
+        <f t="shared" si="32"/>
+        <v>102.05078295400003</v>
       </c>
       <c r="AZ10" s="4">
-        <f t="shared" si="34"/>
-        <v>159.64385822386805</v>
+        <f t="shared" si="32"/>
+        <v>106.74734834442003</v>
       </c>
       <c r="BA10" s="4">
-        <f t="shared" si="34"/>
-        <v>164.64436704965669</v>
+        <f t="shared" si="32"/>
+        <v>110.49966865905662</v>
       </c>
       <c r="BB10" s="4">
-        <f t="shared" ref="BB10:BF10" si="35">BB8+BB9</f>
-        <v>168.55383290353257</v>
+        <f t="shared" ref="BB10:BF10" si="33">BB8+BB9</f>
+        <v>113.3543083884185</v>
       </c>
       <c r="BC10" s="4">
-        <f t="shared" si="35"/>
-        <v>171.24972758564775</v>
+        <f t="shared" si="33"/>
+        <v>115.40305212615151</v>
       </c>
       <c r="BD10" s="4">
-        <f t="shared" si="35"/>
-        <v>174.01304380092435</v>
+        <f t="shared" si="33"/>
+        <v>117.49713758723991</v>
       </c>
       <c r="BE10" s="4">
-        <f t="shared" si="35"/>
-        <v>176.84485990723516</v>
+        <f t="shared" si="33"/>
+        <v>119.63738426917874</v>
       </c>
       <c r="BF10" s="4">
-        <f t="shared" si="35"/>
-        <v>179.74628123106635</v>
+        <f t="shared" si="33"/>
+        <v>121.82462980615249</v>
       </c>
     </row>
     <row r="11" spans="2:58" s="1" customFormat="1" x14ac:dyDescent="0.3">
@@ -2633,148 +2624,148 @@
         <v>26</v>
       </c>
       <c r="C11" s="7">
-        <f t="shared" ref="C11:P11" si="36">C7-C10</f>
+        <f t="shared" ref="C11:P11" si="34">C7-C10</f>
         <v>16.199999999999996</v>
       </c>
       <c r="D11" s="7">
-        <f t="shared" si="36"/>
+        <f t="shared" si="34"/>
         <v>18.600000000000001</v>
       </c>
       <c r="E11" s="7">
-        <f t="shared" si="36"/>
+        <f t="shared" si="34"/>
         <v>16.400000000000006</v>
       </c>
       <c r="F11" s="7">
-        <f t="shared" si="36"/>
+        <f t="shared" si="34"/>
         <v>17.700000000000003</v>
       </c>
       <c r="G11" s="7">
-        <f t="shared" si="36"/>
+        <f t="shared" si="34"/>
         <v>16.099999999999994</v>
       </c>
       <c r="H11" s="7">
-        <f t="shared" si="36"/>
+        <f t="shared" si="34"/>
         <v>17.399999999999999</v>
       </c>
       <c r="I11" s="7">
-        <f t="shared" si="36"/>
+        <f t="shared" si="34"/>
         <v>17.600000000000001</v>
       </c>
       <c r="J11" s="7">
-        <f t="shared" si="36"/>
+        <f t="shared" si="34"/>
         <v>19.800000000000004</v>
       </c>
       <c r="K11" s="7">
-        <f t="shared" si="36"/>
+        <f t="shared" si="34"/>
         <v>14.79999999999999</v>
       </c>
       <c r="L11" s="7">
-        <f t="shared" si="36"/>
+        <f t="shared" si="34"/>
         <v>15.600000000000001</v>
       </c>
       <c r="M11" s="7">
-        <f t="shared" si="36"/>
+        <f t="shared" si="34"/>
         <v>18.600000000000001</v>
       </c>
       <c r="N11" s="7">
-        <f t="shared" si="36"/>
+        <f t="shared" si="34"/>
         <v>15.100000000000001</v>
       </c>
       <c r="O11" s="7">
-        <f t="shared" si="36"/>
+        <f t="shared" si="34"/>
         <v>17.200000000000003</v>
       </c>
       <c r="P11" s="7">
-        <f t="shared" si="36"/>
+        <f t="shared" si="34"/>
         <v>21.900000000000006</v>
       </c>
       <c r="Q11" s="7">
-        <f t="shared" ref="Q11:U11" si="37">Q7-Q10</f>
+        <f t="shared" ref="Q11:U11" si="35">Q7-Q10</f>
         <v>25.200000000000003</v>
       </c>
       <c r="R11" s="7">
+        <f t="shared" si="35"/>
+        <v>26.499999999999993</v>
+      </c>
+      <c r="S11" s="7">
+        <f t="shared" si="35"/>
+        <v>18.5</v>
+      </c>
+      <c r="T11" s="7">
+        <f t="shared" ref="T11" si="36">T7-T10</f>
+        <v>20.399999999999999</v>
+      </c>
+      <c r="U11" s="7">
+        <f t="shared" si="35"/>
+        <v>18.899999999999999</v>
+      </c>
+      <c r="V11" s="7">
+        <f t="shared" ref="V11:W11" si="37">V7-V10</f>
+        <v>18.20000000000001</v>
+      </c>
+      <c r="W11" s="7">
         <f t="shared" si="37"/>
-        <v>26.499999999999993</v>
-      </c>
-      <c r="S11" s="7">
-        <f t="shared" si="37"/>
-        <v>18.5</v>
-      </c>
-      <c r="T11" s="7">
-        <f t="shared" ref="T11" si="38">T7-T10</f>
-        <v>20.399999999999999</v>
-      </c>
-      <c r="U11" s="7">
-        <f t="shared" si="37"/>
-        <v>18.899999999999999</v>
-      </c>
-      <c r="V11" s="7">
-        <f t="shared" ref="V11:W11" si="39">V7-V10</f>
-        <v>18.20000000000001</v>
-      </c>
-      <c r="W11" s="7">
-        <f t="shared" si="39"/>
         <v>15.299999999999997</v>
       </c>
       <c r="X11" s="7">
-        <f t="shared" ref="X11:Y11" si="40">X7-X10</f>
+        <f t="shared" ref="X11:Y11" si="38">X7-X10</f>
         <v>17.700000000000003</v>
       </c>
       <c r="Y11" s="7">
-        <f t="shared" si="40"/>
+        <f t="shared" si="38"/>
         <v>17.899999999999991</v>
       </c>
       <c r="Z11" s="7">
-        <f t="shared" ref="Z11" si="41">Z7-Z10</f>
+        <f t="shared" ref="Z11" si="39">Z7-Z10</f>
         <v>15.899999999999999</v>
       </c>
       <c r="AA11" s="7">
-        <f t="shared" ref="AA11" si="42">AA7-AA10</f>
+        <f t="shared" ref="AA11" si="40">AA7-AA10</f>
         <v>18.199999999999996</v>
       </c>
       <c r="AB11" s="7">
-        <f t="shared" ref="AB11:AC11" si="43">AB7-AB10</f>
+        <f t="shared" ref="AB11:AC11" si="41">AB7-AB10</f>
         <v>17.999999999999993</v>
       </c>
       <c r="AC11" s="7">
-        <f t="shared" si="43"/>
+        <f t="shared" si="41"/>
         <v>-5.8999999999999986</v>
       </c>
       <c r="AD11" s="7">
-        <f t="shared" ref="AD11" si="44">AD7-AD10</f>
+        <f t="shared" ref="AD11" si="42">AD7-AD10</f>
         <v>13.200000000000003</v>
       </c>
       <c r="AE11" s="7">
-        <f t="shared" ref="AE11" si="45">AE7-AE10</f>
+        <f t="shared" ref="AE11" si="43">AE7-AE10</f>
         <v>17.5</v>
       </c>
       <c r="AF11" s="7">
-        <f t="shared" ref="AF11:AH11" si="46">AF7-AF10</f>
+        <f t="shared" ref="AF11:AH11" si="44">AF7-AF10</f>
         <v>23.1</v>
       </c>
       <c r="AG11" s="7">
-        <f t="shared" si="46"/>
+        <f t="shared" si="44"/>
         <v>18.799999999999997</v>
       </c>
       <c r="AH11" s="7">
-        <f t="shared" si="46"/>
+        <f t="shared" si="44"/>
         <v>17.899999999999991</v>
       </c>
       <c r="AI11" s="7">
-        <f t="shared" ref="AI11:AL11" si="47">AI7-AI10</f>
+        <f t="shared" ref="AI11:AL11" si="45">AI7-AI10</f>
         <v>15</v>
       </c>
       <c r="AJ11" s="7">
-        <f t="shared" si="47"/>
-        <v>19.246010000000002</v>
+        <f t="shared" si="45"/>
+        <v>15</v>
       </c>
       <c r="AK11" s="7">
-        <f t="shared" si="47"/>
-        <v>19.850999999999999</v>
+        <f t="shared" si="45"/>
+        <v>15.948</v>
       </c>
       <c r="AL11" s="7">
-        <f t="shared" si="47"/>
-        <v>18.6892</v>
+        <f t="shared" si="45"/>
+        <v>16.143800000000002</v>
       </c>
       <c r="AN11" s="7">
         <f>AN7-AN10</f>
@@ -2793,64 +2784,64 @@
         <v>90.799999999999955</v>
       </c>
       <c r="AR11" s="7">
-        <f t="shared" ref="AR11:BA11" si="48">AR7-AR10</f>
+        <f t="shared" ref="AR11:BA11" si="46">AR7-AR10</f>
         <v>75.999999999999972</v>
       </c>
       <c r="AS11" s="7">
-        <f t="shared" si="48"/>
+        <f t="shared" si="46"/>
         <v>66.799999999999983</v>
       </c>
       <c r="AT11" s="7">
-        <f t="shared" si="48"/>
+        <f t="shared" si="46"/>
         <v>43.500000000000057</v>
       </c>
       <c r="AU11" s="7">
-        <f t="shared" si="48"/>
+        <f t="shared" si="46"/>
         <v>77.299999999999983</v>
       </c>
       <c r="AV11" s="7">
-        <f t="shared" si="48"/>
-        <v>72.78621000000004</v>
+        <f t="shared" si="46"/>
+        <v>62.091799999999978</v>
       </c>
       <c r="AW11" s="7">
-        <f t="shared" si="48"/>
-        <v>74.995192499999973</v>
+        <f t="shared" si="46"/>
+        <v>63.039389999999983</v>
       </c>
       <c r="AX11" s="7">
-        <f t="shared" si="48"/>
-        <v>80.600641230000008</v>
+        <f t="shared" si="46"/>
+        <v>68.714102699999998</v>
       </c>
       <c r="AY11" s="7">
-        <f t="shared" si="48"/>
-        <v>84.709842440400024</v>
+        <f t="shared" si="46"/>
+        <v>73.102134845999984</v>
       </c>
       <c r="AZ11" s="7">
-        <f t="shared" si="48"/>
-        <v>87.648379856531989</v>
+        <f t="shared" si="46"/>
+        <v>76.649324513580012</v>
       </c>
       <c r="BA11" s="7">
-        <f t="shared" si="48"/>
-        <v>89.881857135783349</v>
+        <f t="shared" si="46"/>
+        <v>79.094980162283434</v>
       </c>
       <c r="BB11" s="7">
-        <f t="shared" ref="BB11:BF11" si="49">BB7-BB10</f>
-        <v>91.843394895847609</v>
+        <f t="shared" ref="BB11:BF11" si="47">BB7-BB10</f>
+        <v>80.848241455146763</v>
       </c>
       <c r="BC11" s="7">
-        <f t="shared" si="49"/>
-        <v>93.500784040662495</v>
+        <f t="shared" si="47"/>
+        <v>82.407165891455477</v>
       </c>
       <c r="BD11" s="7">
-        <f t="shared" si="49"/>
-        <v>95.194910543435668</v>
+        <f t="shared" si="47"/>
+        <v>83.998429624346244</v>
       </c>
       <c r="BE11" s="7">
-        <f t="shared" si="49"/>
-        <v>96.926437359825115</v>
+        <f t="shared" si="47"/>
+        <v>85.622656223593623</v>
       </c>
       <c r="BF11" s="7">
-        <f t="shared" si="49"/>
-        <v>98.696042140431985</v>
+        <f t="shared" si="47"/>
+        <v>87.280482194690748</v>
       </c>
     </row>
     <row r="12" spans="2:58" x14ac:dyDescent="0.3">
@@ -2957,16 +2948,13 @@
         <v>4.5</v>
       </c>
       <c r="AJ12" s="4">
-        <f t="shared" ref="AJ12:AL12" si="50">AF12*1.02</f>
-        <v>5.61</v>
+        <v>4.5</v>
       </c>
       <c r="AK12" s="4">
-        <f t="shared" si="50"/>
-        <v>5.3040000000000003</v>
+        <v>4.5</v>
       </c>
       <c r="AL12" s="4">
-        <f t="shared" si="50"/>
-        <v>5.7119999999999997</v>
+        <v>5</v>
       </c>
       <c r="AN12" s="4">
         <f>SUM(C12:F12)</f>
@@ -3002,47 +2990,47 @@
       </c>
       <c r="AV12" s="4">
         <f>SUM(AI12:AL12)</f>
-        <v>21.125999999999998</v>
+        <v>18.5</v>
       </c>
       <c r="AW12" s="4">
         <f>AV12*1.04</f>
-        <v>21.971039999999999</v>
+        <v>19.240000000000002</v>
       </c>
       <c r="AX12" s="4">
         <f>AW12*1.03</f>
-        <v>22.630171199999999</v>
+        <v>19.817200000000003</v>
       </c>
       <c r="AY12" s="4">
         <f>AX12*1.02</f>
-        <v>23.082774623999999</v>
+        <v>20.213544000000002</v>
       </c>
       <c r="AZ12" s="4">
         <f>AY12*1.02</f>
-        <v>23.544430116480001</v>
+        <v>20.617814880000005</v>
       </c>
       <c r="BA12" s="4">
         <f>AZ12*1.02</f>
-        <v>24.015318718809603</v>
+        <v>21.030171177600003</v>
       </c>
       <c r="BB12" s="4">
-        <f t="shared" ref="BB12:BF12" si="51">BA12*1.02</f>
-        <v>24.495625093185794</v>
+        <f t="shared" ref="BB12:BF12" si="48">BA12*1.02</f>
+        <v>21.450774601152006</v>
       </c>
       <c r="BC12" s="4">
-        <f t="shared" si="51"/>
-        <v>24.985537595049511</v>
+        <f t="shared" si="48"/>
+        <v>21.879790093175046</v>
       </c>
       <c r="BD12" s="4">
-        <f t="shared" si="51"/>
-        <v>25.485248346950502</v>
+        <f t="shared" si="48"/>
+        <v>22.317385895038548</v>
       </c>
       <c r="BE12" s="4">
-        <f t="shared" si="51"/>
-        <v>25.994953313889514</v>
+        <f t="shared" si="48"/>
+        <v>22.763733612939319</v>
       </c>
       <c r="BF12" s="4">
-        <f t="shared" si="51"/>
-        <v>26.514852380167305</v>
+        <f t="shared" si="48"/>
+        <v>23.219008285198107</v>
       </c>
     </row>
     <row r="13" spans="2:58" x14ac:dyDescent="0.3">
@@ -3149,16 +3137,13 @@
         <v>3.9</v>
       </c>
       <c r="AJ13" s="4">
-        <f>AJ7*0.1</f>
-        <v>5.0287000000000006</v>
+        <v>3.9</v>
       </c>
       <c r="AK13" s="4">
-        <f>AK7*0.1</f>
-        <v>5.5034999999999998</v>
+        <v>3.9</v>
       </c>
       <c r="AL13" s="4">
-        <f>AL7*0.1</f>
-        <v>4.8489000000000004</v>
+        <v>3.9</v>
       </c>
       <c r="AN13" s="4">
         <f>SUM(C13:F13)</f>
@@ -3194,47 +3179,47 @@
       </c>
       <c r="AV13" s="4">
         <f>SUM(AI13:AL13)</f>
-        <v>19.281100000000002</v>
+        <v>15.6</v>
       </c>
       <c r="AW13" s="4">
-        <f>AW7*0.08</f>
-        <v>16.698484000000001</v>
+        <f>AW7*0.09</f>
+        <v>13.544729999999998</v>
       </c>
       <c r="AX13" s="4">
-        <f t="shared" ref="AX13:BF13" si="52">AX7*0.08</f>
-        <v>18.002915120000001</v>
+        <f t="shared" ref="AX13:BF13" si="49">AX7*0.09</f>
+        <v>14.764256099999999</v>
       </c>
       <c r="AY13" s="4">
-        <f t="shared" si="52"/>
-        <v>19.060241462400001</v>
+        <f t="shared" si="49"/>
+        <v>15.763762602</v>
       </c>
       <c r="AZ13" s="4">
-        <f t="shared" si="52"/>
-        <v>19.783379046432003</v>
+        <f t="shared" si="49"/>
+        <v>16.505700557220003</v>
       </c>
       <c r="BA13" s="4">
-        <f t="shared" si="52"/>
-        <v>20.362097934835205</v>
+        <f t="shared" si="49"/>
+        <v>17.063518393920603</v>
       </c>
       <c r="BB13" s="4">
-        <f t="shared" si="52"/>
-        <v>20.831778223950415</v>
+        <f t="shared" si="49"/>
+        <v>17.478229485920874</v>
       </c>
       <c r="BC13" s="4">
-        <f t="shared" si="52"/>
-        <v>21.18004093010482</v>
+        <f t="shared" si="49"/>
+        <v>17.802919621584628</v>
       </c>
       <c r="BD13" s="4">
-        <f t="shared" si="52"/>
-        <v>21.536636347548804</v>
+        <f t="shared" si="49"/>
+        <v>18.134601049042754</v>
       </c>
       <c r="BE13" s="4">
-        <f t="shared" si="52"/>
-        <v>21.901703781364823</v>
+        <f t="shared" si="49"/>
+        <v>18.473403644349514</v>
       </c>
       <c r="BF13" s="4">
-        <f t="shared" si="52"/>
-        <v>22.275385869719866</v>
+        <f t="shared" si="49"/>
+        <v>18.819460080075892</v>
       </c>
     </row>
     <row r="14" spans="2:58" x14ac:dyDescent="0.3">
@@ -3341,16 +3326,13 @@
         <v>4.5</v>
       </c>
       <c r="AJ14" s="4">
-        <f t="shared" ref="AJ14:AL14" si="53">AF14*1.01</f>
-        <v>5.8579999999999997</v>
+        <v>4.5</v>
       </c>
       <c r="AK14" s="4">
-        <f t="shared" si="53"/>
-        <v>4.8479999999999999</v>
+        <v>4.5</v>
       </c>
       <c r="AL14" s="4">
-        <f t="shared" si="53"/>
-        <v>4.5449999999999999</v>
+        <v>5</v>
       </c>
       <c r="AN14" s="4">
         <f>SUM(C14:F14)</f>
@@ -3386,47 +3368,47 @@
       </c>
       <c r="AV14" s="4">
         <f>SUM(AI14:AL14)</f>
-        <v>19.750999999999998</v>
+        <v>18.5</v>
       </c>
       <c r="AW14" s="4">
         <f>AV14*1.02</f>
-        <v>20.146019999999996</v>
+        <v>18.87</v>
       </c>
       <c r="AX14" s="4">
         <f>AW14*1.01</f>
-        <v>20.347480199999996</v>
+        <v>19.058700000000002</v>
       </c>
       <c r="AY14" s="4">
         <f>AX14*1.01</f>
-        <v>20.550955001999995</v>
+        <v>19.249287000000002</v>
       </c>
       <c r="AZ14" s="4">
         <f>AY14*1.01</f>
-        <v>20.756464552019995</v>
+        <v>19.441779870000001</v>
       </c>
       <c r="BA14" s="4">
         <f>AZ14*1.01</f>
-        <v>20.964029197540196</v>
+        <v>19.636197668700003</v>
       </c>
       <c r="BB14" s="4">
-        <f t="shared" ref="BB14:BF14" si="54">BA14*1.01</f>
-        <v>21.173669489515596</v>
+        <f t="shared" ref="BB14:BF14" si="50">BA14*1.01</f>
+        <v>19.832559645387004</v>
       </c>
       <c r="BC14" s="4">
-        <f t="shared" si="54"/>
-        <v>21.385406184410751</v>
+        <f t="shared" si="50"/>
+        <v>20.030885241840874</v>
       </c>
       <c r="BD14" s="4">
-        <f t="shared" si="54"/>
-        <v>21.599260246254858</v>
+        <f t="shared" si="50"/>
+        <v>20.231194094259283</v>
       </c>
       <c r="BE14" s="4">
-        <f t="shared" si="54"/>
-        <v>21.815252848717407</v>
+        <f t="shared" si="50"/>
+        <v>20.433506035201876</v>
       </c>
       <c r="BF14" s="4">
-        <f t="shared" si="54"/>
-        <v>22.033405377204581</v>
+        <f t="shared" si="50"/>
+        <v>20.637841095553895</v>
       </c>
     </row>
     <row r="15" spans="2:58" x14ac:dyDescent="0.3">
@@ -3547,13 +3529,16 @@
         <v>2.5</v>
       </c>
       <c r="AJ15" s="4">
-        <v>3</v>
+        <f>2.1+0.4</f>
+        <v>2.5</v>
       </c>
       <c r="AK15" s="4">
-        <v>3</v>
+        <f t="shared" ref="AK15:AL15" si="51">2.1+0.4</f>
+        <v>2.5</v>
       </c>
       <c r="AL15" s="4">
-        <v>3</v>
+        <f t="shared" si="51"/>
+        <v>2.5</v>
       </c>
       <c r="AN15" s="4">
         <f>SUM(C15:F15)</f>
@@ -3589,7 +3574,7 @@
       </c>
       <c r="AV15" s="4">
         <f>SUM(AI15:AL15)</f>
-        <v>11.5</v>
+        <v>10</v>
       </c>
       <c r="AW15" s="4">
         <v>0</v>
@@ -3627,148 +3612,148 @@
         <v>30</v>
       </c>
       <c r="C16" s="4">
-        <f t="shared" ref="C16:P16" si="55">C12+C13+C14+C15</f>
+        <f t="shared" ref="C16:P16" si="52">C12+C13+C14+C15</f>
         <v>27.2</v>
       </c>
       <c r="D16" s="4">
+        <f t="shared" si="52"/>
+        <v>22.8</v>
+      </c>
+      <c r="E16" s="4">
+        <f t="shared" si="52"/>
+        <v>22.7</v>
+      </c>
+      <c r="F16" s="4">
+        <f t="shared" si="52"/>
+        <v>16.899999999999999</v>
+      </c>
+      <c r="G16" s="4">
+        <f t="shared" si="52"/>
+        <v>18.2</v>
+      </c>
+      <c r="H16" s="4">
+        <f t="shared" si="52"/>
+        <v>18.399999999999999</v>
+      </c>
+      <c r="I16" s="4">
+        <f t="shared" si="52"/>
+        <v>35.299999999999997</v>
+      </c>
+      <c r="J16" s="4">
+        <f t="shared" si="52"/>
+        <v>18.999999999999996</v>
+      </c>
+      <c r="K16" s="4">
+        <f t="shared" si="52"/>
+        <v>17.299999999999997</v>
+      </c>
+      <c r="L16" s="4">
+        <f t="shared" si="52"/>
+        <v>20.799999999999997</v>
+      </c>
+      <c r="M16" s="4">
+        <f t="shared" si="52"/>
+        <v>21.9</v>
+      </c>
+      <c r="N16" s="4">
+        <f t="shared" si="52"/>
+        <v>23.6</v>
+      </c>
+      <c r="O16" s="4">
+        <f t="shared" si="52"/>
+        <v>25</v>
+      </c>
+      <c r="P16" s="4">
+        <f t="shared" si="52"/>
+        <v>27.3</v>
+      </c>
+      <c r="Q16" s="4">
+        <f t="shared" ref="Q16:U16" si="53">Q12+Q13+Q14+Q15</f>
+        <v>28.6</v>
+      </c>
+      <c r="R16" s="4">
+        <f t="shared" si="53"/>
+        <v>35</v>
+      </c>
+      <c r="S16" s="4">
+        <f t="shared" si="53"/>
+        <v>34.700000000000003</v>
+      </c>
+      <c r="T16" s="4">
+        <f t="shared" ref="T16" si="54">T12+T13+T14+T15</f>
+        <v>30.9</v>
+      </c>
+      <c r="U16" s="4">
+        <f t="shared" si="53"/>
+        <v>28.9</v>
+      </c>
+      <c r="V16" s="4">
+        <f t="shared" ref="V16:W16" si="55">V12+V13+V14+V15</f>
+        <v>27.9</v>
+      </c>
+      <c r="W16" s="4">
         <f t="shared" si="55"/>
-        <v>22.8</v>
-      </c>
-      <c r="E16" s="4">
-        <f t="shared" si="55"/>
-        <v>22.7</v>
-      </c>
-      <c r="F16" s="4">
-        <f t="shared" si="55"/>
-        <v>16.899999999999999</v>
-      </c>
-      <c r="G16" s="4">
-        <f t="shared" si="55"/>
-        <v>18.2</v>
-      </c>
-      <c r="H16" s="4">
-        <f t="shared" si="55"/>
-        <v>18.399999999999999</v>
-      </c>
-      <c r="I16" s="4">
-        <f t="shared" si="55"/>
-        <v>35.299999999999997</v>
-      </c>
-      <c r="J16" s="4">
-        <f t="shared" si="55"/>
-        <v>18.999999999999996</v>
-      </c>
-      <c r="K16" s="4">
-        <f t="shared" si="55"/>
-        <v>17.299999999999997</v>
-      </c>
-      <c r="L16" s="4">
-        <f t="shared" si="55"/>
-        <v>20.799999999999997</v>
-      </c>
-      <c r="M16" s="4">
-        <f t="shared" si="55"/>
-        <v>21.9</v>
-      </c>
-      <c r="N16" s="4">
-        <f t="shared" si="55"/>
-        <v>23.6</v>
-      </c>
-      <c r="O16" s="4">
-        <f t="shared" si="55"/>
-        <v>25</v>
-      </c>
-      <c r="P16" s="4">
-        <f t="shared" si="55"/>
-        <v>27.3</v>
-      </c>
-      <c r="Q16" s="4">
-        <f t="shared" ref="Q16:U16" si="56">Q12+Q13+Q14+Q15</f>
-        <v>28.6</v>
-      </c>
-      <c r="R16" s="4">
+        <v>37</v>
+      </c>
+      <c r="X16" s="4">
+        <f t="shared" ref="X16:Y16" si="56">X12+X13+X14+X15</f>
+        <v>27.799999999999997</v>
+      </c>
+      <c r="Y16" s="4">
         <f t="shared" si="56"/>
-        <v>35</v>
-      </c>
-      <c r="S16" s="4">
-        <f t="shared" si="56"/>
-        <v>34.700000000000003</v>
-      </c>
-      <c r="T16" s="4">
-        <f t="shared" ref="T16" si="57">T12+T13+T14+T15</f>
-        <v>30.9</v>
-      </c>
-      <c r="U16" s="4">
-        <f t="shared" si="56"/>
-        <v>28.9</v>
-      </c>
-      <c r="V16" s="4">
-        <f t="shared" ref="V16:W16" si="58">V12+V13+V14+V15</f>
-        <v>27.9</v>
-      </c>
-      <c r="W16" s="4">
-        <f t="shared" si="58"/>
-        <v>37</v>
-      </c>
-      <c r="X16" s="4">
-        <f t="shared" ref="X16:Y16" si="59">X12+X13+X14+X15</f>
-        <v>27.799999999999997</v>
-      </c>
-      <c r="Y16" s="4">
+        <v>29.8</v>
+      </c>
+      <c r="Z16" s="4">
+        <f t="shared" ref="Z16" si="57">Z12+Z13+Z14+Z15</f>
+        <v>30</v>
+      </c>
+      <c r="AA16" s="4">
+        <f t="shared" ref="AA16" si="58">AA12+AA13+AA14+AA15</f>
+        <v>21.3</v>
+      </c>
+      <c r="AB16" s="4">
+        <f t="shared" ref="AB16:AC16" si="59">AB12+AB13+AB14+AB15</f>
+        <v>22.2</v>
+      </c>
+      <c r="AC16" s="4">
         <f t="shared" si="59"/>
-        <v>29.8</v>
-      </c>
-      <c r="Z16" s="4">
-        <f t="shared" ref="Z16" si="60">Z12+Z13+Z14+Z15</f>
-        <v>30</v>
-      </c>
-      <c r="AA16" s="4">
-        <f t="shared" ref="AA16" si="61">AA12+AA13+AA14+AA15</f>
-        <v>21.3</v>
-      </c>
-      <c r="AB16" s="4">
-        <f t="shared" ref="AB16:AC16" si="62">AB12+AB13+AB14+AB15</f>
-        <v>22.2</v>
-      </c>
-      <c r="AC16" s="4">
+        <v>20.3</v>
+      </c>
+      <c r="AD16" s="4">
+        <f t="shared" ref="AD16" si="60">AD12+AD13+AD14+AD15</f>
+        <v>24.5</v>
+      </c>
+      <c r="AE16" s="4">
+        <f t="shared" ref="AE16" si="61">AE12+AE13+AE14+AE15</f>
+        <v>18.600000000000001</v>
+      </c>
+      <c r="AF16" s="4">
+        <f t="shared" ref="AF16:AH16" si="62">AF12+AF13+AF14+AF15</f>
+        <v>20.7</v>
+      </c>
+      <c r="AG16" s="4">
         <f t="shared" si="62"/>
-        <v>20.3</v>
-      </c>
-      <c r="AD16" s="4">
-        <f t="shared" ref="AD16" si="63">AD12+AD13+AD14+AD15</f>
-        <v>24.5</v>
-      </c>
-      <c r="AE16" s="4">
-        <f t="shared" ref="AE16" si="64">AE12+AE13+AE14+AE15</f>
-        <v>18.600000000000001</v>
-      </c>
-      <c r="AF16" s="4">
-        <f t="shared" ref="AF16:AH16" si="65">AF12+AF13+AF14+AF15</f>
-        <v>20.7</v>
-      </c>
-      <c r="AG16" s="4">
-        <f t="shared" si="65"/>
         <v>17.8</v>
       </c>
       <c r="AH16" s="4">
-        <f t="shared" si="65"/>
+        <f t="shared" si="62"/>
         <v>16.2</v>
       </c>
       <c r="AI16" s="4">
-        <f t="shared" ref="AI16:AL16" si="66">AI12+AI13+AI14+AI15</f>
+        <f t="shared" ref="AI16:AL16" si="63">AI12+AI13+AI14+AI15</f>
         <v>15.4</v>
       </c>
       <c r="AJ16" s="4">
-        <f t="shared" si="66"/>
-        <v>19.496700000000001</v>
+        <f t="shared" si="63"/>
+        <v>15.4</v>
       </c>
       <c r="AK16" s="4">
-        <f t="shared" si="66"/>
-        <v>18.6555</v>
+        <f t="shared" si="63"/>
+        <v>15.4</v>
       </c>
       <c r="AL16" s="4">
-        <f t="shared" si="66"/>
-        <v>18.105899999999998</v>
+        <f t="shared" si="63"/>
+        <v>16.399999999999999</v>
       </c>
       <c r="AN16" s="4">
         <f>AN12+AN13+AN14+AN15</f>
@@ -3791,60 +3776,60 @@
         <v>122.4</v>
       </c>
       <c r="AS16" s="4">
-        <f t="shared" ref="AS16:BA16" si="67">AS12+AS13+AS14+AS15</f>
+        <f t="shared" ref="AS16:BA16" si="64">AS12+AS13+AS14+AS15</f>
         <v>124.60000000000001</v>
       </c>
       <c r="AT16" s="4">
-        <f t="shared" si="67"/>
+        <f t="shared" si="64"/>
         <v>88.300000000000011</v>
       </c>
       <c r="AU16" s="4">
-        <f t="shared" si="67"/>
+        <f t="shared" si="64"/>
         <v>73.3</v>
       </c>
       <c r="AV16" s="4">
-        <f t="shared" si="67"/>
-        <v>71.65809999999999</v>
+        <f t="shared" si="64"/>
+        <v>62.6</v>
       </c>
       <c r="AW16" s="4">
-        <f t="shared" si="67"/>
-        <v>58.815543999999989</v>
+        <f t="shared" si="64"/>
+        <v>51.654730000000001</v>
       </c>
       <c r="AX16" s="4">
-        <f t="shared" si="67"/>
-        <v>60.980566519999996</v>
+        <f t="shared" si="64"/>
+        <v>53.640156100000006</v>
       </c>
       <c r="AY16" s="4">
-        <f t="shared" si="67"/>
-        <v>62.693971088399991</v>
+        <f t="shared" si="64"/>
+        <v>55.226593602000001</v>
       </c>
       <c r="AZ16" s="4">
-        <f t="shared" si="67"/>
-        <v>64.084273714931996</v>
+        <f t="shared" si="64"/>
+        <v>56.565295307220012</v>
       </c>
       <c r="BA16" s="4">
-        <f t="shared" si="67"/>
-        <v>65.341445851185</v>
+        <f t="shared" si="64"/>
+        <v>57.729887240220606</v>
       </c>
       <c r="BB16" s="4">
-        <f t="shared" ref="BB16:BF16" si="68">BB12+BB13+BB14+BB15</f>
-        <v>66.501072806651806</v>
+        <f t="shared" ref="BB16:BF16" si="65">BB12+BB13+BB14+BB15</f>
+        <v>58.761563732459891</v>
       </c>
       <c r="BC16" s="4">
-        <f t="shared" si="68"/>
-        <v>67.550984709565085</v>
+        <f t="shared" si="65"/>
+        <v>59.713594956600545</v>
       </c>
       <c r="BD16" s="4">
-        <f t="shared" si="68"/>
-        <v>68.621144940754164</v>
+        <f t="shared" si="65"/>
+        <v>60.683181038340578</v>
       </c>
       <c r="BE16" s="4">
-        <f t="shared" si="68"/>
-        <v>69.711909943971747</v>
+        <f t="shared" si="65"/>
+        <v>61.670643292490709</v>
       </c>
       <c r="BF16" s="4">
-        <f t="shared" si="68"/>
-        <v>70.823643627091741</v>
+        <f t="shared" si="65"/>
+        <v>62.676309460827895</v>
       </c>
     </row>
     <row r="17" spans="2:168" s="1" customFormat="1" x14ac:dyDescent="0.3">
@@ -3852,148 +3837,148 @@
         <v>31</v>
       </c>
       <c r="C17" s="7">
-        <f t="shared" ref="C17:P17" si="69">C11-C16</f>
+        <f t="shared" ref="C17:P17" si="66">C11-C16</f>
         <v>-11.000000000000004</v>
       </c>
       <c r="D17" s="7">
+        <f t="shared" si="66"/>
+        <v>-4.1999999999999993</v>
+      </c>
+      <c r="E17" s="7">
+        <f t="shared" si="66"/>
+        <v>-6.2999999999999936</v>
+      </c>
+      <c r="F17" s="7">
+        <f t="shared" si="66"/>
+        <v>0.80000000000000426</v>
+      </c>
+      <c r="G17" s="7">
+        <f t="shared" si="66"/>
+        <v>-2.100000000000005</v>
+      </c>
+      <c r="H17" s="7">
+        <f t="shared" si="66"/>
+        <v>-1</v>
+      </c>
+      <c r="I17" s="7">
+        <f t="shared" si="66"/>
+        <v>-17.699999999999996</v>
+      </c>
+      <c r="J17" s="7">
+        <f t="shared" si="66"/>
+        <v>0.80000000000000782</v>
+      </c>
+      <c r="K17" s="7">
+        <f t="shared" si="66"/>
+        <v>-2.5000000000000071</v>
+      </c>
+      <c r="L17" s="7">
+        <f t="shared" si="66"/>
+        <v>-5.1999999999999957</v>
+      </c>
+      <c r="M17" s="7">
+        <f t="shared" si="66"/>
+        <v>-3.2999999999999972</v>
+      </c>
+      <c r="N17" s="7">
+        <f t="shared" si="66"/>
+        <v>-8.5</v>
+      </c>
+      <c r="O17" s="7">
+        <f t="shared" si="66"/>
+        <v>-7.7999999999999972</v>
+      </c>
+      <c r="P17" s="7">
+        <f t="shared" si="66"/>
+        <v>-5.399999999999995</v>
+      </c>
+      <c r="Q17" s="7">
+        <f t="shared" ref="Q17:U17" si="67">Q11-Q16</f>
+        <v>-3.3999999999999986</v>
+      </c>
+      <c r="R17" s="7">
+        <f t="shared" si="67"/>
+        <v>-8.5000000000000071</v>
+      </c>
+      <c r="S17" s="7">
+        <f t="shared" si="67"/>
+        <v>-16.200000000000003</v>
+      </c>
+      <c r="T17" s="7">
+        <f t="shared" ref="T17" si="68">T11-T16</f>
+        <v>-10.5</v>
+      </c>
+      <c r="U17" s="7">
+        <f t="shared" si="67"/>
+        <v>-10</v>
+      </c>
+      <c r="V17" s="7">
+        <f t="shared" ref="V17:W17" si="69">V11-V16</f>
+        <v>-9.6999999999999886</v>
+      </c>
+      <c r="W17" s="7">
         <f t="shared" si="69"/>
-        <v>-4.1999999999999993</v>
-      </c>
-      <c r="E17" s="7">
-        <f t="shared" si="69"/>
-        <v>-6.2999999999999936</v>
-      </c>
-      <c r="F17" s="7">
-        <f t="shared" si="69"/>
-        <v>0.80000000000000426</v>
-      </c>
-      <c r="G17" s="7">
-        <f t="shared" si="69"/>
-        <v>-2.100000000000005</v>
-      </c>
-      <c r="H17" s="7">
-        <f t="shared" si="69"/>
-        <v>-1</v>
-      </c>
-      <c r="I17" s="7">
-        <f t="shared" si="69"/>
-        <v>-17.699999999999996</v>
-      </c>
-      <c r="J17" s="7">
-        <f t="shared" si="69"/>
-        <v>0.80000000000000782</v>
-      </c>
-      <c r="K17" s="7">
-        <f t="shared" si="69"/>
-        <v>-2.5000000000000071</v>
-      </c>
-      <c r="L17" s="7">
-        <f t="shared" si="69"/>
-        <v>-5.1999999999999957</v>
-      </c>
-      <c r="M17" s="7">
-        <f t="shared" si="69"/>
-        <v>-3.2999999999999972</v>
-      </c>
-      <c r="N17" s="7">
-        <f t="shared" si="69"/>
-        <v>-8.5</v>
-      </c>
-      <c r="O17" s="7">
-        <f t="shared" si="69"/>
-        <v>-7.7999999999999972</v>
-      </c>
-      <c r="P17" s="7">
-        <f t="shared" si="69"/>
-        <v>-5.399999999999995</v>
-      </c>
-      <c r="Q17" s="7">
-        <f t="shared" ref="Q17:U17" si="70">Q11-Q16</f>
-        <v>-3.3999999999999986</v>
-      </c>
-      <c r="R17" s="7">
+        <v>-21.700000000000003</v>
+      </c>
+      <c r="X17" s="7">
+        <f t="shared" ref="X17:Y17" si="70">X11-X16</f>
+        <v>-10.099999999999994</v>
+      </c>
+      <c r="Y17" s="7">
         <f t="shared" si="70"/>
-        <v>-8.5000000000000071</v>
-      </c>
-      <c r="S17" s="7">
-        <f t="shared" si="70"/>
-        <v>-16.200000000000003</v>
-      </c>
-      <c r="T17" s="7">
-        <f t="shared" ref="T17" si="71">T11-T16</f>
-        <v>-10.5</v>
-      </c>
-      <c r="U17" s="7">
-        <f t="shared" si="70"/>
-        <v>-10</v>
-      </c>
-      <c r="V17" s="7">
-        <f t="shared" ref="V17:W17" si="72">V11-V16</f>
-        <v>-9.6999999999999886</v>
-      </c>
-      <c r="W17" s="7">
-        <f t="shared" si="72"/>
-        <v>-21.700000000000003</v>
-      </c>
-      <c r="X17" s="7">
-        <f t="shared" ref="X17:Y17" si="73">X11-X16</f>
-        <v>-10.099999999999994</v>
-      </c>
-      <c r="Y17" s="7">
+        <v>-11.900000000000009</v>
+      </c>
+      <c r="Z17" s="7">
+        <f t="shared" ref="Z17" si="71">Z11-Z16</f>
+        <v>-14.100000000000001</v>
+      </c>
+      <c r="AA17" s="7">
+        <f t="shared" ref="AA17" si="72">AA11-AA16</f>
+        <v>-3.100000000000005</v>
+      </c>
+      <c r="AB17" s="7">
+        <f t="shared" ref="AB17:AC17" si="73">AB11-AB16</f>
+        <v>-4.2000000000000064</v>
+      </c>
+      <c r="AC17" s="7">
         <f t="shared" si="73"/>
-        <v>-11.900000000000009</v>
-      </c>
-      <c r="Z17" s="7">
-        <f t="shared" ref="Z17" si="74">Z11-Z16</f>
-        <v>-14.100000000000001</v>
-      </c>
-      <c r="AA17" s="7">
-        <f t="shared" ref="AA17" si="75">AA11-AA16</f>
-        <v>-3.100000000000005</v>
-      </c>
-      <c r="AB17" s="7">
-        <f t="shared" ref="AB17:AC17" si="76">AB11-AB16</f>
-        <v>-4.2000000000000064</v>
-      </c>
-      <c r="AC17" s="7">
+        <v>-26.2</v>
+      </c>
+      <c r="AD17" s="7">
+        <f t="shared" ref="AD17" si="74">AD11-AD16</f>
+        <v>-11.299999999999997</v>
+      </c>
+      <c r="AE17" s="7">
+        <f t="shared" ref="AE17" si="75">AE11-AE16</f>
+        <v>-1.1000000000000014</v>
+      </c>
+      <c r="AF17" s="7">
+        <f t="shared" ref="AF17:AH17" si="76">AF11-AF16</f>
+        <v>2.4000000000000021</v>
+      </c>
+      <c r="AG17" s="7">
         <f t="shared" si="76"/>
-        <v>-26.2</v>
-      </c>
-      <c r="AD17" s="7">
-        <f t="shared" ref="AD17" si="77">AD11-AD16</f>
-        <v>-11.299999999999997</v>
-      </c>
-      <c r="AE17" s="7">
-        <f t="shared" ref="AE17" si="78">AE11-AE16</f>
-        <v>-1.1000000000000014</v>
-      </c>
-      <c r="AF17" s="7">
-        <f t="shared" ref="AF17:AH17" si="79">AF11-AF16</f>
-        <v>2.4000000000000021</v>
-      </c>
-      <c r="AG17" s="7">
-        <f t="shared" si="79"/>
         <v>0.99999999999999645</v>
       </c>
       <c r="AH17" s="7">
-        <f t="shared" si="79"/>
+        <f t="shared" si="76"/>
         <v>1.6999999999999922</v>
       </c>
       <c r="AI17" s="7">
-        <f t="shared" ref="AI17:AL17" si="80">AI11-AI16</f>
+        <f t="shared" ref="AI17:AL17" si="77">AI11-AI16</f>
         <v>-0.40000000000000036</v>
       </c>
       <c r="AJ17" s="7">
-        <f t="shared" si="80"/>
-        <v>-0.25068999999999875</v>
+        <f t="shared" si="77"/>
+        <v>-0.40000000000000036</v>
       </c>
       <c r="AK17" s="7">
-        <f t="shared" si="80"/>
-        <v>1.1954999999999991</v>
+        <f t="shared" si="77"/>
+        <v>0.54800000000000004</v>
       </c>
       <c r="AL17" s="7">
-        <f t="shared" si="80"/>
-        <v>0.58330000000000126</v>
+        <f t="shared" si="77"/>
+        <v>-0.25619999999999621</v>
       </c>
       <c r="AN17" s="7">
         <f>AN11-AN16</f>
@@ -4016,60 +4001,60 @@
         <v>-46.400000000000034</v>
       </c>
       <c r="AS17" s="7">
-        <f t="shared" ref="AS17:BA17" si="81">AS11-AS16</f>
+        <f t="shared" ref="AS17:BA17" si="78">AS11-AS16</f>
         <v>-57.800000000000026</v>
       </c>
       <c r="AT17" s="7">
-        <f t="shared" si="81"/>
+        <f t="shared" si="78"/>
         <v>-44.799999999999955</v>
       </c>
       <c r="AU17" s="7">
-        <f t="shared" si="81"/>
+        <f t="shared" si="78"/>
         <v>3.9999999999999858</v>
       </c>
       <c r="AV17" s="7">
-        <f t="shared" si="81"/>
-        <v>1.1281100000000492</v>
+        <f t="shared" si="78"/>
+        <v>-0.50820000000002352</v>
       </c>
       <c r="AW17" s="7">
-        <f t="shared" si="81"/>
-        <v>16.179648499999985</v>
+        <f t="shared" si="78"/>
+        <v>11.384659999999982</v>
       </c>
       <c r="AX17" s="7">
-        <f t="shared" si="81"/>
-        <v>19.620074710000011</v>
+        <f t="shared" si="78"/>
+        <v>15.073946599999992</v>
       </c>
       <c r="AY17" s="7">
-        <f t="shared" si="81"/>
-        <v>22.015871352000033</v>
+        <f t="shared" si="78"/>
+        <v>17.875541243999983</v>
       </c>
       <c r="AZ17" s="7">
-        <f t="shared" si="81"/>
-        <v>23.564106141599993</v>
+        <f t="shared" si="78"/>
+        <v>20.08402920636</v>
       </c>
       <c r="BA17" s="7">
-        <f t="shared" si="81"/>
-        <v>24.540411284598349</v>
+        <f t="shared" si="78"/>
+        <v>21.365092922062829</v>
       </c>
       <c r="BB17" s="7">
-        <f t="shared" ref="BB17:BF17" si="82">BB11-BB16</f>
-        <v>25.342322089195804</v>
+        <f t="shared" ref="BB17:BF17" si="79">BB11-BB16</f>
+        <v>22.086677722686872</v>
       </c>
       <c r="BC17" s="7">
-        <f t="shared" si="82"/>
-        <v>25.94979933109741</v>
+        <f t="shared" si="79"/>
+        <v>22.693570934854932</v>
       </c>
       <c r="BD17" s="7">
-        <f t="shared" si="82"/>
-        <v>26.573765602681505</v>
+        <f t="shared" si="79"/>
+        <v>23.315248586005666</v>
       </c>
       <c r="BE17" s="7">
-        <f t="shared" si="82"/>
-        <v>27.214527415853368</v>
+        <f t="shared" si="79"/>
+        <v>23.952012931102914</v>
       </c>
       <c r="BF17" s="7">
-        <f t="shared" si="82"/>
-        <v>27.872398513340244</v>
+        <f t="shared" si="79"/>
+        <v>24.604172733862853</v>
       </c>
     </row>
     <row r="18" spans="2:168" x14ac:dyDescent="0.3">
@@ -4180,7 +4165,7 @@
         <v>1</v>
       </c>
       <c r="AJ18" s="4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AK18" s="4">
         <v>2</v>
@@ -4222,47 +4207,47 @@
       </c>
       <c r="AV18" s="4">
         <f>SUM(AI18:AL18)</f>
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AW18" s="4">
-        <f t="shared" ref="AW18:BA18" si="83">AV18*0.8</f>
-        <v>5.6000000000000005</v>
+        <f t="shared" ref="AW18:BA18" si="80">AV18*0.8</f>
+        <v>4.8000000000000007</v>
       </c>
       <c r="AX18" s="4">
-        <f t="shared" si="83"/>
-        <v>4.4800000000000004</v>
+        <f t="shared" si="80"/>
+        <v>3.8400000000000007</v>
       </c>
       <c r="AY18" s="4">
-        <f t="shared" si="83"/>
-        <v>3.5840000000000005</v>
+        <f t="shared" si="80"/>
+        <v>3.072000000000001</v>
       </c>
       <c r="AZ18" s="4">
-        <f t="shared" si="83"/>
-        <v>2.8672000000000004</v>
+        <f t="shared" si="80"/>
+        <v>2.4576000000000011</v>
       </c>
       <c r="BA18" s="4">
-        <f t="shared" si="83"/>
-        <v>2.2937600000000002</v>
+        <f t="shared" si="80"/>
+        <v>1.9660800000000009</v>
       </c>
       <c r="BB18" s="4">
-        <f t="shared" ref="BB18:BB19" si="84">BA18*0.8</f>
-        <v>1.8350080000000002</v>
+        <f t="shared" ref="BB18:BB19" si="81">BA18*0.8</f>
+        <v>1.5728640000000009</v>
       </c>
       <c r="BC18" s="4">
-        <f t="shared" ref="BC18:BC19" si="85">BB18*0.8</f>
-        <v>1.4680064000000002</v>
+        <f t="shared" ref="BC18:BC19" si="82">BB18*0.8</f>
+        <v>1.2582912000000008</v>
       </c>
       <c r="BD18" s="4">
-        <f t="shared" ref="BD18:BD19" si="86">BC18*0.8</f>
-        <v>1.1744051200000001</v>
+        <f t="shared" ref="BD18:BD19" si="83">BC18*0.8</f>
+        <v>1.0066329600000008</v>
       </c>
       <c r="BE18" s="4">
-        <f t="shared" ref="BE18:BE19" si="87">BD18*0.8</f>
-        <v>0.93952409600000009</v>
+        <f t="shared" ref="BE18:BE19" si="84">BD18*0.8</f>
+        <v>0.80530636800000066</v>
       </c>
       <c r="BF18" s="4">
-        <f t="shared" ref="BF18:BF19" si="88">BE18*0.8</f>
-        <v>0.75161927680000007</v>
+        <f t="shared" ref="BF18:BF19" si="85">BE18*0.8</f>
+        <v>0.64424509440000055</v>
       </c>
     </row>
     <row r="19" spans="2:168" x14ac:dyDescent="0.3">
@@ -4372,7 +4357,7 @@
         <v>-0.3</v>
       </c>
       <c r="AJ19" s="4">
-        <v>-1</v>
+        <v>-0.3</v>
       </c>
       <c r="AK19" s="4">
         <v>-1</v>
@@ -4414,47 +4399,47 @@
       </c>
       <c r="AV19" s="4">
         <f>SUM(AI19:AL19)</f>
-        <v>-3.3</v>
+        <v>-2.6</v>
       </c>
       <c r="AW19" s="4">
-        <f t="shared" ref="AW19:BA19" si="89">AV19*0.8</f>
-        <v>-2.64</v>
+        <f t="shared" ref="AW19:BA19" si="86">AV19*0.8</f>
+        <v>-2.08</v>
       </c>
       <c r="AX19" s="4">
-        <f t="shared" si="89"/>
-        <v>-2.1120000000000001</v>
+        <f t="shared" si="86"/>
+        <v>-1.6640000000000001</v>
       </c>
       <c r="AY19" s="4">
-        <f t="shared" si="89"/>
-        <v>-1.6896000000000002</v>
+        <f t="shared" si="86"/>
+        <v>-1.3312000000000002</v>
       </c>
       <c r="AZ19" s="4">
-        <f t="shared" si="89"/>
-        <v>-1.3516800000000002</v>
+        <f t="shared" si="86"/>
+        <v>-1.0649600000000001</v>
       </c>
       <c r="BA19" s="4">
-        <f t="shared" si="89"/>
-        <v>-1.0813440000000003</v>
+        <f t="shared" si="86"/>
+        <v>-0.85196800000000017</v>
       </c>
       <c r="BB19" s="4">
+        <f t="shared" si="81"/>
+        <v>-0.68157440000000014</v>
+      </c>
+      <c r="BC19" s="4">
+        <f t="shared" si="82"/>
+        <v>-0.54525952000000011</v>
+      </c>
+      <c r="BD19" s="4">
+        <f t="shared" si="83"/>
+        <v>-0.43620761600000013</v>
+      </c>
+      <c r="BE19" s="4">
         <f t="shared" si="84"/>
-        <v>-0.86507520000000027</v>
-      </c>
-      <c r="BC19" s="4">
+        <v>-0.34896609280000013</v>
+      </c>
+      <c r="BF19" s="4">
         <f t="shared" si="85"/>
-        <v>-0.69206016000000026</v>
-      </c>
-      <c r="BD19" s="4">
-        <f t="shared" si="86"/>
-        <v>-0.55364812800000018</v>
-      </c>
-      <c r="BE19" s="4">
-        <f t="shared" si="87"/>
-        <v>-0.44291850240000019</v>
-      </c>
-      <c r="BF19" s="4">
-        <f t="shared" si="88"/>
-        <v>-0.35433480192000016</v>
+        <v>-0.27917287424000009</v>
       </c>
     </row>
     <row r="20" spans="2:168" s="1" customFormat="1" x14ac:dyDescent="0.3">
@@ -4462,148 +4447,148 @@
         <v>37</v>
       </c>
       <c r="C20" s="7">
-        <f t="shared" ref="C20:P20" si="90">C17-C18-C19</f>
+        <f t="shared" ref="C20:P20" si="87">C17-C18-C19</f>
         <v>-15.800000000000002</v>
       </c>
       <c r="D20" s="7">
+        <f t="shared" si="87"/>
+        <v>-10.1</v>
+      </c>
+      <c r="E20" s="7">
+        <f t="shared" si="87"/>
+        <v>-13.299999999999994</v>
+      </c>
+      <c r="F20" s="7">
+        <f t="shared" si="87"/>
+        <v>-4.9999999999999956</v>
+      </c>
+      <c r="G20" s="7">
+        <f t="shared" si="87"/>
+        <v>-7.2000000000000046</v>
+      </c>
+      <c r="H20" s="7">
+        <f t="shared" si="87"/>
+        <v>-6.5</v>
+      </c>
+      <c r="I20" s="7">
+        <f t="shared" si="87"/>
+        <v>-22.999999999999996</v>
+      </c>
+      <c r="J20" s="7">
+        <f t="shared" si="87"/>
+        <v>-4.5999999999999917</v>
+      </c>
+      <c r="K20" s="7">
+        <f t="shared" si="87"/>
+        <v>-7.9000000000000066</v>
+      </c>
+      <c r="L20" s="7">
+        <f t="shared" si="87"/>
+        <v>-10.299999999999995</v>
+      </c>
+      <c r="M20" s="7">
+        <f t="shared" si="87"/>
+        <v>-8.6999999999999975</v>
+      </c>
+      <c r="N20" s="7">
+        <f t="shared" si="87"/>
+        <v>-13.1</v>
+      </c>
+      <c r="O20" s="7">
+        <f t="shared" si="87"/>
+        <v>-18.099999999999998</v>
+      </c>
+      <c r="P20" s="7">
+        <f t="shared" si="87"/>
+        <v>-74.899999999999991</v>
+      </c>
+      <c r="Q20" s="7">
+        <f t="shared" ref="Q20:U20" si="88">Q17-Q18-Q19</f>
+        <v>-5.1999999999999993</v>
+      </c>
+      <c r="R20" s="7">
+        <f t="shared" si="88"/>
+        <v>-12.000000000000007</v>
+      </c>
+      <c r="S20" s="7">
+        <f t="shared" si="88"/>
+        <v>-16.700000000000003</v>
+      </c>
+      <c r="T20" s="7">
+        <f t="shared" ref="T20" si="89">T17-T18-T19</f>
+        <v>-12.799999999999999</v>
+      </c>
+      <c r="U20" s="7">
+        <f t="shared" si="88"/>
+        <v>-7.2</v>
+      </c>
+      <c r="V20" s="7">
+        <f t="shared" ref="V20:W20" si="90">V17-V18-V19</f>
+        <v>-10.799999999999988</v>
+      </c>
+      <c r="W20" s="7">
         <f t="shared" si="90"/>
-        <v>-10.1</v>
-      </c>
-      <c r="E20" s="7">
-        <f t="shared" si="90"/>
-        <v>-13.299999999999994</v>
-      </c>
-      <c r="F20" s="7">
-        <f t="shared" si="90"/>
-        <v>-4.9999999999999956</v>
-      </c>
-      <c r="G20" s="7">
-        <f t="shared" si="90"/>
-        <v>-7.2000000000000046</v>
-      </c>
-      <c r="H20" s="7">
-        <f t="shared" si="90"/>
-        <v>-6.5</v>
-      </c>
-      <c r="I20" s="7">
-        <f t="shared" si="90"/>
-        <v>-22.999999999999996</v>
-      </c>
-      <c r="J20" s="7">
-        <f t="shared" si="90"/>
-        <v>-4.5999999999999917</v>
-      </c>
-      <c r="K20" s="7">
-        <f t="shared" si="90"/>
-        <v>-7.9000000000000066</v>
-      </c>
-      <c r="L20" s="7">
-        <f t="shared" si="90"/>
-        <v>-10.299999999999995</v>
-      </c>
-      <c r="M20" s="7">
-        <f t="shared" si="90"/>
-        <v>-8.6999999999999975</v>
-      </c>
-      <c r="N20" s="7">
-        <f t="shared" si="90"/>
-        <v>-13.1</v>
-      </c>
-      <c r="O20" s="7">
-        <f t="shared" si="90"/>
-        <v>-18.099999999999998</v>
-      </c>
-      <c r="P20" s="7">
-        <f t="shared" si="90"/>
-        <v>-74.899999999999991</v>
-      </c>
-      <c r="Q20" s="7">
-        <f t="shared" ref="Q20:U20" si="91">Q17-Q18-Q19</f>
-        <v>-5.1999999999999993</v>
-      </c>
-      <c r="R20" s="7">
+        <v>-25.5</v>
+      </c>
+      <c r="X20" s="7">
+        <f t="shared" ref="X20:Y20" si="91">X17-X18-X19</f>
+        <v>-12.799999999999994</v>
+      </c>
+      <c r="Y20" s="7">
         <f t="shared" si="91"/>
-        <v>-12.000000000000007</v>
-      </c>
-      <c r="S20" s="7">
-        <f t="shared" si="91"/>
-        <v>-16.700000000000003</v>
-      </c>
-      <c r="T20" s="7">
-        <f t="shared" ref="T20" si="92">T17-T18-T19</f>
-        <v>-12.799999999999999</v>
-      </c>
-      <c r="U20" s="7">
-        <f t="shared" si="91"/>
-        <v>-7.2</v>
-      </c>
-      <c r="V20" s="7">
-        <f t="shared" ref="V20:W20" si="93">V17-V18-V19</f>
-        <v>-10.799999999999988</v>
-      </c>
-      <c r="W20" s="7">
-        <f t="shared" si="93"/>
-        <v>-25.5</v>
-      </c>
-      <c r="X20" s="7">
-        <f t="shared" ref="X20:Y20" si="94">X17-X18-X19</f>
-        <v>-12.799999999999994</v>
-      </c>
-      <c r="Y20" s="7">
+        <v>-15.70000000000001</v>
+      </c>
+      <c r="Z20" s="7">
+        <f t="shared" ref="Z20" si="92">Z17-Z18-Z19</f>
+        <v>-14.400000000000002</v>
+      </c>
+      <c r="AA20" s="7">
+        <f t="shared" ref="AA20" si="93">AA17-AA18-AA19</f>
+        <v>-4.3000000000000052</v>
+      </c>
+      <c r="AB20" s="7">
+        <f t="shared" ref="AB20:AC20" si="94">AB17-AB18-AB19</f>
+        <v>-5.5000000000000062</v>
+      </c>
+      <c r="AC20" s="7">
         <f t="shared" si="94"/>
-        <v>-15.70000000000001</v>
-      </c>
-      <c r="Z20" s="7">
-        <f t="shared" ref="Z20" si="95">Z17-Z18-Z19</f>
-        <v>-14.400000000000002</v>
-      </c>
-      <c r="AA20" s="7">
-        <f t="shared" ref="AA20" si="96">AA17-AA18-AA19</f>
-        <v>-4.3000000000000052</v>
-      </c>
-      <c r="AB20" s="7">
-        <f t="shared" ref="AB20:AC20" si="97">AB17-AB18-AB19</f>
-        <v>-5.5000000000000062</v>
-      </c>
-      <c r="AC20" s="7">
+        <v>-29.7</v>
+      </c>
+      <c r="AD20" s="7">
+        <f t="shared" ref="AD20" si="95">AD17-AD18-AD19</f>
+        <v>-14.299999999999997</v>
+      </c>
+      <c r="AE20" s="7">
+        <f t="shared" ref="AE20" si="96">AE17-AE18-AE19</f>
+        <v>-3.7000000000000015</v>
+      </c>
+      <c r="AF20" s="7">
+        <f t="shared" ref="AF20:AL20" si="97">AF17-AF18-AF19</f>
+        <v>1.0000000000000022</v>
+      </c>
+      <c r="AG20" s="7">
         <f t="shared" si="97"/>
-        <v>-29.7</v>
-      </c>
-      <c r="AD20" s="7">
-        <f t="shared" ref="AD20" si="98">AD17-AD18-AD19</f>
-        <v>-14.299999999999997</v>
-      </c>
-      <c r="AE20" s="7">
-        <f t="shared" ref="AE20" si="99">AE17-AE18-AE19</f>
-        <v>-3.7000000000000015</v>
-      </c>
-      <c r="AF20" s="7">
-        <f t="shared" ref="AF20:AL20" si="100">AF17-AF18-AF19</f>
-        <v>1.0000000000000022</v>
-      </c>
-      <c r="AG20" s="7">
-        <f t="shared" si="100"/>
         <v>7.599999999999997</v>
       </c>
       <c r="AH20" s="7">
-        <f t="shared" si="100"/>
+        <f t="shared" si="97"/>
         <v>-16.000000000000007</v>
       </c>
       <c r="AI20" s="7">
-        <f t="shared" si="100"/>
+        <f t="shared" si="97"/>
         <v>-1.1000000000000003</v>
       </c>
       <c r="AJ20" s="7">
-        <f t="shared" si="100"/>
-        <v>-1.2506899999999987</v>
+        <f t="shared" si="97"/>
+        <v>-1.1000000000000003</v>
       </c>
       <c r="AK20" s="7">
-        <f t="shared" si="100"/>
-        <v>0.19549999999999912</v>
+        <f t="shared" si="97"/>
+        <v>-0.45199999999999996</v>
       </c>
       <c r="AL20" s="7">
-        <f t="shared" si="100"/>
-        <v>-0.41669999999999874</v>
+        <f t="shared" si="97"/>
+        <v>-1.2561999999999962</v>
       </c>
       <c r="AN20" s="7">
         <f>AN17-AN18-AN19</f>
@@ -4622,64 +4607,64 @@
         <v>-110.20000000000006</v>
       </c>
       <c r="AR20" s="7">
-        <f t="shared" ref="AR20:BA20" si="101">AR17-AR18-AR19</f>
+        <f t="shared" ref="AR20:BA20" si="98">AR17-AR18-AR19</f>
         <v>-47.500000000000036</v>
       </c>
       <c r="AS20" s="7">
-        <f t="shared" si="101"/>
+        <f t="shared" si="98"/>
         <v>-68.40000000000002</v>
       </c>
       <c r="AT20" s="7">
-        <f t="shared" si="101"/>
+        <f t="shared" si="98"/>
         <v>-53.799999999999955</v>
       </c>
       <c r="AU20" s="7">
-        <f t="shared" si="101"/>
+        <f t="shared" si="98"/>
         <v>-11.100000000000012</v>
       </c>
       <c r="AV20" s="7">
-        <f t="shared" si="101"/>
-        <v>-2.5718899999999509</v>
+        <f t="shared" si="98"/>
+        <v>-3.9082000000000234</v>
       </c>
       <c r="AW20" s="7">
-        <f t="shared" si="101"/>
-        <v>13.219648499999984</v>
+        <f t="shared" si="98"/>
+        <v>8.6646599999999818</v>
       </c>
       <c r="AX20" s="7">
-        <f t="shared" si="101"/>
-        <v>17.252074710000009</v>
+        <f t="shared" si="98"/>
+        <v>12.897946599999992</v>
       </c>
       <c r="AY20" s="7">
-        <f t="shared" si="101"/>
-        <v>20.121471352000032</v>
+        <f t="shared" si="98"/>
+        <v>16.134741243999983</v>
       </c>
       <c r="AZ20" s="7">
-        <f t="shared" si="101"/>
-        <v>22.048586141599994</v>
+        <f t="shared" si="98"/>
+        <v>18.69138920636</v>
       </c>
       <c r="BA20" s="7">
-        <f t="shared" si="101"/>
-        <v>23.327995284598352</v>
+        <f t="shared" si="98"/>
+        <v>20.250980922062826</v>
       </c>
       <c r="BB20" s="7">
-        <f t="shared" ref="BB20:BF20" si="102">BB17-BB18-BB19</f>
-        <v>24.372389289195802</v>
+        <f t="shared" ref="BB20:BF20" si="99">BB17-BB18-BB19</f>
+        <v>21.195388122686868</v>
       </c>
       <c r="BC20" s="7">
-        <f t="shared" si="102"/>
-        <v>25.17385309109741</v>
+        <f t="shared" si="99"/>
+        <v>21.980539254854932</v>
       </c>
       <c r="BD20" s="7">
-        <f t="shared" si="102"/>
-        <v>25.953008610681504</v>
+        <f t="shared" si="99"/>
+        <v>22.744823242005666</v>
       </c>
       <c r="BE20" s="7">
-        <f t="shared" si="102"/>
-        <v>26.71792182225337</v>
+        <f t="shared" si="99"/>
+        <v>23.495672655902915</v>
       </c>
       <c r="BF20" s="7">
-        <f t="shared" si="102"/>
-        <v>27.475114038460244</v>
+        <f t="shared" si="99"/>
+        <v>24.239100513702851</v>
       </c>
     </row>
     <row r="21" spans="2:168" x14ac:dyDescent="0.3">
@@ -4831,44 +4816,44 @@
         <v>0</v>
       </c>
       <c r="AW21" s="4">
-        <f t="shared" ref="AW21:BA21" si="103">AW20*0.2</f>
-        <v>2.6439296999999971</v>
+        <f t="shared" ref="AW21:BA21" si="100">AW20*0.2</f>
+        <v>1.7329319999999964</v>
       </c>
       <c r="AX21" s="4">
-        <f t="shared" si="103"/>
-        <v>3.4504149420000019</v>
+        <f t="shared" si="100"/>
+        <v>2.5795893199999984</v>
       </c>
       <c r="AY21" s="4">
-        <f t="shared" si="103"/>
-        <v>4.0242942704000066</v>
+        <f t="shared" si="100"/>
+        <v>3.2269482487999968</v>
       </c>
       <c r="AZ21" s="4">
-        <f t="shared" si="103"/>
-        <v>4.409717228319999</v>
+        <f t="shared" si="100"/>
+        <v>3.7382778412720001</v>
       </c>
       <c r="BA21" s="4">
-        <f t="shared" si="103"/>
-        <v>4.6655990569196701</v>
+        <f t="shared" si="100"/>
+        <v>4.0501961844125658</v>
       </c>
       <c r="BB21" s="4">
-        <f t="shared" ref="BB21:BF21" si="104">BB20*0.2</f>
-        <v>4.8744778578391603</v>
+        <f t="shared" ref="BB21:BF21" si="101">BB20*0.2</f>
+        <v>4.2390776245373738</v>
       </c>
       <c r="BC21" s="4">
-        <f t="shared" si="104"/>
-        <v>5.0347706182194827</v>
+        <f t="shared" si="101"/>
+        <v>4.3961078509709868</v>
       </c>
       <c r="BD21" s="4">
-        <f t="shared" si="104"/>
-        <v>5.190601722136301</v>
+        <f t="shared" si="101"/>
+        <v>4.5489646484011335</v>
       </c>
       <c r="BE21" s="4">
-        <f t="shared" si="104"/>
-        <v>5.343584364450674</v>
+        <f t="shared" si="101"/>
+        <v>4.699134531180583</v>
       </c>
       <c r="BF21" s="4">
-        <f t="shared" si="104"/>
-        <v>5.4950228076920489</v>
+        <f t="shared" si="101"/>
+        <v>4.8478201027405703</v>
       </c>
     </row>
     <row r="22" spans="2:168" x14ac:dyDescent="0.3">
@@ -5021,43 +5006,43 @@
         <v>-0.4</v>
       </c>
       <c r="AW22" s="4">
-        <f t="shared" ref="AW22:BA22" si="105">AV22*1.1</f>
+        <f t="shared" ref="AW22:BA22" si="102">AV22*1.1</f>
         <v>-0.44000000000000006</v>
       </c>
       <c r="AX22" s="4">
-        <f t="shared" si="105"/>
+        <f t="shared" si="102"/>
         <v>-0.4840000000000001</v>
       </c>
       <c r="AY22" s="4">
-        <f t="shared" si="105"/>
+        <f t="shared" si="102"/>
         <v>-0.5324000000000001</v>
       </c>
       <c r="AZ22" s="4">
-        <f t="shared" si="105"/>
+        <f t="shared" si="102"/>
         <v>-0.58564000000000016</v>
       </c>
       <c r="BA22" s="4">
-        <f t="shared" si="105"/>
+        <f t="shared" si="102"/>
         <v>-0.64420400000000022</v>
       </c>
       <c r="BB22" s="4">
-        <f t="shared" ref="BB22" si="106">BA22*1.1</f>
+        <f t="shared" ref="BB22" si="103">BA22*1.1</f>
         <v>-0.70862440000000027</v>
       </c>
       <c r="BC22" s="4">
-        <f t="shared" ref="BC22" si="107">BB22*1.1</f>
+        <f t="shared" ref="BC22" si="104">BB22*1.1</f>
         <v>-0.77948684000000035</v>
       </c>
       <c r="BD22" s="4">
-        <f t="shared" ref="BD22" si="108">BC22*1.1</f>
+        <f t="shared" ref="BD22" si="105">BC22*1.1</f>
         <v>-0.85743552400000045</v>
       </c>
       <c r="BE22" s="4">
-        <f t="shared" ref="BE22" si="109">BD22*1.1</f>
+        <f t="shared" ref="BE22" si="106">BD22*1.1</f>
         <v>-0.94317907640000054</v>
       </c>
       <c r="BF22" s="4">
-        <f t="shared" ref="BF22" si="110">BE22*1.1</f>
+        <f t="shared" ref="BF22" si="107">BE22*1.1</f>
         <v>-1.0374969840400006</v>
       </c>
     </row>
@@ -5066,148 +5051,148 @@
         <v>34</v>
       </c>
       <c r="C23" s="7">
-        <f t="shared" ref="C23:P23" si="111">C20-C21-C22</f>
+        <f t="shared" ref="C23:P23" si="108">C20-C21-C22</f>
         <v>-16.100000000000001</v>
       </c>
       <c r="D23" s="7">
+        <f t="shared" si="108"/>
+        <v>-10.7</v>
+      </c>
+      <c r="E23" s="7">
+        <f t="shared" si="108"/>
+        <v>-13.699999999999994</v>
+      </c>
+      <c r="F23" s="7">
+        <f t="shared" si="108"/>
+        <v>-3.7999999999999954</v>
+      </c>
+      <c r="G23" s="7">
+        <f t="shared" si="108"/>
+        <v>-7.600000000000005</v>
+      </c>
+      <c r="H23" s="7">
+        <f t="shared" si="108"/>
+        <v>-6.8</v>
+      </c>
+      <c r="I23" s="7">
+        <f t="shared" si="108"/>
+        <v>-23.499999999999996</v>
+      </c>
+      <c r="J23" s="7">
+        <f t="shared" si="108"/>
+        <v>-4.1999999999999913</v>
+      </c>
+      <c r="K23" s="7">
+        <f t="shared" si="108"/>
+        <v>-8.2000000000000064</v>
+      </c>
+      <c r="L23" s="7">
+        <f t="shared" si="108"/>
+        <v>-10.699999999999996</v>
+      </c>
+      <c r="M23" s="7">
+        <f t="shared" si="108"/>
+        <v>-8.8999999999999968</v>
+      </c>
+      <c r="N23" s="7">
+        <f t="shared" si="108"/>
+        <v>-12.799999999999999</v>
+      </c>
+      <c r="O23" s="7">
+        <f t="shared" si="108"/>
+        <v>-18.2</v>
+      </c>
+      <c r="P23" s="7">
+        <f t="shared" si="108"/>
+        <v>-74.8</v>
+      </c>
+      <c r="Q23" s="7">
+        <f t="shared" ref="Q23:U23" si="109">Q20-Q21-Q22</f>
+        <v>-5.3999999999999995</v>
+      </c>
+      <c r="R23" s="7">
+        <f t="shared" si="109"/>
+        <v>-12.600000000000007</v>
+      </c>
+      <c r="S23" s="7">
+        <f t="shared" si="109"/>
+        <v>-17.8</v>
+      </c>
+      <c r="T23" s="7">
+        <f t="shared" ref="T23" si="110">T20-T21-T22</f>
+        <v>-13.899999999999999</v>
+      </c>
+      <c r="U23" s="7">
+        <f t="shared" si="109"/>
+        <v>-9</v>
+      </c>
+      <c r="V23" s="7">
+        <f t="shared" ref="V23:W23" si="111">V20-V21-V22</f>
+        <v>-11.399999999999988</v>
+      </c>
+      <c r="W23" s="7">
         <f t="shared" si="111"/>
-        <v>-10.7</v>
-      </c>
-      <c r="E23" s="7">
-        <f t="shared" si="111"/>
-        <v>-13.699999999999994</v>
-      </c>
-      <c r="F23" s="7">
-        <f t="shared" si="111"/>
-        <v>-3.7999999999999954</v>
-      </c>
-      <c r="G23" s="7">
-        <f t="shared" si="111"/>
-        <v>-7.600000000000005</v>
-      </c>
-      <c r="H23" s="7">
-        <f t="shared" si="111"/>
-        <v>-6.8</v>
-      </c>
-      <c r="I23" s="7">
-        <f t="shared" si="111"/>
-        <v>-23.499999999999996</v>
-      </c>
-      <c r="J23" s="7">
-        <f t="shared" si="111"/>
-        <v>-4.1999999999999913</v>
-      </c>
-      <c r="K23" s="7">
-        <f t="shared" si="111"/>
-        <v>-8.2000000000000064</v>
-      </c>
-      <c r="L23" s="7">
-        <f t="shared" si="111"/>
-        <v>-10.699999999999996</v>
-      </c>
-      <c r="M23" s="7">
-        <f t="shared" si="111"/>
-        <v>-8.8999999999999968</v>
-      </c>
-      <c r="N23" s="7">
-        <f t="shared" si="111"/>
-        <v>-12.799999999999999</v>
-      </c>
-      <c r="O23" s="7">
-        <f t="shared" si="111"/>
-        <v>-18.2</v>
-      </c>
-      <c r="P23" s="7">
-        <f t="shared" si="111"/>
-        <v>-74.8</v>
-      </c>
-      <c r="Q23" s="7">
-        <f t="shared" ref="Q23:U23" si="112">Q20-Q21-Q22</f>
-        <v>-5.3999999999999995</v>
-      </c>
-      <c r="R23" s="7">
+        <v>-25.9</v>
+      </c>
+      <c r="X23" s="7">
+        <f t="shared" ref="X23:Y23" si="112">X20-X21-X22</f>
+        <v>-13.199999999999992</v>
+      </c>
+      <c r="Y23" s="7">
         <f t="shared" si="112"/>
-        <v>-12.600000000000007</v>
-      </c>
-      <c r="S23" s="7">
-        <f t="shared" si="112"/>
-        <v>-17.8</v>
-      </c>
-      <c r="T23" s="7">
-        <f t="shared" ref="T23" si="113">T20-T21-T22</f>
-        <v>-13.899999999999999</v>
-      </c>
-      <c r="U23" s="7">
-        <f t="shared" si="112"/>
-        <v>-9</v>
-      </c>
-      <c r="V23" s="7">
-        <f t="shared" ref="V23:W23" si="114">V20-V21-V22</f>
-        <v>-11.399999999999988</v>
-      </c>
-      <c r="W23" s="7">
-        <f t="shared" si="114"/>
-        <v>-25.9</v>
-      </c>
-      <c r="X23" s="7">
-        <f t="shared" ref="X23:Y23" si="115">X20-X21-X22</f>
-        <v>-13.199999999999992</v>
-      </c>
-      <c r="Y23" s="7">
+        <v>-16.400000000000009</v>
+      </c>
+      <c r="Z23" s="7">
+        <f t="shared" ref="Z23" si="113">Z20-Z21-Z22</f>
+        <v>-15.200000000000001</v>
+      </c>
+      <c r="AA23" s="7">
+        <f t="shared" ref="AA23" si="114">AA20-AA21-AA22</f>
+        <v>-5.3000000000000052</v>
+      </c>
+      <c r="AB23" s="7">
+        <f t="shared" ref="AB23:AC23" si="115">AB20-AB21-AB22</f>
+        <v>-6.5000000000000062</v>
+      </c>
+      <c r="AC23" s="7">
         <f t="shared" si="115"/>
-        <v>-16.400000000000009</v>
-      </c>
-      <c r="Z23" s="7">
-        <f t="shared" ref="Z23" si="116">Z20-Z21-Z22</f>
-        <v>-15.200000000000001</v>
-      </c>
-      <c r="AA23" s="7">
-        <f t="shared" ref="AA23" si="117">AA20-AA21-AA22</f>
-        <v>-5.3000000000000052</v>
-      </c>
-      <c r="AB23" s="7">
-        <f t="shared" ref="AB23:AC23" si="118">AB20-AB21-AB22</f>
-        <v>-6.5000000000000062</v>
-      </c>
-      <c r="AC23" s="7">
+        <v>-30.5</v>
+      </c>
+      <c r="AD23" s="7">
+        <f t="shared" ref="AD23" si="116">AD20-AD21-AD22</f>
+        <v>-15.399999999999999</v>
+      </c>
+      <c r="AE23" s="7">
+        <f t="shared" ref="AE23" si="117">AE20-AE21-AE22</f>
+        <v>-4.700000000000002</v>
+      </c>
+      <c r="AF23" s="7">
+        <f t="shared" ref="AF23:AH23" si="118">AF20-AF21-AF22</f>
+        <v>-9.9999999999997868E-2</v>
+      </c>
+      <c r="AG23" s="7">
         <f t="shared" si="118"/>
-        <v>-30.5</v>
-      </c>
-      <c r="AD23" s="7">
-        <f t="shared" ref="AD23" si="119">AD20-AD21-AD22</f>
-        <v>-15.399999999999999</v>
-      </c>
-      <c r="AE23" s="7">
-        <f t="shared" ref="AE23" si="120">AE20-AE21-AE22</f>
-        <v>-4.700000000000002</v>
-      </c>
-      <c r="AF23" s="7">
-        <f t="shared" ref="AF23:AH23" si="121">AF20-AF21-AF22</f>
-        <v>-9.9999999999997868E-2</v>
-      </c>
-      <c r="AG23" s="7">
-        <f t="shared" si="121"/>
         <v>8.1999999999999975</v>
       </c>
       <c r="AH23" s="7">
-        <f t="shared" si="121"/>
+        <f t="shared" si="118"/>
         <v>-0.20000000000000817</v>
       </c>
       <c r="AI23" s="7">
-        <f t="shared" ref="AI23:AL23" si="122">AI20-AI21-AI22</f>
+        <f t="shared" ref="AI23:AL23" si="119">AI20-AI21-AI22</f>
         <v>-0.70000000000000029</v>
       </c>
       <c r="AJ23" s="7">
-        <f t="shared" si="122"/>
-        <v>-1.2506899999999987</v>
+        <f t="shared" si="119"/>
+        <v>-1.1000000000000003</v>
       </c>
       <c r="AK23" s="7">
-        <f t="shared" si="122"/>
-        <v>0.19549999999999912</v>
+        <f t="shared" si="119"/>
+        <v>-0.45199999999999996</v>
       </c>
       <c r="AL23" s="7">
-        <f t="shared" si="122"/>
-        <v>-0.41669999999999874</v>
+        <f t="shared" si="119"/>
+        <v>-1.2561999999999962</v>
       </c>
       <c r="AN23" s="7">
         <f>AN20-AN21-AN22</f>
@@ -5226,504 +5211,504 @@
         <v>-111.00000000000006</v>
       </c>
       <c r="AR23" s="7">
-        <f t="shared" ref="AR23:BA23" si="123">AR20-AR21-AR22</f>
+        <f t="shared" ref="AR23:BA23" si="120">AR20-AR21-AR22</f>
         <v>-52.100000000000037</v>
       </c>
       <c r="AS23" s="7">
-        <f t="shared" si="123"/>
+        <f t="shared" si="120"/>
         <v>-70.700000000000017</v>
       </c>
       <c r="AT23" s="7">
-        <f t="shared" si="123"/>
+        <f t="shared" si="120"/>
         <v>-57.699999999999953</v>
       </c>
       <c r="AU23" s="7">
-        <f t="shared" si="123"/>
+        <f t="shared" si="120"/>
         <v>3.1999999999999886</v>
       </c>
       <c r="AV23" s="7">
-        <f t="shared" si="123"/>
-        <v>-2.171889999999951</v>
+        <f t="shared" si="120"/>
+        <v>-3.5082000000000235</v>
       </c>
       <c r="AW23" s="7">
-        <f t="shared" si="123"/>
-        <v>11.015718799999986</v>
+        <f t="shared" si="120"/>
+        <v>7.3717279999999858</v>
       </c>
       <c r="AX23" s="7">
-        <f t="shared" si="123"/>
-        <v>14.285659768000007</v>
+        <f t="shared" si="120"/>
+        <v>10.802357279999994</v>
       </c>
       <c r="AY23" s="7">
-        <f t="shared" si="123"/>
-        <v>16.629577081600026</v>
+        <f t="shared" si="120"/>
+        <v>13.440192995199988</v>
       </c>
       <c r="AZ23" s="7">
-        <f t="shared" si="123"/>
-        <v>18.224508913279998</v>
+        <f t="shared" si="120"/>
+        <v>15.538751365088</v>
       </c>
       <c r="BA23" s="7">
-        <f t="shared" si="123"/>
-        <v>19.306600227678679</v>
+        <f t="shared" si="120"/>
+        <v>16.844988737650262</v>
       </c>
       <c r="BB23" s="7">
-        <f t="shared" ref="BB23:BF23" si="124">BB20-BB21-BB22</f>
-        <v>20.206535831356643</v>
+        <f t="shared" ref="BB23:BF23" si="121">BB20-BB21-BB22</f>
+        <v>17.664934898149497</v>
       </c>
       <c r="BC23" s="7">
-        <f t="shared" si="124"/>
-        <v>20.918569312877928</v>
+        <f t="shared" si="121"/>
+        <v>18.363918243883948</v>
       </c>
       <c r="BD23" s="7">
-        <f t="shared" si="124"/>
-        <v>21.619842412545204</v>
+        <f t="shared" si="121"/>
+        <v>19.053294117604533</v>
       </c>
       <c r="BE23" s="7">
-        <f t="shared" si="124"/>
-        <v>22.317516534202696</v>
+        <f t="shared" si="121"/>
+        <v>19.739717201122332</v>
       </c>
       <c r="BF23" s="7">
-        <f t="shared" si="124"/>
-        <v>23.017588214808196</v>
+        <f t="shared" si="121"/>
+        <v>20.428777395002282</v>
       </c>
       <c r="BG23" s="1">
         <f>BF23*(1+$BI$32)</f>
-        <v>22.787412332660114</v>
+        <v>20.22448962105226</v>
       </c>
       <c r="BH23" s="1">
-        <f t="shared" ref="BH23:DS23" si="125">BG23*(1+$BI$32)</f>
-        <v>22.559538209333514</v>
+        <f t="shared" ref="BH23:DS23" si="122">BG23*(1+$BI$32)</f>
+        <v>20.022244724841737</v>
       </c>
       <c r="BI23" s="1">
-        <f t="shared" si="125"/>
-        <v>22.333942827240179</v>
+        <f t="shared" si="122"/>
+        <v>19.822022277593319</v>
       </c>
       <c r="BJ23" s="1">
-        <f t="shared" si="125"/>
-        <v>22.110603398967775</v>
+        <f t="shared" si="122"/>
+        <v>19.623802054817386</v>
       </c>
       <c r="BK23" s="1">
-        <f t="shared" si="125"/>
-        <v>21.889497364978098</v>
+        <f t="shared" si="122"/>
+        <v>19.42756403426921</v>
       </c>
       <c r="BL23" s="1">
-        <f t="shared" si="125"/>
-        <v>21.670602391328316</v>
+        <f t="shared" si="122"/>
+        <v>19.233288393926518</v>
       </c>
       <c r="BM23" s="1">
-        <f t="shared" si="125"/>
-        <v>21.453896367415034</v>
+        <f t="shared" si="122"/>
+        <v>19.040955509987253</v>
       </c>
       <c r="BN23" s="1">
-        <f t="shared" si="125"/>
-        <v>21.239357403740883</v>
+        <f t="shared" si="122"/>
+        <v>18.85054595488738</v>
       </c>
       <c r="BO23" s="1">
-        <f t="shared" si="125"/>
-        <v>21.026963829703472</v>
+        <f t="shared" si="122"/>
+        <v>18.662040495338506</v>
       </c>
       <c r="BP23" s="1">
-        <f t="shared" si="125"/>
-        <v>20.816694191406437</v>
+        <f t="shared" si="122"/>
+        <v>18.475420090385121</v>
       </c>
       <c r="BQ23" s="1">
-        <f t="shared" si="125"/>
-        <v>20.608527249492372</v>
+        <f t="shared" si="122"/>
+        <v>18.290665889481271</v>
       </c>
       <c r="BR23" s="1">
-        <f t="shared" si="125"/>
-        <v>20.402441976997448</v>
+        <f t="shared" si="122"/>
+        <v>18.10775923058646</v>
       </c>
       <c r="BS23" s="1">
-        <f t="shared" si="125"/>
-        <v>20.198417557227472</v>
+        <f t="shared" si="122"/>
+        <v>17.926681638280595</v>
       </c>
       <c r="BT23" s="1">
-        <f t="shared" si="125"/>
-        <v>19.996433381655198</v>
+        <f t="shared" si="122"/>
+        <v>17.747414821897788</v>
       </c>
       <c r="BU23" s="1">
-        <f t="shared" si="125"/>
-        <v>19.796469047838645</v>
+        <f t="shared" si="122"/>
+        <v>17.569940673678811</v>
       </c>
       <c r="BV23" s="1">
-        <f t="shared" si="125"/>
-        <v>19.598504357360259</v>
+        <f t="shared" si="122"/>
+        <v>17.394241266942021</v>
       </c>
       <c r="BW23" s="1">
-        <f t="shared" si="125"/>
-        <v>19.402519313786655</v>
+        <f t="shared" si="122"/>
+        <v>17.220298854272603</v>
       </c>
       <c r="BX23" s="1">
-        <f t="shared" si="125"/>
-        <v>19.208494120648787</v>
+        <f t="shared" si="122"/>
+        <v>17.048095865729877</v>
       </c>
       <c r="BY23" s="1">
-        <f t="shared" si="125"/>
-        <v>19.016409179442299</v>
+        <f t="shared" si="122"/>
+        <v>16.877614907072577</v>
       </c>
       <c r="BZ23" s="1">
-        <f t="shared" si="125"/>
-        <v>18.826245087647877</v>
+        <f t="shared" si="122"/>
+        <v>16.70883875800185</v>
       </c>
       <c r="CA23" s="1">
-        <f t="shared" si="125"/>
-        <v>18.637982636771397</v>
+        <f t="shared" si="122"/>
+        <v>16.54175037042183</v>
       </c>
       <c r="CB23" s="1">
-        <f t="shared" si="125"/>
-        <v>18.451602810403685</v>
+        <f t="shared" si="122"/>
+        <v>16.376332866717611</v>
       </c>
       <c r="CC23" s="1">
-        <f t="shared" si="125"/>
-        <v>18.267086782299646</v>
+        <f t="shared" si="122"/>
+        <v>16.212569538050435</v>
       </c>
       <c r="CD23" s="1">
-        <f t="shared" si="125"/>
-        <v>18.084415914476651</v>
+        <f t="shared" si="122"/>
+        <v>16.050443842669932</v>
       </c>
       <c r="CE23" s="1">
-        <f t="shared" si="125"/>
-        <v>17.903571755331885</v>
+        <f t="shared" si="122"/>
+        <v>15.889939404243233</v>
       </c>
       <c r="CF23" s="1">
-        <f t="shared" si="125"/>
-        <v>17.724536037778567</v>
+        <f t="shared" si="122"/>
+        <v>15.7310400102008</v>
       </c>
       <c r="CG23" s="1">
-        <f t="shared" si="125"/>
-        <v>17.547290677400781</v>
+        <f t="shared" si="122"/>
+        <v>15.573729610098793</v>
       </c>
       <c r="CH23" s="1">
-        <f t="shared" si="125"/>
-        <v>17.371817770626773</v>
+        <f t="shared" si="122"/>
+        <v>15.417992313997805</v>
       </c>
       <c r="CI23" s="1">
-        <f t="shared" si="125"/>
-        <v>17.198099592920506</v>
+        <f t="shared" si="122"/>
+        <v>15.263812390857828</v>
       </c>
       <c r="CJ23" s="1">
-        <f t="shared" si="125"/>
-        <v>17.026118596991303</v>
+        <f t="shared" si="122"/>
+        <v>15.111174266949249</v>
       </c>
       <c r="CK23" s="1">
-        <f t="shared" si="125"/>
-        <v>16.85585741102139</v>
+        <f t="shared" si="122"/>
+        <v>14.960062524279756</v>
       </c>
       <c r="CL23" s="1">
-        <f t="shared" si="125"/>
-        <v>16.687298836911175</v>
+        <f t="shared" si="122"/>
+        <v>14.810461899036959</v>
       </c>
       <c r="CM23" s="1">
-        <f t="shared" si="125"/>
-        <v>16.520425848542065</v>
+        <f t="shared" si="122"/>
+        <v>14.662357280046589</v>
       </c>
       <c r="CN23" s="1">
-        <f t="shared" si="125"/>
-        <v>16.355221590056644</v>
+        <f t="shared" si="122"/>
+        <v>14.515733707246122</v>
       </c>
       <c r="CO23" s="1">
-        <f t="shared" si="125"/>
-        <v>16.191669374156078</v>
+        <f t="shared" si="122"/>
+        <v>14.37057637017366</v>
       </c>
       <c r="CP23" s="1">
-        <f t="shared" si="125"/>
-        <v>16.029752680414518</v>
+        <f t="shared" si="122"/>
+        <v>14.226870606471923</v>
       </c>
       <c r="CQ23" s="1">
-        <f t="shared" si="125"/>
-        <v>15.869455153610373</v>
+        <f t="shared" si="122"/>
+        <v>14.084601900407204</v>
       </c>
       <c r="CR23" s="1">
-        <f t="shared" si="125"/>
-        <v>15.710760602074268</v>
+        <f t="shared" si="122"/>
+        <v>13.943755881403131</v>
       </c>
       <c r="CS23" s="1">
-        <f t="shared" si="125"/>
-        <v>15.553652996053525</v>
+        <f t="shared" si="122"/>
+        <v>13.804318322589101</v>
       </c>
       <c r="CT23" s="1">
-        <f t="shared" si="125"/>
-        <v>15.39811646609299</v>
+        <f t="shared" si="122"/>
+        <v>13.66627513936321</v>
       </c>
       <c r="CU23" s="1">
-        <f t="shared" si="125"/>
-        <v>15.24413530143206</v>
+        <f t="shared" si="122"/>
+        <v>13.529612387969577</v>
       </c>
       <c r="CV23" s="1">
-        <f t="shared" si="125"/>
-        <v>15.091693948417738</v>
+        <f t="shared" si="122"/>
+        <v>13.394316264089881</v>
       </c>
       <c r="CW23" s="1">
-        <f t="shared" si="125"/>
-        <v>14.94077700893356</v>
+        <f t="shared" si="122"/>
+        <v>13.260373101448982</v>
       </c>
       <c r="CX23" s="1">
-        <f t="shared" si="125"/>
-        <v>14.791369238844224</v>
+        <f t="shared" si="122"/>
+        <v>13.127769370434493</v>
       </c>
       <c r="CY23" s="1">
-        <f t="shared" si="125"/>
-        <v>14.643455546455781</v>
+        <f t="shared" si="122"/>
+        <v>12.996491676730148</v>
       </c>
       <c r="CZ23" s="1">
-        <f t="shared" si="125"/>
-        <v>14.497020990991224</v>
+        <f t="shared" si="122"/>
+        <v>12.866526759962847</v>
       </c>
       <c r="DA23" s="1">
-        <f t="shared" si="125"/>
-        <v>14.352050781081312</v>
+        <f t="shared" si="122"/>
+        <v>12.737861492363217</v>
       </c>
       <c r="DB23" s="1">
-        <f t="shared" si="125"/>
-        <v>14.208530273270499</v>
+        <f t="shared" si="122"/>
+        <v>12.610482877439585</v>
       </c>
       <c r="DC23" s="1">
-        <f t="shared" si="125"/>
-        <v>14.066444970537795</v>
+        <f t="shared" si="122"/>
+        <v>12.484378048665189</v>
       </c>
       <c r="DD23" s="1">
-        <f t="shared" si="125"/>
-        <v>13.925780520832417</v>
+        <f t="shared" si="122"/>
+        <v>12.359534268178537</v>
       </c>
       <c r="DE23" s="1">
-        <f t="shared" si="125"/>
-        <v>13.786522715624093</v>
+        <f t="shared" si="122"/>
+        <v>12.235938925496752</v>
       </c>
       <c r="DF23" s="1">
-        <f t="shared" si="125"/>
-        <v>13.648657488467853</v>
+        <f t="shared" si="122"/>
+        <v>12.113579536241785</v>
       </c>
       <c r="DG23" s="1">
-        <f t="shared" si="125"/>
-        <v>13.512170913583175</v>
+        <f t="shared" si="122"/>
+        <v>11.992443740879366</v>
       </c>
       <c r="DH23" s="1">
-        <f t="shared" si="125"/>
-        <v>13.377049204447342</v>
+        <f t="shared" si="122"/>
+        <v>11.872519303470572</v>
       </c>
       <c r="DI23" s="1">
-        <f t="shared" si="125"/>
-        <v>13.243278712402869</v>
+        <f t="shared" si="122"/>
+        <v>11.753794110435866</v>
       </c>
       <c r="DJ23" s="1">
-        <f t="shared" si="125"/>
-        <v>13.11084592527884</v>
+        <f t="shared" si="122"/>
+        <v>11.636256169331507</v>
       </c>
       <c r="DK23" s="1">
-        <f t="shared" si="125"/>
-        <v>12.979737466026052</v>
+        <f t="shared" si="122"/>
+        <v>11.519893607638192</v>
       </c>
       <c r="DL23" s="1">
-        <f t="shared" si="125"/>
-        <v>12.849940091365792</v>
+        <f t="shared" si="122"/>
+        <v>11.40469467156181</v>
       </c>
       <c r="DM23" s="1">
-        <f t="shared" si="125"/>
-        <v>12.721440690452134</v>
+        <f t="shared" si="122"/>
+        <v>11.290647724846192</v>
       </c>
       <c r="DN23" s="1">
-        <f t="shared" si="125"/>
-        <v>12.594226283547613</v>
+        <f t="shared" si="122"/>
+        <v>11.17774124759773</v>
       </c>
       <c r="DO23" s="1">
-        <f t="shared" si="125"/>
-        <v>12.468284020712137</v>
+        <f t="shared" si="122"/>
+        <v>11.065963835121753</v>
       </c>
       <c r="DP23" s="1">
-        <f t="shared" si="125"/>
-        <v>12.343601180505015</v>
+        <f t="shared" si="122"/>
+        <v>10.955304196770536</v>
       </c>
       <c r="DQ23" s="1">
-        <f t="shared" si="125"/>
-        <v>12.220165168699964</v>
+        <f t="shared" si="122"/>
+        <v>10.84575115480283</v>
       </c>
       <c r="DR23" s="1">
-        <f t="shared" si="125"/>
-        <v>12.097963517012964</v>
+        <f t="shared" si="122"/>
+        <v>10.737293643254802</v>
       </c>
       <c r="DS23" s="1">
-        <f t="shared" si="125"/>
-        <v>11.976983881842834</v>
+        <f t="shared" si="122"/>
+        <v>10.629920706822254</v>
       </c>
       <c r="DT23" s="1">
-        <f t="shared" ref="DT23:FL23" si="126">DS23*(1+$BI$32)</f>
-        <v>11.857214043024406</v>
+        <f t="shared" ref="DT23:FL23" si="123">DS23*(1+$BI$32)</f>
+        <v>10.523621499754032</v>
       </c>
       <c r="DU23" s="1">
-        <f t="shared" si="126"/>
-        <v>11.738641902594162</v>
+        <f t="shared" si="123"/>
+        <v>10.418385284756491</v>
       </c>
       <c r="DV23" s="1">
-        <f t="shared" si="126"/>
-        <v>11.62125548356822</v>
+        <f t="shared" si="123"/>
+        <v>10.314201431908925</v>
       </c>
       <c r="DW23" s="1">
-        <f t="shared" si="126"/>
-        <v>11.505042928732538</v>
+        <f t="shared" si="123"/>
+        <v>10.211059417589835</v>
       </c>
       <c r="DX23" s="1">
-        <f t="shared" si="126"/>
-        <v>11.389992499445212</v>
+        <f t="shared" si="123"/>
+        <v>10.108948823413936</v>
       </c>
       <c r="DY23" s="1">
-        <f t="shared" si="126"/>
-        <v>11.276092574450759</v>
+        <f t="shared" si="123"/>
+        <v>10.007859335179797</v>
       </c>
       <c r="DZ23" s="1">
-        <f t="shared" si="126"/>
-        <v>11.163331648706251</v>
+        <f t="shared" si="123"/>
+        <v>9.9077807418279988</v>
       </c>
       <c r="EA23" s="1">
-        <f t="shared" si="126"/>
-        <v>11.051698332219189</v>
+        <f t="shared" si="123"/>
+        <v>9.8087029344097196</v>
       </c>
       <c r="EB23" s="1">
-        <f t="shared" si="126"/>
-        <v>10.941181348896997</v>
+        <f t="shared" si="123"/>
+        <v>9.7106159050656231</v>
       </c>
       <c r="EC23" s="1">
-        <f t="shared" si="126"/>
-        <v>10.831769535408027</v>
+        <f t="shared" si="123"/>
+        <v>9.6135097460149677</v>
       </c>
       <c r="ED23" s="1">
-        <f t="shared" si="126"/>
-        <v>10.723451840053947</v>
+        <f t="shared" si="123"/>
+        <v>9.5173746485548172</v>
       </c>
       <c r="EE23" s="1">
-        <f t="shared" si="126"/>
-        <v>10.616217321653407</v>
+        <f t="shared" si="123"/>
+        <v>9.4222009020692692</v>
       </c>
       <c r="EF23" s="1">
-        <f t="shared" si="126"/>
-        <v>10.510055148436873</v>
+        <f t="shared" si="123"/>
+        <v>9.3279788930485772</v>
       </c>
       <c r="EG23" s="1">
-        <f t="shared" si="126"/>
-        <v>10.404954596952503</v>
+        <f t="shared" si="123"/>
+        <v>9.234699104118091</v>
       </c>
       <c r="EH23" s="1">
-        <f t="shared" si="126"/>
-        <v>10.300905050982978</v>
+        <f t="shared" si="123"/>
+        <v>9.1423521130769103</v>
       </c>
       <c r="EI23" s="1">
-        <f t="shared" si="126"/>
-        <v>10.197896000473149</v>
+        <f t="shared" si="123"/>
+        <v>9.0509285919461409</v>
       </c>
       <c r="EJ23" s="1">
-        <f t="shared" si="126"/>
-        <v>10.095917040468418</v>
+        <f t="shared" si="123"/>
+        <v>8.9604193060266795</v>
       </c>
       <c r="EK23" s="1">
-        <f t="shared" si="126"/>
-        <v>9.9949578700637343</v>
+        <f t="shared" si="123"/>
+        <v>8.8708151129664135</v>
       </c>
       <c r="EL23" s="1">
-        <f t="shared" si="126"/>
-        <v>9.8950082913630961</v>
+        <f t="shared" si="123"/>
+        <v>8.7821069618367495</v>
       </c>
       <c r="EM23" s="1">
-        <f t="shared" si="126"/>
-        <v>9.7960582084494643</v>
+        <f t="shared" si="123"/>
+        <v>8.6942858922183817</v>
       </c>
       <c r="EN23" s="1">
-        <f t="shared" si="126"/>
-        <v>9.6980976263649694</v>
+        <f t="shared" si="123"/>
+        <v>8.607343033296198</v>
       </c>
       <c r="EO23" s="1">
-        <f t="shared" si="126"/>
-        <v>9.6011166501013196</v>
+        <f t="shared" si="123"/>
+        <v>8.5212696029632351</v>
       </c>
       <c r="EP23" s="1">
-        <f t="shared" si="126"/>
-        <v>9.5051054836003068</v>
+        <f t="shared" si="123"/>
+        <v>8.4360569069336027</v>
       </c>
       <c r="EQ23" s="1">
-        <f t="shared" si="126"/>
-        <v>9.4100544287643029</v>
+        <f t="shared" si="123"/>
+        <v>8.3516963378642668</v>
       </c>
       <c r="ER23" s="1">
-        <f t="shared" si="126"/>
-        <v>9.3159538844766594</v>
+        <f t="shared" si="123"/>
+        <v>8.2681793744856247</v>
       </c>
       <c r="ES23" s="1">
-        <f t="shared" si="126"/>
-        <v>9.2227943456318933</v>
+        <f t="shared" si="123"/>
+        <v>8.1854975807407691</v>
       </c>
       <c r="ET23" s="1">
-        <f t="shared" si="126"/>
-        <v>9.1305664021755746</v>
+        <f t="shared" si="123"/>
+        <v>8.103642604933361</v>
       </c>
       <c r="EU23" s="1">
-        <f t="shared" si="126"/>
-        <v>9.0392607381538195</v>
+        <f t="shared" si="123"/>
+        <v>8.0226061788840273</v>
       </c>
       <c r="EV23" s="1">
-        <f t="shared" si="126"/>
-        <v>8.948868130772281</v>
+        <f t="shared" si="123"/>
+        <v>7.9423801170951869</v>
       </c>
       <c r="EW23" s="1">
-        <f t="shared" si="126"/>
-        <v>8.8593794494645586</v>
+        <f t="shared" si="123"/>
+        <v>7.8629563159242348</v>
       </c>
       <c r="EX23" s="1">
-        <f t="shared" si="126"/>
-        <v>8.770785654969913</v>
+        <f t="shared" si="123"/>
+        <v>7.7843267527649926</v>
       </c>
       <c r="EY23" s="1">
-        <f t="shared" si="126"/>
-        <v>8.6830777984202143</v>
+        <f t="shared" si="123"/>
+        <v>7.7064834852373423</v>
       </c>
       <c r="EZ23" s="1">
-        <f t="shared" si="126"/>
-        <v>8.596247020436012</v>
+        <f t="shared" si="123"/>
+        <v>7.6294186503849684</v>
       </c>
       <c r="FA23" s="1">
-        <f t="shared" si="126"/>
-        <v>8.5102845502316526</v>
+        <f t="shared" si="123"/>
+        <v>7.5531244638811188</v>
       </c>
       <c r="FB23" s="1">
-        <f t="shared" si="126"/>
-        <v>8.4251817047293365</v>
+        <f t="shared" si="123"/>
+        <v>7.4775932192423076</v>
       </c>
       <c r="FC23" s="1">
-        <f t="shared" si="126"/>
-        <v>8.3409298876820426</v>
+        <f t="shared" si="123"/>
+        <v>7.4028172870498841</v>
       </c>
       <c r="FD23" s="1">
-        <f t="shared" si="126"/>
-        <v>8.2575205888052228</v>
+        <f t="shared" si="123"/>
+        <v>7.3287891141793855</v>
       </c>
       <c r="FE23" s="1">
-        <f t="shared" si="126"/>
-        <v>8.174945382917171</v>
+        <f t="shared" si="123"/>
+        <v>7.2555012230375917</v>
       </c>
       <c r="FF23" s="1">
-        <f t="shared" si="126"/>
-        <v>8.0931959290879991</v>
+        <f t="shared" si="123"/>
+        <v>7.1829462108072155</v>
       </c>
       <c r="FG23" s="1">
-        <f t="shared" si="126"/>
-        <v>8.0122639697971199</v>
+        <f t="shared" si="123"/>
+        <v>7.1111167486991436</v>
       </c>
       <c r="FH23" s="1">
-        <f t="shared" si="126"/>
-        <v>7.9321413300991486</v>
+        <f t="shared" si="123"/>
+        <v>7.040005581212152</v>
       </c>
       <c r="FI23" s="1">
-        <f t="shared" si="126"/>
-        <v>7.8528199167981567</v>
+        <f t="shared" si="123"/>
+        <v>6.9696055254000306</v>
       </c>
       <c r="FJ23" s="1">
-        <f t="shared" si="126"/>
-        <v>7.7742917176301747</v>
+        <f t="shared" si="123"/>
+        <v>6.8999094701460306</v>
       </c>
       <c r="FK23" s="1">
-        <f t="shared" si="126"/>
-        <v>7.6965488004538729</v>
+        <f t="shared" si="123"/>
+        <v>6.8309103754445699</v>
       </c>
       <c r="FL23" s="1">
-        <f t="shared" si="126"/>
-        <v>7.6195833124493344</v>
+        <f t="shared" si="123"/>
+        <v>6.7626012716901238</v>
       </c>
     </row>
     <row r="24" spans="2:168" x14ac:dyDescent="0.3">
@@ -5903,148 +5888,148 @@
         <v>38</v>
       </c>
       <c r="C25" s="8">
-        <f t="shared" ref="C25:P25" si="127">C23/C24</f>
+        <f t="shared" ref="C25:P25" si="124">C23/C24</f>
         <v>-0.16570605187319887</v>
       </c>
       <c r="D25" s="8">
+        <f t="shared" si="124"/>
+        <v>-0.11012762453684644</v>
+      </c>
+      <c r="E25" s="8">
+        <f t="shared" si="124"/>
+        <v>-0.14100452861259771</v>
+      </c>
+      <c r="F25" s="8">
+        <f t="shared" si="124"/>
+        <v>-3.9110745162618317E-2</v>
+      </c>
+      <c r="G25" s="8">
+        <f t="shared" si="124"/>
+        <v>-7.8221490325236773E-2</v>
+      </c>
+      <c r="H25" s="8">
+        <f t="shared" si="124"/>
+        <v>-6.9987649238369698E-2</v>
+      </c>
+      <c r="I25" s="8">
+        <f t="shared" si="124"/>
+        <v>-0.2418690819267188</v>
+      </c>
+      <c r="J25" s="8">
+        <f t="shared" si="124"/>
+        <v>-4.3227665706051785E-2</v>
+      </c>
+      <c r="K25" s="8">
+        <f t="shared" si="124"/>
+        <v>-8.4396871140387061E-2</v>
+      </c>
+      <c r="L25" s="8">
+        <f t="shared" si="124"/>
+        <v>-0.11012762453684639</v>
+      </c>
+      <c r="M25" s="8">
+        <f t="shared" si="124"/>
+        <v>-9.1601482091395611E-2</v>
+      </c>
+      <c r="N25" s="8">
+        <f t="shared" si="124"/>
+        <v>-0.13174145738987236</v>
+      </c>
+      <c r="O25" s="8">
+        <f t="shared" si="124"/>
+        <v>-0.18731988472622479</v>
+      </c>
+      <c r="P25" s="8">
+        <f t="shared" si="124"/>
+        <v>-0.76986414162206673</v>
+      </c>
+      <c r="Q25" s="8">
+        <f t="shared" ref="Q25:U25" si="125">Q23/Q24</f>
+        <v>-5.4600606673407472E-2</v>
+      </c>
+      <c r="R25" s="8">
+        <f t="shared" si="125"/>
+        <v>-0.12740141557128418</v>
+      </c>
+      <c r="S25" s="8">
+        <f t="shared" si="125"/>
+        <v>-0.17997977755308392</v>
+      </c>
+      <c r="T25" s="8">
+        <f t="shared" ref="T25" si="126">T23/T24</f>
+        <v>-1.1300813008130079</v>
+      </c>
+      <c r="U25" s="8">
+        <f t="shared" si="125"/>
+        <v>-0.73170731707317072</v>
+      </c>
+      <c r="V25" s="8">
+        <f t="shared" ref="V25:W25" si="127">V23/V24</f>
+        <v>-0.92682926829268186</v>
+      </c>
+      <c r="W25" s="8">
         <f t="shared" si="127"/>
-        <v>-0.11012762453684644</v>
-      </c>
-      <c r="E25" s="8">
-        <f t="shared" si="127"/>
-        <v>-0.14100452861259771</v>
-      </c>
-      <c r="F25" s="8">
-        <f t="shared" si="127"/>
-        <v>-3.9110745162618317E-2</v>
-      </c>
-      <c r="G25" s="8">
-        <f t="shared" si="127"/>
-        <v>-7.8221490325236773E-2</v>
-      </c>
-      <c r="H25" s="8">
-        <f t="shared" si="127"/>
-        <v>-6.9987649238369698E-2</v>
-      </c>
-      <c r="I25" s="8">
-        <f t="shared" si="127"/>
-        <v>-0.2418690819267188</v>
-      </c>
-      <c r="J25" s="8">
-        <f t="shared" si="127"/>
-        <v>-4.3227665706051785E-2</v>
-      </c>
-      <c r="K25" s="8">
-        <f t="shared" si="127"/>
-        <v>-8.4396871140387061E-2</v>
-      </c>
-      <c r="L25" s="8">
-        <f t="shared" si="127"/>
-        <v>-0.11012762453684639</v>
-      </c>
-      <c r="M25" s="8">
-        <f t="shared" si="127"/>
-        <v>-9.1601482091395611E-2</v>
-      </c>
-      <c r="N25" s="8">
-        <f t="shared" si="127"/>
-        <v>-0.13174145738987236</v>
-      </c>
-      <c r="O25" s="8">
-        <f t="shared" si="127"/>
-        <v>-0.18731988472622479</v>
-      </c>
-      <c r="P25" s="8">
-        <f t="shared" si="127"/>
-        <v>-0.76986414162206673</v>
-      </c>
-      <c r="Q25" s="8">
-        <f t="shared" ref="Q25:U25" si="128">Q23/Q24</f>
-        <v>-5.4600606673407472E-2</v>
-      </c>
-      <c r="R25" s="8">
+        <v>-2.1056910569105689</v>
+      </c>
+      <c r="X25" s="8">
+        <f t="shared" ref="X25:Y25" si="128">X23/X24</f>
+        <v>-1.0731707317073165</v>
+      </c>
+      <c r="Y25" s="8">
         <f t="shared" si="128"/>
-        <v>-0.12740141557128418</v>
-      </c>
-      <c r="S25" s="8">
-        <f t="shared" si="128"/>
-        <v>-0.17997977755308392</v>
-      </c>
-      <c r="T25" s="8">
-        <f t="shared" ref="T25" si="129">T23/T24</f>
-        <v>-1.1300813008130079</v>
-      </c>
-      <c r="U25" s="8">
-        <f t="shared" si="128"/>
-        <v>-0.73170731707317072</v>
-      </c>
-      <c r="V25" s="8">
-        <f t="shared" ref="V25:W25" si="130">V23/V24</f>
-        <v>-0.92682926829268186</v>
-      </c>
-      <c r="W25" s="8">
-        <f t="shared" si="130"/>
-        <v>-2.1056910569105689</v>
-      </c>
-      <c r="X25" s="8">
-        <f t="shared" ref="X25:Y25" si="131">X23/X24</f>
-        <v>-1.0731707317073165</v>
-      </c>
-      <c r="Y25" s="8">
+        <v>-1.3333333333333339</v>
+      </c>
+      <c r="Z25" s="8">
+        <f t="shared" ref="Z25" si="129">Z23/Z24</f>
+        <v>-1.2357723577235773</v>
+      </c>
+      <c r="AA25" s="8">
+        <f t="shared" ref="AA25" si="130">AA23/AA24</f>
+        <v>-0.43089430894308983</v>
+      </c>
+      <c r="AB25" s="8">
+        <f t="shared" ref="AB25:AC25" si="131">AB23/AB24</f>
+        <v>-0.52845528455284596</v>
+      </c>
+      <c r="AC25" s="8">
         <f t="shared" si="131"/>
-        <v>-1.3333333333333339</v>
-      </c>
-      <c r="Z25" s="8">
-        <f t="shared" ref="Z25" si="132">Z23/Z24</f>
-        <v>-1.2357723577235773</v>
-      </c>
-      <c r="AA25" s="8">
-        <f t="shared" ref="AA25" si="133">AA23/AA24</f>
-        <v>-0.43089430894308983</v>
-      </c>
-      <c r="AB25" s="8">
-        <f t="shared" ref="AB25:AC25" si="134">AB23/AB24</f>
-        <v>-0.52845528455284596</v>
-      </c>
-      <c r="AC25" s="8">
+        <v>-2.4796747967479673</v>
+      </c>
+      <c r="AD25" s="8">
+        <f t="shared" ref="AD25" si="132">AD23/AD24</f>
+        <v>-1.252032520325203</v>
+      </c>
+      <c r="AE25" s="8">
+        <f t="shared" ref="AE25" si="133">AE23/AE24</f>
+        <v>-0.38211382113821152</v>
+      </c>
+      <c r="AF25" s="8">
+        <f t="shared" ref="AF25:AH25" si="134">AF23/AF24</f>
+        <v>-8.1300813008128338E-3</v>
+      </c>
+      <c r="AG25" s="8">
         <f t="shared" si="134"/>
-        <v>-2.4796747967479673</v>
-      </c>
-      <c r="AD25" s="8">
-        <f t="shared" ref="AD25" si="135">AD23/AD24</f>
-        <v>-1.252032520325203</v>
-      </c>
-      <c r="AE25" s="8">
-        <f t="shared" ref="AE25" si="136">AE23/AE24</f>
-        <v>-0.38211382113821152</v>
-      </c>
-      <c r="AF25" s="8">
-        <f t="shared" ref="AF25:AH25" si="137">AF23/AF24</f>
-        <v>-8.1300813008128338E-3</v>
-      </c>
-      <c r="AG25" s="8">
-        <f t="shared" si="137"/>
         <v>0.54849498327759183</v>
       </c>
       <c r="AH25" s="8">
-        <f t="shared" si="137"/>
+        <f t="shared" si="134"/>
         <v>-1.428571428571487E-2</v>
       </c>
       <c r="AI25" s="8">
-        <f t="shared" ref="AI25:AL25" si="138">AI23/AI24</f>
+        <f t="shared" ref="AI25:AL25" si="135">AI23/AI24</f>
         <v>-4.6666666666666683E-2</v>
       </c>
       <c r="AJ25" s="8">
-        <f t="shared" si="138"/>
-        <v>-8.337933333333325E-2</v>
+        <f t="shared" si="135"/>
+        <v>-7.3333333333333348E-2</v>
       </c>
       <c r="AK25" s="8">
-        <f t="shared" si="138"/>
-        <v>1.3033333333333275E-2</v>
+        <f t="shared" si="135"/>
+        <v>-3.0133333333333331E-2</v>
       </c>
       <c r="AL25" s="8">
-        <f t="shared" si="138"/>
-        <v>-2.7779999999999916E-2</v>
+        <f t="shared" si="135"/>
+        <v>-8.3746666666666414E-2</v>
       </c>
       <c r="AN25" s="8">
         <f>AN23/AN24</f>
@@ -6063,64 +6048,64 @@
         <v>-1.1424454508028001</v>
       </c>
       <c r="AR25" s="8">
-        <f t="shared" ref="AR25:BA25" si="139">AR23/AR24</f>
+        <f t="shared" ref="AR25:BA25" si="136">AR23/AR24</f>
         <v>-0.52679474216380218</v>
       </c>
       <c r="AS25" s="8">
-        <f t="shared" si="139"/>
+        <f t="shared" si="136"/>
         <v>-0.71486349848331665</v>
       </c>
       <c r="AT25" s="8">
-        <f t="shared" si="139"/>
+        <f t="shared" si="136"/>
         <v>-0.5834175935288165</v>
       </c>
       <c r="AU25" s="8">
-        <f t="shared" si="139"/>
+        <f t="shared" si="136"/>
         <v>0.22857142857142776</v>
       </c>
       <c r="AV25" s="8">
-        <f t="shared" si="139"/>
-        <v>-0.14479266666666341</v>
+        <f t="shared" si="136"/>
+        <v>-0.23388000000000156</v>
       </c>
       <c r="AW25" s="8">
-        <f t="shared" si="139"/>
-        <v>0.73438125333333237</v>
+        <f t="shared" si="136"/>
+        <v>0.49144853333333238</v>
       </c>
       <c r="AX25" s="8">
-        <f t="shared" si="139"/>
-        <v>0.95237731786666713</v>
+        <f t="shared" si="136"/>
+        <v>0.72015715199999952</v>
       </c>
       <c r="AY25" s="8">
-        <f t="shared" si="139"/>
-        <v>1.1086384721066684</v>
+        <f t="shared" si="136"/>
+        <v>0.89601286634666588</v>
       </c>
       <c r="AZ25" s="8">
-        <f t="shared" si="139"/>
-        <v>1.2149672608853332</v>
+        <f t="shared" si="136"/>
+        <v>1.0359167576725334</v>
       </c>
       <c r="BA25" s="8">
-        <f t="shared" si="139"/>
-        <v>1.2871066818452452</v>
+        <f t="shared" si="136"/>
+        <v>1.122999249176684</v>
       </c>
       <c r="BB25" s="8">
-        <f t="shared" ref="BB25:BF25" si="140">BB23/BB24</f>
-        <v>1.3471023887571094</v>
+        <f t="shared" ref="BB25:BF25" si="137">BB23/BB24</f>
+        <v>1.1776623265432997</v>
       </c>
       <c r="BC25" s="8">
-        <f t="shared" si="140"/>
-        <v>1.3945712875251952</v>
+        <f t="shared" si="137"/>
+        <v>1.2242612162589299</v>
       </c>
       <c r="BD25" s="8">
-        <f t="shared" si="140"/>
-        <v>1.4413228275030137</v>
+        <f t="shared" si="137"/>
+        <v>1.2702196078403023</v>
       </c>
       <c r="BE25" s="8">
-        <f t="shared" si="140"/>
-        <v>1.4878344356135131</v>
+        <f t="shared" si="137"/>
+        <v>1.3159811467414888</v>
       </c>
       <c r="BF25" s="8">
-        <f t="shared" si="140"/>
-        <v>1.534505880987213</v>
+        <f t="shared" si="137"/>
+        <v>1.3619184930001522</v>
       </c>
     </row>
     <row r="27" spans="2:168" x14ac:dyDescent="0.3">
@@ -6128,91 +6113,91 @@
         <v>82</v>
       </c>
       <c r="AD27" s="9">
-        <f t="shared" ref="AD27:AD28" si="141">AD3/Z3-1</f>
+        <f t="shared" ref="AD27:AD28" si="138">AD3/Z3-1</f>
         <v>-0.2558139534883721</v>
       </c>
       <c r="AE27" s="9">
-        <f t="shared" ref="AE27:AE28" si="142">AE3/AA3-1</f>
+        <f t="shared" ref="AE27:AE28" si="139">AE3/AA3-1</f>
         <v>-0.33478260869565213</v>
       </c>
       <c r="AF27" s="9">
-        <f t="shared" ref="AF27:AH28" si="143">AF3/AB3-1</f>
+        <f t="shared" ref="AF27:AH28" si="140">AF3/AB3-1</f>
         <v>0.37037037037037046</v>
       </c>
       <c r="AG27" s="9">
-        <f t="shared" si="143"/>
+        <f t="shared" si="140"/>
         <v>0.43555555555555547</v>
       </c>
       <c r="AH27" s="9">
-        <f t="shared" si="143"/>
+        <f t="shared" si="140"/>
         <v>0.59375</v>
       </c>
       <c r="AI27" s="9">
-        <f t="shared" ref="AI27:AI31" si="144">AI3/AE3-1</f>
+        <f t="shared" ref="AI27:AI31" si="141">AI3/AE3-1</f>
         <v>0.1633986928104576</v>
       </c>
       <c r="AJ27" s="9">
-        <f t="shared" ref="AJ27:AJ31" si="145">AJ3/AF3-1</f>
+        <f t="shared" ref="AJ27:AJ31" si="142">AJ3/AF3-1</f>
+        <v>-0.31274131274131267</v>
+      </c>
+      <c r="AK27" s="9">
+        <f t="shared" ref="AK27:AK31" si="143">AK3/AG3-1</f>
+        <v>-0.41176470588235292</v>
+      </c>
+      <c r="AL27" s="9">
+        <f t="shared" ref="AL27:AL31" si="144">AL3/AH3-1</f>
+        <v>-0.25490196078431371</v>
+      </c>
+      <c r="AT27" s="9">
+        <f t="shared" ref="AO27:BA30" si="145">AT3/AS3-1</f>
+        <v>-0.43902439024390238</v>
+      </c>
+      <c r="AU27" s="9">
+        <f t="shared" ref="AU27:AU28" si="146">AU3/AT3-1</f>
+        <v>0.22981366459627339</v>
+      </c>
+      <c r="AV27" s="9">
+        <f t="shared" ref="AV27:AV28" si="147">AV3/AU3-1</f>
+        <v>-0.25656565656565666</v>
+      </c>
+      <c r="AW27" s="9">
+        <f t="shared" ref="AW27:AW28" si="148">AW3/AV3-1</f>
+        <v>0.14999999999999991</v>
+      </c>
+      <c r="AX27" s="9">
+        <f t="shared" ref="AX27:AX28" si="149">AX3/AW3-1</f>
         <v>0.10000000000000009</v>
       </c>
-      <c r="AK27" s="9">
-        <f t="shared" ref="AK27:AK31" si="146">AK3/AG3-1</f>
-        <v>-3.0000000000000027E-2</v>
-      </c>
-      <c r="AL27" s="9">
-        <f t="shared" ref="AL27:AL31" si="147">AL3/AH3-1</f>
-        <v>0.30000000000000004</v>
-      </c>
-      <c r="AT27" s="9">
-        <f t="shared" ref="AO27:BA30" si="148">AT3/AS3-1</f>
-        <v>-0.43902439024390238</v>
-      </c>
-      <c r="AU27" s="9">
-        <f t="shared" ref="AU27:AU28" si="149">AU3/AT3-1</f>
-        <v>0.22981366459627339</v>
-      </c>
-      <c r="AV27" s="9">
-        <f t="shared" ref="AV27:AV28" si="150">AV3/AU3-1</f>
-        <v>0.11889898989899006</v>
-      </c>
-      <c r="AW27" s="9">
-        <f t="shared" ref="AW27:AW28" si="151">AW3/AV3-1</f>
-        <v>0.14999999999999991</v>
-      </c>
-      <c r="AX27" s="9">
-        <f t="shared" ref="AX27:AX28" si="152">AX3/AW3-1</f>
-        <v>9.9999999999999867E-2</v>
-      </c>
       <c r="AY27" s="9">
-        <f t="shared" ref="AY27:AY28" si="153">AY3/AX3-1</f>
+        <f t="shared" ref="AY27:AY28" si="150">AY3/AX3-1</f>
         <v>8.0000000000000071E-2</v>
       </c>
       <c r="AZ27" s="9">
-        <f t="shared" ref="AZ27:AZ28" si="154">AZ3/AY3-1</f>
+        <f t="shared" ref="AZ27:AZ28" si="151">AZ3/AY3-1</f>
         <v>5.0000000000000044E-2</v>
       </c>
       <c r="BA27" s="9">
-        <f t="shared" ref="BA27:BA28" si="155">BA3/AZ3-1</f>
+        <f t="shared" ref="BA27:BA28" si="152">BA3/AZ3-1</f>
         <v>4.0000000000000036E-2</v>
       </c>
       <c r="BB27" s="9">
-        <f t="shared" ref="BB27:BB28" si="156">BB3/BA3-1</f>
+        <f t="shared" ref="BB27:BB28" si="153">BB3/BA3-1</f>
         <v>3.0000000000000027E-2</v>
       </c>
       <c r="BC27" s="9">
-        <f t="shared" ref="BC27:BC28" si="157">BC3/BB3-1</f>
+        <f t="shared" ref="BC27:BC28" si="154">BC3/BB3-1</f>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="BD27" s="9">
-        <f t="shared" ref="BD27:BD28" si="158">BD3/BC3-1</f>
+        <f t="shared" ref="BD27:BD28" si="155">BD3/BC3-1</f>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="BE27" s="9">
-        <f t="shared" ref="BE27:BE28" si="159">BE3/BD3-1</f>
+        <f t="shared" ref="BE27:BE28" si="156">BE3/BD3-1</f>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="BF27" s="9">
-        <f t="shared" ref="BF27:BF28" si="160">BF3/BE3-1</f>
+        <f t="shared" ref="BF27:BF28" si="157">BF3/BE3-1</f>
         <v>2.0000000000000018E-2</v>
       </c>
     </row>
@@ -6221,92 +6206,92 @@
         <v>83</v>
       </c>
       <c r="AD28" s="9">
+        <f t="shared" si="138"/>
+        <v>-0.24848484848484842</v>
+      </c>
+      <c r="AE28" s="9">
+        <f t="shared" si="139"/>
+        <v>0.19327731092436973</v>
+      </c>
+      <c r="AF28" s="9">
+        <f t="shared" si="140"/>
+        <v>-0.31794871794871793</v>
+      </c>
+      <c r="AG28" s="9">
+        <f t="shared" si="140"/>
+        <v>-0.12612612612612617</v>
+      </c>
+      <c r="AH28" s="9">
+        <f t="shared" si="140"/>
+        <v>-0.16129032258064513</v>
+      </c>
+      <c r="AI28" s="9">
         <f t="shared" si="141"/>
-        <v>-0.24848484848484842</v>
-      </c>
-      <c r="AE28" s="9">
+        <v>-0.86619718309859151</v>
+      </c>
+      <c r="AJ28" s="9">
         <f t="shared" si="142"/>
-        <v>0.19327731092436973</v>
-      </c>
-      <c r="AF28" s="9">
+        <v>-0.85714285714285721</v>
+      </c>
+      <c r="AK28" s="9">
         <f t="shared" si="143"/>
-        <v>-0.31794871794871793</v>
-      </c>
-      <c r="AG28" s="9">
-        <f t="shared" si="143"/>
-        <v>-0.12612612612612617</v>
-      </c>
-      <c r="AH28" s="9">
-        <f t="shared" si="143"/>
-        <v>-0.16129032258064513</v>
-      </c>
-      <c r="AI28" s="9">
+        <v>-0.79381443298969068</v>
+      </c>
+      <c r="AL28" s="9">
         <f t="shared" si="144"/>
-        <v>-0.86619718309859151</v>
-      </c>
-      <c r="AJ28" s="9">
+        <v>-0.80769230769230771</v>
+      </c>
+      <c r="AT28" s="9">
         <f t="shared" si="145"/>
-        <v>-0.26338345864661672</v>
-      </c>
-      <c r="AK28" s="9">
+        <v>0.25917431192660545</v>
+      </c>
+      <c r="AU28" s="9">
         <f t="shared" si="146"/>
-        <v>8.2886597938144568E-2</v>
-      </c>
-      <c r="AL28" s="9">
+        <v>-0.13296903460837883</v>
+      </c>
+      <c r="AV28" s="9">
         <f t="shared" si="147"/>
-        <v>-0.81548076923076929</v>
-      </c>
-      <c r="AT28" s="9">
+        <v>-0.83613445378151263</v>
+      </c>
+      <c r="AW28" s="9">
         <f t="shared" si="148"/>
-        <v>0.25917431192660545</v>
-      </c>
-      <c r="AU28" s="9">
+        <v>-1.9999999999999907E-2</v>
+      </c>
+      <c r="AX28" s="9">
         <f t="shared" si="149"/>
-        <v>-0.13296903460837883</v>
-      </c>
-      <c r="AV28" s="9">
+        <v>-2.0000000000000129E-2</v>
+      </c>
+      <c r="AY28" s="9">
         <f t="shared" si="150"/>
-        <v>-0.49327731092436977</v>
-      </c>
-      <c r="AW28" s="9">
+        <v>-1.9999999999999907E-2</v>
+      </c>
+      <c r="AZ28" s="9">
         <f t="shared" si="151"/>
-        <v>-2.0000000000000129E-2</v>
-      </c>
-      <c r="AX28" s="9">
+        <v>-2.0000000000000018E-2</v>
+      </c>
+      <c r="BA28" s="9">
         <f t="shared" si="152"/>
         <v>-2.0000000000000018E-2</v>
       </c>
-      <c r="AY28" s="9">
+      <c r="BB28" s="9">
         <f t="shared" si="153"/>
         <v>-2.0000000000000018E-2</v>
       </c>
-      <c r="AZ28" s="9">
+      <c r="BC28" s="9">
         <f t="shared" si="154"/>
-        <v>-1.9999999999999907E-2</v>
-      </c>
-      <c r="BA28" s="9">
+        <v>-2.0000000000000018E-2</v>
+      </c>
+      <c r="BD28" s="9">
         <f t="shared" si="155"/>
-        <v>-2.0000000000000129E-2</v>
-      </c>
-      <c r="BB28" s="9">
+        <v>-2.0000000000000018E-2</v>
+      </c>
+      <c r="BE28" s="9">
         <f t="shared" si="156"/>
         <v>-2.0000000000000018E-2</v>
       </c>
-      <c r="BC28" s="9">
+      <c r="BF28" s="9">
         <f t="shared" si="157"/>
-        <v>-1.9999999999999907E-2</v>
-      </c>
-      <c r="BD28" s="9">
-        <f t="shared" si="158"/>
-        <v>-1.9999999999999907E-2</v>
-      </c>
-      <c r="BE28" s="9">
-        <f t="shared" si="159"/>
         <v>-2.0000000000000018E-2</v>
-      </c>
-      <c r="BF28" s="9">
-        <f t="shared" si="160"/>
-        <v>-1.9999999999999907E-2</v>
       </c>
     </row>
     <row r="29" spans="2:168" x14ac:dyDescent="0.3">
@@ -6318,201 +6303,201 @@
         <v>-0.25515463917525771</v>
       </c>
       <c r="H29" s="9">
-        <f t="shared" ref="H29:R29" si="161">H5/D5-1</f>
+        <f t="shared" ref="H29:R29" si="158">H5/D5-1</f>
         <v>-0.26620370370370372</v>
       </c>
       <c r="I29" s="9">
-        <f t="shared" si="161"/>
+        <f t="shared" si="158"/>
         <v>-0.19158878504672894</v>
       </c>
       <c r="J29" s="9">
-        <f t="shared" si="161"/>
+        <f t="shared" si="158"/>
         <v>0.26100628930817615</v>
       </c>
       <c r="K29" s="9">
-        <f t="shared" si="161"/>
+        <f t="shared" si="158"/>
         <v>0.134948096885813</v>
       </c>
       <c r="L29" s="9">
-        <f t="shared" si="161"/>
+        <f t="shared" si="158"/>
         <v>0.26182965299684535</v>
       </c>
       <c r="M29" s="9">
-        <f t="shared" si="161"/>
+        <f t="shared" si="158"/>
         <v>0.32658959537572252</v>
       </c>
       <c r="N29" s="9">
-        <f t="shared" si="161"/>
+        <f t="shared" si="158"/>
         <v>-0.11471321695760606</v>
       </c>
       <c r="O29" s="9">
-        <f t="shared" si="161"/>
+        <f t="shared" si="158"/>
         <v>0.23170731707317072</v>
       </c>
       <c r="P29" s="9">
-        <f t="shared" si="161"/>
+        <f t="shared" si="158"/>
         <v>0.65500000000000003</v>
       </c>
       <c r="Q29" s="9">
-        <f t="shared" si="161"/>
+        <f t="shared" si="158"/>
         <v>0.68409586056644889</v>
       </c>
       <c r="R29" s="9">
-        <f t="shared" si="161"/>
+        <f t="shared" si="158"/>
         <v>1.0309859154929577</v>
       </c>
       <c r="S29" s="9">
-        <f t="shared" ref="S29:V31" si="162">S5/O5-1</f>
+        <f t="shared" ref="S29:V31" si="159">S5/O5-1</f>
         <v>6.4356435643564414E-2</v>
       </c>
       <c r="T29" s="9">
-        <f t="shared" si="162"/>
+        <f t="shared" si="159"/>
         <v>-0.21752265861027198</v>
       </c>
       <c r="U29" s="9">
-        <f t="shared" si="162"/>
+        <f t="shared" si="159"/>
         <v>-0.26261319534282013</v>
       </c>
       <c r="V29" s="9">
-        <f t="shared" si="162"/>
+        <f t="shared" si="159"/>
         <v>-8.1830790568654499E-2</v>
       </c>
       <c r="W29" s="9">
-        <f t="shared" ref="W29:W31" si="163">W5/S5-1</f>
+        <f t="shared" ref="W29:W31" si="160">W5/S5-1</f>
         <v>0.26744186046511631</v>
       </c>
       <c r="X29" s="9">
-        <f t="shared" ref="X29:X31" si="164">X5/T5-1</f>
+        <f t="shared" ref="X29:X31" si="161">X5/T5-1</f>
         <v>6.1776061776061875E-2</v>
       </c>
       <c r="Y29" s="9">
-        <f t="shared" ref="Y29:Y31" si="165">Y5/U5-1</f>
+        <f t="shared" ref="Y29:Y31" si="162">Y5/U5-1</f>
         <v>9.8245614035087803E-2</v>
       </c>
       <c r="Z29" s="9">
-        <f t="shared" ref="Z29:Z31" si="166">Z5/V5-1</f>
+        <f t="shared" ref="Z29:Z31" si="163">Z5/V5-1</f>
         <v>-0.42598187311178248</v>
       </c>
       <c r="AA29" s="9">
-        <f t="shared" ref="AA29:AA31" si="167">AA5/W5-1</f>
+        <f t="shared" ref="AA29:AA31" si="164">AA5/W5-1</f>
         <v>-0.3596330275229358</v>
       </c>
       <c r="AB29" s="9">
-        <f t="shared" ref="AB29:AB31" si="168">AB5/X5-1</f>
+        <f t="shared" ref="AB29:AB31" si="165">AB5/X5-1</f>
         <v>-0.30181818181818187</v>
       </c>
       <c r="AC29" s="9">
-        <f t="shared" ref="AC29:AC31" si="169">AC5/Y5-1</f>
+        <f t="shared" ref="AC29:AC31" si="166">AC5/Y5-1</f>
         <v>-0.46325878594249204</v>
       </c>
       <c r="AD29" s="9">
-        <f t="shared" ref="AD29:AD31" si="170">AD5/Z5-1</f>
+        <f t="shared" ref="AD29:AD31" si="167">AD5/Z5-1</f>
         <v>-0.25263157894736843</v>
       </c>
       <c r="AE29" s="9">
-        <f t="shared" ref="AE29:AE31" si="171">AE5/AA5-1</f>
+        <f t="shared" ref="AE29:AE31" si="168">AE5/AA5-1</f>
         <v>-0.15472779369627498</v>
       </c>
       <c r="AF29" s="9">
-        <f t="shared" ref="AF29:AF31" si="172">AF5/AB5-1</f>
+        <f t="shared" ref="AF29:AF31" si="169">AF5/AB5-1</f>
         <v>2.0833333333333481E-2</v>
       </c>
       <c r="AG29" s="9">
-        <f t="shared" ref="AG29:AG31" si="173">AG5/AC5-1</f>
+        <f t="shared" ref="AG29:AG31" si="170">AG5/AC5-1</f>
         <v>0.25</v>
       </c>
       <c r="AH29" s="9">
-        <f t="shared" ref="AH29:AH31" si="174">AH5/AD5-1</f>
+        <f t="shared" ref="AH29:AH31" si="171">AH5/AD5-1</f>
         <v>0.2640845070422535</v>
       </c>
       <c r="AI29" s="9">
+        <f t="shared" si="141"/>
+        <v>-0.33220338983050846</v>
+      </c>
+      <c r="AJ29" s="9">
+        <f t="shared" si="142"/>
+        <v>-0.49744897959183676</v>
+      </c>
+      <c r="AK29" s="9">
+        <f t="shared" si="143"/>
+        <v>-0.5</v>
+      </c>
+      <c r="AL29" s="9">
         <f t="shared" si="144"/>
-        <v>-0.33220338983050846</v>
-      </c>
-      <c r="AJ29" s="9">
-        <f t="shared" si="145"/>
-        <v>-2.3290816326530739E-2</v>
-      </c>
-      <c r="AK29" s="9">
-        <f t="shared" si="146"/>
-        <v>-3.9285714285716145E-3</v>
-      </c>
-      <c r="AL29" s="9">
-        <f t="shared" si="147"/>
-        <v>-2.3147632311977806E-2</v>
+        <v>-0.41504178272980496</v>
       </c>
       <c r="AN29" s="9"/>
       <c r="AO29" s="9">
-        <f t="shared" si="148"/>
+        <f t="shared" si="145"/>
         <v>-0.13601532567049812</v>
       </c>
       <c r="AP29" s="9">
-        <f t="shared" si="148"/>
+        <f t="shared" si="145"/>
         <v>0.13968957871396892</v>
       </c>
       <c r="AQ29" s="9">
-        <f t="shared" si="148"/>
+        <f t="shared" si="145"/>
         <v>0.66018158236057056</v>
       </c>
       <c r="AR29" s="9">
-        <f t="shared" si="148"/>
+        <f t="shared" si="145"/>
         <v>-0.14843749999999989</v>
       </c>
       <c r="AS29" s="9">
-        <f t="shared" si="148"/>
+        <f t="shared" si="145"/>
         <v>-3.6238532110091759E-2</v>
       </c>
       <c r="AT29" s="9">
-        <f t="shared" si="148"/>
+        <f t="shared" si="145"/>
         <v>-0.35602094240837689</v>
       </c>
       <c r="AU29" s="9">
-        <f t="shared" si="148"/>
+        <f t="shared" si="145"/>
         <v>8.3518107908351569E-2</v>
       </c>
       <c r="AV29" s="9">
-        <f t="shared" si="148"/>
-        <v>-7.9870395634379143E-2</v>
+        <f t="shared" si="145"/>
+        <v>-0.44474761255115969</v>
       </c>
       <c r="AW29" s="9">
-        <f t="shared" si="148"/>
-        <v>0.11960212319576535</v>
+        <f t="shared" si="145"/>
+        <v>0.13371007371007382</v>
       </c>
       <c r="AX29" s="9">
-        <f t="shared" si="148"/>
-        <v>8.1218168605373009E-2</v>
+        <f t="shared" si="145"/>
+        <v>9.0060248797191322E-2</v>
       </c>
       <c r="AY29" s="9">
-        <f t="shared" si="148"/>
-        <v>6.5813690442577455E-2</v>
+        <f t="shared" si="145"/>
+        <v>7.2553197411564518E-2</v>
       </c>
       <c r="AZ29" s="9">
-        <f t="shared" si="148"/>
-        <v>4.0869128025226686E-2</v>
+        <f t="shared" si="145"/>
+        <v>4.5237059953767034E-2</v>
       </c>
       <c r="BA29" s="9">
-        <f t="shared" si="148"/>
-        <v>3.2631223030544332E-2</v>
+        <f t="shared" si="145"/>
+        <v>3.6172284936957011E-2</v>
       </c>
       <c r="BB29" s="9">
-        <f t="shared" ref="BB29:BB31" si="175">BB5/BA5-1</f>
-        <v>2.4172329491070066E-2</v>
+        <f t="shared" ref="BB29:BB31" si="172">BB5/BA5-1</f>
+        <v>2.6983158740174984E-2</v>
       </c>
       <c r="BC29" s="9">
-        <f t="shared" ref="BC29:BC31" si="176">BC5/BB5-1</f>
-        <v>1.5538940520613886E-2</v>
+        <f t="shared" ref="BC29:BC31" si="173">BC5/BB5-1</f>
+        <v>1.7696940278354223E-2</v>
       </c>
       <c r="BD29" s="9">
-        <f t="shared" ref="BD29:BD31" si="177">BD5/BC5-1</f>
-        <v>1.5695055979284112E-2</v>
+        <f t="shared" ref="BD29:BD31" si="174">BD5/BC5-1</f>
+        <v>1.7782248881877072E-2</v>
       </c>
       <c r="BE29" s="9">
-        <f t="shared" ref="BE29:BE31" si="178">BE5/BD5-1</f>
-        <v>1.5846346681057666E-2</v>
+        <f t="shared" ref="BE29:BE31" si="175">BE5/BD5-1</f>
+        <v>1.7864576535749022E-2</v>
       </c>
       <c r="BF29" s="9">
-        <f t="shared" ref="BF29:BF31" si="179">BF5/BE5-1</f>
-        <v>1.5992917368002901E-2</v>
+        <f t="shared" ref="BF29:BF31" si="176">BF5/BE5-1</f>
+        <v>1.7944014318595825E-2</v>
       </c>
     </row>
     <row r="30" spans="2:168" x14ac:dyDescent="0.3">
@@ -6524,200 +6509,200 @@
         <v>7.8313253012048056E-2</v>
       </c>
       <c r="H30" s="9">
-        <f t="shared" ref="H30:R30" si="180">H6/D6-1</f>
+        <f t="shared" ref="H30:R30" si="177">H6/D6-1</f>
         <v>3.5928143712574911E-2</v>
       </c>
       <c r="I30" s="9">
-        <f t="shared" si="180"/>
+        <f t="shared" si="177"/>
         <v>8.8435374149659962E-2</v>
       </c>
       <c r="J30" s="9">
-        <f t="shared" si="180"/>
+        <f t="shared" si="177"/>
         <v>8.1081081081080919E-2</v>
       </c>
       <c r="K30" s="9">
-        <f t="shared" si="180"/>
+        <f t="shared" si="177"/>
         <v>-0.11731843575418988</v>
       </c>
       <c r="L30" s="9">
-        <f t="shared" si="180"/>
+        <f t="shared" si="177"/>
         <v>-7.5144508670520249E-2</v>
       </c>
       <c r="M30" s="9">
-        <f t="shared" si="180"/>
+        <f t="shared" si="177"/>
         <v>5.0000000000000044E-2</v>
       </c>
       <c r="N30" s="9">
-        <f t="shared" si="180"/>
+        <f t="shared" si="177"/>
         <v>5.6249999999999911E-2</v>
       </c>
       <c r="O30" s="9">
-        <f t="shared" si="180"/>
+        <f t="shared" si="177"/>
         <v>4.4303797468354444E-2</v>
       </c>
       <c r="P30" s="9">
-        <f t="shared" si="180"/>
+        <f t="shared" si="177"/>
         <v>-9.9999999999999978E-2</v>
       </c>
       <c r="Q30" s="9">
-        <f t="shared" si="180"/>
+        <f t="shared" si="177"/>
         <v>-0.23214285714285721</v>
       </c>
       <c r="R30" s="9">
-        <f t="shared" si="180"/>
+        <f t="shared" si="177"/>
         <v>-0.17159763313609455</v>
       </c>
       <c r="S30" s="9">
+        <f t="shared" si="159"/>
+        <v>-0.11515151515151523</v>
+      </c>
+      <c r="T30" s="9">
+        <f t="shared" si="159"/>
+        <v>-3.472222222222221E-2</v>
+      </c>
+      <c r="U30" s="9">
+        <f t="shared" si="159"/>
+        <v>-0.28682170542635665</v>
+      </c>
+      <c r="V30" s="9">
+        <f t="shared" si="159"/>
+        <v>-0.52142857142857135</v>
+      </c>
+      <c r="W30" s="9">
+        <f t="shared" si="160"/>
+        <v>-0.52739726027397249</v>
+      </c>
+      <c r="X30" s="9">
+        <f t="shared" si="161"/>
+        <v>-0.51798561151079137</v>
+      </c>
+      <c r="Y30" s="9">
         <f t="shared" si="162"/>
-        <v>-0.11515151515151523</v>
-      </c>
-      <c r="T30" s="9">
-        <f t="shared" si="162"/>
-        <v>-3.472222222222221E-2</v>
-      </c>
-      <c r="U30" s="9">
-        <f t="shared" si="162"/>
-        <v>-0.28682170542635665</v>
-      </c>
-      <c r="V30" s="9">
-        <f t="shared" si="162"/>
-        <v>-0.52142857142857135</v>
-      </c>
-      <c r="W30" s="9">
+        <v>-0.29347826086956519</v>
+      </c>
+      <c r="Z30" s="9">
         <f t="shared" si="163"/>
-        <v>-0.52739726027397249</v>
-      </c>
-      <c r="X30" s="9">
+        <v>1.2388059701492535</v>
+      </c>
+      <c r="AA30" s="9">
         <f t="shared" si="164"/>
-        <v>-0.51798561151079137</v>
-      </c>
-      <c r="Y30" s="9">
+        <v>1.3043478260869565</v>
+      </c>
+      <c r="AB30" s="9">
         <f t="shared" si="165"/>
-        <v>-0.29347826086956519</v>
-      </c>
-      <c r="Z30" s="9">
+        <v>1.2686567164179103</v>
+      </c>
+      <c r="AC30" s="9">
         <f t="shared" si="166"/>
-        <v>1.2388059701492535</v>
-      </c>
-      <c r="AA30" s="9">
+        <v>0.10769230769230775</v>
+      </c>
+      <c r="AD30" s="9">
         <f t="shared" si="167"/>
-        <v>1.3043478260869565</v>
-      </c>
-      <c r="AB30" s="9">
+        <v>-4.6666666666666634E-2</v>
+      </c>
+      <c r="AE30" s="9">
         <f t="shared" si="168"/>
-        <v>1.2686567164179103</v>
-      </c>
-      <c r="AC30" s="9">
+        <v>-1.8867924528301883E-2</v>
+      </c>
+      <c r="AF30" s="9">
         <f t="shared" si="169"/>
-        <v>0.10769230769230775</v>
-      </c>
-      <c r="AD30" s="9">
+        <v>0.31578947368421062</v>
+      </c>
+      <c r="AG30" s="9">
         <f t="shared" si="170"/>
-        <v>-4.6666666666666634E-2</v>
-      </c>
-      <c r="AE30" s="9">
+        <v>0.66666666666666652</v>
+      </c>
+      <c r="AH30" s="9">
         <f t="shared" si="171"/>
-        <v>-1.8867924528301883E-2</v>
-      </c>
-      <c r="AF30" s="9">
-        <f t="shared" si="172"/>
-        <v>0.31578947368421062</v>
-      </c>
-      <c r="AG30" s="9">
-        <f t="shared" si="173"/>
-        <v>0.66666666666666652</v>
-      </c>
-      <c r="AH30" s="9">
-        <f t="shared" si="174"/>
         <v>-0.14685314685314699</v>
       </c>
       <c r="AI30" s="9">
+        <f t="shared" si="141"/>
+        <v>-0.23076923076923073</v>
+      </c>
+      <c r="AJ30" s="9">
+        <f t="shared" si="142"/>
+        <v>-0.4</v>
+      </c>
+      <c r="AK30" s="9">
+        <f t="shared" si="143"/>
+        <v>0.10000000000000009</v>
+      </c>
+      <c r="AL30" s="9">
         <f t="shared" si="144"/>
-        <v>-0.23076923076923073</v>
-      </c>
-      <c r="AJ30" s="9">
-        <f t="shared" si="145"/>
-        <v>-0.4</v>
-      </c>
-      <c r="AK30" s="9">
-        <f t="shared" si="146"/>
-        <v>0.10000000000000009</v>
-      </c>
-      <c r="AL30" s="9">
-        <f t="shared" si="147"/>
         <v>0.10000000000000009</v>
       </c>
       <c r="AN30" s="9"/>
       <c r="AO30" s="9">
-        <f t="shared" si="148"/>
+        <f t="shared" si="145"/>
         <v>7.0063694267515908E-2</v>
       </c>
       <c r="AP30" s="9">
-        <f t="shared" si="148"/>
+        <f t="shared" si="145"/>
         <v>-2.5297619047619069E-2</v>
       </c>
       <c r="AQ30" s="9">
-        <f t="shared" si="148"/>
+        <f t="shared" si="145"/>
         <v>-0.11755725190839694</v>
       </c>
       <c r="AR30" s="9">
-        <f t="shared" si="148"/>
+        <f t="shared" si="145"/>
         <v>-0.23183391003460196</v>
       </c>
       <c r="AS30" s="9">
-        <f t="shared" si="148"/>
+        <f t="shared" si="145"/>
         <v>-0.20945945945945954</v>
       </c>
       <c r="AT30" s="9">
-        <f t="shared" si="148"/>
+        <f t="shared" si="145"/>
         <v>0.49857549857549865</v>
       </c>
       <c r="AU30" s="9">
-        <f t="shared" si="148"/>
+        <f t="shared" si="145"/>
         <v>0.13688212927756638</v>
       </c>
       <c r="AV30" s="9">
-        <f t="shared" si="148"/>
+        <f t="shared" si="145"/>
         <v>-0.15351170568561856</v>
       </c>
       <c r="AW30" s="9">
-        <f t="shared" si="148"/>
-        <v>0.1399999999999999</v>
+        <f t="shared" si="145"/>
+        <v>0.14999999999999991</v>
       </c>
       <c r="AX30" s="9">
-        <f t="shared" si="148"/>
-        <v>7.0000000000000062E-2</v>
+        <f t="shared" si="145"/>
+        <v>9.000000000000008E-2</v>
       </c>
       <c r="AY30" s="9">
-        <f t="shared" si="148"/>
-        <v>4.0000000000000036E-2</v>
+        <f t="shared" si="145"/>
+        <v>6.0000000000000053E-2</v>
       </c>
       <c r="AZ30" s="9">
-        <f t="shared" si="148"/>
+        <f t="shared" si="145"/>
+        <v>5.0000000000000044E-2</v>
+      </c>
+      <c r="BA30" s="9">
+        <f t="shared" si="145"/>
         <v>3.0000000000000027E-2</v>
       </c>
-      <c r="BA30" s="9">
-        <f t="shared" si="148"/>
+      <c r="BB30" s="9">
+        <f t="shared" si="172"/>
         <v>2.0000000000000018E-2</v>
       </c>
-      <c r="BB30" s="9">
+      <c r="BC30" s="9">
+        <f t="shared" si="173"/>
+        <v>2.0000000000000018E-2</v>
+      </c>
+      <c r="BD30" s="9">
+        <f t="shared" si="174"/>
+        <v>2.0000000000000018E-2</v>
+      </c>
+      <c r="BE30" s="9">
         <f t="shared" si="175"/>
         <v>2.0000000000000018E-2</v>
       </c>
-      <c r="BC30" s="9">
+      <c r="BF30" s="9">
         <f t="shared" si="176"/>
-        <v>2.0000000000000018E-2</v>
-      </c>
-      <c r="BD30" s="9">
-        <f t="shared" si="177"/>
-        <v>2.0000000000000018E-2</v>
-      </c>
-      <c r="BE30" s="9">
-        <f t="shared" si="178"/>
-        <v>2.0000000000000018E-2</v>
-      </c>
-      <c r="BF30" s="9">
-        <f t="shared" si="179"/>
         <v>2.0000000000000018E-2</v>
       </c>
     </row>
@@ -6730,128 +6715,128 @@
         <v>-0.15523465703971118</v>
       </c>
       <c r="H31" s="9">
-        <f t="shared" ref="H31:R31" si="181">H7/D7-1</f>
+        <f t="shared" ref="H31:R31" si="178">H7/D7-1</f>
         <v>-0.1819699499165276</v>
       </c>
       <c r="I31" s="9">
-        <f t="shared" si="181"/>
+        <f t="shared" si="178"/>
         <v>-0.12</v>
       </c>
       <c r="J31" s="9">
-        <f t="shared" si="181"/>
+        <f t="shared" si="178"/>
         <v>0.20386266094420602</v>
       </c>
       <c r="K31" s="9">
-        <f t="shared" si="181"/>
+        <f t="shared" si="178"/>
         <v>3.8461538461538325E-2</v>
       </c>
       <c r="L31" s="9">
-        <f t="shared" si="181"/>
+        <f t="shared" si="178"/>
         <v>0.14285714285714279</v>
       </c>
       <c r="M31" s="9">
-        <f t="shared" si="181"/>
+        <f t="shared" si="178"/>
         <v>0.23913043478260865</v>
       </c>
       <c r="N31" s="9">
-        <f t="shared" si="181"/>
+        <f t="shared" si="178"/>
         <v>-6.5953654188948385E-2</v>
       </c>
       <c r="O31" s="9">
-        <f t="shared" si="181"/>
+        <f t="shared" si="178"/>
         <v>0.17078189300411539</v>
       </c>
       <c r="P31" s="9">
-        <f t="shared" si="181"/>
+        <f t="shared" si="178"/>
         <v>0.4392857142857145</v>
       </c>
       <c r="Q31" s="9">
-        <f t="shared" si="181"/>
+        <f t="shared" si="178"/>
         <v>0.43859649122807021</v>
       </c>
       <c r="R31" s="9">
-        <f t="shared" si="181"/>
+        <f t="shared" si="178"/>
         <v>0.64312977099236646</v>
       </c>
       <c r="S31" s="9">
+        <f t="shared" si="159"/>
+        <v>1.2302284710017597E-2</v>
+      </c>
+      <c r="T31" s="9">
+        <f t="shared" si="159"/>
+        <v>-0.18486352357320102</v>
+      </c>
+      <c r="U31" s="9">
+        <f t="shared" si="159"/>
+        <v>-0.26607538802660757</v>
+      </c>
+      <c r="V31" s="9">
+        <f t="shared" si="159"/>
+        <v>-0.15331010452961658</v>
+      </c>
+      <c r="W31" s="9">
+        <f t="shared" si="160"/>
+        <v>6.5972222222222099E-2</v>
+      </c>
+      <c r="X31" s="9">
+        <f t="shared" si="161"/>
+        <v>-6.0882800608828003E-2</v>
+      </c>
+      <c r="Y31" s="9">
         <f t="shared" si="162"/>
-        <v>1.2302284710017597E-2</v>
-      </c>
-      <c r="T31" s="9">
-        <f t="shared" si="162"/>
-        <v>-0.18486352357320102</v>
-      </c>
-      <c r="U31" s="9">
-        <f t="shared" si="162"/>
-        <v>-0.26607538802660757</v>
-      </c>
-      <c r="V31" s="9">
-        <f t="shared" si="162"/>
-        <v>-0.15331010452961658</v>
-      </c>
-      <c r="W31" s="9">
+        <v>4.3806646525679671E-2</v>
+      </c>
+      <c r="Z31" s="9">
         <f t="shared" si="163"/>
-        <v>6.5972222222222099E-2</v>
-      </c>
-      <c r="X31" s="9">
+        <v>-0.27297668038408784</v>
+      </c>
+      <c r="AA31" s="9">
         <f t="shared" si="164"/>
-        <v>-6.0882800608828003E-2</v>
-      </c>
-      <c r="Y31" s="9">
+        <v>-0.17263843648208477</v>
+      </c>
+      <c r="AB31" s="9">
         <f t="shared" si="165"/>
-        <v>4.3806646525679671E-2</v>
-      </c>
-      <c r="Z31" s="9">
+        <v>-0.13128038897893046</v>
+      </c>
+      <c r="AC31" s="9">
         <f t="shared" si="166"/>
-        <v>-0.27297668038408784</v>
-      </c>
-      <c r="AA31" s="9">
+        <v>-0.40955137481910264</v>
+      </c>
+      <c r="AD31" s="9">
         <f t="shared" si="167"/>
-        <v>-0.17263843648208477</v>
-      </c>
-      <c r="AB31" s="9">
+        <v>-0.19433962264150939</v>
+      </c>
+      <c r="AE31" s="9">
         <f t="shared" si="168"/>
-        <v>-0.13128038897893046</v>
-      </c>
-      <c r="AC31" s="9">
+        <v>-0.11220472440944873</v>
+      </c>
+      <c r="AF31" s="9">
         <f t="shared" si="169"/>
-        <v>-0.40955137481910264</v>
-      </c>
-      <c r="AD31" s="9">
+        <v>0.10447761194029859</v>
+      </c>
+      <c r="AG31" s="9">
         <f t="shared" si="170"/>
-        <v>-0.19433962264150939</v>
-      </c>
-      <c r="AE31" s="9">
+        <v>0.32352941176470584</v>
+      </c>
+      <c r="AH31" s="9">
         <f t="shared" si="171"/>
-        <v>-0.11220472440944873</v>
-      </c>
-      <c r="AF31" s="9">
-        <f t="shared" si="172"/>
-        <v>0.10447761194029859</v>
-      </c>
-      <c r="AG31" s="9">
-        <f t="shared" si="173"/>
-        <v>0.32352941176470584</v>
-      </c>
-      <c r="AH31" s="9">
-        <f t="shared" si="174"/>
         <v>0.12646370023419173</v>
       </c>
       <c r="AI31" s="9">
+        <f t="shared" si="141"/>
+        <v>-0.29711751662971175</v>
+      </c>
+      <c r="AJ31" s="9">
+        <f t="shared" si="142"/>
+        <v>-0.46452702702702708</v>
+      </c>
+      <c r="AK31" s="9">
+        <f t="shared" si="143"/>
+        <v>-0.36666666666666659</v>
+      </c>
+      <c r="AL31" s="9">
         <f t="shared" si="144"/>
-        <v>-0.29711751662971175</v>
-      </c>
-      <c r="AJ31" s="9">
-        <f t="shared" si="145"/>
-        <v>-0.15055743243243247</v>
-      </c>
-      <c r="AK31" s="9">
-        <f t="shared" si="146"/>
-        <v>1.9166666666666554E-2</v>
-      </c>
-      <c r="AL31" s="9">
-        <f t="shared" si="147"/>
-        <v>8.0873180873182182E-3</v>
+        <v>-0.28440748440748431</v>
       </c>
       <c r="AN31" s="9"/>
       <c r="AO31" s="9">
@@ -6859,72 +6844,72 @@
         <v>-7.70282588878759E-2</v>
       </c>
       <c r="AP31" s="9">
-        <f t="shared" ref="AP31:BA31" si="182">AP7/AO7-1</f>
+        <f t="shared" ref="AP31:BA31" si="179">AP7/AO7-1</f>
         <v>8.4938271604938276E-2</v>
       </c>
       <c r="AQ31" s="9">
-        <f t="shared" si="182"/>
+        <f t="shared" si="179"/>
         <v>0.4283113336367772</v>
       </c>
       <c r="AR31" s="9">
-        <f t="shared" si="182"/>
+        <f t="shared" si="179"/>
         <v>-0.16379859783301465</v>
       </c>
       <c r="AS31" s="9">
-        <f t="shared" si="182"/>
+        <f t="shared" si="179"/>
         <v>-6.5548780487804881E-2</v>
       </c>
       <c r="AT31" s="9">
-        <f t="shared" si="182"/>
+        <f t="shared" si="179"/>
         <v>-0.23368678629690032</v>
       </c>
       <c r="AU31" s="9">
-        <f t="shared" si="182"/>
+        <f t="shared" si="179"/>
         <v>9.8456625864821401E-2</v>
       </c>
       <c r="AV31" s="9">
-        <f t="shared" si="182"/>
-        <v>-0.10120639534883702</v>
+        <f t="shared" si="179"/>
+        <v>-0.36036821705426358</v>
       </c>
       <c r="AW31" s="9">
-        <f t="shared" si="182"/>
-        <v>0.1251680493340015</v>
+        <f t="shared" si="179"/>
+        <v>0.13995606726253595</v>
       </c>
       <c r="AX31" s="9">
-        <f t="shared" si="182"/>
-        <v>7.8116739220159159E-2</v>
+        <f t="shared" si="179"/>
+        <v>9.0036944258025109E-2</v>
       </c>
       <c r="AY31" s="9">
-        <f t="shared" si="182"/>
-        <v>5.8730840830626629E-2</v>
+        <f t="shared" si="179"/>
+        <v>6.769772179717215E-2</v>
       </c>
       <c r="AZ31" s="9">
-        <f t="shared" si="182"/>
-        <v>3.7939581482140605E-2</v>
+        <f t="shared" si="179"/>
+        <v>4.7066044697087195E-2</v>
       </c>
       <c r="BA31" s="9">
-        <f t="shared" si="182"/>
-        <v>2.9252782704356717E-2</v>
+        <f t="shared" si="179"/>
+        <v>3.3795465679679948E-2</v>
       </c>
       <c r="BB31" s="9">
+        <f t="shared" si="172"/>
+        <v>2.4303961376923366E-2</v>
+      </c>
+      <c r="BC31" s="9">
+        <f t="shared" si="173"/>
+        <v>1.8576832162851442E-2</v>
+      </c>
+      <c r="BD31" s="9">
+        <f t="shared" si="174"/>
+        <v>1.8630732178107845E-2</v>
+      </c>
+      <c r="BE31" s="9">
         <f t="shared" si="175"/>
-        <v>2.3066399671503701E-2</v>
-      </c>
-      <c r="BC31" s="9">
+        <v>1.8682660533336781E-2</v>
+      </c>
+      <c r="BF31" s="9">
         <f t="shared" si="176"/>
-        <v>1.6717857804092962E-2</v>
-      </c>
-      <c r="BD31" s="9">
-        <f t="shared" si="177"/>
-        <v>1.6836389439508936E-2</v>
-      </c>
-      <c r="BE31" s="9">
-        <f t="shared" si="178"/>
-        <v>1.6950995871626517E-2</v>
-      </c>
-      <c r="BF31" s="9">
-        <f t="shared" si="179"/>
-        <v>1.7061781680792976E-2</v>
+        <v>1.8732684154401991E-2</v>
       </c>
     </row>
     <row r="32" spans="2:168" x14ac:dyDescent="0.3">
@@ -6936,220 +6921,220 @@
         <v>0.17525773195876282</v>
       </c>
       <c r="D32" s="9">
-        <f t="shared" ref="D32:R32" si="183">(D5-D8)/D5</f>
+        <f t="shared" ref="D32:R32" si="180">(D5-D8)/D5</f>
         <v>0.17592592592592596</v>
       </c>
       <c r="E32" s="9">
+        <f t="shared" si="180"/>
+        <v>0.12850467289719628</v>
+      </c>
+      <c r="F32" s="9">
+        <f t="shared" si="180"/>
+        <v>0.16037735849056609</v>
+      </c>
+      <c r="G32" s="9">
+        <f t="shared" si="180"/>
+        <v>0.17647058823529405</v>
+      </c>
+      <c r="H32" s="9">
+        <f t="shared" si="180"/>
+        <v>0.22397476340694</v>
+      </c>
+      <c r="I32" s="9">
+        <f t="shared" si="180"/>
+        <v>0.22543352601156069</v>
+      </c>
+      <c r="J32" s="9">
+        <f t="shared" si="180"/>
+        <v>0.24688279301745641</v>
+      </c>
+      <c r="K32" s="9">
+        <f t="shared" si="180"/>
+        <v>0.15853658536585355</v>
+      </c>
+      <c r="L32" s="9">
+        <f t="shared" si="180"/>
+        <v>0.15</v>
+      </c>
+      <c r="M32" s="9">
+        <f t="shared" si="180"/>
+        <v>0.17429193899782136</v>
+      </c>
+      <c r="N32" s="9">
+        <f t="shared" si="180"/>
+        <v>0.14084507042253522</v>
+      </c>
+      <c r="O32" s="9">
+        <f t="shared" si="180"/>
+        <v>0.18564356435643564</v>
+      </c>
+      <c r="P32" s="9">
+        <f t="shared" si="180"/>
+        <v>0.19637462235649547</v>
+      </c>
+      <c r="Q32" s="9">
+        <f t="shared" si="180"/>
+        <v>0.22250970245795598</v>
+      </c>
+      <c r="R32" s="9">
+        <f t="shared" si="180"/>
+        <v>0.25104022191400827</v>
+      </c>
+      <c r="S32" s="9">
+        <f t="shared" ref="S32:V33" si="181">(S5-S8)/S5</f>
+        <v>0.2232558139534884</v>
+      </c>
+      <c r="T32" s="9">
+        <f t="shared" si="181"/>
+        <v>0.23359073359073348</v>
+      </c>
+      <c r="U32" s="9">
+        <f t="shared" si="181"/>
+        <v>0.2350877192982456</v>
+      </c>
+      <c r="V32" s="9">
+        <f t="shared" si="181"/>
+        <v>0.21752265861027198</v>
+      </c>
+      <c r="W32" s="9">
+        <f t="shared" ref="W32:AH32" si="182">(W5-W8)/W5</f>
+        <v>0.21284403669724775</v>
+      </c>
+      <c r="X32" s="9">
+        <f t="shared" si="182"/>
+        <v>0.25999999999999995</v>
+      </c>
+      <c r="Y32" s="9">
+        <f t="shared" si="182"/>
+        <v>0.2300319488817891</v>
+      </c>
+      <c r="Z32" s="9">
+        <f t="shared" si="182"/>
+        <v>0.13157894736842105</v>
+      </c>
+      <c r="AA32" s="9">
+        <f t="shared" si="182"/>
+        <v>0.19770773638968478</v>
+      </c>
+      <c r="AB32" s="9">
+        <f t="shared" si="182"/>
+        <v>0.20312499999999994</v>
+      </c>
+      <c r="AC32" s="9">
+        <f t="shared" si="182"/>
+        <v>-0.29761904761904762</v>
+      </c>
+      <c r="AD32" s="9">
+        <f t="shared" si="182"/>
+        <v>8.4507042253521084E-2</v>
+      </c>
+      <c r="AE32" s="9">
+        <f t="shared" si="182"/>
+        <v>0.23050847457627122</v>
+      </c>
+      <c r="AF32" s="9">
+        <f t="shared" si="182"/>
+        <v>0.22193877551020413</v>
+      </c>
+      <c r="AG32" s="9">
+        <f t="shared" si="182"/>
+        <v>0.19999999999999996</v>
+      </c>
+      <c r="AH32" s="9">
+        <f t="shared" si="182"/>
+        <v>0.20334261838440104</v>
+      </c>
+      <c r="AI32" s="9">
+        <f t="shared" ref="AI32:AL32" si="183">(AI5-AI8)/AI5</f>
+        <v>0.21827411167512686</v>
+      </c>
+      <c r="AJ32" s="9">
         <f t="shared" si="183"/>
-        <v>0.12850467289719628</v>
-      </c>
-      <c r="F32" s="9">
+        <v>0.21827411167512686</v>
+      </c>
+      <c r="AK32" s="9">
         <f t="shared" si="183"/>
-        <v>0.16037735849056609</v>
-      </c>
-      <c r="G32" s="9">
+        <v>0.19999999999999996</v>
+      </c>
+      <c r="AL32" s="9">
         <f t="shared" si="183"/>
-        <v>0.17647058823529405</v>
-      </c>
-      <c r="H32" s="9">
-        <f t="shared" si="183"/>
-        <v>0.22397476340694</v>
-      </c>
-      <c r="I32" s="9">
-        <f t="shared" si="183"/>
-        <v>0.22543352601156069</v>
-      </c>
-      <c r="J32" s="9">
-        <f t="shared" si="183"/>
-        <v>0.24688279301745641</v>
-      </c>
-      <c r="K32" s="9">
-        <f t="shared" si="183"/>
-        <v>0.15853658536585355</v>
-      </c>
-      <c r="L32" s="9">
-        <f t="shared" si="183"/>
-        <v>0.15</v>
-      </c>
-      <c r="M32" s="9">
-        <f t="shared" si="183"/>
-        <v>0.17429193899782136</v>
-      </c>
-      <c r="N32" s="9">
-        <f t="shared" si="183"/>
-        <v>0.14084507042253522</v>
-      </c>
-      <c r="O32" s="9">
-        <f t="shared" si="183"/>
-        <v>0.18564356435643564</v>
-      </c>
-      <c r="P32" s="9">
-        <f t="shared" si="183"/>
-        <v>0.19637462235649547</v>
-      </c>
-      <c r="Q32" s="9">
-        <f t="shared" si="183"/>
-        <v>0.22250970245795598</v>
-      </c>
-      <c r="R32" s="9">
-        <f t="shared" si="183"/>
-        <v>0.25104022191400827</v>
-      </c>
-      <c r="S32" s="9">
-        <f t="shared" ref="S32:V33" si="184">(S5-S8)/S5</f>
-        <v>0.2232558139534884</v>
-      </c>
-      <c r="T32" s="9">
+        <v>0.19999999999999996</v>
+      </c>
+      <c r="AN32" s="9">
+        <f t="shared" ref="AN32:BA32" si="184">(AN5-AN8)/AN5</f>
+        <v>0.15964240102171137</v>
+      </c>
+      <c r="AO32" s="9">
         <f t="shared" si="184"/>
-        <v>0.23359073359073348</v>
-      </c>
-      <c r="U32" s="9">
+        <v>0.22099039172209889</v>
+      </c>
+      <c r="AP32" s="9">
         <f t="shared" si="184"/>
-        <v>0.2350877192982456</v>
-      </c>
-      <c r="V32" s="9">
+        <v>0.15693904020752264</v>
+      </c>
+      <c r="AQ32" s="9">
         <f t="shared" si="184"/>
-        <v>0.21752265861027198</v>
-      </c>
-      <c r="W32" s="9">
-        <f t="shared" ref="W32:AH32" si="185">(W5-W8)/W5</f>
-        <v>0.21284403669724775</v>
-      </c>
-      <c r="X32" s="9">
+        <v>0.21796874999999996</v>
+      </c>
+      <c r="AR32" s="9">
+        <f t="shared" si="184"/>
+        <v>0.22706422018348624</v>
+      </c>
+      <c r="AS32" s="9">
+        <f t="shared" si="184"/>
+        <v>0.2156116135173726</v>
+      </c>
+      <c r="AT32" s="9">
+        <f t="shared" si="184"/>
+        <v>5.2475979305247764E-2</v>
+      </c>
+      <c r="AU32" s="9">
+        <f t="shared" si="184"/>
+        <v>0.21282401091405176</v>
+      </c>
+      <c r="AV32" s="9">
+        <f t="shared" si="184"/>
+        <v>0.20884520884520869</v>
+      </c>
+      <c r="AW32" s="9">
+        <f t="shared" si="184"/>
+        <v>0.20999999999999996</v>
+      </c>
+      <c r="AX32" s="9">
+        <f t="shared" si="184"/>
+        <v>0.20999999999999996</v>
+      </c>
+      <c r="AY32" s="9">
+        <f t="shared" si="184"/>
+        <v>0.20999999999999994</v>
+      </c>
+      <c r="AZ32" s="9">
+        <f t="shared" si="184"/>
+        <v>0.20999999999999991</v>
+      </c>
+      <c r="BA32" s="9">
+        <f t="shared" si="184"/>
+        <v>0.20999999999999994</v>
+      </c>
+      <c r="BB32" s="9">
+        <f t="shared" ref="BB32:BF32" si="185">(BB5-BB8)/BB5</f>
+        <v>0.21</v>
+      </c>
+      <c r="BC32" s="9">
         <f t="shared" si="185"/>
-        <v>0.25999999999999995</v>
-      </c>
-      <c r="Y32" s="9">
+        <v>0.21000000000000002</v>
+      </c>
+      <c r="BD32" s="9">
         <f t="shared" si="185"/>
-        <v>0.2300319488817891</v>
-      </c>
-      <c r="Z32" s="9">
+        <v>0.20999999999999994</v>
+      </c>
+      <c r="BE32" s="9">
         <f t="shared" si="185"/>
-        <v>0.13157894736842105</v>
-      </c>
-      <c r="AA32" s="9">
+        <v>0.20999999999999994</v>
+      </c>
+      <c r="BF32" s="9">
         <f t="shared" si="185"/>
-        <v>0.19770773638968478</v>
-      </c>
-      <c r="AB32" s="9">
-        <f t="shared" si="185"/>
-        <v>0.20312499999999994</v>
-      </c>
-      <c r="AC32" s="9">
-        <f t="shared" si="185"/>
-        <v>-0.29761904761904762</v>
-      </c>
-      <c r="AD32" s="9">
-        <f t="shared" si="185"/>
-        <v>8.4507042253521084E-2</v>
-      </c>
-      <c r="AE32" s="9">
-        <f t="shared" si="185"/>
-        <v>0.23050847457627122</v>
-      </c>
-      <c r="AF32" s="9">
-        <f t="shared" si="185"/>
-        <v>0.22193877551020413</v>
-      </c>
-      <c r="AG32" s="9">
-        <f t="shared" si="185"/>
-        <v>0.19999999999999996</v>
-      </c>
-      <c r="AH32" s="9">
-        <f t="shared" si="185"/>
-        <v>0.20334261838440104</v>
-      </c>
-      <c r="AI32" s="9">
-        <f t="shared" ref="AI32:AL32" si="186">(AI5-AI8)/AI5</f>
-        <v>0.21827411167512686</v>
-      </c>
-      <c r="AJ32" s="9">
-        <f t="shared" si="186"/>
-        <v>0.23</v>
-      </c>
-      <c r="AK32" s="9">
-        <f t="shared" si="186"/>
-        <v>0.19999999999999996</v>
-      </c>
-      <c r="AL32" s="9">
-        <f t="shared" si="186"/>
-        <v>0.19999999999999993</v>
-      </c>
-      <c r="AN32" s="9">
-        <f t="shared" ref="AN32:BA32" si="187">(AN5-AN8)/AN5</f>
-        <v>0.15964240102171137</v>
-      </c>
-      <c r="AO32" s="9">
-        <f t="shared" si="187"/>
-        <v>0.22099039172209889</v>
-      </c>
-      <c r="AP32" s="9">
-        <f t="shared" si="187"/>
-        <v>0.15693904020752264</v>
-      </c>
-      <c r="AQ32" s="9">
-        <f t="shared" si="187"/>
-        <v>0.21796874999999996</v>
-      </c>
-      <c r="AR32" s="9">
-        <f t="shared" si="187"/>
-        <v>0.22706422018348624</v>
-      </c>
-      <c r="AS32" s="9">
-        <f t="shared" si="187"/>
-        <v>0.2156116135173726</v>
-      </c>
-      <c r="AT32" s="9">
-        <f t="shared" si="187"/>
-        <v>5.2475979305247764E-2</v>
-      </c>
-      <c r="AU32" s="9">
-        <f t="shared" si="187"/>
-        <v>0.21282401091405176</v>
-      </c>
-      <c r="AV32" s="9">
-        <f t="shared" si="187"/>
-        <v>0.21118391886782684</v>
-      </c>
-      <c r="AW32" s="9">
-        <f t="shared" si="187"/>
-        <v>0.21</v>
-      </c>
-      <c r="AX32" s="9">
-        <f t="shared" si="187"/>
-        <v>0.21000000000000002</v>
-      </c>
-      <c r="AY32" s="9">
-        <f t="shared" si="187"/>
-        <v>0.21000000000000002</v>
-      </c>
-      <c r="AZ32" s="9">
-        <f t="shared" si="187"/>
-        <v>0.20999999999999996</v>
-      </c>
-      <c r="BA32" s="9">
-        <f t="shared" si="187"/>
         <v>0.20999999999999991</v>
-      </c>
-      <c r="BB32" s="9">
-        <f t="shared" ref="BB32:BF32" si="188">(BB5-BB8)/BB5</f>
-        <v>0.20999999999999996</v>
-      </c>
-      <c r="BC32" s="9">
-        <f t="shared" si="188"/>
-        <v>0.21000000000000002</v>
-      </c>
-      <c r="BD32" s="9">
-        <f t="shared" si="188"/>
-        <v>0.20999999999999991</v>
-      </c>
-      <c r="BE32" s="9">
-        <f t="shared" si="188"/>
-        <v>0.21000000000000002</v>
-      </c>
-      <c r="BF32" s="9">
-        <f t="shared" si="188"/>
-        <v>0.21</v>
       </c>
       <c r="BH32" t="s">
         <v>51</v>
@@ -7167,219 +7152,219 @@
         <v>0.5662650602409639</v>
       </c>
       <c r="D33" s="9">
-        <f t="shared" ref="D33:R33" si="189">(D6-D9)/D6</f>
+        <f t="shared" ref="D33:R33" si="186">(D6-D9)/D6</f>
         <v>0.6586826347305389</v>
       </c>
       <c r="E33" s="9">
+        <f t="shared" si="186"/>
+        <v>0.74149659863945572</v>
+      </c>
+      <c r="F33" s="9">
+        <f t="shared" si="186"/>
+        <v>0.85135135135135143</v>
+      </c>
+      <c r="G33" s="9">
+        <f t="shared" si="186"/>
+        <v>0.61452513966480438</v>
+      </c>
+      <c r="H33" s="9">
+        <f t="shared" si="186"/>
+        <v>0.59537572254335258</v>
+      </c>
+      <c r="I33" s="9">
+        <f t="shared" si="186"/>
+        <v>0.61250000000000004</v>
+      </c>
+      <c r="J33" s="9">
+        <f t="shared" si="186"/>
+        <v>0.61875000000000002</v>
+      </c>
+      <c r="K33" s="9">
+        <f t="shared" si="186"/>
+        <v>0.60759493670886078</v>
+      </c>
+      <c r="L33" s="9">
+        <f t="shared" si="186"/>
+        <v>0.6</v>
+      </c>
+      <c r="M33" s="9">
+        <f t="shared" si="186"/>
+        <v>0.63095238095238104</v>
+      </c>
+      <c r="N33" s="9">
+        <f t="shared" si="186"/>
+        <v>0.5976331360946745</v>
+      </c>
+      <c r="O33" s="9">
+        <f t="shared" si="186"/>
+        <v>0.58787878787878789</v>
+      </c>
+      <c r="P33" s="9">
+        <f t="shared" si="186"/>
+        <v>0.61805555555555558</v>
+      </c>
+      <c r="Q33" s="9">
+        <f t="shared" si="186"/>
+        <v>0.62015503875968991</v>
+      </c>
+      <c r="R33" s="9">
+        <f t="shared" si="186"/>
+        <v>0.6</v>
+      </c>
+      <c r="S33" s="9">
+        <f t="shared" si="181"/>
+        <v>0.60958904109589029</v>
+      </c>
+      <c r="T33" s="9">
+        <f t="shared" si="181"/>
+        <v>0.59712230215827344</v>
+      </c>
+      <c r="U33" s="9">
+        <f t="shared" si="181"/>
+        <v>0.59782608695652173</v>
+      </c>
+      <c r="V33" s="9">
+        <f t="shared" si="181"/>
+        <v>0.56716417910447758</v>
+      </c>
+      <c r="W33" s="9">
+        <f t="shared" ref="W33:AH33" si="187">(W6-W9)/W6</f>
+        <v>0.53623188405797106</v>
+      </c>
+      <c r="X33" s="9">
+        <f t="shared" si="187"/>
+        <v>0.5074626865671642</v>
+      </c>
+      <c r="Y33" s="9">
+        <f t="shared" si="187"/>
+        <v>0.53846153846153844</v>
+      </c>
+      <c r="Z33" s="9">
+        <f t="shared" si="187"/>
+        <v>0.72666666666666668</v>
+      </c>
+      <c r="AA33" s="9">
+        <f t="shared" si="187"/>
+        <v>0.71069182389937113</v>
+      </c>
+      <c r="AB33" s="9">
+        <f t="shared" si="187"/>
+        <v>0.67105263157894735</v>
+      </c>
+      <c r="AC33" s="9">
+        <f t="shared" si="187"/>
+        <v>0.56944444444444442</v>
+      </c>
+      <c r="AD33" s="9">
+        <f t="shared" si="187"/>
+        <v>0.75524475524475521</v>
+      </c>
+      <c r="AE33" s="9">
+        <f t="shared" si="187"/>
+        <v>0.6858974358974359</v>
+      </c>
+      <c r="AF33" s="9">
+        <f t="shared" si="187"/>
+        <v>0.72</v>
+      </c>
+      <c r="AG33" s="9">
+        <f t="shared" si="187"/>
+        <v>0.8666666666666667</v>
+      </c>
+      <c r="AH33" s="9">
+        <f t="shared" si="187"/>
+        <v>0.86885245901639352</v>
+      </c>
+      <c r="AI33" s="9">
+        <f t="shared" ref="AI33:AL33" si="188">(AI6-AI9)/AI6</f>
+        <v>0.89166666666666661</v>
+      </c>
+      <c r="AJ33" s="9">
+        <f t="shared" si="188"/>
+        <v>0.89166666666666661</v>
+      </c>
+      <c r="AK33" s="9">
+        <f t="shared" si="188"/>
+        <v>0.89</v>
+      </c>
+      <c r="AL33" s="9">
+        <f t="shared" si="188"/>
+        <v>0.89</v>
+      </c>
+      <c r="AN33" s="9">
+        <f t="shared" ref="AN33:BA33" si="189">(AN6-AN9)/AN6</f>
+        <v>0.69904458598726116</v>
+      </c>
+      <c r="AO33" s="9">
         <f t="shared" si="189"/>
-        <v>0.74149659863945572</v>
-      </c>
-      <c r="F33" s="9">
+        <v>0.61011904761904756</v>
+      </c>
+      <c r="AP33" s="9">
         <f t="shared" si="189"/>
-        <v>0.85135135135135143</v>
-      </c>
-      <c r="G33" s="9">
+        <v>0.6091603053435114</v>
+      </c>
+      <c r="AQ33" s="9">
         <f t="shared" si="189"/>
-        <v>0.61452513966480438</v>
-      </c>
-      <c r="H33" s="9">
+        <v>0.60553633217993075</v>
+      </c>
+      <c r="AR33" s="9">
         <f t="shared" si="189"/>
-        <v>0.59537572254335258</v>
-      </c>
-      <c r="I33" s="9">
+        <v>0.59684684684684697</v>
+      </c>
+      <c r="AS33" s="9">
         <f t="shared" si="189"/>
-        <v>0.61250000000000004</v>
-      </c>
-      <c r="J33" s="9">
+        <v>0.61253561253561251</v>
+      </c>
+      <c r="AT33" s="9">
         <f t="shared" si="189"/>
-        <v>0.61875000000000002</v>
-      </c>
-      <c r="K33" s="9">
+        <v>0.69201520912547532</v>
+      </c>
+      <c r="AU33" s="9">
         <f t="shared" si="189"/>
-        <v>0.60759493670886078</v>
-      </c>
-      <c r="L33" s="9">
+        <v>0.77090301003344475</v>
+      </c>
+      <c r="AV33" s="9">
         <f t="shared" si="189"/>
-        <v>0.6</v>
-      </c>
-      <c r="M33" s="9">
+        <v>0.89079020150138288</v>
+      </c>
+      <c r="AW33" s="9">
         <f t="shared" si="189"/>
-        <v>0.63095238095238104</v>
-      </c>
-      <c r="N33" s="9">
+        <v>0.75</v>
+      </c>
+      <c r="AX33" s="9">
         <f t="shared" si="189"/>
-        <v>0.5976331360946745</v>
-      </c>
-      <c r="O33" s="9">
+        <v>0.75</v>
+      </c>
+      <c r="AY33" s="9">
         <f t="shared" si="189"/>
-        <v>0.58787878787878789</v>
-      </c>
-      <c r="P33" s="9">
+        <v>0.75</v>
+      </c>
+      <c r="AZ33" s="9">
         <f t="shared" si="189"/>
-        <v>0.61805555555555558</v>
-      </c>
-      <c r="Q33" s="9">
+        <v>0.75</v>
+      </c>
+      <c r="BA33" s="9">
         <f t="shared" si="189"/>
-        <v>0.62015503875968991</v>
-      </c>
-      <c r="R33" s="9">
-        <f t="shared" si="189"/>
-        <v>0.6</v>
-      </c>
-      <c r="S33" s="9">
-        <f t="shared" si="184"/>
-        <v>0.60958904109589029</v>
-      </c>
-      <c r="T33" s="9">
-        <f t="shared" si="184"/>
-        <v>0.59712230215827344</v>
-      </c>
-      <c r="U33" s="9">
-        <f t="shared" si="184"/>
-        <v>0.59782608695652173</v>
-      </c>
-      <c r="V33" s="9">
-        <f t="shared" si="184"/>
-        <v>0.56716417910447758</v>
-      </c>
-      <c r="W33" s="9">
-        <f t="shared" ref="W33:AH33" si="190">(W6-W9)/W6</f>
-        <v>0.53623188405797106</v>
-      </c>
-      <c r="X33" s="9">
+        <v>0.75</v>
+      </c>
+      <c r="BB33" s="9">
+        <f t="shared" ref="BB33:BF33" si="190">(BB6-BB9)/BB6</f>
+        <v>0.75</v>
+      </c>
+      <c r="BC33" s="9">
         <f t="shared" si="190"/>
-        <v>0.5074626865671642</v>
-      </c>
-      <c r="Y33" s="9">
+        <v>0.75</v>
+      </c>
+      <c r="BD33" s="9">
         <f t="shared" si="190"/>
-        <v>0.53846153846153844</v>
-      </c>
-      <c r="Z33" s="9">
+        <v>0.75</v>
+      </c>
+      <c r="BE33" s="9">
         <f t="shared" si="190"/>
-        <v>0.72666666666666668</v>
-      </c>
-      <c r="AA33" s="9">
+        <v>0.75</v>
+      </c>
+      <c r="BF33" s="9">
         <f t="shared" si="190"/>
-        <v>0.71069182389937113</v>
-      </c>
-      <c r="AB33" s="9">
-        <f t="shared" si="190"/>
-        <v>0.67105263157894735</v>
-      </c>
-      <c r="AC33" s="9">
-        <f t="shared" si="190"/>
-        <v>0.56944444444444442</v>
-      </c>
-      <c r="AD33" s="9">
-        <f t="shared" si="190"/>
-        <v>0.75524475524475521</v>
-      </c>
-      <c r="AE33" s="9">
-        <f t="shared" si="190"/>
-        <v>0.6858974358974359</v>
-      </c>
-      <c r="AF33" s="9">
-        <f t="shared" si="190"/>
-        <v>0.72</v>
-      </c>
-      <c r="AG33" s="9">
-        <f t="shared" si="190"/>
-        <v>0.8666666666666667</v>
-      </c>
-      <c r="AH33" s="9">
-        <f t="shared" si="190"/>
-        <v>0.86885245901639352</v>
-      </c>
-      <c r="AI33" s="9">
-        <f t="shared" ref="AI33:AL33" si="191">(AI6-AI9)/AI6</f>
-        <v>0.89166666666666661</v>
-      </c>
-      <c r="AJ33" s="9">
-        <f t="shared" si="191"/>
-        <v>0.87</v>
-      </c>
-      <c r="AK33" s="9">
-        <f t="shared" si="191"/>
-        <v>0.87000000000000011</v>
-      </c>
-      <c r="AL33" s="9">
-        <f t="shared" si="191"/>
-        <v>0.87</v>
-      </c>
-      <c r="AN33" s="9">
-        <f t="shared" ref="AN33:BA33" si="192">(AN6-AN9)/AN6</f>
-        <v>0.69904458598726116</v>
-      </c>
-      <c r="AO33" s="9">
-        <f t="shared" si="192"/>
-        <v>0.61011904761904756</v>
-      </c>
-      <c r="AP33" s="9">
-        <f t="shared" si="192"/>
-        <v>0.6091603053435114</v>
-      </c>
-      <c r="AQ33" s="9">
-        <f t="shared" si="192"/>
-        <v>0.60553633217993075</v>
-      </c>
-      <c r="AR33" s="9">
-        <f t="shared" si="192"/>
-        <v>0.59684684684684697</v>
-      </c>
-      <c r="AS33" s="9">
-        <f t="shared" si="192"/>
-        <v>0.61253561253561251</v>
-      </c>
-      <c r="AT33" s="9">
-        <f t="shared" si="192"/>
-        <v>0.69201520912547532</v>
-      </c>
-      <c r="AU33" s="9">
-        <f t="shared" si="192"/>
-        <v>0.77090301003344475</v>
-      </c>
-      <c r="AV33" s="9">
-        <f t="shared" si="192"/>
-        <v>0.8751363097589886</v>
-      </c>
-      <c r="AW33" s="9">
-        <f t="shared" si="192"/>
-        <v>0.75000000000000011</v>
-      </c>
-      <c r="AX33" s="9">
-        <f t="shared" si="192"/>
-        <v>0.75</v>
-      </c>
-      <c r="AY33" s="9">
-        <f t="shared" si="192"/>
-        <v>0.75</v>
-      </c>
-      <c r="AZ33" s="9">
-        <f t="shared" si="192"/>
-        <v>0.75</v>
-      </c>
-      <c r="BA33" s="9">
-        <f t="shared" si="192"/>
-        <v>0.75</v>
-      </c>
-      <c r="BB33" s="9">
-        <f t="shared" ref="BB33:BF33" si="193">(BB6-BB9)/BB6</f>
-        <v>0.75</v>
-      </c>
-      <c r="BC33" s="9">
-        <f t="shared" si="193"/>
-        <v>0.75</v>
-      </c>
-      <c r="BD33" s="9">
-        <f t="shared" si="193"/>
-        <v>0.75</v>
-      </c>
-      <c r="BE33" s="9">
-        <f t="shared" si="193"/>
-        <v>0.75</v>
-      </c>
-      <c r="BF33" s="9">
-        <f t="shared" si="193"/>
         <v>0.75</v>
       </c>
       <c r="BH33" t="s">
@@ -7398,63 +7383,63 @@
         <v>0.29241877256317683</v>
       </c>
       <c r="D34" s="9">
-        <f t="shared" ref="D34:R34" si="194">D11/D7</f>
+        <f t="shared" ref="D34:R34" si="191">D11/D7</f>
         <v>0.31051752921535891</v>
       </c>
       <c r="E34" s="9">
-        <f t="shared" si="194"/>
+        <f t="shared" si="191"/>
         <v>0.28521739130434792</v>
       </c>
       <c r="F34" s="9">
-        <f t="shared" si="194"/>
+        <f t="shared" si="191"/>
         <v>0.37982832618025758</v>
       </c>
       <c r="G34" s="9">
-        <f t="shared" si="194"/>
+        <f t="shared" si="191"/>
         <v>0.34401709401709391</v>
       </c>
       <c r="H34" s="9">
-        <f t="shared" si="194"/>
+        <f t="shared" si="191"/>
         <v>0.35510204081632651</v>
       </c>
       <c r="I34" s="9">
-        <f t="shared" si="194"/>
+        <f t="shared" si="191"/>
         <v>0.34782608695652178</v>
       </c>
       <c r="J34" s="9">
-        <f t="shared" si="194"/>
+        <f t="shared" si="191"/>
         <v>0.35294117647058831</v>
       </c>
       <c r="K34" s="9">
-        <f t="shared" si="194"/>
+        <f t="shared" si="191"/>
         <v>0.30452674897119325</v>
       </c>
       <c r="L34" s="9">
-        <f t="shared" si="194"/>
+        <f t="shared" si="191"/>
         <v>0.27857142857142858</v>
       </c>
       <c r="M34" s="9">
-        <f t="shared" si="194"/>
+        <f t="shared" si="191"/>
         <v>0.29665071770334928</v>
       </c>
       <c r="N34" s="9">
-        <f t="shared" si="194"/>
+        <f t="shared" si="191"/>
         <v>0.28816793893129772</v>
       </c>
       <c r="O34" s="9">
-        <f t="shared" si="194"/>
+        <f t="shared" si="191"/>
         <v>0.30228471001757473</v>
       </c>
       <c r="P34" s="9">
-        <f t="shared" si="194"/>
+        <f t="shared" si="191"/>
         <v>0.27171215880893307</v>
       </c>
       <c r="Q34" s="9">
-        <f t="shared" si="194"/>
+        <f t="shared" si="191"/>
         <v>0.27937915742793795</v>
       </c>
       <c r="R34" s="9">
-        <f t="shared" si="194"/>
+        <f t="shared" si="191"/>
         <v>0.30778164924506379</v>
       </c>
       <c r="S34" s="9">
@@ -7474,151 +7459,151 @@
         <v>0.24965706447187941</v>
       </c>
       <c r="W34" s="9">
-        <f t="shared" ref="W34:AH34" si="195">W11/W7</f>
+        <f t="shared" ref="W34:AH34" si="192">W11/W7</f>
         <v>0.24918566775244297</v>
       </c>
       <c r="X34" s="9">
+        <f t="shared" si="192"/>
+        <v>0.286871961102107</v>
+      </c>
+      <c r="Y34" s="9">
+        <f t="shared" si="192"/>
+        <v>0.25904486251808961</v>
+      </c>
+      <c r="Z34" s="9">
+        <f t="shared" si="192"/>
+        <v>0.3</v>
+      </c>
+      <c r="AA34" s="9">
+        <f t="shared" si="192"/>
+        <v>0.35826771653543299</v>
+      </c>
+      <c r="AB34" s="9">
+        <f t="shared" si="192"/>
+        <v>0.33582089552238797</v>
+      </c>
+      <c r="AC34" s="9">
+        <f t="shared" si="192"/>
+        <v>-0.14460784313725486</v>
+      </c>
+      <c r="AD34" s="9">
+        <f t="shared" si="192"/>
+        <v>0.30913348946135838</v>
+      </c>
+      <c r="AE34" s="9">
+        <f t="shared" si="192"/>
+        <v>0.38802660753880264</v>
+      </c>
+      <c r="AF34" s="9">
+        <f t="shared" si="192"/>
+        <v>0.39020270270270269</v>
+      </c>
+      <c r="AG34" s="9">
+        <f t="shared" si="192"/>
+        <v>0.3481481481481481</v>
+      </c>
+      <c r="AH34" s="9">
+        <f t="shared" si="192"/>
+        <v>0.372141372141372</v>
+      </c>
+      <c r="AI34" s="9">
+        <f t="shared" ref="AI34:AL34" si="193">AI11/AI7</f>
+        <v>0.47318611987381703</v>
+      </c>
+      <c r="AJ34" s="9">
+        <f t="shared" si="193"/>
+        <v>0.47318611987381703</v>
+      </c>
+      <c r="AK34" s="9">
+        <f t="shared" si="193"/>
+        <v>0.46631578947368418</v>
+      </c>
+      <c r="AL34" s="9">
+        <f t="shared" si="193"/>
+        <v>0.46902382335851256</v>
+      </c>
+      <c r="AN34" s="9">
+        <f t="shared" ref="AN34:BA34" si="194">AN11/AN7</f>
+        <v>0.31403828623518681</v>
+      </c>
+      <c r="AO34" s="9">
+        <f t="shared" si="194"/>
+        <v>0.35012345679012336</v>
+      </c>
+      <c r="AP34" s="9">
+        <f t="shared" si="194"/>
+        <v>0.29176149294492487</v>
+      </c>
+      <c r="AQ34" s="9">
+        <f t="shared" si="194"/>
+        <v>0.28935627788400242</v>
+      </c>
+      <c r="AR34" s="9">
+        <f t="shared" si="194"/>
+        <v>0.28963414634146334</v>
+      </c>
+      <c r="AS34" s="9">
+        <f t="shared" si="194"/>
+        <v>0.27243066884176176</v>
+      </c>
+      <c r="AT34" s="9">
+        <f t="shared" si="194"/>
+        <v>0.23150612027674322</v>
+      </c>
+      <c r="AU34" s="9">
+        <f t="shared" si="194"/>
+        <v>0.37451550387596894</v>
+      </c>
+      <c r="AV34" s="9">
+        <f t="shared" si="194"/>
+        <v>0.47032116346008168</v>
+      </c>
+      <c r="AW34" s="9">
+        <f t="shared" si="194"/>
+        <v>0.41887472839990159</v>
+      </c>
+      <c r="AX34" s="9">
+        <f t="shared" si="194"/>
+        <v>0.41886764907850654</v>
+      </c>
+      <c r="AY34" s="9">
+        <f t="shared" si="194"/>
+        <v>0.41736178742664359</v>
+      </c>
+      <c r="AZ34" s="9">
+        <f t="shared" si="194"/>
+        <v>0.41794283025476625</v>
+      </c>
+      <c r="BA34" s="9">
+        <f t="shared" si="194"/>
+        <v>0.41717939115895974</v>
+      </c>
+      <c r="BB34" s="9">
+        <f t="shared" ref="BB34:BF34" si="195">BB11/BB7</f>
+        <v>0.41630885650199717</v>
+      </c>
+      <c r="BC34" s="9">
         <f t="shared" si="195"/>
-        <v>0.286871961102107</v>
-      </c>
-      <c r="Y34" s="9">
+        <v>0.41659711372503749</v>
+      </c>
+      <c r="BD34" s="9">
         <f t="shared" si="195"/>
-        <v>0.25904486251808961</v>
-      </c>
-      <c r="Z34" s="9">
+        <v>0.41687482651239322</v>
+      </c>
+      <c r="BE34" s="9">
         <f t="shared" si="195"/>
-        <v>0.3</v>
-      </c>
-      <c r="AA34" s="9">
+        <v>0.41714235278351014</v>
+      </c>
+      <c r="BF34" s="9">
         <f t="shared" si="195"/>
-        <v>0.35826771653543299</v>
-      </c>
-      <c r="AB34" s="9">
-        <f t="shared" si="195"/>
-        <v>0.33582089552238797</v>
-      </c>
-      <c r="AC34" s="9">
-        <f t="shared" si="195"/>
-        <v>-0.14460784313725486</v>
-      </c>
-      <c r="AD34" s="9">
-        <f t="shared" si="195"/>
-        <v>0.30913348946135838</v>
-      </c>
-      <c r="AE34" s="9">
-        <f t="shared" si="195"/>
-        <v>0.38802660753880264</v>
-      </c>
-      <c r="AF34" s="9">
-        <f t="shared" si="195"/>
-        <v>0.39020270270270269</v>
-      </c>
-      <c r="AG34" s="9">
-        <f t="shared" si="195"/>
-        <v>0.3481481481481481</v>
-      </c>
-      <c r="AH34" s="9">
-        <f t="shared" si="195"/>
-        <v>0.372141372141372</v>
-      </c>
-      <c r="AI34" s="9">
-        <f t="shared" ref="AI34:AL34" si="196">AI11/AI7</f>
-        <v>0.47318611987381703</v>
-      </c>
-      <c r="AJ34" s="9">
-        <f t="shared" si="196"/>
-        <v>0.38272336786843525</v>
-      </c>
-      <c r="AK34" s="9">
-        <f t="shared" si="196"/>
-        <v>0.36069773780321612</v>
-      </c>
-      <c r="AL34" s="9">
-        <f t="shared" si="196"/>
-        <v>0.38543174740662833</v>
-      </c>
-      <c r="AN34" s="9">
-        <f t="shared" ref="AN34:BA34" si="197">AN11/AN7</f>
-        <v>0.31403828623518681</v>
-      </c>
-      <c r="AO34" s="9">
-        <f t="shared" si="197"/>
-        <v>0.35012345679012336</v>
-      </c>
-      <c r="AP34" s="9">
-        <f t="shared" si="197"/>
-        <v>0.29176149294492487</v>
-      </c>
-      <c r="AQ34" s="9">
-        <f t="shared" si="197"/>
-        <v>0.28935627788400242</v>
-      </c>
-      <c r="AR34" s="9">
-        <f t="shared" si="197"/>
-        <v>0.28963414634146334</v>
-      </c>
-      <c r="AS34" s="9">
-        <f t="shared" si="197"/>
-        <v>0.27243066884176176</v>
-      </c>
-      <c r="AT34" s="9">
-        <f t="shared" si="197"/>
-        <v>0.23150612027674322</v>
-      </c>
-      <c r="AU34" s="9">
-        <f t="shared" si="197"/>
-        <v>0.37451550387596894</v>
-      </c>
-      <c r="AV34" s="9">
-        <f t="shared" si="197"/>
-        <v>0.3923552242185101</v>
-      </c>
-      <c r="AW34" s="9">
-        <f t="shared" si="197"/>
-        <v>0.35929102306532729</v>
-      </c>
-      <c r="AX34" s="9">
-        <f t="shared" si="197"/>
-        <v>0.35816706657893749</v>
-      </c>
-      <c r="AY34" s="9">
-        <f t="shared" si="197"/>
-        <v>0.35554572635401921</v>
-      </c>
-      <c r="AZ34" s="9">
-        <f t="shared" si="197"/>
-        <v>0.3544323935797597</v>
-      </c>
-      <c r="BA34" s="9">
-        <f t="shared" si="197"/>
-        <v>0.35313397440060312</v>
-      </c>
-      <c r="BB34" s="9">
-        <f t="shared" ref="BB34:BF34" si="198">BB11/BB7</f>
-        <v>0.35270496415041414</v>
-      </c>
-      <c r="BC34" s="9">
-        <f t="shared" si="198"/>
-        <v>0.35316564061125166</v>
-      </c>
-      <c r="BD34" s="9">
-        <f t="shared" si="198"/>
-        <v>0.3536110616615219</v>
-      </c>
-      <c r="BE34" s="9">
-        <f t="shared" si="198"/>
-        <v>0.35404163375561848</v>
-      </c>
-      <c r="BF34" s="9">
-        <f t="shared" si="198"/>
-        <v>0.35445775967309223</v>
+        <v>0.41740004038896372</v>
       </c>
       <c r="BH34" t="s">
         <v>53</v>
       </c>
       <c r="BI34" s="4">
-        <f>NPV(BI33,AU23:FL23)</f>
-        <v>125.42907233865714</v>
+        <f>NPV(BI33,AV23:FL23)</f>
+        <v>115.55638041965513</v>
       </c>
     </row>
     <row r="35" spans="2:61" x14ac:dyDescent="0.3">
@@ -7630,63 +7615,63 @@
         <v>-0.19855595667870043</v>
       </c>
       <c r="D35" s="9">
-        <f t="shared" ref="D35:R35" si="199">D17/D7</f>
+        <f t="shared" ref="D35:R35" si="196">D17/D7</f>
         <v>-7.0116861435726194E-2</v>
       </c>
       <c r="E35" s="9">
-        <f t="shared" si="199"/>
+        <f t="shared" si="196"/>
         <v>-0.10956521739130423</v>
       </c>
       <c r="F35" s="9">
-        <f t="shared" si="199"/>
+        <f t="shared" si="196"/>
         <v>1.7167381974249017E-2</v>
       </c>
       <c r="G35" s="9">
-        <f t="shared" si="199"/>
+        <f t="shared" si="196"/>
         <v>-4.4871794871794983E-2</v>
       </c>
       <c r="H35" s="9">
-        <f t="shared" si="199"/>
+        <f t="shared" si="196"/>
         <v>-2.0408163265306121E-2</v>
       </c>
       <c r="I35" s="9">
-        <f t="shared" si="199"/>
+        <f t="shared" si="196"/>
         <v>-0.3498023715415019</v>
       </c>
       <c r="J35" s="9">
-        <f t="shared" si="199"/>
+        <f t="shared" si="196"/>
         <v>1.4260249554367341E-2</v>
       </c>
       <c r="K35" s="9">
-        <f t="shared" si="199"/>
+        <f t="shared" si="196"/>
         <v>-5.144032921810715E-2</v>
       </c>
       <c r="L35" s="9">
-        <f t="shared" si="199"/>
+        <f t="shared" si="196"/>
         <v>-9.2857142857142777E-2</v>
       </c>
       <c r="M35" s="9">
-        <f t="shared" si="199"/>
+        <f t="shared" si="196"/>
         <v>-5.2631578947368376E-2</v>
       </c>
       <c r="N35" s="9">
-        <f t="shared" si="199"/>
+        <f t="shared" si="196"/>
         <v>-0.16221374045801526</v>
       </c>
       <c r="O35" s="9">
-        <f t="shared" si="199"/>
+        <f t="shared" si="196"/>
         <v>-0.1370826010544815</v>
       </c>
       <c r="P35" s="9">
-        <f t="shared" si="199"/>
+        <f t="shared" si="196"/>
         <v>-6.6997518610421761E-2</v>
       </c>
       <c r="Q35" s="9">
-        <f t="shared" si="199"/>
+        <f t="shared" si="196"/>
         <v>-3.7694013303769383E-2</v>
       </c>
       <c r="R35" s="9">
-        <f t="shared" si="199"/>
+        <f t="shared" si="196"/>
         <v>-9.8722415795586618E-2</v>
       </c>
       <c r="S35" s="9">
@@ -7706,144 +7691,144 @@
         <v>-0.13305898491083659</v>
       </c>
       <c r="W35" s="9">
-        <f t="shared" ref="W35:AH35" si="200">W17/W7</f>
+        <f t="shared" ref="W35:AH35" si="197">W17/W7</f>
         <v>-0.35342019543973946</v>
       </c>
       <c r="X35" s="9">
+        <f t="shared" si="197"/>
+        <v>-0.16369529983792536</v>
+      </c>
+      <c r="Y35" s="9">
+        <f t="shared" si="197"/>
+        <v>-0.17221418234442851</v>
+      </c>
+      <c r="Z35" s="9">
+        <f t="shared" si="197"/>
+        <v>-0.26603773584905666</v>
+      </c>
+      <c r="AA35" s="9">
+        <f t="shared" si="197"/>
+        <v>-6.1023622047244194E-2</v>
+      </c>
+      <c r="AB35" s="9">
+        <f t="shared" si="197"/>
+        <v>-7.835820895522401E-2</v>
+      </c>
+      <c r="AC35" s="9">
+        <f t="shared" si="197"/>
+        <v>-0.64215686274509798</v>
+      </c>
+      <c r="AD35" s="9">
+        <f t="shared" si="197"/>
+        <v>-0.26463700234192028</v>
+      </c>
+      <c r="AE35" s="9">
+        <f t="shared" si="197"/>
+        <v>-2.4390243902439056E-2</v>
+      </c>
+      <c r="AF35" s="9">
+        <f t="shared" si="197"/>
+        <v>4.0540540540540577E-2</v>
+      </c>
+      <c r="AG35" s="9">
+        <f t="shared" si="197"/>
+        <v>1.8518518518518452E-2</v>
+      </c>
+      <c r="AH35" s="9">
+        <f t="shared" si="197"/>
+        <v>3.5343035343035185E-2</v>
+      </c>
+      <c r="AI35" s="9">
+        <f t="shared" ref="AI35:AL35" si="198">AI17/AI7</f>
+        <v>-1.2618296529968466E-2</v>
+      </c>
+      <c r="AJ35" s="9">
+        <f t="shared" si="198"/>
+        <v>-1.2618296529968466E-2</v>
+      </c>
+      <c r="AK35" s="9">
+        <f t="shared" si="198"/>
+        <v>1.6023391812865499E-2</v>
+      </c>
+      <c r="AL35" s="9">
+        <f t="shared" si="198"/>
+        <v>-7.443346891342132E-3</v>
+      </c>
+      <c r="AN35" s="9">
+        <f t="shared" ref="AN35:BA35" si="199">AN17/AN7</f>
+        <v>-9.4348222424795042E-2</v>
+      </c>
+      <c r="AO35" s="9">
+        <f t="shared" si="199"/>
+        <v>-9.8765432098765579E-2</v>
+      </c>
+      <c r="AP35" s="9">
+        <f t="shared" si="199"/>
+        <v>-8.8757396449704151E-2</v>
+      </c>
+      <c r="AQ35" s="9">
+        <f t="shared" si="199"/>
+        <v>-7.9987253027406127E-2</v>
+      </c>
+      <c r="AR35" s="9">
+        <f t="shared" si="199"/>
+        <v>-0.17682926829268308</v>
+      </c>
+      <c r="AS35" s="9">
+        <f t="shared" si="199"/>
+        <v>-0.23572593800978806</v>
+      </c>
+      <c r="AT35" s="9">
+        <f t="shared" si="199"/>
+        <v>-0.23842469398616256</v>
+      </c>
+      <c r="AU35" s="9">
+        <f t="shared" si="199"/>
+        <v>1.9379844961240244E-2</v>
+      </c>
+      <c r="AV35" s="9">
+        <f t="shared" si="199"/>
+        <v>-3.8494167550372944E-3</v>
+      </c>
+      <c r="AW35" s="9">
+        <f t="shared" si="199"/>
+        <v>7.5647089310750273E-2</v>
+      </c>
+      <c r="AX35" s="9">
+        <f t="shared" si="199"/>
+        <v>9.188781234971935E-2</v>
+      </c>
+      <c r="AY35" s="9">
+        <f t="shared" si="199"/>
+        <v>0.10205677112619578</v>
+      </c>
+      <c r="AZ35" s="9">
+        <f t="shared" si="199"/>
+        <v>0.10951141530201378</v>
+      </c>
+      <c r="BA35" s="9">
+        <f t="shared" si="199"/>
+        <v>0.11268826971058507</v>
+      </c>
+      <c r="BB35" s="9">
+        <f t="shared" ref="BB35:BF35" si="200">BB17/BB7</f>
+        <v>0.11373011188822295</v>
+      </c>
+      <c r="BC35" s="9">
         <f t="shared" si="200"/>
-        <v>-0.16369529983792536</v>
-      </c>
-      <c r="Y35" s="9">
+        <v>0.11472395694359423</v>
+      </c>
+      <c r="BD35" s="9">
         <f t="shared" si="200"/>
-        <v>-0.17221418234442851</v>
-      </c>
-      <c r="Z35" s="9">
+        <v>0.11571097522717622</v>
+      </c>
+      <c r="BE35" s="9">
         <f t="shared" si="200"/>
-        <v>-0.26603773584905666</v>
-      </c>
-      <c r="AA35" s="9">
+        <v>0.11669106599414471</v>
+      </c>
+      <c r="BF35" s="9">
         <f t="shared" si="200"/>
-        <v>-6.1023622047244194E-2</v>
-      </c>
-      <c r="AB35" s="9">
-        <f t="shared" si="200"/>
-        <v>-7.835820895522401E-2</v>
-      </c>
-      <c r="AC35" s="9">
-        <f t="shared" si="200"/>
-        <v>-0.64215686274509798</v>
-      </c>
-      <c r="AD35" s="9">
-        <f t="shared" si="200"/>
-        <v>-0.26463700234192028</v>
-      </c>
-      <c r="AE35" s="9">
-        <f t="shared" si="200"/>
-        <v>-2.4390243902439056E-2</v>
-      </c>
-      <c r="AF35" s="9">
-        <f t="shared" si="200"/>
-        <v>4.0540540540540577E-2</v>
-      </c>
-      <c r="AG35" s="9">
-        <f t="shared" si="200"/>
-        <v>1.8518518518518452E-2</v>
-      </c>
-      <c r="AH35" s="9">
-        <f t="shared" si="200"/>
-        <v>3.5343035343035185E-2</v>
-      </c>
-      <c r="AI35" s="9">
-        <f t="shared" ref="AI35:AL35" si="201">AI17/AI7</f>
-        <v>-1.2618296529968466E-2</v>
-      </c>
-      <c r="AJ35" s="9">
-        <f t="shared" si="201"/>
-        <v>-4.9851850378825292E-3</v>
-      </c>
-      <c r="AK35" s="9">
-        <f t="shared" si="201"/>
-        <v>2.172254020168982E-2</v>
-      </c>
-      <c r="AL35" s="9">
-        <f t="shared" si="201"/>
-        <v>1.2029532471282174E-2</v>
-      </c>
-      <c r="AN35" s="9">
-        <f t="shared" ref="AN35:BA35" si="202">AN17/AN7</f>
-        <v>-9.4348222424795042E-2</v>
-      </c>
-      <c r="AO35" s="9">
-        <f t="shared" si="202"/>
-        <v>-9.8765432098765579E-2</v>
-      </c>
-      <c r="AP35" s="9">
-        <f t="shared" si="202"/>
-        <v>-8.8757396449704151E-2</v>
-      </c>
-      <c r="AQ35" s="9">
-        <f t="shared" si="202"/>
-        <v>-7.9987253027406127E-2</v>
-      </c>
-      <c r="AR35" s="9">
-        <f t="shared" si="202"/>
-        <v>-0.17682926829268308</v>
-      </c>
-      <c r="AS35" s="9">
-        <f t="shared" si="202"/>
-        <v>-0.23572593800978806</v>
-      </c>
-      <c r="AT35" s="9">
-        <f t="shared" si="202"/>
-        <v>-0.23842469398616256</v>
-      </c>
-      <c r="AU35" s="9">
-        <f t="shared" si="202"/>
-        <v>1.9379844961240244E-2</v>
-      </c>
-      <c r="AV35" s="9">
-        <f t="shared" si="202"/>
-        <v>6.0810949215952103E-3</v>
-      </c>
-      <c r="AW35" s="9">
-        <f t="shared" si="202"/>
-        <v>7.7514334834227996E-2</v>
-      </c>
-      <c r="AX35" s="9">
-        <f t="shared" si="202"/>
-        <v>8.7186212140514766E-2</v>
-      </c>
-      <c r="AY35" s="9">
-        <f t="shared" si="202"/>
-        <v>9.2405424749442258E-2</v>
-      </c>
-      <c r="AZ35" s="9">
-        <f t="shared" si="202"/>
-        <v>9.5288498840545063E-2</v>
-      </c>
-      <c r="BA35" s="9">
-        <f t="shared" si="202"/>
-        <v>9.6416042642108873E-2</v>
-      </c>
-      <c r="BB35" s="9">
-        <f t="shared" ref="BB35:BF35" si="203">BB17/BB7</f>
-        <v>9.7321781431254265E-2</v>
-      </c>
-      <c r="BC35" s="9">
-        <f t="shared" si="203"/>
-        <v>9.8016049796062349E-2</v>
-      </c>
-      <c r="BD35" s="9">
-        <f t="shared" si="203"/>
-        <v>9.8710922815785043E-2</v>
-      </c>
-      <c r="BE35" s="9">
-        <f t="shared" si="203"/>
-        <v>9.9406065162871898E-2</v>
-      </c>
-      <c r="BF35" s="9">
-        <f t="shared" si="203"/>
-        <v>0.10010115623174438</v>
+        <v>0.11766413789904684</v>
       </c>
       <c r="BH35" t="s">
         <v>54</v>
@@ -7862,51 +7847,51 @@
       <c r="E36" s="9"/>
       <c r="F36" s="9"/>
       <c r="G36" s="9">
-        <f t="shared" ref="G36:R36" si="204">G12/C12-1</f>
+        <f t="shared" ref="G36:R36" si="201">G12/C12-1</f>
         <v>-0.20634920634920628</v>
       </c>
       <c r="H36" s="9">
-        <f t="shared" si="204"/>
+        <f t="shared" si="201"/>
         <v>-7.4074074074074181E-2</v>
       </c>
       <c r="I36" s="9">
-        <f t="shared" si="204"/>
+        <f t="shared" si="201"/>
         <v>3.9215686274509887E-2</v>
       </c>
       <c r="J36" s="9">
-        <f t="shared" si="204"/>
+        <f t="shared" si="201"/>
         <v>0.15217391304347827</v>
       </c>
       <c r="K36" s="9">
-        <f t="shared" si="204"/>
+        <f t="shared" si="201"/>
         <v>-0.30000000000000004</v>
       </c>
       <c r="L36" s="9">
-        <f t="shared" si="204"/>
+        <f t="shared" si="201"/>
         <v>4.0000000000000036E-2</v>
       </c>
       <c r="M36" s="9">
-        <f t="shared" si="204"/>
+        <f t="shared" si="201"/>
         <v>0.26415094339622658</v>
       </c>
       <c r="N36" s="9">
-        <f t="shared" si="204"/>
+        <f t="shared" si="201"/>
         <v>0.60377358490566047</v>
       </c>
       <c r="O36" s="9">
-        <f t="shared" si="204"/>
+        <f t="shared" si="201"/>
         <v>1.3428571428571425</v>
       </c>
       <c r="P36" s="9">
-        <f t="shared" si="204"/>
+        <f t="shared" si="201"/>
         <v>1.0192307692307692</v>
       </c>
       <c r="Q36" s="9">
-        <f t="shared" si="204"/>
+        <f t="shared" si="201"/>
         <v>0.59701492537313428</v>
       </c>
       <c r="R36" s="9">
-        <f t="shared" si="204"/>
+        <f t="shared" si="201"/>
         <v>0.82352941176470584</v>
       </c>
       <c r="S36" s="9">
@@ -7926,140 +7911,140 @@
         <v>-0.11612903225806459</v>
       </c>
       <c r="W36" s="9">
-        <f t="shared" ref="W36:AH36" si="205">W12/S12-1</f>
+        <f t="shared" ref="W36:AH36" si="202">W12/S12-1</f>
         <v>0.27397260273972623</v>
       </c>
       <c r="X36" s="9">
-        <f t="shared" si="205"/>
+        <f t="shared" si="202"/>
         <v>0.15254237288135575</v>
       </c>
       <c r="Y36" s="9">
-        <f t="shared" si="205"/>
+        <f t="shared" si="202"/>
         <v>0.22222222222222232</v>
       </c>
       <c r="Z36" s="9">
-        <f t="shared" si="205"/>
+        <f t="shared" si="202"/>
         <v>-0.51094890510948909</v>
       </c>
       <c r="AA36" s="9">
-        <f t="shared" si="205"/>
+        <f t="shared" si="202"/>
         <v>-0.79569892473118276</v>
       </c>
       <c r="AB36" s="9">
-        <f t="shared" si="205"/>
+        <f t="shared" si="202"/>
         <v>-0.53676470588235292</v>
       </c>
       <c r="AC36" s="9">
-        <f t="shared" si="205"/>
+        <f t="shared" si="202"/>
         <v>-0.41558441558441561</v>
       </c>
       <c r="AD36" s="9">
-        <f t="shared" si="205"/>
+        <f t="shared" si="202"/>
         <v>-0.13432835820895528</v>
       </c>
       <c r="AE36" s="9">
-        <f t="shared" si="205"/>
+        <f t="shared" si="202"/>
         <v>0.31578947368421062</v>
       </c>
       <c r="AF36" s="9">
-        <f t="shared" si="205"/>
+        <f t="shared" si="202"/>
         <v>-0.12698412698412698</v>
       </c>
       <c r="AG36" s="9">
-        <f t="shared" si="205"/>
+        <f t="shared" si="202"/>
         <v>-0.42222222222222217</v>
       </c>
       <c r="AH36" s="9">
-        <f t="shared" si="205"/>
+        <f t="shared" si="202"/>
         <v>-3.4482758620689724E-2</v>
       </c>
       <c r="AI36" s="9">
-        <f t="shared" ref="AI36" si="206">AI12/AE12-1</f>
+        <f t="shared" ref="AI36" si="203">AI12/AE12-1</f>
         <v>-9.9999999999999978E-2</v>
       </c>
       <c r="AJ36" s="9">
-        <f t="shared" ref="AJ36" si="207">AJ12/AF12-1</f>
-        <v>2.0000000000000018E-2</v>
+        <f t="shared" ref="AJ36" si="204">AJ12/AF12-1</f>
+        <v>-0.18181818181818177</v>
       </c>
       <c r="AK36" s="9">
-        <f t="shared" ref="AK36" si="208">AK12/AG12-1</f>
-        <v>2.0000000000000018E-2</v>
+        <f t="shared" ref="AK36" si="205">AK12/AG12-1</f>
+        <v>-0.13461538461538469</v>
       </c>
       <c r="AL36" s="9">
-        <f t="shared" ref="AL36" si="209">AL12/AH12-1</f>
-        <v>2.0000000000000018E-2</v>
+        <f t="shared" ref="AL36" si="206">AL12/AH12-1</f>
+        <v>-0.1071428571428571</v>
       </c>
       <c r="AN36" s="9"/>
       <c r="AO36" s="9">
-        <f t="shared" ref="AO36:BA36" si="210">AO12/AN12-1</f>
+        <f t="shared" ref="AO36:BA36" si="207">AO12/AN12-1</f>
         <v>-3.7383177570093351E-2</v>
       </c>
       <c r="AP36" s="9">
-        <f t="shared" si="210"/>
+        <f t="shared" si="207"/>
         <v>0.16019417475728148</v>
       </c>
       <c r="AQ36" s="9">
-        <f t="shared" si="210"/>
+        <f t="shared" si="207"/>
         <v>0.87866108786610875</v>
       </c>
       <c r="AR36" s="9">
-        <f t="shared" si="210"/>
+        <f t="shared" si="207"/>
         <v>0.17371937639198221</v>
       </c>
       <c r="AS36" s="9">
-        <f t="shared" si="210"/>
+        <f t="shared" si="207"/>
         <v>3.0360531309297834E-2</v>
       </c>
       <c r="AT36" s="9">
-        <f t="shared" si="210"/>
+        <f t="shared" si="207"/>
         <v>-0.54143646408839774</v>
       </c>
       <c r="AU36" s="9">
-        <f t="shared" si="210"/>
+        <f t="shared" si="207"/>
         <v>-0.14457831325301218</v>
       </c>
       <c r="AV36" s="9">
-        <f t="shared" si="210"/>
-        <v>-8.169014084506987E-3</v>
+        <f t="shared" si="207"/>
+        <v>-0.13145539906103276</v>
       </c>
       <c r="AW36" s="9">
-        <f t="shared" si="210"/>
+        <f t="shared" si="207"/>
         <v>4.0000000000000036E-2</v>
       </c>
       <c r="AX36" s="9">
-        <f t="shared" si="210"/>
+        <f t="shared" si="207"/>
         <v>3.0000000000000027E-2</v>
       </c>
       <c r="AY36" s="9">
-        <f t="shared" si="210"/>
+        <f t="shared" si="207"/>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="AZ36" s="9">
-        <f t="shared" si="210"/>
+        <f t="shared" si="207"/>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="BA36" s="9">
-        <f t="shared" si="210"/>
+        <f t="shared" si="207"/>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="BB36" s="9">
-        <f t="shared" ref="BB36" si="211">BB12/BA12-1</f>
+        <f t="shared" ref="BB36" si="208">BB12/BA12-1</f>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="BC36" s="9">
-        <f t="shared" ref="BC36" si="212">BC12/BB12-1</f>
+        <f t="shared" ref="BC36" si="209">BC12/BB12-1</f>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="BD36" s="9">
-        <f t="shared" ref="BD36" si="213">BD12/BC12-1</f>
+        <f t="shared" ref="BD36" si="210">BD12/BC12-1</f>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="BE36" s="9">
-        <f t="shared" ref="BE36" si="214">BE12/BD12-1</f>
+        <f t="shared" ref="BE36" si="211">BE12/BD12-1</f>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="BF36" s="9">
-        <f t="shared" ref="BF36" si="215">BF12/BE12-1</f>
+        <f t="shared" ref="BF36" si="212">BF12/BE12-1</f>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="BH36" t="s">
@@ -8067,7 +8052,7 @@
       </c>
       <c r="BI36" s="4">
         <f>BI34+BI35</f>
-        <v>103.82907233865714</v>
+        <v>93.956380419655133</v>
       </c>
     </row>
     <row r="37" spans="2:61" x14ac:dyDescent="0.3">
@@ -8079,63 +8064,63 @@
         <v>0.12996389891696752</v>
       </c>
       <c r="D37" s="9">
-        <f t="shared" ref="D37:R37" si="216">D13/D7</f>
+        <f t="shared" ref="D37:R37" si="213">D13/D7</f>
         <v>0.11686143572621034</v>
       </c>
       <c r="E37" s="9">
-        <f t="shared" si="216"/>
+        <f t="shared" si="213"/>
         <v>0.10782608695652174</v>
       </c>
       <c r="F37" s="9">
-        <f t="shared" si="216"/>
+        <f t="shared" si="213"/>
         <v>0.10085836909871244</v>
       </c>
       <c r="G37" s="9">
-        <f t="shared" si="216"/>
+        <f t="shared" si="213"/>
         <v>0.1153846153846154</v>
       </c>
       <c r="H37" s="9">
-        <f t="shared" si="216"/>
+        <f t="shared" si="213"/>
         <v>0.11428571428571428</v>
       </c>
       <c r="I37" s="9">
-        <f t="shared" si="216"/>
+        <f t="shared" si="213"/>
         <v>0.116600790513834</v>
       </c>
       <c r="J37" s="9">
-        <f t="shared" si="216"/>
+        <f t="shared" si="213"/>
         <v>0.1087344028520499</v>
       </c>
       <c r="K37" s="9">
-        <f t="shared" si="216"/>
+        <f t="shared" si="213"/>
         <v>0.13168724279835392</v>
       </c>
       <c r="L37" s="9">
-        <f t="shared" si="216"/>
+        <f t="shared" si="213"/>
         <v>0.12857142857142859</v>
       </c>
       <c r="M37" s="9">
-        <f t="shared" si="216"/>
+        <f t="shared" si="213"/>
         <v>0.11483253588516747</v>
       </c>
       <c r="N37" s="9">
-        <f t="shared" si="216"/>
+        <f t="shared" si="213"/>
         <v>0.15458015267175573</v>
       </c>
       <c r="O37" s="9">
-        <f t="shared" si="216"/>
+        <f t="shared" si="213"/>
         <v>0.15465729349736382</v>
       </c>
       <c r="P37" s="9">
-        <f t="shared" si="216"/>
+        <f t="shared" si="213"/>
         <v>0.10669975186104216</v>
       </c>
       <c r="Q37" s="9">
-        <f t="shared" si="216"/>
+        <f t="shared" si="213"/>
         <v>9.3126385809312637E-2</v>
       </c>
       <c r="R37" s="9">
-        <f t="shared" si="216"/>
+        <f t="shared" si="213"/>
         <v>0.11498257839721256</v>
       </c>
       <c r="S37" s="9">
@@ -8155,151 +8140,151 @@
         <v>0.11248285322359394</v>
       </c>
       <c r="W37" s="9">
-        <f t="shared" ref="W37:AH37" si="217">W13/W7</f>
+        <f t="shared" ref="W37:AH37" si="214">W13/W7</f>
         <v>0.15960912052117265</v>
       </c>
       <c r="X37" s="9">
+        <f t="shared" si="214"/>
+        <v>0.12479740680713128</v>
+      </c>
+      <c r="Y37" s="9">
+        <f t="shared" si="214"/>
+        <v>0.12011577424023157</v>
+      </c>
+      <c r="Z37" s="9">
+        <f t="shared" si="214"/>
+        <v>0.14339622641509434</v>
+      </c>
+      <c r="AA37" s="9">
+        <f t="shared" si="214"/>
+        <v>0.12795275590551181</v>
+      </c>
+      <c r="AB37" s="9">
+        <f t="shared" si="214"/>
+        <v>0.1082089552238806</v>
+      </c>
+      <c r="AC37" s="9">
+        <f t="shared" si="214"/>
+        <v>0.13235294117647059</v>
+      </c>
+      <c r="AD37" s="9">
+        <f t="shared" si="214"/>
+        <v>9.601873536299764E-2</v>
+      </c>
+      <c r="AE37" s="9">
+        <f t="shared" si="214"/>
+        <v>0.11086474501108647</v>
+      </c>
+      <c r="AF37" s="9">
+        <f t="shared" si="214"/>
+        <v>9.1216216216216214E-2</v>
+      </c>
+      <c r="AG37" s="9">
+        <f t="shared" si="214"/>
+        <v>7.5925925925925924E-2</v>
+      </c>
+      <c r="AH37" s="9">
+        <f t="shared" si="214"/>
+        <v>7.9002079002079006E-2</v>
+      </c>
+      <c r="AI37" s="9">
+        <f t="shared" ref="AI37:AL37" si="215">AI13/AI7</f>
+        <v>0.12302839116719243</v>
+      </c>
+      <c r="AJ37" s="9">
+        <f t="shared" si="215"/>
+        <v>0.12302839116719243</v>
+      </c>
+      <c r="AK37" s="9">
+        <f t="shared" si="215"/>
+        <v>0.11403508771929824</v>
+      </c>
+      <c r="AL37" s="9">
+        <f t="shared" si="215"/>
+        <v>0.11330621731551423</v>
+      </c>
+      <c r="AN37" s="9">
+        <f t="shared" ref="AN37:BA37" si="216">AN13/AN7</f>
+        <v>0.11440291704649043</v>
+      </c>
+      <c r="AO37" s="9">
+        <f t="shared" si="216"/>
+        <v>0.11358024691358025</v>
+      </c>
+      <c r="AP37" s="9">
+        <f t="shared" si="216"/>
+        <v>0.13154301319981793</v>
+      </c>
+      <c r="AQ37" s="9">
+        <f t="shared" si="216"/>
+        <v>0.11376673040152964</v>
+      </c>
+      <c r="AR37" s="9">
+        <f t="shared" si="216"/>
+        <v>0.14557926829268295</v>
+      </c>
+      <c r="AS37" s="9">
+        <f t="shared" si="216"/>
+        <v>0.13621533442088091</v>
+      </c>
+      <c r="AT37" s="9">
+        <f t="shared" si="216"/>
+        <v>0.11601915912719532</v>
+      </c>
+      <c r="AU37" s="9">
+        <f t="shared" si="216"/>
+        <v>8.8662790697674437E-2</v>
+      </c>
+      <c r="AV37" s="9">
+        <f t="shared" si="216"/>
+        <v>0.11816391455840025</v>
+      </c>
+      <c r="AW37" s="9">
+        <f t="shared" si="216"/>
+        <v>0.09</v>
+      </c>
+      <c r="AX37" s="9">
+        <f t="shared" si="216"/>
+        <v>0.09</v>
+      </c>
+      <c r="AY37" s="9">
+        <f t="shared" si="216"/>
+        <v>0.09</v>
+      </c>
+      <c r="AZ37" s="9">
+        <f t="shared" si="216"/>
+        <v>0.09</v>
+      </c>
+      <c r="BA37" s="9">
+        <f t="shared" si="216"/>
+        <v>8.9999999999999983E-2</v>
+      </c>
+      <c r="BB37" s="9">
+        <f t="shared" ref="BB37:BF37" si="217">BB13/BB7</f>
+        <v>0.09</v>
+      </c>
+      <c r="BC37" s="9">
         <f t="shared" si="217"/>
-        <v>0.12479740680713128</v>
-      </c>
-      <c r="Y37" s="9">
+        <v>0.09</v>
+      </c>
+      <c r="BD37" s="9">
         <f t="shared" si="217"/>
-        <v>0.12011577424023157</v>
-      </c>
-      <c r="Z37" s="9">
+        <v>0.09</v>
+      </c>
+      <c r="BE37" s="9">
         <f t="shared" si="217"/>
-        <v>0.14339622641509434</v>
-      </c>
-      <c r="AA37" s="9">
+        <v>9.0000000000000011E-2</v>
+      </c>
+      <c r="BF37" s="9">
         <f t="shared" si="217"/>
-        <v>0.12795275590551181</v>
-      </c>
-      <c r="AB37" s="9">
-        <f t="shared" si="217"/>
-        <v>0.1082089552238806</v>
-      </c>
-      <c r="AC37" s="9">
-        <f t="shared" si="217"/>
-        <v>0.13235294117647059</v>
-      </c>
-      <c r="AD37" s="9">
-        <f t="shared" si="217"/>
-        <v>9.601873536299764E-2</v>
-      </c>
-      <c r="AE37" s="9">
-        <f t="shared" si="217"/>
-        <v>0.11086474501108647</v>
-      </c>
-      <c r="AF37" s="9">
-        <f t="shared" si="217"/>
-        <v>9.1216216216216214E-2</v>
-      </c>
-      <c r="AG37" s="9">
-        <f t="shared" si="217"/>
-        <v>7.5925925925925924E-2</v>
-      </c>
-      <c r="AH37" s="9">
-        <f t="shared" si="217"/>
-        <v>7.9002079002079006E-2</v>
-      </c>
-      <c r="AI37" s="9">
-        <f t="shared" ref="AI37:AL37" si="218">AI13/AI7</f>
-        <v>0.12302839116719243</v>
-      </c>
-      <c r="AJ37" s="9">
-        <f t="shared" si="218"/>
-        <v>0.10000000000000002</v>
-      </c>
-      <c r="AK37" s="9">
-        <f t="shared" si="218"/>
-        <v>0.1</v>
-      </c>
-      <c r="AL37" s="9">
-        <f t="shared" si="218"/>
-        <v>0.10000000000000002</v>
-      </c>
-      <c r="AN37" s="9">
-        <f t="shared" ref="AN37:BA37" si="219">AN13/AN7</f>
-        <v>0.11440291704649043</v>
-      </c>
-      <c r="AO37" s="9">
-        <f t="shared" si="219"/>
-        <v>0.11358024691358025</v>
-      </c>
-      <c r="AP37" s="9">
-        <f t="shared" si="219"/>
-        <v>0.13154301319981793</v>
-      </c>
-      <c r="AQ37" s="9">
-        <f t="shared" si="219"/>
-        <v>0.11376673040152964</v>
-      </c>
-      <c r="AR37" s="9">
-        <f t="shared" si="219"/>
-        <v>0.14557926829268295</v>
-      </c>
-      <c r="AS37" s="9">
-        <f t="shared" si="219"/>
-        <v>0.13621533442088091</v>
-      </c>
-      <c r="AT37" s="9">
-        <f t="shared" si="219"/>
-        <v>0.11601915912719532</v>
-      </c>
-      <c r="AU37" s="9">
-        <f t="shared" si="219"/>
-        <v>8.8662790697674437E-2</v>
-      </c>
-      <c r="AV37" s="9">
-        <f t="shared" si="219"/>
-        <v>0.10393507662618388</v>
-      </c>
-      <c r="AW37" s="9">
-        <f t="shared" si="219"/>
-        <v>8.0000000000000016E-2</v>
-      </c>
-      <c r="AX37" s="9">
-        <f t="shared" si="219"/>
-        <v>0.08</v>
-      </c>
-      <c r="AY37" s="9">
-        <f t="shared" si="219"/>
-        <v>0.08</v>
-      </c>
-      <c r="AZ37" s="9">
-        <f t="shared" si="219"/>
-        <v>0.08</v>
-      </c>
-      <c r="BA37" s="9">
-        <f t="shared" si="219"/>
-        <v>0.08</v>
-      </c>
-      <c r="BB37" s="9">
-        <f t="shared" ref="BB37:BF37" si="220">BB13/BB7</f>
-        <v>0.08</v>
-      </c>
-      <c r="BC37" s="9">
-        <f t="shared" si="220"/>
-        <v>0.08</v>
-      </c>
-      <c r="BD37" s="9">
-        <f t="shared" si="220"/>
-        <v>0.08</v>
-      </c>
-      <c r="BE37" s="9">
-        <f t="shared" si="220"/>
-        <v>0.08</v>
-      </c>
-      <c r="BF37" s="9">
-        <f t="shared" si="220"/>
-        <v>0.08</v>
+        <v>9.0000000000000011E-2</v>
       </c>
       <c r="BH37" t="s">
         <v>56</v>
       </c>
       <c r="BI37" s="10">
         <f>BI36/BA24</f>
-        <v>6.9219381559104765</v>
+        <v>6.2637586946436752</v>
       </c>
     </row>
     <row r="38" spans="2:61" x14ac:dyDescent="0.3">
@@ -8311,51 +8296,51 @@
       <c r="E38" s="9"/>
       <c r="F38" s="9"/>
       <c r="G38" s="9">
-        <f t="shared" ref="G38:R38" si="221">G14/C14-1</f>
+        <f t="shared" ref="G38:R38" si="218">G14/C14-1</f>
         <v>-0.45833333333333337</v>
       </c>
       <c r="H38" s="9">
-        <f t="shared" si="221"/>
+        <f t="shared" si="218"/>
         <v>-0.22222222222222221</v>
       </c>
       <c r="I38" s="9">
-        <f t="shared" si="221"/>
+        <f t="shared" si="218"/>
         <v>-0.18309859154929575</v>
       </c>
       <c r="J38" s="9">
-        <f t="shared" si="221"/>
+        <f t="shared" si="218"/>
         <v>-6.944444444444442E-2</v>
       </c>
       <c r="K38" s="9">
-        <f t="shared" si="221"/>
+        <f t="shared" si="218"/>
         <v>0</v>
       </c>
       <c r="L38" s="9">
-        <f t="shared" si="221"/>
+        <f t="shared" si="218"/>
         <v>0.19047619047619047</v>
       </c>
       <c r="M38" s="9">
-        <f t="shared" si="221"/>
+        <f t="shared" si="218"/>
         <v>0.22413793103448265</v>
       </c>
       <c r="N38" s="9">
-        <f t="shared" si="221"/>
+        <f t="shared" si="218"/>
         <v>-7.4626865671641784E-2</v>
       </c>
       <c r="O38" s="9">
-        <f t="shared" si="221"/>
+        <f t="shared" si="218"/>
         <v>0.10769230769230775</v>
       </c>
       <c r="P38" s="9">
-        <f t="shared" si="221"/>
+        <f t="shared" si="218"/>
         <v>-1.3333333333333308E-2</v>
       </c>
       <c r="Q38" s="9">
-        <f t="shared" si="221"/>
+        <f t="shared" si="218"/>
         <v>0.22535211267605626</v>
       </c>
       <c r="R38" s="9">
-        <f t="shared" si="221"/>
+        <f t="shared" si="218"/>
         <v>0.19354838709677424</v>
       </c>
       <c r="S38" s="9">
@@ -8375,140 +8360,140 @@
         <v>-0.24324324324324331</v>
       </c>
       <c r="W38" s="9">
-        <f t="shared" ref="W38:AH38" si="222">W14/S14-1</f>
+        <f t="shared" ref="W38:AH38" si="219">W14/S14-1</f>
         <v>-4.6511627906976827E-2</v>
       </c>
       <c r="X38" s="9">
-        <f t="shared" si="222"/>
+        <f t="shared" si="219"/>
         <v>-0.17567567567567577</v>
       </c>
       <c r="Y38" s="9">
-        <f t="shared" si="222"/>
+        <f t="shared" si="219"/>
         <v>-0.13636363636363624</v>
       </c>
       <c r="Z38" s="9">
-        <f t="shared" si="222"/>
+        <f t="shared" si="219"/>
         <v>0.26785714285714279</v>
       </c>
       <c r="AA38" s="9">
-        <f t="shared" si="222"/>
+        <f t="shared" si="219"/>
         <v>-0.30487804878048774</v>
       </c>
       <c r="AB38" s="9">
-        <f t="shared" si="222"/>
+        <f t="shared" si="219"/>
         <v>-0.11475409836065564</v>
       </c>
       <c r="AC38" s="9">
-        <f t="shared" si="222"/>
+        <f t="shared" si="219"/>
         <v>-0.14035087719298245</v>
       </c>
       <c r="AD38" s="9">
-        <f t="shared" si="222"/>
+        <f t="shared" si="219"/>
         <v>-0.29577464788732388</v>
       </c>
       <c r="AE38" s="9">
-        <f t="shared" si="222"/>
+        <f t="shared" si="219"/>
         <v>-0.1228070175438597</v>
       </c>
       <c r="AF38" s="9">
-        <f t="shared" si="222"/>
+        <f t="shared" si="219"/>
         <v>7.4074074074073959E-2</v>
       </c>
       <c r="AG38" s="9">
-        <f t="shared" si="222"/>
+        <f t="shared" si="219"/>
         <v>-2.0408163265306256E-2</v>
       </c>
       <c r="AH38" s="9">
-        <f t="shared" si="222"/>
+        <f t="shared" si="219"/>
         <v>-9.9999999999999978E-2</v>
       </c>
       <c r="AI38" s="9">
-        <f t="shared" ref="AI38" si="223">AI14/AE14-1</f>
+        <f t="shared" ref="AI38" si="220">AI14/AE14-1</f>
         <v>-9.9999999999999978E-2</v>
       </c>
       <c r="AJ38" s="9">
-        <f t="shared" ref="AJ38" si="224">AJ14/AF14-1</f>
-        <v>1.0000000000000009E-2</v>
+        <f t="shared" ref="AJ38" si="221">AJ14/AF14-1</f>
+        <v>-0.22413793103448276</v>
       </c>
       <c r="AK38" s="9">
-        <f t="shared" ref="AK38" si="225">AK14/AG14-1</f>
-        <v>1.0000000000000009E-2</v>
+        <f t="shared" ref="AK38" si="222">AK14/AG14-1</f>
+        <v>-6.25E-2</v>
       </c>
       <c r="AL38" s="9">
-        <f t="shared" ref="AL38" si="226">AL14/AH14-1</f>
-        <v>1.0000000000000009E-2</v>
+        <f t="shared" ref="AL38" si="223">AL14/AH14-1</f>
+        <v>0.11111111111111116</v>
       </c>
       <c r="AN38" s="9"/>
       <c r="AO38" s="9">
-        <f t="shared" ref="AO38:BA38" si="227">AO14/AN14-1</f>
+        <f t="shared" ref="AO38:BA38" si="224">AO14/AN14-1</f>
         <v>-0.26453488372093037</v>
       </c>
       <c r="AP38" s="9">
-        <f t="shared" si="227"/>
+        <f t="shared" si="224"/>
         <v>7.9051383399209474E-2</v>
       </c>
       <c r="AQ38" s="9">
-        <f t="shared" si="227"/>
+        <f t="shared" si="224"/>
         <v>0.12454212454212454</v>
       </c>
       <c r="AR38" s="9">
-        <f t="shared" si="227"/>
+        <f t="shared" si="224"/>
         <v>-8.1433224755700362E-2</v>
       </c>
       <c r="AS38" s="9">
-        <f t="shared" si="227"/>
+        <f t="shared" si="224"/>
         <v>-3.9007092198581561E-2</v>
       </c>
       <c r="AT38" s="9">
-        <f t="shared" si="227"/>
+        <f t="shared" si="224"/>
         <v>-0.22509225092250928</v>
       </c>
       <c r="AU38" s="9">
-        <f t="shared" si="227"/>
+        <f t="shared" si="224"/>
         <v>-4.2857142857142816E-2</v>
       </c>
       <c r="AV38" s="9">
-        <f t="shared" si="227"/>
-        <v>-1.7363184079602134E-2</v>
+        <f t="shared" si="224"/>
+        <v>-7.9601990049751326E-2</v>
       </c>
       <c r="AW38" s="9">
-        <f t="shared" si="227"/>
+        <f t="shared" si="224"/>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="AX38" s="9">
-        <f t="shared" si="227"/>
+        <f t="shared" si="224"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="AY38" s="9">
-        <f t="shared" si="227"/>
+        <f t="shared" si="224"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="AZ38" s="9">
-        <f t="shared" si="227"/>
+        <f t="shared" si="224"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="BA38" s="9">
-        <f t="shared" si="227"/>
+        <f t="shared" si="224"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="BB38" s="9">
-        <f t="shared" ref="BB38" si="228">BB14/BA14-1</f>
+        <f t="shared" ref="BB38" si="225">BB14/BA14-1</f>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="BC38" s="9">
-        <f t="shared" ref="BC38" si="229">BC14/BB14-1</f>
+        <f t="shared" ref="BC38" si="226">BC14/BB14-1</f>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="BD38" s="9">
-        <f t="shared" ref="BD38" si="230">BD14/BC14-1</f>
+        <f t="shared" ref="BD38" si="227">BD14/BC14-1</f>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="BE38" s="9">
-        <f t="shared" ref="BE38" si="231">BE14/BD14-1</f>
+        <f t="shared" ref="BE38" si="228">BE14/BD14-1</f>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="BF38" s="9">
-        <f t="shared" ref="BF38" si="232">BF14/BE14-1</f>
+        <f t="shared" ref="BF38" si="229">BF14/BE14-1</f>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="BH38" t="s">
@@ -8516,7 +8501,7 @@
       </c>
       <c r="BI38" s="10">
         <f>Main!D3</f>
-        <v>8.4700000000000006</v>
+        <v>12.28</v>
       </c>
     </row>
     <row r="39" spans="2:61" x14ac:dyDescent="0.3">
@@ -8528,63 +8513,63 @@
         <v>-1.8987341772151896E-2</v>
       </c>
       <c r="D39" s="9">
-        <f t="shared" ref="D39:R39" si="233">D21/D20</f>
+        <f t="shared" ref="D39:R39" si="230">D21/D20</f>
         <v>-5.9405940594059403E-2</v>
       </c>
       <c r="E39" s="9">
-        <f t="shared" si="233"/>
+        <f t="shared" si="230"/>
         <v>-3.0075187969924828E-2</v>
       </c>
       <c r="F39" s="9">
-        <f t="shared" si="233"/>
+        <f t="shared" si="230"/>
         <v>0.22000000000000022</v>
       </c>
       <c r="G39" s="9">
-        <f t="shared" si="233"/>
+        <f t="shared" si="230"/>
         <v>-5.5555555555555525E-2</v>
       </c>
       <c r="H39" s="9">
-        <f t="shared" si="233"/>
+        <f t="shared" si="230"/>
         <v>-4.6153846153846149E-2</v>
       </c>
       <c r="I39" s="9">
-        <f t="shared" si="233"/>
+        <f t="shared" si="230"/>
         <v>-2.1739130434782612E-2</v>
       </c>
       <c r="J39" s="9">
-        <f t="shared" si="233"/>
+        <f t="shared" si="230"/>
         <v>8.6956521739130599E-2</v>
       </c>
       <c r="K39" s="9">
-        <f t="shared" si="233"/>
+        <f t="shared" si="230"/>
         <v>-3.7974683544303764E-2</v>
       </c>
       <c r="L39" s="9">
-        <f t="shared" si="233"/>
+        <f t="shared" si="230"/>
         <v>-2.9126213592233021E-2</v>
       </c>
       <c r="M39" s="9">
-        <f t="shared" si="233"/>
+        <f t="shared" si="230"/>
         <v>-2.2988505747126443E-2</v>
       </c>
       <c r="N39" s="9">
-        <f t="shared" si="233"/>
+        <f t="shared" si="230"/>
         <v>2.2900763358778626E-2</v>
       </c>
       <c r="O39" s="9">
-        <f t="shared" si="233"/>
+        <f t="shared" si="230"/>
         <v>-5.5248618784530393E-3</v>
       </c>
       <c r="P39" s="9">
-        <f t="shared" si="233"/>
+        <f t="shared" si="230"/>
         <v>1.3351134846461951E-3</v>
       </c>
       <c r="Q39" s="9">
-        <f t="shared" si="233"/>
+        <f t="shared" si="230"/>
         <v>-3.8461538461538471E-2</v>
       </c>
       <c r="R39" s="9">
-        <f t="shared" si="233"/>
+        <f t="shared" si="230"/>
         <v>-4.9999999999999968E-2</v>
       </c>
       <c r="S39" s="9">
@@ -8604,143 +8589,143 @@
         <v>0</v>
       </c>
       <c r="W39" s="9">
-        <f t="shared" ref="W39:AH39" si="234">W21/W20</f>
+        <f t="shared" ref="W39:AH39" si="231">W21/W20</f>
         <v>1.1764705882352941E-2</v>
       </c>
       <c r="X39" s="9">
+        <f t="shared" si="231"/>
+        <v>2.343750000000001E-2</v>
+      </c>
+      <c r="Y39" s="9">
+        <f t="shared" si="231"/>
+        <v>0</v>
+      </c>
+      <c r="Z39" s="9">
+        <f t="shared" si="231"/>
+        <v>-6.9444444444444441E-3</v>
+      </c>
+      <c r="AA39" s="9">
+        <f t="shared" si="231"/>
+        <v>-6.9767441860465032E-2</v>
+      </c>
+      <c r="AB39" s="9">
+        <f t="shared" si="231"/>
+        <v>-5.454545454545448E-2</v>
+      </c>
+      <c r="AC39" s="9">
+        <f t="shared" si="231"/>
+        <v>0</v>
+      </c>
+      <c r="AD39" s="9">
+        <f t="shared" si="231"/>
+        <v>-2.0979020979020983E-2</v>
+      </c>
+      <c r="AE39" s="9">
+        <f t="shared" si="231"/>
+        <v>-5.4054054054054036E-2</v>
+      </c>
+      <c r="AF39" s="9">
+        <f t="shared" si="231"/>
+        <v>0.29999999999999932</v>
+      </c>
+      <c r="AG39" s="9">
+        <f t="shared" si="231"/>
+        <v>0</v>
+      </c>
+      <c r="AH39" s="9">
+        <f t="shared" si="231"/>
+        <v>-6.2499999999999977E-3</v>
+      </c>
+      <c r="AI39" s="9">
+        <f t="shared" ref="AI39:AL39" si="232">AI21/AI20</f>
+        <v>0</v>
+      </c>
+      <c r="AJ39" s="9">
+        <f t="shared" si="232"/>
+        <v>0</v>
+      </c>
+      <c r="AK39" s="9">
+        <f t="shared" si="232"/>
+        <v>0</v>
+      </c>
+      <c r="AL39" s="9">
+        <f t="shared" si="232"/>
+        <v>0</v>
+      </c>
+      <c r="AN39" s="9">
+        <f t="shared" ref="AN39:BA39" si="233">AN21/AN20</f>
+        <v>-4.5248868778280452E-3</v>
+      </c>
+      <c r="AO39" s="9">
+        <f t="shared" si="233"/>
+        <v>-1.9370460048426137E-2</v>
+      </c>
+      <c r="AP39" s="9">
+        <f t="shared" si="233"/>
+        <v>-1.2500000000000001E-2</v>
+      </c>
+      <c r="AQ39" s="9">
+        <f t="shared" si="233"/>
+        <v>-7.2595281306715026E-3</v>
+      </c>
+      <c r="AR39" s="9">
+        <f t="shared" si="233"/>
+        <v>-8.421052631578942E-3</v>
+      </c>
+      <c r="AS39" s="9">
+        <f t="shared" si="233"/>
+        <v>7.3099415204678341E-3</v>
+      </c>
+      <c r="AT39" s="9">
+        <f t="shared" si="233"/>
+        <v>-1.6728624535315997E-2</v>
+      </c>
+      <c r="AU39" s="9">
+        <f t="shared" si="233"/>
+        <v>-5.4054054054053995E-2</v>
+      </c>
+      <c r="AV39" s="9">
+        <f t="shared" si="233"/>
+        <v>0</v>
+      </c>
+      <c r="AW39" s="9">
+        <f t="shared" si="233"/>
+        <v>0.2</v>
+      </c>
+      <c r="AX39" s="9">
+        <f t="shared" si="233"/>
+        <v>0.2</v>
+      </c>
+      <c r="AY39" s="9">
+        <f t="shared" si="233"/>
+        <v>0.2</v>
+      </c>
+      <c r="AZ39" s="9">
+        <f t="shared" si="233"/>
+        <v>0.2</v>
+      </c>
+      <c r="BA39" s="9">
+        <f t="shared" si="233"/>
+        <v>0.20000000000000004</v>
+      </c>
+      <c r="BB39" s="9">
+        <f t="shared" ref="BB39:BF39" si="234">BB21/BB20</f>
+        <v>0.2</v>
+      </c>
+      <c r="BC39" s="9">
         <f t="shared" si="234"/>
-        <v>2.343750000000001E-2</v>
-      </c>
-      <c r="Y39" s="9">
+        <v>0.2</v>
+      </c>
+      <c r="BD39" s="9">
         <f t="shared" si="234"/>
-        <v>0</v>
-      </c>
-      <c r="Z39" s="9">
+        <v>0.2</v>
+      </c>
+      <c r="BE39" s="9">
         <f t="shared" si="234"/>
-        <v>-6.9444444444444441E-3</v>
-      </c>
-      <c r="AA39" s="9">
+        <v>0.2</v>
+      </c>
+      <c r="BF39" s="9">
         <f t="shared" si="234"/>
-        <v>-6.9767441860465032E-2</v>
-      </c>
-      <c r="AB39" s="9">
-        <f t="shared" si="234"/>
-        <v>-5.454545454545448E-2</v>
-      </c>
-      <c r="AC39" s="9">
-        <f t="shared" si="234"/>
-        <v>0</v>
-      </c>
-      <c r="AD39" s="9">
-        <f t="shared" si="234"/>
-        <v>-2.0979020979020983E-2</v>
-      </c>
-      <c r="AE39" s="9">
-        <f t="shared" si="234"/>
-        <v>-5.4054054054054036E-2</v>
-      </c>
-      <c r="AF39" s="9">
-        <f t="shared" si="234"/>
-        <v>0.29999999999999932</v>
-      </c>
-      <c r="AG39" s="9">
-        <f t="shared" si="234"/>
-        <v>0</v>
-      </c>
-      <c r="AH39" s="9">
-        <f t="shared" si="234"/>
-        <v>-6.2499999999999977E-3</v>
-      </c>
-      <c r="AI39" s="9">
-        <f t="shared" ref="AI39:AL39" si="235">AI21/AI20</f>
-        <v>0</v>
-      </c>
-      <c r="AJ39" s="9">
-        <f t="shared" si="235"/>
-        <v>0</v>
-      </c>
-      <c r="AK39" s="9">
-        <f t="shared" si="235"/>
-        <v>0</v>
-      </c>
-      <c r="AL39" s="9">
-        <f t="shared" si="235"/>
-        <v>0</v>
-      </c>
-      <c r="AN39" s="9">
-        <f t="shared" ref="AN39:BA39" si="236">AN21/AN20</f>
-        <v>-4.5248868778280452E-3</v>
-      </c>
-      <c r="AO39" s="9">
-        <f t="shared" si="236"/>
-        <v>-1.9370460048426137E-2</v>
-      </c>
-      <c r="AP39" s="9">
-        <f t="shared" si="236"/>
-        <v>-1.2500000000000001E-2</v>
-      </c>
-      <c r="AQ39" s="9">
-        <f t="shared" si="236"/>
-        <v>-7.2595281306715026E-3</v>
-      </c>
-      <c r="AR39" s="9">
-        <f t="shared" si="236"/>
-        <v>-8.421052631578942E-3</v>
-      </c>
-      <c r="AS39" s="9">
-        <f t="shared" si="236"/>
-        <v>7.3099415204678341E-3</v>
-      </c>
-      <c r="AT39" s="9">
-        <f t="shared" si="236"/>
-        <v>-1.6728624535315997E-2</v>
-      </c>
-      <c r="AU39" s="9">
-        <f t="shared" si="236"/>
-        <v>-5.4054054054053995E-2</v>
-      </c>
-      <c r="AV39" s="9">
-        <f t="shared" si="236"/>
-        <v>0</v>
-      </c>
-      <c r="AW39" s="9">
-        <f t="shared" si="236"/>
-        <v>0.2</v>
-      </c>
-      <c r="AX39" s="9">
-        <f t="shared" si="236"/>
-        <v>0.2</v>
-      </c>
-      <c r="AY39" s="9">
-        <f t="shared" si="236"/>
-        <v>0.2</v>
-      </c>
-      <c r="AZ39" s="9">
-        <f t="shared" si="236"/>
-        <v>0.2</v>
-      </c>
-      <c r="BA39" s="9">
-        <f t="shared" si="236"/>
-        <v>0.19999999999999998</v>
-      </c>
-      <c r="BB39" s="9">
-        <f t="shared" ref="BB39:BF39" si="237">BB21/BB20</f>
-        <v>0.2</v>
-      </c>
-      <c r="BC39" s="9">
-        <f t="shared" si="237"/>
-        <v>0.20000000000000004</v>
-      </c>
-      <c r="BD39" s="9">
-        <f t="shared" si="237"/>
-        <v>0.2</v>
-      </c>
-      <c r="BE39" s="9">
-        <f t="shared" si="237"/>
-        <v>0.2</v>
-      </c>
-      <c r="BF39" s="9">
-        <f t="shared" si="237"/>
         <v>0.2</v>
       </c>
       <c r="BH39" s="1" t="s">
@@ -8748,7 +8733,7 @@
       </c>
       <c r="BI39" s="11">
         <f>BI37/BI38-1</f>
-        <v>-0.18276999339899935</v>
+        <v>-0.48992193040360954</v>
       </c>
     </row>
     <row r="40" spans="2:61" x14ac:dyDescent="0.3">

--- a/Financial Analysis/INSG.xlsx
+++ b/Financial Analysis/INSG.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\antos\Documents\GitHub\FinanceModels\Financial Analysis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F0A2E40F-35E9-4430-83A3-E9C5621DB011}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{30C2321A-FFCA-4B3C-9A28-328B4BD60457}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{34A2EE39-018E-4F29-BBB7-6210648CE1A5}"/>
   </bookViews>
@@ -84,7 +84,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="96" uniqueCount="89">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="95" uniqueCount="89">
   <si>
     <t>INSG</t>
   </si>
@@ -350,7 +350,7 @@
     <t>Q425</t>
   </si>
   <si>
-    <t>Overvalued</t>
+    <t>Heavily overvalued</t>
   </si>
 </sst>
 </file>
@@ -466,14 +466,14 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>35</xdr:col>
-      <xdr:colOff>15240</xdr:colOff>
+      <xdr:col>37</xdr:col>
+      <xdr:colOff>22860</xdr:colOff>
       <xdr:row>0</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>35</xdr:col>
-      <xdr:colOff>15240</xdr:colOff>
+      <xdr:col>37</xdr:col>
+      <xdr:colOff>22860</xdr:colOff>
       <xdr:row>39</xdr:row>
       <xdr:rowOff>83820</xdr:rowOff>
     </xdr:to>
@@ -490,7 +490,7 @@
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="22090380" y="0"/>
+          <a:off x="23317200" y="0"/>
           <a:ext cx="0" cy="7216140"/>
         </a:xfrm>
         <a:prstGeom prst="line">
@@ -889,17 +889,17 @@
         <v>1</v>
       </c>
       <c r="D3" s="10">
-        <v>12.28</v>
+        <v>11.61</v>
       </c>
       <c r="E3" s="3">
-        <v>45898</v>
+        <v>45975</v>
       </c>
       <c r="F3" s="3">
         <f ca="1">TODAY()</f>
-        <v>45898</v>
+        <v>45975</v>
       </c>
       <c r="G3" s="3">
-        <v>45959</v>
+        <v>46084</v>
       </c>
     </row>
     <row r="4" spans="2:7" x14ac:dyDescent="0.3">
@@ -907,10 +907,10 @@
         <v>2</v>
       </c>
       <c r="D4" s="4">
-        <v>15</v>
+        <v>15.1</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
     </row>
     <row r="5" spans="2:7" x14ac:dyDescent="0.3">
@@ -919,7 +919,7 @@
       </c>
       <c r="D5" s="4">
         <f>D3*D4</f>
-        <v>184.2</v>
+        <v>175.31099999999998</v>
       </c>
     </row>
     <row r="6" spans="2:7" x14ac:dyDescent="0.3">
@@ -927,11 +927,11 @@
         <v>4</v>
       </c>
       <c r="D6" s="4">
-        <f>35.1</f>
-        <v>35.1</v>
+        <f>14.6</f>
+        <v>14.6</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
     </row>
     <row r="7" spans="2:7" x14ac:dyDescent="0.3">
@@ -939,11 +939,8 @@
         <v>5</v>
       </c>
       <c r="D7" s="4">
-        <f>14.9+41.8</f>
-        <v>56.699999999999996</v>
-      </c>
-      <c r="E7" s="2" t="s">
-        <v>85</v>
+        <f>41.7</f>
+        <v>41.7</v>
       </c>
     </row>
     <row r="8" spans="2:7" x14ac:dyDescent="0.3">
@@ -952,7 +949,7 @@
       </c>
       <c r="D8" s="4">
         <f>D6-D7</f>
-        <v>-21.599999999999994</v>
+        <v>-27.1</v>
       </c>
     </row>
     <row r="9" spans="2:7" x14ac:dyDescent="0.3">
@@ -961,7 +958,7 @@
       </c>
       <c r="D9" s="4">
         <f>D5-D8</f>
-        <v>205.79999999999998</v>
+        <v>202.41099999999997</v>
       </c>
     </row>
   </sheetData>
@@ -1211,10 +1208,10 @@
         <v>17.8</v>
       </c>
       <c r="AK3" s="6">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="AL3" s="6">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="AS3" s="4">
         <v>143.5</v>
@@ -1228,47 +1225,47 @@
       </c>
       <c r="AV3" s="4">
         <f>SUM(AI3:AL3)</f>
-        <v>73.599999999999994</v>
+        <v>67.599999999999994</v>
       </c>
       <c r="AW3" s="4">
         <f>AV3*1.15</f>
-        <v>84.639999999999986</v>
+        <v>77.739999999999981</v>
       </c>
       <c r="AX3" s="4">
         <f>AW3*1.1</f>
-        <v>93.103999999999999</v>
+        <v>85.513999999999982</v>
       </c>
       <c r="AY3" s="4">
         <f>AX3*1.08</f>
-        <v>100.55232000000001</v>
+        <v>92.355119999999985</v>
       </c>
       <c r="AZ3" s="4">
         <f>AY3*1.05</f>
-        <v>105.57993600000002</v>
+        <v>96.972875999999985</v>
       </c>
       <c r="BA3" s="4">
         <f>AZ3*1.04</f>
-        <v>109.80313344000002</v>
+        <v>100.85179103999999</v>
       </c>
       <c r="BB3" s="4">
         <f>BA3*1.03</f>
-        <v>113.09722744320003</v>
+        <v>103.8773447712</v>
       </c>
       <c r="BC3" s="4">
         <f>BB3*1.02</f>
-        <v>115.35917199206403</v>
+        <v>105.95489166662401</v>
       </c>
       <c r="BD3" s="4">
         <f>BC3*1.02</f>
-        <v>117.66635543190532</v>
+        <v>108.07398949995648</v>
       </c>
       <c r="BE3" s="4">
         <f>BD3*1.02</f>
-        <v>120.01968254054343</v>
+        <v>110.23546928995562</v>
       </c>
       <c r="BF3" s="4">
         <f>BE3*1.02</f>
-        <v>122.4200761913543</v>
+        <v>112.44017867575474</v>
       </c>
     </row>
     <row r="4" spans="2:58" x14ac:dyDescent="0.3">
@@ -1332,10 +1329,10 @@
         <v>1.9</v>
       </c>
       <c r="AK4" s="6">
-        <v>2</v>
+        <v>17.7</v>
       </c>
       <c r="AL4" s="6">
-        <v>2</v>
+        <v>18.5</v>
       </c>
       <c r="AS4" s="4">
         <v>43.6</v>
@@ -1349,47 +1346,47 @@
       </c>
       <c r="AV4" s="4">
         <f>SUM(AI4:AL4)</f>
-        <v>7.8</v>
+        <v>40</v>
       </c>
       <c r="AW4" s="4">
         <f t="shared" ref="AW4:BF4" si="0">AV4*0.98</f>
-        <v>7.6440000000000001</v>
+        <v>39.200000000000003</v>
       </c>
       <c r="AX4" s="4">
         <f t="shared" si="0"/>
-        <v>7.4911199999999996</v>
+        <v>38.416000000000004</v>
       </c>
       <c r="AY4" s="4">
         <f t="shared" si="0"/>
-        <v>7.3412975999999999</v>
+        <v>37.647680000000001</v>
       </c>
       <c r="AZ4" s="4">
         <f t="shared" si="0"/>
-        <v>7.1944716479999995</v>
+        <v>36.894726400000003</v>
       </c>
       <c r="BA4" s="4">
         <f t="shared" si="0"/>
-        <v>7.0505822150399995</v>
+        <v>36.156831872000005</v>
       </c>
       <c r="BB4" s="4">
         <f t="shared" si="0"/>
-        <v>6.9095705707391994</v>
+        <v>35.433695234560005</v>
       </c>
       <c r="BC4" s="4">
         <f t="shared" si="0"/>
-        <v>6.7713791593244155</v>
+        <v>34.725021329868802</v>
       </c>
       <c r="BD4" s="4">
         <f t="shared" si="0"/>
-        <v>6.6359515761379271</v>
+        <v>34.030520903271423</v>
       </c>
       <c r="BE4" s="4">
         <f t="shared" si="0"/>
-        <v>6.5032325446151686</v>
+        <v>33.349910485205996</v>
       </c>
       <c r="BF4" s="4">
         <f t="shared" si="0"/>
-        <v>6.3731678937228651</v>
+        <v>32.682912275501877</v>
       </c>
     </row>
     <row r="5" spans="2:58" x14ac:dyDescent="0.3">
@@ -1511,11 +1508,11 @@
       </c>
       <c r="AK5" s="6">
         <f t="shared" si="2"/>
-        <v>21</v>
+        <v>33.700000000000003</v>
       </c>
       <c r="AL5" s="6">
         <f t="shared" si="2"/>
-        <v>21</v>
+        <v>34.5</v>
       </c>
       <c r="AN5" s="4">
         <f>SUM(C5:F5)</f>
@@ -1551,47 +1548,47 @@
       </c>
       <c r="AV5" s="4">
         <f>AV3+AV4</f>
-        <v>81.399999999999991</v>
+        <v>107.6</v>
       </c>
       <c r="AW5" s="4">
         <f t="shared" ref="AW5:BF5" si="3">AW3+AW4</f>
-        <v>92.283999999999992</v>
+        <v>116.93999999999998</v>
       </c>
       <c r="AX5" s="4">
         <f t="shared" si="3"/>
-        <v>100.59511999999999</v>
+        <v>123.92999999999998</v>
       </c>
       <c r="AY5" s="4">
         <f t="shared" si="3"/>
-        <v>107.89361760000001</v>
+        <v>130.00279999999998</v>
       </c>
       <c r="AZ5" s="4">
         <f t="shared" si="3"/>
-        <v>112.77440764800002</v>
+        <v>133.86760239999998</v>
       </c>
       <c r="BA5" s="4">
         <f t="shared" si="3"/>
-        <v>116.85371565504002</v>
+        <v>137.00862291199999</v>
       </c>
       <c r="BB5" s="4">
         <f t="shared" si="3"/>
-        <v>120.00679801393923</v>
+        <v>139.31104000575999</v>
       </c>
       <c r="BC5" s="4">
         <f t="shared" si="3"/>
-        <v>122.13055115138845</v>
+        <v>140.67991299649282</v>
       </c>
       <c r="BD5" s="4">
         <f t="shared" si="3"/>
-        <v>124.30230700804324</v>
+        <v>142.10451040322789</v>
       </c>
       <c r="BE5" s="4">
         <f t="shared" si="3"/>
-        <v>126.5229150851586</v>
+        <v>143.58537977516161</v>
       </c>
       <c r="BF5" s="4">
         <f t="shared" si="3"/>
-        <v>128.79324408507716</v>
+        <v>145.12309095125661</v>
       </c>
     </row>
     <row r="6" spans="2:58" x14ac:dyDescent="0.3">
@@ -1701,12 +1698,11 @@
         <v>12</v>
       </c>
       <c r="AK6" s="6">
-        <f>AG6*1.1</f>
-        <v>13.200000000000001</v>
+        <v>12.2</v>
       </c>
       <c r="AL6" s="6">
-        <f>AH6*1.1</f>
-        <v>13.42</v>
+        <f>AH6*1.05</f>
+        <v>12.81</v>
       </c>
       <c r="AN6" s="4">
         <f>SUM(C6:F6)</f>
@@ -1742,47 +1738,47 @@
       </c>
       <c r="AV6" s="4">
         <f>SUM(AI6:AL6)</f>
-        <v>50.620000000000005</v>
+        <v>49.010000000000005</v>
       </c>
       <c r="AW6" s="4">
         <f>AV6*1.15</f>
-        <v>58.213000000000001</v>
+        <v>56.361499999999999</v>
       </c>
       <c r="AX6" s="4">
         <f>AW6*1.09</f>
-        <v>63.452170000000002</v>
+        <v>61.434035000000002</v>
       </c>
       <c r="AY6" s="4">
         <f>AX6*1.06</f>
-        <v>67.259300200000013</v>
+        <v>65.120077100000003</v>
       </c>
       <c r="AZ6" s="4">
         <f>AY6*1.05</f>
-        <v>70.622265210000023</v>
+        <v>68.376080955000006</v>
       </c>
       <c r="BA6" s="4">
         <f>AZ6*1.03</f>
-        <v>72.740933166300024</v>
+        <v>70.427363383650004</v>
       </c>
       <c r="BB6" s="4">
         <f t="shared" ref="BB6:BF6" si="4">BA6*1.02</f>
-        <v>74.195751829626033</v>
+        <v>71.835910651323005</v>
       </c>
       <c r="BC6" s="4">
         <f t="shared" si="4"/>
-        <v>75.679666866218554</v>
+        <v>73.272628864349471</v>
       </c>
       <c r="BD6" s="4">
         <f t="shared" si="4"/>
-        <v>77.19326020354292</v>
+        <v>74.738081441636467</v>
       </c>
       <c r="BE6" s="4">
         <f t="shared" si="4"/>
-        <v>78.737125407613775</v>
+        <v>76.232843070469201</v>
       </c>
       <c r="BF6" s="4">
         <f t="shared" si="4"/>
-        <v>80.311867915766058</v>
+        <v>77.757499931878584</v>
       </c>
     </row>
     <row r="7" spans="2:58" s="1" customFormat="1" x14ac:dyDescent="0.3">
@@ -1927,11 +1923,11 @@
       </c>
       <c r="AK7" s="7">
         <f t="shared" si="15"/>
-        <v>34.200000000000003</v>
+        <v>45.900000000000006</v>
       </c>
       <c r="AL7" s="7">
         <f t="shared" si="15"/>
-        <v>34.42</v>
+        <v>47.31</v>
       </c>
       <c r="AN7" s="7">
         <f>AN5+AN6</f>
@@ -1967,47 +1963,47 @@
       </c>
       <c r="AV7" s="7">
         <f t="shared" si="16"/>
-        <v>132.01999999999998</v>
+        <v>156.61000000000001</v>
       </c>
       <c r="AW7" s="7">
         <f t="shared" si="16"/>
-        <v>150.49699999999999</v>
+        <v>173.30149999999998</v>
       </c>
       <c r="AX7" s="7">
         <f t="shared" si="16"/>
-        <v>164.04729</v>
+        <v>185.36403499999997</v>
       </c>
       <c r="AY7" s="7">
         <f t="shared" si="16"/>
-        <v>175.15291780000001</v>
+        <v>195.12287709999998</v>
       </c>
       <c r="AZ7" s="7">
         <f t="shared" si="16"/>
-        <v>183.39667285800004</v>
+        <v>202.24368335499997</v>
       </c>
       <c r="BA7" s="7">
         <f t="shared" si="16"/>
-        <v>189.59464882134006</v>
+        <v>207.43598629565</v>
       </c>
       <c r="BB7" s="7">
         <f t="shared" ref="BB7:BF7" si="17">BB5+BB6</f>
-        <v>194.20254984356527</v>
+        <v>211.14695065708298</v>
       </c>
       <c r="BC7" s="7">
         <f t="shared" si="17"/>
-        <v>197.81021801760699</v>
+        <v>213.9525418608423</v>
       </c>
       <c r="BD7" s="7">
         <f t="shared" si="17"/>
-        <v>201.49556721158615</v>
+        <v>216.84259184486436</v>
       </c>
       <c r="BE7" s="7">
         <f t="shared" si="17"/>
-        <v>205.26004049277236</v>
+        <v>219.81822284563083</v>
       </c>
       <c r="BF7" s="7">
         <f t="shared" si="17"/>
-        <v>209.10511200084323</v>
+        <v>222.8805908831352</v>
       </c>
     </row>
     <row r="8" spans="2:58" x14ac:dyDescent="0.3">
@@ -2117,12 +2113,11 @@
         <v>15.4</v>
       </c>
       <c r="AK8" s="4">
-        <f>AK5*0.8</f>
-        <v>16.8</v>
+        <v>25.3</v>
       </c>
       <c r="AL8" s="4">
         <f>AL5*0.8</f>
-        <v>16.8</v>
+        <v>27.6</v>
       </c>
       <c r="AN8" s="4">
         <f>SUM(C8:F8)</f>
@@ -2158,47 +2153,47 @@
       </c>
       <c r="AV8" s="4">
         <f>SUM(AI8:AL8)</f>
-        <v>64.400000000000006</v>
+        <v>83.7</v>
       </c>
       <c r="AW8" s="4">
         <f t="shared" ref="AW8:BF8" si="18">AW5*0.79</f>
-        <v>72.904359999999997</v>
+        <v>92.382599999999996</v>
       </c>
       <c r="AX8" s="4">
         <f t="shared" si="18"/>
-        <v>79.4701448</v>
+        <v>97.904699999999991</v>
       </c>
       <c r="AY8" s="4">
         <f t="shared" si="18"/>
-        <v>85.235957904000017</v>
+        <v>102.70221199999999</v>
       </c>
       <c r="AZ8" s="4">
         <f t="shared" si="18"/>
-        <v>89.091782041920027</v>
+        <v>105.75540589599998</v>
       </c>
       <c r="BA8" s="4">
         <f t="shared" si="18"/>
-        <v>92.314435367481622</v>
+        <v>108.23681210047999</v>
       </c>
       <c r="BB8" s="4">
         <f t="shared" si="18"/>
-        <v>94.805370431011994</v>
+        <v>110.0557216045504</v>
       </c>
       <c r="BC8" s="4">
         <f t="shared" si="18"/>
-        <v>96.483135409596869</v>
+        <v>111.13713126722934</v>
       </c>
       <c r="BD8" s="4">
         <f t="shared" si="18"/>
-        <v>98.198822536354172</v>
+        <v>112.26256321855004</v>
       </c>
       <c r="BE8" s="4">
         <f t="shared" si="18"/>
-        <v>99.953102917275302</v>
+        <v>113.43245002237768</v>
       </c>
       <c r="BF8" s="4">
         <f t="shared" si="18"/>
-        <v>101.74666282721097</v>
+        <v>114.64724185149274</v>
       </c>
     </row>
     <row r="9" spans="2:58" x14ac:dyDescent="0.3">
@@ -2310,12 +2305,11 @@
         <v>1.3</v>
       </c>
       <c r="AK9" s="4">
-        <f>AK6*0.11</f>
-        <v>1.4520000000000002</v>
+        <v>1.6</v>
       </c>
       <c r="AL9" s="4">
         <f>AL6*0.11</f>
-        <v>1.4762</v>
+        <v>1.4091</v>
       </c>
       <c r="AN9" s="4">
         <f>SUM(C9:F9)</f>
@@ -2351,47 +2345,47 @@
       </c>
       <c r="AV9" s="4">
         <f>SUM(AI9:AL9)</f>
-        <v>5.5282</v>
+        <v>5.6090999999999998</v>
       </c>
       <c r="AW9" s="4">
         <f t="shared" ref="AW9:BF9" si="19">AW6*0.25</f>
-        <v>14.55325</v>
+        <v>14.090375</v>
       </c>
       <c r="AX9" s="4">
         <f t="shared" si="19"/>
-        <v>15.863042500000001</v>
+        <v>15.35850875</v>
       </c>
       <c r="AY9" s="4">
         <f t="shared" si="19"/>
-        <v>16.814825050000003</v>
+        <v>16.280019275000001</v>
       </c>
       <c r="AZ9" s="4">
         <f t="shared" si="19"/>
-        <v>17.655566302500006</v>
+        <v>17.094020238750002</v>
       </c>
       <c r="BA9" s="4">
         <f t="shared" si="19"/>
-        <v>18.185233291575006</v>
+        <v>17.606840845912501</v>
       </c>
       <c r="BB9" s="4">
         <f t="shared" si="19"/>
-        <v>18.548937957406508</v>
+        <v>17.958977662830751</v>
       </c>
       <c r="BC9" s="4">
         <f t="shared" si="19"/>
-        <v>18.919916716554638</v>
+        <v>18.318157216087368</v>
       </c>
       <c r="BD9" s="4">
         <f t="shared" si="19"/>
-        <v>19.29831505088573</v>
+        <v>18.684520360409117</v>
       </c>
       <c r="BE9" s="4">
         <f t="shared" si="19"/>
-        <v>19.684281351903444</v>
+        <v>19.0582107676173</v>
       </c>
       <c r="BF9" s="4">
         <f t="shared" si="19"/>
-        <v>20.077966978941514</v>
+        <v>19.439374982969646</v>
       </c>
     </row>
     <row r="10" spans="2:58" x14ac:dyDescent="0.3">
@@ -2536,11 +2530,11 @@
       </c>
       <c r="AK10" s="4">
         <f t="shared" si="31"/>
-        <v>18.252000000000002</v>
+        <v>26.900000000000002</v>
       </c>
       <c r="AL10" s="4">
         <f t="shared" si="31"/>
-        <v>18.276199999999999</v>
+        <v>29.0091</v>
       </c>
       <c r="AN10" s="4">
         <f>AN8+AN9</f>
@@ -2576,47 +2570,47 @@
       </c>
       <c r="AV10" s="4">
         <f t="shared" si="32"/>
-        <v>69.928200000000004</v>
+        <v>89.309100000000001</v>
       </c>
       <c r="AW10" s="4">
         <f t="shared" si="32"/>
-        <v>87.457610000000003</v>
+        <v>106.47297499999999</v>
       </c>
       <c r="AX10" s="4">
         <f t="shared" si="32"/>
-        <v>95.333187300000006</v>
+        <v>113.26320874999999</v>
       </c>
       <c r="AY10" s="4">
         <f t="shared" si="32"/>
-        <v>102.05078295400003</v>
+        <v>118.98223127499999</v>
       </c>
       <c r="AZ10" s="4">
         <f t="shared" si="32"/>
-        <v>106.74734834442003</v>
+        <v>122.84942613474999</v>
       </c>
       <c r="BA10" s="4">
         <f t="shared" si="32"/>
-        <v>110.49966865905662</v>
+        <v>125.8436529463925</v>
       </c>
       <c r="BB10" s="4">
         <f t="shared" ref="BB10:BF10" si="33">BB8+BB9</f>
-        <v>113.3543083884185</v>
+        <v>128.01469926738116</v>
       </c>
       <c r="BC10" s="4">
         <f t="shared" si="33"/>
-        <v>115.40305212615151</v>
+        <v>129.45528848331671</v>
       </c>
       <c r="BD10" s="4">
         <f t="shared" si="33"/>
-        <v>117.49713758723991</v>
+        <v>130.94708357895917</v>
       </c>
       <c r="BE10" s="4">
         <f t="shared" si="33"/>
-        <v>119.63738426917874</v>
+        <v>132.49066078999499</v>
       </c>
       <c r="BF10" s="4">
         <f t="shared" si="33"/>
-        <v>121.82462980615249</v>
+        <v>134.08661683446238</v>
       </c>
     </row>
     <row r="11" spans="2:58" s="1" customFormat="1" x14ac:dyDescent="0.3">
@@ -2761,11 +2755,11 @@
       </c>
       <c r="AK11" s="7">
         <f t="shared" si="45"/>
-        <v>15.948</v>
+        <v>19.000000000000004</v>
       </c>
       <c r="AL11" s="7">
         <f t="shared" si="45"/>
-        <v>16.143800000000002</v>
+        <v>18.300900000000002</v>
       </c>
       <c r="AN11" s="7">
         <f>AN7-AN10</f>
@@ -2801,47 +2795,47 @@
       </c>
       <c r="AV11" s="7">
         <f t="shared" si="46"/>
-        <v>62.091799999999978</v>
+        <v>67.300900000000013</v>
       </c>
       <c r="AW11" s="7">
         <f t="shared" si="46"/>
-        <v>63.039389999999983</v>
+        <v>66.828524999999985</v>
       </c>
       <c r="AX11" s="7">
         <f t="shared" si="46"/>
-        <v>68.714102699999998</v>
+        <v>72.100826249999983</v>
       </c>
       <c r="AY11" s="7">
         <f t="shared" si="46"/>
-        <v>73.102134845999984</v>
+        <v>76.140645824999993</v>
       </c>
       <c r="AZ11" s="7">
         <f t="shared" si="46"/>
-        <v>76.649324513580012</v>
+        <v>79.394257220249983</v>
       </c>
       <c r="BA11" s="7">
         <f t="shared" si="46"/>
-        <v>79.094980162283434</v>
+        <v>81.592333349257501</v>
       </c>
       <c r="BB11" s="7">
         <f t="shared" ref="BB11:BF11" si="47">BB7-BB10</f>
-        <v>80.848241455146763</v>
+        <v>83.132251389701821</v>
       </c>
       <c r="BC11" s="7">
         <f t="shared" si="47"/>
-        <v>82.407165891455477</v>
+        <v>84.497253377525595</v>
       </c>
       <c r="BD11" s="7">
         <f t="shared" si="47"/>
-        <v>83.998429624346244</v>
+        <v>85.895508265905193</v>
       </c>
       <c r="BE11" s="7">
         <f t="shared" si="47"/>
-        <v>85.622656223593623</v>
+        <v>87.327562055635838</v>
       </c>
       <c r="BF11" s="7">
         <f t="shared" si="47"/>
-        <v>87.280482194690748</v>
+        <v>88.793974048672823</v>
       </c>
     </row>
     <row r="12" spans="2:58" x14ac:dyDescent="0.3">
@@ -2951,7 +2945,7 @@
         <v>4.5</v>
       </c>
       <c r="AK12" s="4">
-        <v>4.5</v>
+        <v>4.9000000000000004</v>
       </c>
       <c r="AL12" s="4">
         <v>5</v>
@@ -2990,47 +2984,47 @@
       </c>
       <c r="AV12" s="4">
         <f>SUM(AI12:AL12)</f>
-        <v>18.5</v>
+        <v>18.899999999999999</v>
       </c>
       <c r="AW12" s="4">
         <f>AV12*1.04</f>
-        <v>19.240000000000002</v>
+        <v>19.655999999999999</v>
       </c>
       <c r="AX12" s="4">
         <f>AW12*1.03</f>
-        <v>19.817200000000003</v>
+        <v>20.24568</v>
       </c>
       <c r="AY12" s="4">
         <f>AX12*1.02</f>
-        <v>20.213544000000002</v>
+        <v>20.650593600000001</v>
       </c>
       <c r="AZ12" s="4">
         <f>AY12*1.02</f>
-        <v>20.617814880000005</v>
+        <v>21.063605472000003</v>
       </c>
       <c r="BA12" s="4">
         <f>AZ12*1.02</f>
-        <v>21.030171177600003</v>
+        <v>21.484877581440003</v>
       </c>
       <c r="BB12" s="4">
         <f t="shared" ref="BB12:BF12" si="48">BA12*1.02</f>
-        <v>21.450774601152006</v>
+        <v>21.914575133068805</v>
       </c>
       <c r="BC12" s="4">
         <f t="shared" si="48"/>
-        <v>21.879790093175046</v>
+        <v>22.35286663573018</v>
       </c>
       <c r="BD12" s="4">
         <f t="shared" si="48"/>
-        <v>22.317385895038548</v>
+        <v>22.799923968444784</v>
       </c>
       <c r="BE12" s="4">
         <f t="shared" si="48"/>
-        <v>22.763733612939319</v>
+        <v>23.255922447813681</v>
       </c>
       <c r="BF12" s="4">
         <f t="shared" si="48"/>
-        <v>23.219008285198107</v>
+        <v>23.721040896769956</v>
       </c>
     </row>
     <row r="13" spans="2:58" x14ac:dyDescent="0.3">
@@ -3140,7 +3134,7 @@
         <v>3.9</v>
       </c>
       <c r="AK13" s="4">
-        <v>3.9</v>
+        <v>4.2</v>
       </c>
       <c r="AL13" s="4">
         <v>3.9</v>
@@ -3179,47 +3173,47 @@
       </c>
       <c r="AV13" s="4">
         <f>SUM(AI13:AL13)</f>
-        <v>15.6</v>
+        <v>15.9</v>
       </c>
       <c r="AW13" s="4">
         <f>AW7*0.09</f>
-        <v>13.544729999999998</v>
+        <v>15.597134999999998</v>
       </c>
       <c r="AX13" s="4">
         <f t="shared" ref="AX13:BF13" si="49">AX7*0.09</f>
-        <v>14.764256099999999</v>
+        <v>16.682763149999996</v>
       </c>
       <c r="AY13" s="4">
         <f t="shared" si="49"/>
-        <v>15.763762602</v>
+        <v>17.561058938999999</v>
       </c>
       <c r="AZ13" s="4">
         <f t="shared" si="49"/>
-        <v>16.505700557220003</v>
+        <v>18.201931501949996</v>
       </c>
       <c r="BA13" s="4">
         <f t="shared" si="49"/>
-        <v>17.063518393920603</v>
+        <v>18.669238766608498</v>
       </c>
       <c r="BB13" s="4">
         <f t="shared" si="49"/>
-        <v>17.478229485920874</v>
+        <v>19.003225559137469</v>
       </c>
       <c r="BC13" s="4">
         <f t="shared" si="49"/>
-        <v>17.802919621584628</v>
+        <v>19.255728767475805</v>
       </c>
       <c r="BD13" s="4">
         <f t="shared" si="49"/>
-        <v>18.134601049042754</v>
+        <v>19.515833266037792</v>
       </c>
       <c r="BE13" s="4">
         <f t="shared" si="49"/>
-        <v>18.473403644349514</v>
+        <v>19.783640056106773</v>
       </c>
       <c r="BF13" s="4">
         <f t="shared" si="49"/>
-        <v>18.819460080075892</v>
+        <v>20.059253179482166</v>
       </c>
     </row>
     <row r="14" spans="2:58" x14ac:dyDescent="0.3">
@@ -3329,7 +3323,7 @@
         <v>4.5</v>
       </c>
       <c r="AK14" s="4">
-        <v>4.5</v>
+        <v>5.7</v>
       </c>
       <c r="AL14" s="4">
         <v>5</v>
@@ -3368,47 +3362,47 @@
       </c>
       <c r="AV14" s="4">
         <f>SUM(AI14:AL14)</f>
-        <v>18.5</v>
+        <v>19.7</v>
       </c>
       <c r="AW14" s="4">
         <f>AV14*1.02</f>
-        <v>18.87</v>
+        <v>20.094000000000001</v>
       </c>
       <c r="AX14" s="4">
         <f>AW14*1.01</f>
-        <v>19.058700000000002</v>
+        <v>20.29494</v>
       </c>
       <c r="AY14" s="4">
         <f>AX14*1.01</f>
-        <v>19.249287000000002</v>
+        <v>20.497889400000002</v>
       </c>
       <c r="AZ14" s="4">
         <f>AY14*1.01</f>
-        <v>19.441779870000001</v>
+        <v>20.702868294000002</v>
       </c>
       <c r="BA14" s="4">
         <f>AZ14*1.01</f>
-        <v>19.636197668700003</v>
+        <v>20.909896976940001</v>
       </c>
       <c r="BB14" s="4">
         <f t="shared" ref="BB14:BF14" si="50">BA14*1.01</f>
-        <v>19.832559645387004</v>
+        <v>21.118995946709401</v>
       </c>
       <c r="BC14" s="4">
         <f t="shared" si="50"/>
-        <v>20.030885241840874</v>
+        <v>21.330185906176496</v>
       </c>
       <c r="BD14" s="4">
         <f t="shared" si="50"/>
-        <v>20.231194094259283</v>
+        <v>21.543487765238261</v>
       </c>
       <c r="BE14" s="4">
         <f t="shared" si="50"/>
-        <v>20.433506035201876</v>
+        <v>21.758922642890642</v>
       </c>
       <c r="BF14" s="4">
         <f t="shared" si="50"/>
-        <v>20.637841095553895</v>
+        <v>21.976511869319548</v>
       </c>
     </row>
     <row r="15" spans="2:58" x14ac:dyDescent="0.3">
@@ -3533,11 +3527,10 @@
         <v>2.5</v>
       </c>
       <c r="AK15" s="4">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="AL15" s="4">
         <f t="shared" ref="AK15:AL15" si="51">2.1+0.4</f>
-        <v>2.5</v>
-      </c>
-      <c r="AL15" s="4">
-        <f t="shared" si="51"/>
         <v>2.5</v>
       </c>
       <c r="AN15" s="4">
@@ -3574,7 +3567,7 @@
       </c>
       <c r="AV15" s="4">
         <f>SUM(AI15:AL15)</f>
-        <v>10</v>
+        <v>9.6999999999999993</v>
       </c>
       <c r="AW15" s="4">
         <v>0</v>
@@ -3749,7 +3742,7 @@
       </c>
       <c r="AK16" s="4">
         <f t="shared" si="63"/>
-        <v>15.4</v>
+        <v>17</v>
       </c>
       <c r="AL16" s="4">
         <f t="shared" si="63"/>
@@ -3789,47 +3782,47 @@
       </c>
       <c r="AV16" s="4">
         <f t="shared" si="64"/>
-        <v>62.6</v>
+        <v>64.2</v>
       </c>
       <c r="AW16" s="4">
         <f t="shared" si="64"/>
-        <v>51.654730000000001</v>
+        <v>55.347135000000002</v>
       </c>
       <c r="AX16" s="4">
         <f t="shared" si="64"/>
-        <v>53.640156100000006</v>
+        <v>57.223383149999989</v>
       </c>
       <c r="AY16" s="4">
         <f t="shared" si="64"/>
-        <v>55.226593602000001</v>
+        <v>58.709541939000005</v>
       </c>
       <c r="AZ16" s="4">
         <f t="shared" si="64"/>
-        <v>56.565295307220012</v>
+        <v>59.968405267950004</v>
       </c>
       <c r="BA16" s="4">
         <f t="shared" si="64"/>
-        <v>57.729887240220606</v>
+        <v>61.064013324988508</v>
       </c>
       <c r="BB16" s="4">
         <f t="shared" ref="BB16:BF16" si="65">BB12+BB13+BB14+BB15</f>
-        <v>58.761563732459891</v>
+        <v>62.036796638915675</v>
       </c>
       <c r="BC16" s="4">
         <f t="shared" si="65"/>
-        <v>59.713594956600545</v>
+        <v>62.938781309382478</v>
       </c>
       <c r="BD16" s="4">
         <f t="shared" si="65"/>
-        <v>60.683181038340578</v>
+        <v>63.859244999720836</v>
       </c>
       <c r="BE16" s="4">
         <f t="shared" si="65"/>
-        <v>61.670643292490709</v>
+        <v>64.798485146811089</v>
       </c>
       <c r="BF16" s="4">
         <f t="shared" si="65"/>
-        <v>62.676309460827895</v>
+        <v>65.756805945571671</v>
       </c>
     </row>
     <row r="17" spans="2:168" s="1" customFormat="1" x14ac:dyDescent="0.3">
@@ -3974,11 +3967,11 @@
       </c>
       <c r="AK17" s="7">
         <f t="shared" si="77"/>
-        <v>0.54800000000000004</v>
+        <v>2.0000000000000036</v>
       </c>
       <c r="AL17" s="7">
         <f t="shared" si="77"/>
-        <v>-0.25619999999999621</v>
+        <v>1.9009000000000036</v>
       </c>
       <c r="AN17" s="7">
         <f>AN11-AN16</f>
@@ -4014,47 +4007,47 @@
       </c>
       <c r="AV17" s="7">
         <f t="shared" si="78"/>
-        <v>-0.50820000000002352</v>
+        <v>3.10090000000001</v>
       </c>
       <c r="AW17" s="7">
         <f t="shared" si="78"/>
-        <v>11.384659999999982</v>
+        <v>11.481389999999983</v>
       </c>
       <c r="AX17" s="7">
         <f t="shared" si="78"/>
-        <v>15.073946599999992</v>
+        <v>14.877443099999994</v>
       </c>
       <c r="AY17" s="7">
         <f t="shared" si="78"/>
-        <v>17.875541243999983</v>
+        <v>17.431103885999988</v>
       </c>
       <c r="AZ17" s="7">
         <f t="shared" si="78"/>
-        <v>20.08402920636</v>
+        <v>19.425851952299979</v>
       </c>
       <c r="BA17" s="7">
         <f t="shared" si="78"/>
-        <v>21.365092922062829</v>
+        <v>20.528320024268993</v>
       </c>
       <c r="BB17" s="7">
         <f t="shared" ref="BB17:BF17" si="79">BB11-BB16</f>
-        <v>22.086677722686872</v>
+        <v>21.095454750786146</v>
       </c>
       <c r="BC17" s="7">
         <f t="shared" si="79"/>
-        <v>22.693570934854932</v>
+        <v>21.558472068143118</v>
       </c>
       <c r="BD17" s="7">
         <f t="shared" si="79"/>
-        <v>23.315248586005666</v>
+        <v>22.036263266184356</v>
       </c>
       <c r="BE17" s="7">
         <f t="shared" si="79"/>
-        <v>23.952012931102914</v>
+        <v>22.529076908824749</v>
       </c>
       <c r="BF17" s="7">
         <f t="shared" si="79"/>
-        <v>24.604172733862853</v>
+        <v>23.037168103101152</v>
       </c>
     </row>
     <row r="18" spans="2:168" x14ac:dyDescent="0.3">
@@ -4168,7 +4161,7 @@
         <v>1</v>
       </c>
       <c r="AK18" s="4">
-        <v>2</v>
+        <v>0.9</v>
       </c>
       <c r="AL18" s="4">
         <v>2</v>
@@ -4207,47 +4200,47 @@
       </c>
       <c r="AV18" s="4">
         <f>SUM(AI18:AL18)</f>
-        <v>6</v>
+        <v>4.9000000000000004</v>
       </c>
       <c r="AW18" s="4">
         <f t="shared" ref="AW18:BA18" si="80">AV18*0.8</f>
-        <v>4.8000000000000007</v>
+        <v>3.9200000000000004</v>
       </c>
       <c r="AX18" s="4">
         <f t="shared" si="80"/>
-        <v>3.8400000000000007</v>
+        <v>3.1360000000000006</v>
       </c>
       <c r="AY18" s="4">
         <f t="shared" si="80"/>
-        <v>3.072000000000001</v>
+        <v>2.5088000000000008</v>
       </c>
       <c r="AZ18" s="4">
         <f t="shared" si="80"/>
-        <v>2.4576000000000011</v>
+        <v>2.0070400000000008</v>
       </c>
       <c r="BA18" s="4">
         <f t="shared" si="80"/>
-        <v>1.9660800000000009</v>
+        <v>1.6056320000000008</v>
       </c>
       <c r="BB18" s="4">
         <f t="shared" ref="BB18:BB19" si="81">BA18*0.8</f>
-        <v>1.5728640000000009</v>
+        <v>1.2845056000000008</v>
       </c>
       <c r="BC18" s="4">
         <f t="shared" ref="BC18:BC19" si="82">BB18*0.8</f>
-        <v>1.2582912000000008</v>
+        <v>1.0276044800000006</v>
       </c>
       <c r="BD18" s="4">
         <f t="shared" ref="BD18:BD19" si="83">BC18*0.8</f>
-        <v>1.0066329600000008</v>
+        <v>0.82208358400000048</v>
       </c>
       <c r="BE18" s="4">
         <f t="shared" ref="BE18:BE19" si="84">BD18*0.8</f>
-        <v>0.80530636800000066</v>
+        <v>0.65766686720000045</v>
       </c>
       <c r="BF18" s="4">
         <f t="shared" ref="BF18:BF19" si="85">BE18*0.8</f>
-        <v>0.64424509440000055</v>
+        <v>0.5261334937600004</v>
       </c>
     </row>
     <row r="19" spans="2:168" x14ac:dyDescent="0.3">
@@ -4360,7 +4353,7 @@
         <v>-0.3</v>
       </c>
       <c r="AK19" s="4">
-        <v>-1</v>
+        <v>-0.1</v>
       </c>
       <c r="AL19" s="4">
         <v>-1</v>
@@ -4399,47 +4392,47 @@
       </c>
       <c r="AV19" s="4">
         <f>SUM(AI19:AL19)</f>
-        <v>-2.6</v>
+        <v>-1.7</v>
       </c>
       <c r="AW19" s="4">
         <f t="shared" ref="AW19:BA19" si="86">AV19*0.8</f>
-        <v>-2.08</v>
+        <v>-1.36</v>
       </c>
       <c r="AX19" s="4">
         <f t="shared" si="86"/>
-        <v>-1.6640000000000001</v>
+        <v>-1.0880000000000001</v>
       </c>
       <c r="AY19" s="4">
         <f t="shared" si="86"/>
-        <v>-1.3312000000000002</v>
+        <v>-0.87040000000000006</v>
       </c>
       <c r="AZ19" s="4">
         <f t="shared" si="86"/>
-        <v>-1.0649600000000001</v>
+        <v>-0.69632000000000005</v>
       </c>
       <c r="BA19" s="4">
         <f t="shared" si="86"/>
-        <v>-0.85196800000000017</v>
+        <v>-0.55705600000000011</v>
       </c>
       <c r="BB19" s="4">
         <f t="shared" si="81"/>
-        <v>-0.68157440000000014</v>
+        <v>-0.44564480000000012</v>
       </c>
       <c r="BC19" s="4">
         <f t="shared" si="82"/>
-        <v>-0.54525952000000011</v>
+        <v>-0.35651584000000014</v>
       </c>
       <c r="BD19" s="4">
         <f t="shared" si="83"/>
-        <v>-0.43620761600000013</v>
+        <v>-0.28521267200000011</v>
       </c>
       <c r="BE19" s="4">
         <f t="shared" si="84"/>
-        <v>-0.34896609280000013</v>
+        <v>-0.2281701376000001</v>
       </c>
       <c r="BF19" s="4">
         <f t="shared" si="85"/>
-        <v>-0.27917287424000009</v>
+        <v>-0.18253611008000009</v>
       </c>
     </row>
     <row r="20" spans="2:168" s="1" customFormat="1" x14ac:dyDescent="0.3">
@@ -4584,11 +4577,11 @@
       </c>
       <c r="AK20" s="7">
         <f t="shared" si="97"/>
-        <v>-0.45199999999999996</v>
+        <v>1.2000000000000037</v>
       </c>
       <c r="AL20" s="7">
         <f t="shared" si="97"/>
-        <v>-1.2561999999999962</v>
+        <v>0.90090000000000359</v>
       </c>
       <c r="AN20" s="7">
         <f>AN17-AN18-AN19</f>
@@ -4624,47 +4617,47 @@
       </c>
       <c r="AV20" s="7">
         <f t="shared" si="98"/>
-        <v>-3.9082000000000234</v>
+        <v>-9.9099999999990418E-2</v>
       </c>
       <c r="AW20" s="7">
         <f t="shared" si="98"/>
-        <v>8.6646599999999818</v>
+        <v>8.9213899999999828</v>
       </c>
       <c r="AX20" s="7">
         <f t="shared" si="98"/>
-        <v>12.897946599999992</v>
+        <v>12.829443099999992</v>
       </c>
       <c r="AY20" s="7">
         <f t="shared" si="98"/>
-        <v>16.134741243999983</v>
+        <v>15.792703885999988</v>
       </c>
       <c r="AZ20" s="7">
         <f t="shared" si="98"/>
-        <v>18.69138920636</v>
+        <v>18.115131952299979</v>
       </c>
       <c r="BA20" s="7">
         <f t="shared" si="98"/>
-        <v>20.250980922062826</v>
+        <v>19.479744024268992</v>
       </c>
       <c r="BB20" s="7">
         <f t="shared" ref="BB20:BF20" si="99">BB17-BB18-BB19</f>
-        <v>21.195388122686868</v>
+        <v>20.256593950786147</v>
       </c>
       <c r="BC20" s="7">
         <f t="shared" si="99"/>
-        <v>21.980539254854932</v>
+        <v>20.887383428143117</v>
       </c>
       <c r="BD20" s="7">
         <f t="shared" si="99"/>
-        <v>22.744823242005666</v>
+        <v>21.499392354184355</v>
       </c>
       <c r="BE20" s="7">
         <f t="shared" si="99"/>
-        <v>23.495672655902915</v>
+        <v>22.099580179224748</v>
       </c>
       <c r="BF20" s="7">
         <f t="shared" si="99"/>
-        <v>24.239100513702851</v>
+        <v>22.693570719421153</v>
       </c>
     </row>
     <row r="21" spans="2:168" x14ac:dyDescent="0.3">
@@ -4817,43 +4810,43 @@
       </c>
       <c r="AW21" s="4">
         <f t="shared" ref="AW21:BA21" si="100">AW20*0.2</f>
-        <v>1.7329319999999964</v>
+        <v>1.7842779999999967</v>
       </c>
       <c r="AX21" s="4">
         <f t="shared" si="100"/>
-        <v>2.5795893199999984</v>
+        <v>2.5658886199999986</v>
       </c>
       <c r="AY21" s="4">
         <f t="shared" si="100"/>
-        <v>3.2269482487999968</v>
+        <v>3.1585407771999976</v>
       </c>
       <c r="AZ21" s="4">
         <f t="shared" si="100"/>
-        <v>3.7382778412720001</v>
+        <v>3.6230263904599962</v>
       </c>
       <c r="BA21" s="4">
         <f t="shared" si="100"/>
-        <v>4.0501961844125658</v>
+        <v>3.8959488048537985</v>
       </c>
       <c r="BB21" s="4">
         <f t="shared" ref="BB21:BF21" si="101">BB20*0.2</f>
-        <v>4.2390776245373738</v>
+        <v>4.0513187901572296</v>
       </c>
       <c r="BC21" s="4">
         <f t="shared" si="101"/>
-        <v>4.3961078509709868</v>
+        <v>4.1774766856286236</v>
       </c>
       <c r="BD21" s="4">
         <f t="shared" si="101"/>
-        <v>4.5489646484011335</v>
+        <v>4.2998784708368714</v>
       </c>
       <c r="BE21" s="4">
         <f t="shared" si="101"/>
-        <v>4.699134531180583</v>
+        <v>4.4199160358449499</v>
       </c>
       <c r="BF21" s="4">
         <f t="shared" si="101"/>
-        <v>4.8478201027405703</v>
+        <v>4.5387141438842304</v>
       </c>
     </row>
     <row r="22" spans="2:168" x14ac:dyDescent="0.3">
@@ -5188,11 +5181,11 @@
       </c>
       <c r="AK23" s="7">
         <f t="shared" si="119"/>
-        <v>-0.45199999999999996</v>
+        <v>1.2000000000000037</v>
       </c>
       <c r="AL23" s="7">
         <f t="shared" si="119"/>
-        <v>-1.2561999999999962</v>
+        <v>0.90090000000000359</v>
       </c>
       <c r="AN23" s="7">
         <f>AN20-AN21-AN22</f>
@@ -5228,487 +5221,487 @@
       </c>
       <c r="AV23" s="7">
         <f t="shared" si="120"/>
-        <v>-3.5082000000000235</v>
+        <v>0.3009000000000096</v>
       </c>
       <c r="AW23" s="7">
         <f t="shared" si="120"/>
-        <v>7.3717279999999858</v>
+        <v>7.5771119999999863</v>
       </c>
       <c r="AX23" s="7">
         <f t="shared" si="120"/>
-        <v>10.802357279999994</v>
+        <v>10.747554479999993</v>
       </c>
       <c r="AY23" s="7">
         <f t="shared" si="120"/>
-        <v>13.440192995199988</v>
+        <v>13.166563108799991</v>
       </c>
       <c r="AZ23" s="7">
         <f t="shared" si="120"/>
-        <v>15.538751365088</v>
+        <v>15.077745561839983</v>
       </c>
       <c r="BA23" s="7">
         <f t="shared" si="120"/>
-        <v>16.844988737650262</v>
+        <v>16.227999219415196</v>
       </c>
       <c r="BB23" s="7">
         <f t="shared" ref="BB23:BF23" si="121">BB20-BB21-BB22</f>
-        <v>17.664934898149497</v>
+        <v>16.91389956062892</v>
       </c>
       <c r="BC23" s="7">
         <f t="shared" si="121"/>
-        <v>18.363918243883948</v>
+        <v>17.489393582514495</v>
       </c>
       <c r="BD23" s="7">
         <f t="shared" si="121"/>
-        <v>19.053294117604533</v>
+        <v>18.056949407347485</v>
       </c>
       <c r="BE23" s="7">
         <f t="shared" si="121"/>
-        <v>19.739717201122332</v>
+        <v>18.622843219779799</v>
       </c>
       <c r="BF23" s="7">
         <f t="shared" si="121"/>
-        <v>20.428777395002282</v>
+        <v>19.192353559576922</v>
       </c>
       <c r="BG23" s="1">
         <f>BF23*(1+$BI$32)</f>
-        <v>20.22448962105226</v>
+        <v>19.000430023981153</v>
       </c>
       <c r="BH23" s="1">
         <f t="shared" ref="BH23:DS23" si="122">BG23*(1+$BI$32)</f>
-        <v>20.022244724841737</v>
+        <v>18.810425723741343</v>
       </c>
       <c r="BI23" s="1">
         <f t="shared" si="122"/>
-        <v>19.822022277593319</v>
+        <v>18.62232146650393</v>
       </c>
       <c r="BJ23" s="1">
         <f t="shared" si="122"/>
-        <v>19.623802054817386</v>
+        <v>18.436098251838892</v>
       </c>
       <c r="BK23" s="1">
         <f t="shared" si="122"/>
-        <v>19.42756403426921</v>
+        <v>18.251737269320504</v>
       </c>
       <c r="BL23" s="1">
         <f t="shared" si="122"/>
-        <v>19.233288393926518</v>
+        <v>18.069219896627299</v>
       </c>
       <c r="BM23" s="1">
         <f t="shared" si="122"/>
-        <v>19.040955509987253</v>
+        <v>17.888527697661026</v>
       </c>
       <c r="BN23" s="1">
         <f t="shared" si="122"/>
-        <v>18.85054595488738</v>
+        <v>17.709642420684414</v>
       </c>
       <c r="BO23" s="1">
         <f t="shared" si="122"/>
-        <v>18.662040495338506</v>
+        <v>17.53254599647757</v>
       </c>
       <c r="BP23" s="1">
         <f t="shared" si="122"/>
-        <v>18.475420090385121</v>
+        <v>17.357220536512795</v>
       </c>
       <c r="BQ23" s="1">
         <f t="shared" si="122"/>
-        <v>18.290665889481271</v>
+        <v>17.183648331147666</v>
       </c>
       <c r="BR23" s="1">
         <f t="shared" si="122"/>
-        <v>18.10775923058646</v>
+        <v>17.011811847836189</v>
       </c>
       <c r="BS23" s="1">
         <f t="shared" si="122"/>
-        <v>17.926681638280595</v>
+        <v>16.841693729357825</v>
       </c>
       <c r="BT23" s="1">
         <f t="shared" si="122"/>
-        <v>17.747414821897788</v>
+        <v>16.673276792064247</v>
       </c>
       <c r="BU23" s="1">
         <f t="shared" si="122"/>
-        <v>17.569940673678811</v>
+        <v>16.506544024143604</v>
       </c>
       <c r="BV23" s="1">
         <f t="shared" si="122"/>
-        <v>17.394241266942021</v>
+        <v>16.34147858390217</v>
       </c>
       <c r="BW23" s="1">
         <f t="shared" si="122"/>
-        <v>17.220298854272603</v>
+        <v>16.178063798063146</v>
       </c>
       <c r="BX23" s="1">
         <f t="shared" si="122"/>
-        <v>17.048095865729877</v>
+        <v>16.016283160082516</v>
       </c>
       <c r="BY23" s="1">
         <f t="shared" si="122"/>
-        <v>16.877614907072577</v>
+        <v>15.856120328481691</v>
       </c>
       <c r="BZ23" s="1">
         <f t="shared" si="122"/>
-        <v>16.70883875800185</v>
+        <v>15.697559125196873</v>
       </c>
       <c r="CA23" s="1">
         <f t="shared" si="122"/>
-        <v>16.54175037042183</v>
+        <v>15.540583533944904</v>
       </c>
       <c r="CB23" s="1">
         <f t="shared" si="122"/>
-        <v>16.376332866717611</v>
+        <v>15.385177698605455</v>
       </c>
       <c r="CC23" s="1">
         <f t="shared" si="122"/>
-        <v>16.212569538050435</v>
+        <v>15.231325921619399</v>
       </c>
       <c r="CD23" s="1">
         <f t="shared" si="122"/>
-        <v>16.050443842669932</v>
+        <v>15.079012662403205</v>
       </c>
       <c r="CE23" s="1">
         <f t="shared" si="122"/>
-        <v>15.889939404243233</v>
+        <v>14.928222535779172</v>
       </c>
       <c r="CF23" s="1">
         <f t="shared" si="122"/>
-        <v>15.7310400102008</v>
+        <v>14.77894031042138</v>
       </c>
       <c r="CG23" s="1">
         <f t="shared" si="122"/>
-        <v>15.573729610098793</v>
+        <v>14.631150907317165</v>
       </c>
       <c r="CH23" s="1">
         <f t="shared" si="122"/>
-        <v>15.417992313997805</v>
+        <v>14.484839398243993</v>
       </c>
       <c r="CI23" s="1">
         <f t="shared" si="122"/>
-        <v>15.263812390857828</v>
+        <v>14.339991004261554</v>
       </c>
       <c r="CJ23" s="1">
         <f t="shared" si="122"/>
-        <v>15.111174266949249</v>
+        <v>14.196591094218938</v>
       </c>
       <c r="CK23" s="1">
         <f t="shared" si="122"/>
-        <v>14.960062524279756</v>
+        <v>14.054625183276748</v>
       </c>
       <c r="CL23" s="1">
         <f t="shared" si="122"/>
-        <v>14.810461899036959</v>
+        <v>13.91407893144398</v>
       </c>
       <c r="CM23" s="1">
         <f t="shared" si="122"/>
-        <v>14.662357280046589</v>
+        <v>13.774938142129539</v>
       </c>
       <c r="CN23" s="1">
         <f t="shared" si="122"/>
-        <v>14.515733707246122</v>
+        <v>13.637188760708243</v>
       </c>
       <c r="CO23" s="1">
         <f t="shared" si="122"/>
-        <v>14.37057637017366</v>
+        <v>13.50081687310116</v>
       </c>
       <c r="CP23" s="1">
         <f t="shared" si="122"/>
-        <v>14.226870606471923</v>
+        <v>13.365808704370147</v>
       </c>
       <c r="CQ23" s="1">
         <f t="shared" si="122"/>
-        <v>14.084601900407204</v>
+        <v>13.232150617326447</v>
       </c>
       <c r="CR23" s="1">
         <f t="shared" si="122"/>
-        <v>13.943755881403131</v>
+        <v>13.099829111153182</v>
       </c>
       <c r="CS23" s="1">
         <f t="shared" si="122"/>
-        <v>13.804318322589101</v>
+        <v>12.968830820041651</v>
       </c>
       <c r="CT23" s="1">
         <f t="shared" si="122"/>
-        <v>13.66627513936321</v>
+        <v>12.839142511841235</v>
       </c>
       <c r="CU23" s="1">
         <f t="shared" si="122"/>
-        <v>13.529612387969577</v>
+        <v>12.710751086722823</v>
       </c>
       <c r="CV23" s="1">
         <f t="shared" si="122"/>
-        <v>13.394316264089881</v>
+        <v>12.583643575855595</v>
       </c>
       <c r="CW23" s="1">
         <f t="shared" si="122"/>
-        <v>13.260373101448982</v>
+        <v>12.457807140097039</v>
       </c>
       <c r="CX23" s="1">
         <f t="shared" si="122"/>
-        <v>13.127769370434493</v>
+        <v>12.333229068696069</v>
       </c>
       <c r="CY23" s="1">
         <f t="shared" si="122"/>
-        <v>12.996491676730148</v>
+        <v>12.209896778009108</v>
       </c>
       <c r="CZ23" s="1">
         <f t="shared" si="122"/>
-        <v>12.866526759962847</v>
+        <v>12.087797810229016</v>
       </c>
       <c r="DA23" s="1">
         <f t="shared" si="122"/>
-        <v>12.737861492363217</v>
+        <v>11.966919832126726</v>
       </c>
       <c r="DB23" s="1">
         <f t="shared" si="122"/>
-        <v>12.610482877439585</v>
+        <v>11.847250633805459</v>
       </c>
       <c r="DC23" s="1">
         <f t="shared" si="122"/>
-        <v>12.484378048665189</v>
+        <v>11.728778127467404</v>
       </c>
       <c r="DD23" s="1">
         <f t="shared" si="122"/>
-        <v>12.359534268178537</v>
+        <v>11.611490346192729</v>
       </c>
       <c r="DE23" s="1">
         <f t="shared" si="122"/>
-        <v>12.235938925496752</v>
+        <v>11.495375442730802</v>
       </c>
       <c r="DF23" s="1">
         <f t="shared" si="122"/>
-        <v>12.113579536241785</v>
+        <v>11.380421688303494</v>
       </c>
       <c r="DG23" s="1">
         <f t="shared" si="122"/>
-        <v>11.992443740879366</v>
+        <v>11.26661747142046</v>
       </c>
       <c r="DH23" s="1">
         <f t="shared" si="122"/>
-        <v>11.872519303470572</v>
+        <v>11.153951296706255</v>
       </c>
       <c r="DI23" s="1">
         <f t="shared" si="122"/>
-        <v>11.753794110435866</v>
+        <v>11.042411783739192</v>
       </c>
       <c r="DJ23" s="1">
         <f t="shared" si="122"/>
-        <v>11.636256169331507</v>
+        <v>10.931987665901801</v>
       </c>
       <c r="DK23" s="1">
         <f t="shared" si="122"/>
-        <v>11.519893607638192</v>
+        <v>10.822667789242782</v>
       </c>
       <c r="DL23" s="1">
         <f t="shared" si="122"/>
-        <v>11.40469467156181</v>
+        <v>10.714441111350354</v>
       </c>
       <c r="DM23" s="1">
         <f t="shared" si="122"/>
-        <v>11.290647724846192</v>
+        <v>10.60729670023685</v>
       </c>
       <c r="DN23" s="1">
         <f t="shared" si="122"/>
-        <v>11.17774124759773</v>
+        <v>10.501223733234481</v>
       </c>
       <c r="DO23" s="1">
         <f t="shared" si="122"/>
-        <v>11.065963835121753</v>
+        <v>10.396211495902136</v>
       </c>
       <c r="DP23" s="1">
         <f t="shared" si="122"/>
-        <v>10.955304196770536</v>
+        <v>10.292249380943115</v>
       </c>
       <c r="DQ23" s="1">
         <f t="shared" si="122"/>
-        <v>10.84575115480283</v>
+        <v>10.189326887133683</v>
       </c>
       <c r="DR23" s="1">
         <f t="shared" si="122"/>
-        <v>10.737293643254802</v>
+        <v>10.087433618262347</v>
       </c>
       <c r="DS23" s="1">
         <f t="shared" si="122"/>
-        <v>10.629920706822254</v>
+        <v>9.9865592820797229</v>
       </c>
       <c r="DT23" s="1">
         <f t="shared" ref="DT23:FL23" si="123">DS23*(1+$BI$32)</f>
-        <v>10.523621499754032</v>
+        <v>9.8866936892589248</v>
       </c>
       <c r="DU23" s="1">
         <f t="shared" si="123"/>
-        <v>10.418385284756491</v>
+        <v>9.7878267523663354</v>
       </c>
       <c r="DV23" s="1">
         <f t="shared" si="123"/>
-        <v>10.314201431908925</v>
+        <v>9.689948484842672</v>
       </c>
       <c r="DW23" s="1">
         <f t="shared" si="123"/>
-        <v>10.211059417589835</v>
+        <v>9.5930489999942452</v>
       </c>
       <c r="DX23" s="1">
         <f t="shared" si="123"/>
-        <v>10.108948823413936</v>
+        <v>9.4971185099943032</v>
       </c>
       <c r="DY23" s="1">
         <f t="shared" si="123"/>
-        <v>10.007859335179797</v>
+        <v>9.4021473248943597</v>
       </c>
       <c r="DZ23" s="1">
         <f t="shared" si="123"/>
-        <v>9.9077807418279988</v>
+        <v>9.3081258516454159</v>
       </c>
       <c r="EA23" s="1">
         <f t="shared" si="123"/>
-        <v>9.8087029344097196</v>
+        <v>9.2150445931289617</v>
       </c>
       <c r="EB23" s="1">
         <f t="shared" si="123"/>
-        <v>9.7106159050656231</v>
+        <v>9.1228941471976714</v>
       </c>
       <c r="EC23" s="1">
         <f t="shared" si="123"/>
-        <v>9.6135097460149677</v>
+        <v>9.0316652057256945</v>
       </c>
       <c r="ED23" s="1">
         <f t="shared" si="123"/>
-        <v>9.5173746485548172</v>
+        <v>8.9413485536684369</v>
       </c>
       <c r="EE23" s="1">
         <f t="shared" si="123"/>
-        <v>9.4222009020692692</v>
+        <v>8.8519350681317519</v>
       </c>
       <c r="EF23" s="1">
         <f t="shared" si="123"/>
-        <v>9.3279788930485772</v>
+        <v>8.7634157174504335</v>
       </c>
       <c r="EG23" s="1">
         <f t="shared" si="123"/>
-        <v>9.234699104118091</v>
+        <v>8.6757815602759294</v>
       </c>
       <c r="EH23" s="1">
         <f t="shared" si="123"/>
-        <v>9.1423521130769103</v>
+        <v>8.5890237446731703</v>
       </c>
       <c r="EI23" s="1">
         <f t="shared" si="123"/>
-        <v>9.0509285919461409</v>
+        <v>8.5031335072264387</v>
       </c>
       <c r="EJ23" s="1">
         <f t="shared" si="123"/>
-        <v>8.9604193060266795</v>
+        <v>8.4181021721541747</v>
       </c>
       <c r="EK23" s="1">
         <f t="shared" si="123"/>
-        <v>8.8708151129664135</v>
+        <v>8.3339211504326336</v>
       </c>
       <c r="EL23" s="1">
         <f t="shared" si="123"/>
-        <v>8.7821069618367495</v>
+        <v>8.2505819389283079</v>
       </c>
       <c r="EM23" s="1">
         <f t="shared" si="123"/>
-        <v>8.6942858922183817</v>
+        <v>8.168076119539025</v>
       </c>
       <c r="EN23" s="1">
         <f t="shared" si="123"/>
-        <v>8.607343033296198</v>
+        <v>8.0863953583436352</v>
       </c>
       <c r="EO23" s="1">
         <f t="shared" si="123"/>
-        <v>8.5212696029632351</v>
+        <v>8.0055314047601982</v>
       </c>
       <c r="EP23" s="1">
         <f t="shared" si="123"/>
-        <v>8.4360569069336027</v>
+        <v>7.9254760907125963</v>
       </c>
       <c r="EQ23" s="1">
         <f t="shared" si="123"/>
-        <v>8.3516963378642668</v>
+        <v>7.8462213298054699</v>
       </c>
       <c r="ER23" s="1">
         <f t="shared" si="123"/>
-        <v>8.2681793744856247</v>
+        <v>7.7677591165074151</v>
       </c>
       <c r="ES23" s="1">
         <f t="shared" si="123"/>
-        <v>8.1854975807407691</v>
+        <v>7.6900815253423414</v>
       </c>
       <c r="ET23" s="1">
         <f t="shared" si="123"/>
-        <v>8.103642604933361</v>
+        <v>7.6131807100889182</v>
       </c>
       <c r="EU23" s="1">
         <f t="shared" si="123"/>
-        <v>8.0226061788840273</v>
+        <v>7.5370489029880288</v>
       </c>
       <c r="EV23" s="1">
         <f t="shared" si="123"/>
-        <v>7.9423801170951869</v>
+        <v>7.4616784139581487</v>
       </c>
       <c r="EW23" s="1">
         <f t="shared" si="123"/>
-        <v>7.8629563159242348</v>
+        <v>7.3870616298185672</v>
       </c>
       <c r="EX23" s="1">
         <f t="shared" si="123"/>
-        <v>7.7843267527649926</v>
+        <v>7.313191013520381</v>
       </c>
       <c r="EY23" s="1">
         <f t="shared" si="123"/>
-        <v>7.7064834852373423</v>
+        <v>7.2400591033851773</v>
       </c>
       <c r="EZ23" s="1">
         <f t="shared" si="123"/>
-        <v>7.6294186503849684</v>
+        <v>7.1676585123513252</v>
       </c>
       <c r="FA23" s="1">
         <f t="shared" si="123"/>
-        <v>7.5531244638811188</v>
+        <v>7.095981927227812</v>
       </c>
       <c r="FB23" s="1">
         <f t="shared" si="123"/>
-        <v>7.4775932192423076</v>
+        <v>7.0250221079555342</v>
       </c>
       <c r="FC23" s="1">
         <f t="shared" si="123"/>
-        <v>7.4028172870498841</v>
+        <v>6.9547718868759789</v>
       </c>
       <c r="FD23" s="1">
         <f t="shared" si="123"/>
-        <v>7.3287891141793855</v>
+        <v>6.8852241680072188</v>
       </c>
       <c r="FE23" s="1">
         <f t="shared" si="123"/>
-        <v>7.2555012230375917</v>
+        <v>6.8163719263271467</v>
       </c>
       <c r="FF23" s="1">
         <f t="shared" si="123"/>
-        <v>7.1829462108072155</v>
+        <v>6.7482082070638754</v>
       </c>
       <c r="FG23" s="1">
         <f t="shared" si="123"/>
-        <v>7.1111167486991436</v>
+        <v>6.6807261249932361</v>
       </c>
       <c r="FH23" s="1">
         <f t="shared" si="123"/>
-        <v>7.040005581212152</v>
+        <v>6.6139188637433035</v>
       </c>
       <c r="FI23" s="1">
         <f t="shared" si="123"/>
-        <v>6.9696055254000306</v>
+        <v>6.5477796751058701</v>
       </c>
       <c r="FJ23" s="1">
         <f t="shared" si="123"/>
-        <v>6.8999094701460306</v>
+        <v>6.4823018783548116</v>
       </c>
       <c r="FK23" s="1">
         <f t="shared" si="123"/>
-        <v>6.8309103754445699</v>
+        <v>6.4174788595712631</v>
       </c>
       <c r="FL23" s="1">
         <f t="shared" si="123"/>
-        <v>6.7626012716901238</v>
+        <v>6.3533040709755504</v>
       </c>
     </row>
     <row r="24" spans="2:168" x14ac:dyDescent="0.3">
@@ -5819,10 +5812,10 @@
         <v>15</v>
       </c>
       <c r="AK24" s="4">
-        <v>15</v>
+        <v>15.1</v>
       </c>
       <c r="AL24" s="4">
-        <v>15</v>
+        <v>15.1</v>
       </c>
       <c r="AN24" s="4">
         <v>97.16</v>
@@ -5850,37 +5843,37 @@
         <v>14</v>
       </c>
       <c r="AV24" s="4">
-        <v>15</v>
+        <v>15.1</v>
       </c>
       <c r="AW24" s="4">
-        <v>15</v>
+        <v>15.1</v>
       </c>
       <c r="AX24" s="4">
-        <v>15</v>
+        <v>15.1</v>
       </c>
       <c r="AY24" s="4">
-        <v>15</v>
+        <v>15.1</v>
       </c>
       <c r="AZ24" s="4">
-        <v>15</v>
+        <v>15.1</v>
       </c>
       <c r="BA24" s="4">
-        <v>15</v>
+        <v>15.1</v>
       </c>
       <c r="BB24" s="4">
-        <v>15</v>
+        <v>15.1</v>
       </c>
       <c r="BC24" s="4">
-        <v>15</v>
+        <v>15.1</v>
       </c>
       <c r="BD24" s="4">
-        <v>15</v>
+        <v>15.1</v>
       </c>
       <c r="BE24" s="4">
-        <v>15</v>
+        <v>15.1</v>
       </c>
       <c r="BF24" s="4">
-        <v>15</v>
+        <v>15.1</v>
       </c>
     </row>
     <row r="25" spans="2:168" s="1" customFormat="1" x14ac:dyDescent="0.3">
@@ -6025,11 +6018,11 @@
       </c>
       <c r="AK25" s="8">
         <f t="shared" si="135"/>
-        <v>-3.0133333333333331E-2</v>
+        <v>7.9470198675496942E-2</v>
       </c>
       <c r="AL25" s="8">
         <f t="shared" si="135"/>
-        <v>-8.3746666666666414E-2</v>
+        <v>5.9662251655629377E-2</v>
       </c>
       <c r="AN25" s="8">
         <f>AN23/AN24</f>
@@ -6065,47 +6058,47 @@
       </c>
       <c r="AV25" s="8">
         <f t="shared" si="136"/>
-        <v>-0.23388000000000156</v>
+        <v>1.992715231788143E-2</v>
       </c>
       <c r="AW25" s="8">
         <f t="shared" si="136"/>
-        <v>0.49144853333333238</v>
+        <v>0.50179549668874079</v>
       </c>
       <c r="AX25" s="8">
         <f t="shared" si="136"/>
-        <v>0.72015715199999952</v>
+        <v>0.71175857483443661</v>
       </c>
       <c r="AY25" s="8">
         <f t="shared" si="136"/>
-        <v>0.89601286634666588</v>
+        <v>0.87195782177483383</v>
       </c>
       <c r="AZ25" s="8">
         <f t="shared" si="136"/>
-        <v>1.0359167576725334</v>
+        <v>0.99852619614834326</v>
       </c>
       <c r="BA25" s="8">
         <f t="shared" si="136"/>
-        <v>1.122999249176684</v>
+        <v>1.0747019350606091</v>
       </c>
       <c r="BB25" s="8">
         <f t="shared" ref="BB25:BF25" si="137">BB23/BB24</f>
-        <v>1.1776623265432997</v>
+        <v>1.1201257987171471</v>
       </c>
       <c r="BC25" s="8">
         <f t="shared" si="137"/>
-        <v>1.2242612162589299</v>
+        <v>1.1582379855969864</v>
       </c>
       <c r="BD25" s="8">
         <f t="shared" si="137"/>
-        <v>1.2702196078403023</v>
+        <v>1.1958244640627473</v>
       </c>
       <c r="BE25" s="8">
         <f t="shared" si="137"/>
-        <v>1.3159811467414888</v>
+        <v>1.233300875482106</v>
       </c>
       <c r="BF25" s="8">
         <f t="shared" si="137"/>
-        <v>1.3619184930001522</v>
+        <v>1.2710167920249618</v>
       </c>
     </row>
     <row r="27" spans="2:168" x14ac:dyDescent="0.3">
@@ -6142,11 +6135,11 @@
       </c>
       <c r="AK27" s="9">
         <f t="shared" ref="AK27:AK31" si="143">AK3/AG3-1</f>
-        <v>-0.41176470588235292</v>
+        <v>-0.50464396284829716</v>
       </c>
       <c r="AL27" s="9">
         <f t="shared" ref="AL27:AL31" si="144">AL3/AH3-1</f>
-        <v>-0.25490196078431371</v>
+        <v>-0.37254901960784315</v>
       </c>
       <c r="AT27" s="9">
         <f t="shared" ref="AO27:BA30" si="145">AT3/AS3-1</f>
@@ -6158,7 +6151,7 @@
       </c>
       <c r="AV27" s="9">
         <f t="shared" ref="AV27:AV28" si="147">AV3/AU3-1</f>
-        <v>-0.25656565656565666</v>
+        <v>-0.31717171717171722</v>
       </c>
       <c r="AW27" s="9">
         <f t="shared" ref="AW27:AW28" si="148">AW3/AV3-1</f>
@@ -6235,11 +6228,11 @@
       </c>
       <c r="AK28" s="9">
         <f t="shared" si="143"/>
-        <v>-0.79381443298969068</v>
+        <v>0.82474226804123707</v>
       </c>
       <c r="AL28" s="9">
         <f t="shared" si="144"/>
-        <v>-0.80769230769230771</v>
+        <v>0.77884615384615374</v>
       </c>
       <c r="AT28" s="9">
         <f t="shared" si="145"/>
@@ -6251,7 +6244,7 @@
       </c>
       <c r="AV28" s="9">
         <f t="shared" si="147"/>
-        <v>-0.83613445378151263</v>
+        <v>-0.15966386554621848</v>
       </c>
       <c r="AW28" s="9">
         <f t="shared" si="148"/>
@@ -6259,19 +6252,19 @@
       </c>
       <c r="AX28" s="9">
         <f t="shared" si="149"/>
-        <v>-2.0000000000000129E-2</v>
+        <v>-2.0000000000000018E-2</v>
       </c>
       <c r="AY28" s="9">
         <f t="shared" si="150"/>
-        <v>-1.9999999999999907E-2</v>
+        <v>-2.0000000000000018E-2</v>
       </c>
       <c r="AZ28" s="9">
         <f t="shared" si="151"/>
-        <v>-2.0000000000000018E-2</v>
+        <v>-1.9999999999999907E-2</v>
       </c>
       <c r="BA28" s="9">
         <f t="shared" si="152"/>
-        <v>-2.0000000000000018E-2</v>
+        <v>-1.9999999999999907E-2</v>
       </c>
       <c r="BB28" s="9">
         <f t="shared" si="153"/>
@@ -6279,11 +6272,11 @@
       </c>
       <c r="BC28" s="9">
         <f t="shared" si="154"/>
-        <v>-2.0000000000000018E-2</v>
+        <v>-2.0000000000000129E-2</v>
       </c>
       <c r="BD28" s="9">
         <f t="shared" si="155"/>
-        <v>-2.0000000000000018E-2</v>
+        <v>-2.0000000000000129E-2</v>
       </c>
       <c r="BE28" s="9">
         <f t="shared" si="156"/>
@@ -6291,7 +6284,7 @@
       </c>
       <c r="BF28" s="9">
         <f t="shared" si="157"/>
-        <v>-2.0000000000000018E-2</v>
+        <v>-1.9999999999999907E-2</v>
       </c>
     </row>
     <row r="29" spans="2:168" x14ac:dyDescent="0.3">
@@ -6420,11 +6413,11 @@
       </c>
       <c r="AK29" s="9">
         <f t="shared" si="143"/>
-        <v>-0.5</v>
+        <v>-0.19761904761904758</v>
       </c>
       <c r="AL29" s="9">
         <f t="shared" si="144"/>
-        <v>-0.41504178272980496</v>
+        <v>-3.8997214484679632E-2</v>
       </c>
       <c r="AN29" s="9"/>
       <c r="AO29" s="9">
@@ -6457,47 +6450,47 @@
       </c>
       <c r="AV29" s="9">
         <f t="shared" si="145"/>
-        <v>-0.44474761255115969</v>
+        <v>-0.26603001364256484</v>
       </c>
       <c r="AW29" s="9">
         <f t="shared" si="145"/>
-        <v>0.13371007371007382</v>
+        <v>8.6802973977694986E-2</v>
       </c>
       <c r="AX29" s="9">
         <f t="shared" si="145"/>
-        <v>9.0060248797191322E-2</v>
+        <v>5.977424320164193E-2</v>
       </c>
       <c r="AY29" s="9">
         <f t="shared" si="145"/>
-        <v>7.2553197411564518E-2</v>
+        <v>4.9001855886387391E-2</v>
       </c>
       <c r="AZ29" s="9">
         <f t="shared" si="145"/>
-        <v>4.5237059953767034E-2</v>
+        <v>2.9728608922269473E-2</v>
       </c>
       <c r="BA29" s="9">
         <f t="shared" si="145"/>
-        <v>3.6172284936957011E-2</v>
+        <v>2.3463634633677621E-2</v>
       </c>
       <c r="BB29" s="9">
         <f t="shared" ref="BB29:BB31" si="172">BB5/BA5-1</f>
-        <v>2.6983158740174984E-2</v>
+        <v>1.6804906471024283E-2</v>
       </c>
       <c r="BC29" s="9">
         <f t="shared" ref="BC29:BC31" si="173">BC5/BB5-1</f>
-        <v>1.7696940278354223E-2</v>
+        <v>9.826019464618474E-3</v>
       </c>
       <c r="BD29" s="9">
         <f t="shared" ref="BD29:BD31" si="174">BD5/BC5-1</f>
-        <v>1.7782248881877072E-2</v>
+        <v>1.0126516120112949E-2</v>
       </c>
       <c r="BE29" s="9">
         <f t="shared" ref="BE29:BE31" si="175">BE5/BD5-1</f>
-        <v>1.7864576535749022E-2</v>
+        <v>1.0420987818976934E-2</v>
       </c>
       <c r="BF29" s="9">
         <f t="shared" ref="BF29:BF31" si="176">BF5/BE5-1</f>
-        <v>1.7944014318595825E-2</v>
+        <v>1.0709385443719244E-2</v>
       </c>
     </row>
     <row r="30" spans="2:168" x14ac:dyDescent="0.3">
@@ -6626,11 +6619,11 @@
       </c>
       <c r="AK30" s="9">
         <f t="shared" si="143"/>
-        <v>0.10000000000000009</v>
+        <v>1.6666666666666607E-2</v>
       </c>
       <c r="AL30" s="9">
         <f t="shared" si="144"/>
-        <v>0.10000000000000009</v>
+        <v>5.0000000000000044E-2</v>
       </c>
       <c r="AN30" s="9"/>
       <c r="AO30" s="9">
@@ -6663,7 +6656,7 @@
       </c>
       <c r="AV30" s="9">
         <f t="shared" si="145"/>
-        <v>-0.15351170568561856</v>
+        <v>-0.1804347826086955</v>
       </c>
       <c r="AW30" s="9">
         <f t="shared" si="145"/>
@@ -6832,11 +6825,11 @@
       </c>
       <c r="AK31" s="9">
         <f t="shared" si="143"/>
-        <v>-0.36666666666666659</v>
+        <v>-0.14999999999999991</v>
       </c>
       <c r="AL31" s="9">
         <f t="shared" si="144"/>
-        <v>-0.28440748440748431</v>
+        <v>-1.6424116424116231E-2</v>
       </c>
       <c r="AN31" s="9"/>
       <c r="AO31" s="9">
@@ -6869,47 +6862,47 @@
       </c>
       <c r="AV31" s="9">
         <f t="shared" si="179"/>
-        <v>-0.36036821705426358</v>
+        <v>-0.2412306201550386</v>
       </c>
       <c r="AW31" s="9">
         <f t="shared" si="179"/>
-        <v>0.13995606726253595</v>
+        <v>0.10658003958878726</v>
       </c>
       <c r="AX31" s="9">
         <f t="shared" si="179"/>
-        <v>9.0036944258025109E-2</v>
+        <v>6.9604331180053158E-2</v>
       </c>
       <c r="AY31" s="9">
         <f t="shared" si="179"/>
-        <v>6.769772179717215E-2</v>
+        <v>5.2646901541607116E-2</v>
       </c>
       <c r="AZ31" s="9">
         <f t="shared" si="179"/>
-        <v>4.7066044697087195E-2</v>
+        <v>3.6493958888022204E-2</v>
       </c>
       <c r="BA31" s="9">
         <f t="shared" si="179"/>
-        <v>3.3795465679679948E-2</v>
+        <v>2.5673498694819274E-2</v>
       </c>
       <c r="BB31" s="9">
         <f t="shared" si="172"/>
-        <v>2.4303961376923366E-2</v>
+        <v>1.7889684561018804E-2</v>
       </c>
       <c r="BC31" s="9">
         <f t="shared" si="173"/>
-        <v>1.8576832162851442E-2</v>
+        <v>1.3287386794023748E-2</v>
       </c>
       <c r="BD31" s="9">
         <f t="shared" si="174"/>
-        <v>1.8630732178107845E-2</v>
+        <v>1.3507902074385125E-2</v>
       </c>
       <c r="BE31" s="9">
         <f t="shared" si="175"/>
-        <v>1.8682660533336781E-2</v>
+        <v>1.3722539356545438E-2</v>
       </c>
       <c r="BF31" s="9">
         <f t="shared" si="176"/>
-        <v>1.8732684154401991E-2</v>
+        <v>1.3931365643215843E-2</v>
       </c>
     </row>
     <row r="32" spans="2:168" x14ac:dyDescent="0.3">
@@ -7054,7 +7047,7 @@
       </c>
       <c r="AK32" s="9">
         <f t="shared" si="183"/>
-        <v>0.19999999999999996</v>
+        <v>0.24925816023738875</v>
       </c>
       <c r="AL32" s="9">
         <f t="shared" si="183"/>
@@ -7094,35 +7087,35 @@
       </c>
       <c r="AV32" s="9">
         <f t="shared" si="184"/>
-        <v>0.20884520884520869</v>
+        <v>0.22211895910780663</v>
       </c>
       <c r="AW32" s="9">
         <f t="shared" si="184"/>
-        <v>0.20999999999999996</v>
+        <v>0.20999999999999991</v>
       </c>
       <c r="AX32" s="9">
         <f t="shared" si="184"/>
-        <v>0.20999999999999996</v>
+        <v>0.20999999999999994</v>
       </c>
       <c r="AY32" s="9">
         <f t="shared" si="184"/>
-        <v>0.20999999999999994</v>
+        <v>0.20999999999999996</v>
       </c>
       <c r="AZ32" s="9">
         <f t="shared" si="184"/>
-        <v>0.20999999999999991</v>
+        <v>0.21</v>
       </c>
       <c r="BA32" s="9">
         <f t="shared" si="184"/>
-        <v>0.20999999999999994</v>
+        <v>0.21</v>
       </c>
       <c r="BB32" s="9">
         <f t="shared" ref="BB32:BF32" si="185">(BB5-BB8)/BB5</f>
-        <v>0.21</v>
+        <v>0.20999999999999996</v>
       </c>
       <c r="BC32" s="9">
         <f t="shared" si="185"/>
-        <v>0.21000000000000002</v>
+        <v>0.20999999999999994</v>
       </c>
       <c r="BD32" s="9">
         <f t="shared" si="185"/>
@@ -7130,7 +7123,7 @@
       </c>
       <c r="BE32" s="9">
         <f t="shared" si="185"/>
-        <v>0.20999999999999994</v>
+        <v>0.20999999999999996</v>
       </c>
       <c r="BF32" s="9">
         <f t="shared" si="185"/>
@@ -7285,7 +7278,7 @@
       </c>
       <c r="AK33" s="9">
         <f t="shared" si="188"/>
-        <v>0.89</v>
+        <v>0.86885245901639352</v>
       </c>
       <c r="AL33" s="9">
         <f t="shared" si="188"/>
@@ -7325,7 +7318,7 @@
       </c>
       <c r="AV33" s="9">
         <f t="shared" si="189"/>
-        <v>0.89079020150138288</v>
+        <v>0.88555192817792294</v>
       </c>
       <c r="AW33" s="9">
         <f t="shared" si="189"/>
@@ -7516,11 +7509,11 @@
       </c>
       <c r="AK34" s="9">
         <f t="shared" si="193"/>
-        <v>0.46631578947368418</v>
+        <v>0.41394335511982572</v>
       </c>
       <c r="AL34" s="9">
         <f t="shared" si="193"/>
-        <v>0.46902382335851256</v>
+        <v>0.38682942295497785</v>
       </c>
       <c r="AN34" s="9">
         <f t="shared" ref="AN34:BA34" si="194">AN11/AN7</f>
@@ -7556,54 +7549,54 @@
       </c>
       <c r="AV34" s="9">
         <f t="shared" si="194"/>
-        <v>0.47032116346008168</v>
+        <v>0.4297356490645553</v>
       </c>
       <c r="AW34" s="9">
         <f t="shared" si="194"/>
-        <v>0.41887472839990159</v>
+        <v>0.38562000328906554</v>
       </c>
       <c r="AX34" s="9">
         <f t="shared" si="194"/>
-        <v>0.41886764907850654</v>
+        <v>0.38896879996165379</v>
       </c>
       <c r="AY34" s="9">
         <f t="shared" si="194"/>
-        <v>0.41736178742664359</v>
+        <v>0.39021895821051317</v>
       </c>
       <c r="AZ34" s="9">
         <f t="shared" si="194"/>
-        <v>0.41794283025476625</v>
+        <v>0.39256730248968319</v>
       </c>
       <c r="BA34" s="9">
         <f t="shared" si="194"/>
-        <v>0.41717939115895974</v>
+        <v>0.39333740883786333</v>
       </c>
       <c r="BB34" s="9">
         <f t="shared" ref="BB34:BF34" si="195">BB11/BB7</f>
-        <v>0.41630885650199717</v>
+        <v>0.39371750873501488</v>
       </c>
       <c r="BC34" s="9">
         <f t="shared" si="195"/>
-        <v>0.41659711372503749</v>
+        <v>0.39493456185476766</v>
       </c>
       <c r="BD34" s="9">
         <f t="shared" si="195"/>
-        <v>0.41687482651239322</v>
+        <v>0.39611917352176546</v>
       </c>
       <c r="BE34" s="9">
         <f t="shared" si="195"/>
-        <v>0.41714235278351014</v>
+        <v>0.39727171353287821</v>
       </c>
       <c r="BF34" s="9">
         <f t="shared" si="195"/>
-        <v>0.41740004038896372</v>
+        <v>0.3983925818611585</v>
       </c>
       <c r="BH34" t="s">
         <v>53</v>
       </c>
       <c r="BI34" s="4">
         <f>NPV(BI33,AV23:FL23)</f>
-        <v>115.55638041965513</v>
+        <v>113.85991573353323</v>
       </c>
     </row>
     <row r="35" spans="2:61" x14ac:dyDescent="0.3">
@@ -7748,11 +7741,11 @@
       </c>
       <c r="AK35" s="9">
         <f t="shared" si="198"/>
-        <v>1.6023391812865499E-2</v>
+        <v>4.357298474945541E-2</v>
       </c>
       <c r="AL35" s="9">
         <f t="shared" si="198"/>
-        <v>-7.443346891342132E-3</v>
+        <v>4.0179666032551332E-2</v>
       </c>
       <c r="AN35" s="9">
         <f t="shared" ref="AN35:BA35" si="199">AN17/AN7</f>
@@ -7788,54 +7781,54 @@
       </c>
       <c r="AV35" s="9">
         <f t="shared" si="199"/>
-        <v>-3.8494167550372944E-3</v>
+        <v>1.980014047634257E-2</v>
       </c>
       <c r="AW35" s="9">
         <f t="shared" si="199"/>
-        <v>7.5647089310750273E-2</v>
+        <v>6.6250955704364844E-2</v>
       </c>
       <c r="AX35" s="9">
         <f t="shared" si="199"/>
-        <v>9.188781234971935E-2</v>
+        <v>8.0260677860190061E-2</v>
       </c>
       <c r="AY35" s="9">
         <f t="shared" si="199"/>
-        <v>0.10205677112619578</v>
+        <v>8.9333983513714757E-2</v>
       </c>
       <c r="AZ35" s="9">
         <f t="shared" si="199"/>
-        <v>0.10951141530201378</v>
+        <v>9.6051711628499292E-2</v>
       </c>
       <c r="BA35" s="9">
         <f t="shared" si="199"/>
-        <v>0.11268826971058507</v>
+        <v>9.8962192582201333E-2</v>
       </c>
       <c r="BB35" s="9">
         <f t="shared" ref="BB35:BF35" si="200">BB17/BB7</f>
-        <v>0.11373011188822295</v>
+        <v>9.9908877135747046E-2</v>
       </c>
       <c r="BC35" s="9">
         <f t="shared" si="200"/>
-        <v>0.11472395694359423</v>
+        <v>0.1007628695627512</v>
       </c>
       <c r="BD35" s="9">
         <f t="shared" si="200"/>
-        <v>0.11571097522717622</v>
+        <v>0.10162331615160621</v>
       </c>
       <c r="BE35" s="9">
         <f t="shared" si="200"/>
-        <v>0.11669106599414471</v>
+        <v>0.10248957805762073</v>
       </c>
       <c r="BF35" s="9">
         <f t="shared" si="200"/>
-        <v>0.11766413789904684</v>
+        <v>0.10336103297204743</v>
       </c>
       <c r="BH35" t="s">
         <v>54</v>
       </c>
       <c r="BI35" s="4">
         <f>Main!D8</f>
-        <v>-21.599999999999994</v>
+        <v>-27.1</v>
       </c>
     </row>
     <row r="36" spans="2:61" x14ac:dyDescent="0.3">
@@ -7968,7 +7961,7 @@
       </c>
       <c r="AK36" s="9">
         <f t="shared" ref="AK36" si="205">AK12/AG12-1</f>
-        <v>-0.13461538461538469</v>
+        <v>-5.7692307692307709E-2</v>
       </c>
       <c r="AL36" s="9">
         <f t="shared" ref="AL36" si="206">AL12/AH12-1</f>
@@ -8005,7 +7998,7 @@
       </c>
       <c r="AV36" s="9">
         <f t="shared" si="207"/>
-        <v>-0.13145539906103276</v>
+        <v>-0.11267605633802813</v>
       </c>
       <c r="AW36" s="9">
         <f t="shared" si="207"/>
@@ -8052,7 +8045,7 @@
       </c>
       <c r="BI36" s="4">
         <f>BI34+BI35</f>
-        <v>93.956380419655133</v>
+        <v>86.759915733533234</v>
       </c>
     </row>
     <row r="37" spans="2:61" x14ac:dyDescent="0.3">
@@ -8197,11 +8190,11 @@
       </c>
       <c r="AK37" s="9">
         <f t="shared" si="215"/>
-        <v>0.11403508771929824</v>
+        <v>9.1503267973856203E-2</v>
       </c>
       <c r="AL37" s="9">
         <f t="shared" si="215"/>
-        <v>0.11330621731551423</v>
+        <v>8.2435003170577045E-2</v>
       </c>
       <c r="AN37" s="9">
         <f t="shared" ref="AN37:BA37" si="216">AN13/AN7</f>
@@ -8237,7 +8230,7 @@
       </c>
       <c r="AV37" s="9">
         <f t="shared" si="216"/>
-        <v>0.11816391455840025</v>
+        <v>0.10152608390268821</v>
       </c>
       <c r="AW37" s="9">
         <f t="shared" si="216"/>
@@ -8261,7 +8254,7 @@
       </c>
       <c r="BB37" s="9">
         <f t="shared" ref="BB37:BF37" si="217">BB13/BB7</f>
-        <v>0.09</v>
+        <v>9.0000000000000011E-2</v>
       </c>
       <c r="BC37" s="9">
         <f t="shared" si="217"/>
@@ -8273,18 +8266,18 @@
       </c>
       <c r="BE37" s="9">
         <f t="shared" si="217"/>
-        <v>9.0000000000000011E-2</v>
+        <v>0.09</v>
       </c>
       <c r="BF37" s="9">
         <f t="shared" si="217"/>
-        <v>9.0000000000000011E-2</v>
+        <v>0.09</v>
       </c>
       <c r="BH37" t="s">
         <v>56</v>
       </c>
       <c r="BI37" s="10">
         <f>BI36/BA24</f>
-        <v>6.2637586946436752</v>
+        <v>5.7456897836776974</v>
       </c>
     </row>
     <row r="38" spans="2:61" x14ac:dyDescent="0.3">
@@ -8417,7 +8410,7 @@
       </c>
       <c r="AK38" s="9">
         <f t="shared" ref="AK38" si="222">AK14/AG14-1</f>
-        <v>-6.25E-2</v>
+        <v>0.1875</v>
       </c>
       <c r="AL38" s="9">
         <f t="shared" ref="AL38" si="223">AL14/AH14-1</f>
@@ -8454,7 +8447,7 @@
       </c>
       <c r="AV38" s="9">
         <f t="shared" si="224"/>
-        <v>-7.9601990049751326E-2</v>
+        <v>-1.9900497512437942E-2</v>
       </c>
       <c r="AW38" s="9">
         <f t="shared" si="224"/>
@@ -8501,7 +8494,7 @@
       </c>
       <c r="BI38" s="10">
         <f>Main!D3</f>
-        <v>12.28</v>
+        <v>11.61</v>
       </c>
     </row>
     <row r="39" spans="2:61" x14ac:dyDescent="0.3">
@@ -8706,7 +8699,7 @@
       </c>
       <c r="BA39" s="9">
         <f t="shared" si="233"/>
-        <v>0.20000000000000004</v>
+        <v>0.2</v>
       </c>
       <c r="BB39" s="9">
         <f t="shared" ref="BB39:BF39" si="234">BB21/BB20</f>
@@ -8726,14 +8719,14 @@
       </c>
       <c r="BF39" s="9">
         <f t="shared" si="234"/>
-        <v>0.2</v>
+        <v>0.19999999999999998</v>
       </c>
       <c r="BH39" s="1" t="s">
         <v>58</v>
       </c>
       <c r="BI39" s="11">
         <f>BI37/BI38-1</f>
-        <v>-0.48992193040360954</v>
+        <v>-0.50510854576419484</v>
       </c>
     </row>
     <row r="40" spans="2:61" x14ac:dyDescent="0.3">
